--- a/Jupyter/Wedge/wedge_data_2026-03-25.xlsx
+++ b/Jupyter/Wedge/wedge_data_2026-03-25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\patri\projects\emma-openmc\Jupyter\Wedge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F34BDA-AD99-4B40-AB8C-3C4A43F6D461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100225AE-D78B-42E7-A4DA-1A50FD7EF77D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4257,15 +4257,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>255270</xdr:colOff>
+      <xdr:colOff>132179</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>68580</xdr:rowOff>
+      <xdr:rowOff>56857</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>560070</xdr:colOff>
+      <xdr:colOff>436979</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>68580</xdr:rowOff>
+      <xdr:rowOff>56857</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6348,6 +6348,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Jupyter/Wedge/wedge_data_2026-03-25.xlsx
+++ b/Jupyter/Wedge/wedge_data_2026-03-25.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\patri\projects\emma-openmc\Jupyter\Wedge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100225AE-D78B-42E7-A4DA-1A50FD7EF77D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D92552F5-14F5-4602-8D22-687681DBA2D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -274,41 +274,53 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$23:$A$33</c:f>
+              <c:f>'Sheet 1'!$A$27:$A$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>15</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>30</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
                   <c:v>60</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
                   <c:v>90</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>120</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="10">
                   <c:v>150</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="11">
                   <c:v>250</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="12">
                   <c:v>500</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="13">
                   <c:v>750</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="14">
                   <c:v>1000</c:v>
                 </c:pt>
               </c:numCache>
@@ -316,42 +328,42 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$F$23:$F$33</c:f>
+              <c:f>'Sheet 1'!$F$27:$F$41</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.60767258302427063</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.65530071246920629</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.67754280833532643</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.7150760468910391</c:v>
+                  <c:v>0.90095484884115951</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.74349815634063066</c:v>
+                  <c:v>0.98605362776739691</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.76438369871068157</c:v>
+                  <c:v>0.98894298080377097</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.78725904477144404</c:v>
+                  <c:v>0.99045126110744741</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.83345315481177829</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.88203918971975193</c:v>
+                  <c:v>1.0286907074262921</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.89495763249258353</c:v>
+                  <c:v>1.0109751026946947</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.8942179214729904</c:v>
+                  <c:v>1.0514992257935214</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.0588139493303126</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0670379652207234</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.0821051236786146</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.0789515024556622</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -390,41 +402,53 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$23:$A$33</c:f>
+              <c:f>'Sheet 1'!$A$27:$A$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>15</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>30</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
                   <c:v>60</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
                   <c:v>90</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>120</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="10">
                   <c:v>150</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="11">
                   <c:v>250</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="12">
                   <c:v>500</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="13">
                   <c:v>750</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="14">
                   <c:v>1000</c:v>
                 </c:pt>
               </c:numCache>
@@ -432,42 +456,42 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$K$23:$K$33</c:f>
+              <c:f>'Sheet 1'!$K$27:$K$41</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.77519648206887304</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.80083243056645892</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.81914690706968962</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.82656078378953657</c:v>
+                  <c:v>1.0035506001332684</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.84465973083032153</c:v>
+                  <c:v>1.0779572449118415</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.8509612295329948</c:v>
+                  <c:v>1.0206668727246053</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.86330946178656565</c:v>
+                  <c:v>1.0298609475740441</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.88204852071416562</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.90265799625796272</c:v>
+                  <c:v>1.0714308642620487</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.90631014559227674</c:v>
+                  <c:v>1.0452657339217364</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.90335830122978089</c:v>
+                  <c:v>1.0670489493344424</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.0639924185567</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0846944326462025</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.0956277405879706</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.0707528532565391</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -826,84 +850,108 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$6:$A$16</c:f>
+              <c:f>'Sheet 1'!$A$6:$A$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>15</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>30</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
                   <c:v>60</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
                   <c:v>90</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>120</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="10">
                   <c:v>150</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="11">
                   <c:v>250</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="12">
                   <c:v>500</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="13">
                   <c:v>750</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>1000</c:v>
+                <c:pt idx="14">
+                  <c:v>999.99</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$F$6:$F$16</c:f>
+              <c:f>'Sheet 1'!$F$6:$F$20</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.0005581562381762</c:v>
+                  <c:v>1.0120583199660715</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0026743854359832</c:v>
+                  <c:v>0.98723674640081305</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0021589302375784</c:v>
+                  <c:v>0.97352011835670349</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0049611638314022</c:v>
+                  <c:v>0.98670947182667379</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.007997543080646</c:v>
+                  <c:v>1.0274179661023068</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0068066975783474</c:v>
+                  <c:v>0.9995818870330847</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0105439212957481</c:v>
+                  <c:v>1.0035538292803527</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0160375172429779</c:v>
+                  <c:v>1.0225693897940391</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.0277465853256991</c:v>
+                  <c:v>1.0133855529616367</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.0410308363977838</c:v>
+                  <c:v>1.0168926589087053</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.0542808874235223</c:v>
+                  <c:v>1.0023371440138709</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.99143857028386306</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.99628894469879192</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.0133076136706871</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.98894242420015732</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -993,84 +1041,96 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$6:$A$16</c:f>
+              <c:f>'Sheet 1'!$A$6:$A$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>15</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>30</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
                   <c:v>60</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
                   <c:v>90</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>120</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="10">
                   <c:v>150</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="11">
                   <c:v>250</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="12">
                   <c:v>500</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="13">
                   <c:v>750</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>1000</c:v>
+                <c:pt idx="14">
+                  <c:v>999.99</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$K$6:$K$16</c:f>
+              <c:f>'Sheet 1'!$K$6:$K$20</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.0003878283273324</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.0027368257083531</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.002132645867061</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.004473547867506</c:v>
+                  <c:v>1.0124595607074192</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0073888101001607</c:v>
+                  <c:v>1.0246126531897757</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0081526090820587</c:v>
+                  <c:v>0.99123212311197628</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.010816520529382</c:v>
+                  <c:v>1.0019803232436455</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0129844821876621</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1.0286922566821892</c:v>
+                  <c:v>1.0235838898658773</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.0410106462729396</c:v>
+                  <c:v>0.99238859087523068</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.0574321213036151</c:v>
+                  <c:v>1.0068419602917082</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.0041778550412717</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0147327958753034</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.0192489706741765</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.9824392574158276</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1355,7 +1415,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Sheet 1'!$F$57</c:f>
+              <c:f>'Sheet 1'!$F$65</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1388,7 +1448,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$58:$A$68</c:f>
+              <c:f>'Sheet 1'!$A$66:$A$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -1430,7 +1490,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$F$58:$F$68</c:f>
+              <c:f>'Sheet 1'!$F$66:$F$76</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="11"/>
@@ -1719,7 +1779,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Sheet 1'!$F$40</c:f>
+              <c:f>'Sheet 1'!$F$48</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1752,7 +1812,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$41:$A$51</c:f>
+              <c:f>'Sheet 1'!$A$49:$A$59</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -1794,7 +1854,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$F$41:$F$51</c:f>
+              <c:f>'Sheet 1'!$F$49:$F$59</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="11"/>
@@ -4258,13 +4318,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>132179</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>56857</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>436979</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>56857</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4300,7 +4360,7 @@
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>605790</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4330,13 +4390,13 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>868680</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>76</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4366,13 +4426,13 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>929640</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>259080</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4664,7 +4724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22416C2-1180-4450-A3B0-0B08DD9AEC85}">
-  <dimension ref="A1:L68"/>
+  <dimension ref="A1:L76"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
@@ -4769,1579 +4829,1774 @@
         <v>1.40420707746021</v>
       </c>
       <c r="D6">
-        <v>1.3831224644600999</v>
+        <v>1.3686193553583801</v>
       </c>
       <c r="E6">
-        <v>1.3838944628918</v>
+        <v>1.38512260545705</v>
       </c>
       <c r="F6" s="10">
         <f>E6/D6</f>
-        <v>1.0005581562381762</v>
+        <v>1.0120583199660715</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6">
         <v>1.4043892076542099</v>
       </c>
       <c r="I6">
-        <v>1.38336349245063</v>
+        <v>1.3681177802680899</v>
       </c>
       <c r="J6">
-        <v>1.3838999999999999</v>
+        <v>1.3851639268062399</v>
       </c>
       <c r="K6" s="10">
         <f>J6/I6</f>
-        <v>1.0003878283273324</v>
+        <v>1.0124595607074192</v>
       </c>
       <c r="L6" s="10"/>
     </row>
-    <row r="7" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
-        <v>15</v>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>0.5</v>
       </c>
       <c r="B7" s="5"/>
-      <c r="C7" s="4">
-        <v>1.3978225806626601</v>
-      </c>
       <c r="D7">
-        <v>1.37702734478371</v>
+        <v>1.3922831524096599</v>
       </c>
       <c r="E7">
-        <v>1.3807100466595501</v>
-      </c>
-      <c r="F7" s="11">
-        <f t="shared" ref="F7:F16" si="0">E7/D7</f>
-        <v>1.0026743854359832</v>
-      </c>
-      <c r="H7" s="4">
-        <v>1.3977474767840601</v>
-      </c>
+        <v>1.37451308945358</v>
+      </c>
+      <c r="F7" s="10">
+        <f t="shared" ref="F7:F20" si="0">E7/D7</f>
+        <v>0.98723674640081305</v>
+      </c>
+      <c r="G7" s="4"/>
       <c r="I7">
-        <v>1.3757277802121</v>
+        <v>1.3884228746446901</v>
       </c>
       <c r="J7">
-        <v>1.3794929073686799</v>
-      </c>
-      <c r="K7" s="11">
-        <f t="shared" ref="K7:K16" si="1">J7/I7</f>
-        <v>1.0027368257083531</v>
-      </c>
-      <c r="L7" s="11"/>
+        <v>1.3739233641712201</v>
+      </c>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>30</v>
+        <v>1.5</v>
       </c>
       <c r="B8" s="5"/>
-      <c r="C8">
-        <v>1.3935791421766499</v>
-      </c>
       <c r="D8">
-        <v>1.3755520515803401</v>
+        <v>1.4141178954362701</v>
       </c>
       <c r="E8">
-        <v>1.37852177249786</v>
+        <v>1.3766722209354501</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="0"/>
-        <v>1.0021589302375784</v>
+        <v>0.97352011835670349</v>
       </c>
       <c r="G8" s="4"/>
-      <c r="H8">
-        <v>1.3923333952149399</v>
-      </c>
       <c r="I8">
-        <v>1.3733520244906201</v>
+        <v>1.4147283449213399</v>
       </c>
       <c r="J8">
-        <v>1.3762808980096699</v>
-      </c>
-      <c r="K8" s="10">
-        <f t="shared" si="1"/>
-        <v>1.002132645867061</v>
-      </c>
+        <v>1.3760578260651899</v>
+      </c>
+      <c r="K8" s="10"/>
       <c r="L8" s="10"/>
     </row>
-    <row r="9" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>60</v>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>10</v>
       </c>
       <c r="B9" s="5"/>
-      <c r="C9" s="4">
-        <v>1.38536063754419</v>
-      </c>
       <c r="D9">
-        <v>1.3645310546268701</v>
+        <v>1.4052374449883001</v>
       </c>
       <c r="E9">
-        <v>1.37130071674191</v>
-      </c>
-      <c r="F9" s="11">
+        <v>1.38656109713547</v>
+      </c>
+      <c r="F9" s="10">
         <f t="shared" si="0"/>
-        <v>1.0049611638314022</v>
-      </c>
-      <c r="H9" s="4">
-        <v>1.3811147115786999</v>
-      </c>
+        <v>0.98670947182667379</v>
+      </c>
+      <c r="G9" s="4"/>
       <c r="I9">
-        <v>1.36149933832843</v>
+        <v>1.3952787310994501</v>
       </c>
       <c r="J9">
-        <v>1.3675900707900199</v>
-      </c>
-      <c r="K9" s="11">
-        <f t="shared" si="1"/>
-        <v>1.004473547867506</v>
-      </c>
-      <c r="L9" s="11"/>
+        <v>1.3887518550334099</v>
+      </c>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="B10" s="5"/>
-      <c r="C10">
-        <v>1.37856347972413</v>
+      <c r="C10" s="4">
+        <v>1.3978225806626601</v>
       </c>
       <c r="D10">
-        <v>1.3579435428314801</v>
+        <v>1.3588321367490299</v>
       </c>
       <c r="E10">
-        <v>1.3688037548163601</v>
+        <v>1.3960885502131399</v>
       </c>
       <c r="F10" s="10">
         <f t="shared" si="0"/>
-        <v>1.007997543080646</v>
-      </c>
-      <c r="G10" s="4"/>
-      <c r="H10">
-        <v>1.3698685473168299</v>
+        <v>1.0274179661023068</v>
+      </c>
+      <c r="H10" s="4">
+        <v>1.3977474767840601</v>
       </c>
       <c r="I10">
-        <v>1.35117281876724</v>
+        <v>1.36086238814935</v>
       </c>
       <c r="J10">
-        <v>1.3611563781376099</v>
-      </c>
-      <c r="K10" s="10">
+        <v>1.3943568221478799</v>
+      </c>
+      <c r="K10" s="11">
+        <f t="shared" ref="K10:K20" si="1">J10/I10</f>
+        <v>1.0246126531897757</v>
+      </c>
+      <c r="L10" s="11"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>30</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11">
+        <v>1.3935791421766499</v>
+      </c>
+      <c r="D11">
+        <v>1.38084479180245</v>
+      </c>
+      <c r="E11">
+        <v>1.3802674426896999</v>
+      </c>
+      <c r="F11" s="10">
+        <f t="shared" si="0"/>
+        <v>0.9995818870330847</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11">
+        <v>1.3923333952149399</v>
+      </c>
+      <c r="I11">
+        <v>1.3852911212816701</v>
+      </c>
+      <c r="J11">
+        <v>1.3731450592762</v>
+      </c>
+      <c r="K11" s="10">
         <f t="shared" si="1"/>
-        <v>1.0073888101001607</v>
-      </c>
-      <c r="L10" s="10"/>
+        <v>0.99123212311197628</v>
+      </c>
+      <c r="L11" s="10"/>
     </row>
-    <row r="11" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4">
-        <v>120</v>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="4">
-        <v>1.3699400435562701</v>
-      </c>
-      <c r="D11">
-        <v>1.3501528303570001</v>
-      </c>
-      <c r="E11">
-        <v>1.35934291235779</v>
-      </c>
-      <c r="F11" s="11">
-        <f t="shared" si="0"/>
-        <v>1.0068066975783474</v>
-      </c>
-      <c r="H11" s="4">
-        <v>1.35986137171571</v>
-      </c>
-      <c r="I11">
-        <v>1.3415734947956099</v>
-      </c>
-      <c r="J11">
-        <v>1.35251081905353</v>
-      </c>
-      <c r="K11" s="11">
-        <f t="shared" si="1"/>
-        <v>1.0081526090820587</v>
-      </c>
-      <c r="L11" s="11"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="B12" s="5"/>
-      <c r="C12">
-        <v>1.3618779251700099</v>
+      <c r="C12" s="4">
+        <v>1.38536063754419</v>
       </c>
       <c r="D12">
-        <v>1.3433447133374901</v>
+        <v>1.35391575819657</v>
       </c>
       <c r="E12">
-        <v>1.35750883426798</v>
+        <v>1.35872734366118</v>
       </c>
       <c r="F12" s="10">
         <f t="shared" si="0"/>
-        <v>1.0105439212957481</v>
-      </c>
-      <c r="G12" s="4"/>
-      <c r="H12">
-        <v>1.34863286309854</v>
+        <v>1.0035538292803527</v>
+      </c>
+      <c r="H12" s="4">
+        <v>1.3811147115786999</v>
       </c>
       <c r="I12">
-        <v>1.3311196421075699</v>
+        <v>1.3558315843768101</v>
       </c>
       <c r="J12">
-        <v>1.34551772504349</v>
-      </c>
-      <c r="K12" s="10">
+        <v>1.35851656917782</v>
+      </c>
+      <c r="K12" s="11">
         <f t="shared" si="1"/>
-        <v>1.010816520529382</v>
-      </c>
-      <c r="L12" s="10"/>
+        <v>1.0019803232436455</v>
+      </c>
+      <c r="L12" s="11"/>
     </row>
-    <row r="13" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4">
-        <v>250</v>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>90</v>
       </c>
       <c r="B13" s="5"/>
-      <c r="C13" s="4">
-        <v>1.34128105403747</v>
+      <c r="C13">
+        <v>1.37856347972413</v>
       </c>
       <c r="D13">
-        <v>1.3183641537176001</v>
+        <v>1.3540665504448699</v>
       </c>
       <c r="E13">
-        <v>1.33950744156537</v>
-      </c>
-      <c r="F13" s="11">
+        <v>1.3846270062289301</v>
+      </c>
+      <c r="F13" s="10">
         <f t="shared" si="0"/>
-        <v>1.0160375172429779</v>
-      </c>
-      <c r="H13" s="4">
-        <v>1.31869938927708</v>
+        <v>1.0225693897940391</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13">
+        <v>1.3698685473168299</v>
       </c>
       <c r="I13">
-        <v>1.3013234683263499</v>
+        <v>1.34423803647162</v>
       </c>
       <c r="J13">
-        <v>1.31822047972122</v>
-      </c>
-      <c r="K13" s="11">
+        <v>1.37594039827729</v>
+      </c>
+      <c r="K13" s="10">
         <f t="shared" si="1"/>
-        <v>1.0129844821876621</v>
-      </c>
-      <c r="L13" s="11"/>
+        <v>1.0235838898658773</v>
+      </c>
+      <c r="L13" s="10"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="B14" s="5"/>
-      <c r="C14">
-        <v>1.2896852557910301</v>
-      </c>
       <c r="D14">
-        <v>1.2700267746399601</v>
+        <v>1.3565730983264299</v>
       </c>
       <c r="E14">
-        <v>1.30526568090843</v>
+        <v>1.37473157938041</v>
       </c>
       <c r="F14" s="10">
         <f t="shared" si="0"/>
-        <v>1.0277465853256991</v>
+        <v>1.0133855529616367</v>
       </c>
       <c r="G14" s="4"/>
-      <c r="H14">
-        <v>1.24433347413396</v>
-      </c>
       <c r="I14">
-        <v>1.2338069312922</v>
+        <v>1.3294388930292</v>
       </c>
       <c r="J14">
-        <v>1.2692076364611</v>
-      </c>
-      <c r="K14" s="10">
-        <f t="shared" si="1"/>
-        <v>1.0286922566821892</v>
-      </c>
+        <v>1.3730626322350199</v>
+      </c>
+      <c r="K14" s="10"/>
       <c r="L14" s="10"/>
     </row>
     <row r="15" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4">
-        <v>750</v>
+      <c r="A15">
+        <v>120</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="4">
-        <v>1.24225887840578</v>
+        <v>1.3699400435562701</v>
       </c>
       <c r="D15">
-        <v>1.2232055342510899</v>
+        <v>1.34077916991197</v>
       </c>
       <c r="E15">
-        <v>1.27339468040781</v>
-      </c>
-      <c r="F15" s="11">
+        <v>1.3634284951011899</v>
+      </c>
+      <c r="F15" s="10">
         <f t="shared" si="0"/>
-        <v>1.0410308363977838</v>
+        <v>1.0168926589087053</v>
       </c>
       <c r="H15" s="4">
-        <v>1.1765306054398399</v>
+        <v>1.35986137171571</v>
       </c>
       <c r="I15">
-        <v>1.1709175184150999</v>
+        <v>1.35581073898229</v>
       </c>
       <c r="J15">
-        <v>1.21893760257761</v>
+        <v>1.34549110875214</v>
       </c>
       <c r="K15" s="11">
         <f t="shared" si="1"/>
-        <v>1.0410106462729396</v>
+        <v>0.99238859087523068</v>
       </c>
       <c r="L15" s="11"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16">
-        <v>1.1938794039418501</v>
+        <v>1.3618779251700099</v>
       </c>
       <c r="D16">
-        <v>1.1763723210775801</v>
+        <v>1.3628583617894401</v>
       </c>
       <c r="E16">
-        <v>1.2402268546061399</v>
+        <v>1.3660435580514501</v>
       </c>
       <c r="F16" s="10">
         <f t="shared" si="0"/>
-        <v>1.0542808874235223</v>
+        <v>1.0023371440138709</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16">
-        <v>1.1108715265371401</v>
+        <v>1.34863286309854</v>
       </c>
       <c r="I16">
-        <v>1.10875726262634</v>
+        <v>1.34642475596859</v>
       </c>
       <c r="J16">
-        <v>1.17243554422976</v>
+        <v>1.3556369406847</v>
       </c>
       <c r="K16" s="10">
         <f t="shared" si="1"/>
-        <v>1.0574321213036151</v>
+        <v>1.0068419602917082</v>
       </c>
       <c r="L16" s="10"/>
     </row>
+    <row r="17" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>250</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="4">
+        <v>1.34128105403747</v>
+      </c>
+      <c r="D17">
+        <v>1.31238054231434</v>
+      </c>
+      <c r="E17">
+        <v>1.30114468854049</v>
+      </c>
+      <c r="F17" s="10">
+        <f t="shared" si="0"/>
+        <v>0.99143857028386306</v>
+      </c>
+      <c r="H17" s="4">
+        <v>1.31869938927708</v>
+      </c>
+      <c r="I17">
+        <v>1.2854468687873799</v>
+      </c>
+      <c r="J17">
+        <v>1.2908172794684301</v>
+      </c>
+      <c r="K17" s="11">
+        <f t="shared" si="1"/>
+        <v>1.0041778550412717</v>
+      </c>
+      <c r="L17" s="11"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>500</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18">
+        <v>1.2896852557910301</v>
+      </c>
+      <c r="D18">
+        <v>1.27106900787611</v>
+      </c>
+      <c r="E18">
+        <v>1.2663520004962301</v>
+      </c>
+      <c r="F18" s="10">
+        <f t="shared" si="0"/>
+        <v>0.99628894469879192</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18">
+        <v>1.24433347413396</v>
+      </c>
+      <c r="I18">
+        <v>1.24215702849295</v>
+      </c>
+      <c r="J18">
+        <v>1.26045747443881</v>
+      </c>
+      <c r="K18" s="10">
+        <f t="shared" si="1"/>
+        <v>1.0147327958753034</v>
+      </c>
+      <c r="L18" s="10"/>
+    </row>
+    <row r="19" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>750</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="4">
+        <v>1.24225887840578</v>
+      </c>
+      <c r="D19">
+        <v>1.2502327359779</v>
+      </c>
+      <c r="E19">
+        <v>1.26687035022674</v>
+      </c>
+      <c r="F19" s="10">
+        <f t="shared" si="0"/>
+        <v>1.0133076136706871</v>
+      </c>
+      <c r="H19" s="4">
+        <v>1.1765306054398399</v>
+      </c>
+      <c r="I19">
+        <v>1.20261020085431</v>
+      </c>
+      <c r="J19">
+        <v>1.2257592093430201</v>
+      </c>
+      <c r="K19" s="11">
+        <f t="shared" si="1"/>
+        <v>1.0192489706741765</v>
+      </c>
+      <c r="L19" s="11"/>
+    </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C20" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="3"/>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="8"/>
-      <c r="H22" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L22" s="7"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>0.1</v>
-      </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="2">
-        <v>3.52725672373683E-5</v>
-      </c>
-      <c r="D23" s="2">
-        <v>3.4352992727381499E-5</v>
-      </c>
-      <c r="E23" s="2">
-        <v>2.0875371825261901E-5</v>
-      </c>
-      <c r="F23" s="10">
-        <f>E23/D23</f>
-        <v>0.60767258302427063</v>
-      </c>
-      <c r="G23" s="4"/>
-      <c r="H23" s="2">
-        <v>3.2364516810043102E-5</v>
-      </c>
-      <c r="I23" s="2">
-        <v>3.0077664875068999E-5</v>
-      </c>
-      <c r="J23" s="2">
-        <v>2.3316099999999999E-5</v>
-      </c>
-      <c r="K23" s="10">
-        <f>J23/I23</f>
-        <v>0.77519648206887304</v>
-      </c>
-      <c r="L23" s="10"/>
+      <c r="A20">
+        <v>999.99</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20">
+        <v>1.1938794039418501</v>
+      </c>
+      <c r="D20">
+        <v>1.2216766905077201</v>
+      </c>
+      <c r="E20">
+        <v>1.20816790789953</v>
+      </c>
+      <c r="F20" s="10">
+        <f t="shared" si="0"/>
+        <v>0.98894242420015732</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20">
+        <v>1.1108715265371401</v>
+      </c>
+      <c r="I20">
+        <v>1.1553240194424299</v>
+      </c>
+      <c r="J20">
+        <v>1.13503567173569</v>
+      </c>
+      <c r="K20" s="10">
+        <f t="shared" si="1"/>
+        <v>0.9824392574158276</v>
+      </c>
+      <c r="L20" s="10"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="4">
-        <v>15</v>
-      </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5">
-        <v>5.02535867346246E-3</v>
-      </c>
-      <c r="D24">
-        <v>4.8415021318079796E-3</v>
-      </c>
-      <c r="E24">
-        <v>3.1726397963949501E-3</v>
-      </c>
-      <c r="F24" s="11">
-        <f t="shared" ref="F24:F33" si="2">E24/D24</f>
-        <v>0.65530071246920629</v>
-      </c>
-      <c r="G24" s="4"/>
-      <c r="H24">
-        <v>4.7442437671726999E-3</v>
-      </c>
-      <c r="I24">
-        <v>4.41670217006298E-3</v>
-      </c>
-      <c r="J24">
-        <v>3.5370383339396899E-3</v>
-      </c>
-      <c r="K24" s="11">
-        <f t="shared" ref="K24:K33" si="3">J24/I24</f>
-        <v>0.80083243056645892</v>
-      </c>
-      <c r="L24" s="11"/>
+      <c r="C24" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="12"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>30</v>
-      </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="2">
-        <v>9.6096776712520909E-3</v>
-      </c>
-      <c r="D25">
-        <v>9.3736870838320892E-3</v>
-      </c>
-      <c r="E25">
-        <v>6.3510742712361698E-3</v>
-      </c>
-      <c r="F25" s="10">
-        <f t="shared" si="2"/>
-        <v>0.67754280833532643</v>
-      </c>
-      <c r="G25" s="4"/>
-      <c r="H25">
-        <v>9.3381817414101998E-3</v>
-      </c>
-      <c r="I25">
-        <v>8.6773810916228808E-3</v>
-      </c>
-      <c r="J25">
-        <v>7.1080498826678901E-3</v>
-      </c>
-      <c r="K25" s="10">
-        <f t="shared" si="3"/>
-        <v>0.81914690706968962</v>
-      </c>
-      <c r="L25" s="10"/>
+      <c r="C25" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="3"/>
+      <c r="H25" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I25" s="3"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="3"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="4">
-        <v>60</v>
-      </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5">
-        <v>1.7956202904139199E-2</v>
-      </c>
-      <c r="D26">
-        <v>1.7499246818678899E-2</v>
-      </c>
-      <c r="E26">
-        <v>1.25132922386715E-2</v>
-      </c>
-      <c r="F26" s="11">
-        <f t="shared" si="2"/>
-        <v>0.7150760468910391</v>
-      </c>
-      <c r="G26" s="4"/>
-      <c r="H26">
-        <v>1.8093633576609602E-2</v>
-      </c>
-      <c r="I26">
-        <v>1.6825678983851101E-2</v>
-      </c>
-      <c r="J26">
-        <v>1.39074464086831E-2</v>
-      </c>
-      <c r="K26" s="11">
-        <f t="shared" si="3"/>
-        <v>0.82656078378953657</v>
-      </c>
-      <c r="L26" s="11"/>
+      <c r="A26" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="8"/>
+      <c r="H26" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="7"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>90</v>
+        <v>0.1</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="2">
-        <v>2.54716677488637E-2</v>
+        <v>3.52725672373683E-5</v>
       </c>
       <c r="D27">
-        <v>2.48286557998008E-2</v>
+        <v>3.2314434653956498E-4</v>
       </c>
       <c r="E27">
-        <v>1.8460059811568001E-2</v>
+        <v>2.9113846589042902E-4</v>
       </c>
       <c r="F27" s="10">
-        <f t="shared" si="2"/>
-        <v>0.74349815634063066</v>
+        <f>E27/D27</f>
+        <v>0.90095484884115951</v>
       </c>
       <c r="G27" s="4"/>
-      <c r="H27">
-        <v>2.63480432958439E-2</v>
+      <c r="H27" s="2">
+        <v>3.2364516810043102E-5</v>
       </c>
       <c r="I27">
-        <v>2.45310107988954E-2</v>
+        <v>2.8864520587018101E-4</v>
       </c>
       <c r="J27">
-        <v>2.0720356978390701E-2</v>
+        <v>2.8967006957661098E-4</v>
       </c>
       <c r="K27" s="10">
-        <f t="shared" si="3"/>
-        <v>0.84465973083032153</v>
+        <f>J27/I27</f>
+        <v>1.0035506001332684</v>
       </c>
       <c r="L27" s="10"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="4">
-        <v>120</v>
+      <c r="A28">
+        <v>0.5</v>
       </c>
       <c r="B28" s="5"/>
-      <c r="C28" s="5">
-        <v>3.2417642839879697E-2</v>
-      </c>
+      <c r="C28" s="2"/>
       <c r="D28">
-        <v>3.1708222423746601E-2</v>
+        <v>1.63531469505055E-3</v>
       </c>
       <c r="E28">
-        <v>2.4237248335804401E-2</v>
-      </c>
-      <c r="F28" s="11">
-        <f t="shared" si="2"/>
-        <v>0.76438369871068157</v>
-      </c>
+        <v>1.5602327945626699E-3</v>
+      </c>
+      <c r="F28" s="10"/>
       <c r="G28" s="4"/>
-      <c r="H28">
-        <v>3.4169678168819703E-2</v>
-      </c>
+      <c r="H28" s="2"/>
       <c r="I28">
-        <v>3.2010350694294497E-2</v>
+        <v>1.4624167995472899E-3</v>
       </c>
       <c r="J28">
-        <v>2.7239567384599199E-2</v>
-      </c>
-      <c r="K28" s="11">
-        <f t="shared" si="3"/>
-        <v>0.8509612295329948</v>
-      </c>
-      <c r="L28" s="11"/>
+        <v>1.55376135488548E-3</v>
+      </c>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>150</v>
+        <v>1.5</v>
       </c>
       <c r="B29" s="5"/>
-      <c r="C29" s="2">
-        <v>3.9055212834252402E-2</v>
-      </c>
+      <c r="C29" s="2"/>
       <c r="D29">
-        <v>3.8101638451620401E-2</v>
+        <v>5.0200091937920499E-3</v>
       </c>
       <c r="E29">
-        <v>2.9995859491649599E-2</v>
-      </c>
-      <c r="F29" s="10">
-        <f t="shared" si="2"/>
-        <v>0.78725904477144404</v>
-      </c>
+        <v>4.4418725803358596E-3</v>
+      </c>
+      <c r="F29" s="10"/>
       <c r="G29" s="4"/>
-      <c r="H29">
-        <v>4.1796462699614498E-2</v>
-      </c>
+      <c r="H29" s="2"/>
       <c r="I29">
-        <v>3.8938267233086299E-2</v>
+        <v>4.4120832608900004E-3</v>
       </c>
       <c r="J29">
-        <v>3.3615774527897199E-2</v>
-      </c>
-      <c r="K29" s="10">
-        <f t="shared" si="3"/>
-        <v>0.86330946178656565</v>
-      </c>
+        <v>4.3968622699160501E-3</v>
+      </c>
+      <c r="K29" s="10"/>
       <c r="L29" s="10"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="4">
-        <v>250</v>
+      <c r="A30">
+        <v>10</v>
       </c>
       <c r="B30" s="5"/>
-      <c r="C30" s="5">
-        <v>5.8983323870902299E-2</v>
-      </c>
+      <c r="C30" s="2"/>
       <c r="D30">
-        <v>5.7845592896108598E-2</v>
+        <v>3.2233154188020502E-2</v>
       </c>
       <c r="E30">
-        <v>4.8211591891219499E-2</v>
-      </c>
-      <c r="F30" s="11">
-        <f t="shared" si="2"/>
-        <v>0.83345315481177829</v>
-      </c>
+        <v>3.1830960117675798E-2</v>
+      </c>
+      <c r="F30" s="10"/>
       <c r="G30" s="4"/>
-      <c r="H30">
-        <v>6.5796691976300697E-2</v>
-      </c>
+      <c r="H30" s="2"/>
       <c r="I30">
-        <v>6.12659256159543E-2</v>
+        <v>2.9294700126228299E-2</v>
       </c>
       <c r="J30">
-        <v>5.4039519059736599E-2</v>
-      </c>
-      <c r="K30" s="11">
-        <f t="shared" si="3"/>
-        <v>0.88204852071416562</v>
-      </c>
-      <c r="L30" s="11"/>
+        <v>2.9963416156383201E-2</v>
+      </c>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>500</v>
+      <c r="A31" s="4">
+        <v>15</v>
       </c>
       <c r="B31" s="5"/>
-      <c r="C31" s="2">
-        <v>0.103595084893309</v>
+      <c r="C31" s="5">
+        <v>5.02535867346246E-3</v>
       </c>
       <c r="D31">
-        <v>0.101681976801287</v>
+        <v>4.8083671005010903E-2</v>
       </c>
       <c r="E31">
-        <v>8.9687488426909795E-2</v>
-      </c>
-      <c r="F31" s="10">
-        <f t="shared" si="2"/>
-        <v>0.88203918971975193</v>
+        <v>4.7413078230864998E-2</v>
+      </c>
+      <c r="F31" s="11">
+        <f t="shared" ref="F31:F41" si="2">E31/D31</f>
+        <v>0.98605362776739691</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31">
-        <v>0.11839645185777101</v>
+        <v>4.7442437671726999E-3</v>
       </c>
       <c r="I31">
-        <v>0.111333610679465</v>
+        <v>4.28280907778881E-2</v>
       </c>
       <c r="J31">
-        <v>0.10049617393209</v>
-      </c>
-      <c r="K31" s="10">
-        <f t="shared" si="3"/>
-        <v>0.90265799625796272</v>
-      </c>
-      <c r="L31" s="10"/>
+        <v>4.61668507397665E-2</v>
+      </c>
+      <c r="K31" s="11">
+        <f t="shared" ref="K31:K41" si="3">J31/I31</f>
+        <v>1.0779572449118415</v>
+      </c>
+      <c r="L31" s="11"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="4">
-        <v>750</v>
+      <c r="A32">
+        <v>30</v>
       </c>
       <c r="B32" s="5"/>
-      <c r="C32" s="5">
-        <v>0.14519436153500101</v>
+      <c r="C32" s="2">
+        <v>9.6096776712520909E-3</v>
       </c>
       <c r="D32">
-        <v>0.142175529915751</v>
+        <v>9.5891818868841697E-2</v>
       </c>
       <c r="E32">
-        <v>0.127241075651779</v>
-      </c>
-      <c r="F32" s="11">
+        <v>9.4831541186847598E-2</v>
+      </c>
+      <c r="F32" s="10">
         <f t="shared" si="2"/>
-        <v>0.89495763249258353</v>
+        <v>0.98894298080377097</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32">
-        <v>0.165934052581929</v>
+        <v>9.3381817414101998E-3</v>
       </c>
       <c r="I32">
-        <v>0.15627146301212599</v>
+        <v>8.7192700810209606E-2</v>
       </c>
       <c r="J32">
-        <v>0.14163041239443799</v>
-      </c>
-      <c r="K32" s="11">
+        <v>8.8994701260368805E-2</v>
+      </c>
+      <c r="K32" s="10">
         <f t="shared" si="3"/>
-        <v>0.90631014559227674</v>
-      </c>
-      <c r="L32" s="11"/>
+        <v>1.0206668727246053</v>
+      </c>
+      <c r="L32" s="10"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>1000</v>
+      <c r="A33" s="4">
+        <v>60</v>
       </c>
       <c r="B33" s="5"/>
-      <c r="C33" s="2">
-        <v>0.185920101577397</v>
+      <c r="C33" s="5">
+        <v>1.7956202904139199E-2</v>
       </c>
       <c r="D33">
-        <v>0.18161105406700601</v>
+        <v>0.18310601049282599</v>
       </c>
       <c r="E33">
-        <v>0.16239985928431699</v>
-      </c>
-      <c r="F33" s="10">
+        <v>0.18135757900897301</v>
+      </c>
+      <c r="F33" s="11">
         <f t="shared" si="2"/>
-        <v>0.8942179214729904</v>
+        <v>0.99045126110744741</v>
       </c>
       <c r="G33" s="4"/>
       <c r="H33">
-        <v>0.211237572970251</v>
+        <v>1.8093633576609602E-2</v>
       </c>
       <c r="I33">
-        <v>0.197961811715788</v>
+        <v>0.168976390095402</v>
       </c>
       <c r="J33">
-        <v>0.17883044593994399</v>
-      </c>
-      <c r="K33" s="10">
+        <v>0.17402218522129201</v>
+      </c>
+      <c r="K33" s="11">
         <f t="shared" si="3"/>
-        <v>0.90335830122978089</v>
-      </c>
-      <c r="L33" s="10"/>
+        <v>1.0298609475740441</v>
+      </c>
+      <c r="L33" s="11"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>90</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="2">
+        <v>2.54716677488637E-2</v>
+      </c>
+      <c r="D34">
+        <v>0.27052609093888302</v>
+      </c>
+      <c r="E34">
+        <v>0.27828767586518899</v>
+      </c>
+      <c r="F34" s="10">
+        <f t="shared" si="2"/>
+        <v>1.0286907074262921</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34">
+        <v>2.63480432958439E-2</v>
+      </c>
+      <c r="I34">
+        <v>0.25226765578979399</v>
+      </c>
+      <c r="J34">
+        <v>0.27028735246822</v>
+      </c>
+      <c r="K34" s="10">
+        <f t="shared" si="3"/>
+        <v>1.0714308642620487</v>
+      </c>
+      <c r="L34" s="10"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="4">
+        <v>100</v>
+      </c>
+      <c r="B35" s="5"/>
+      <c r="C35" s="2"/>
+      <c r="D35">
+        <v>0.29782820153673201</v>
+      </c>
+      <c r="E35">
+        <v>0.31219673881320298</v>
+      </c>
+      <c r="F35" s="10"/>
+      <c r="G35" s="4"/>
+      <c r="I35">
+        <v>0.27710332040764002</v>
+      </c>
+      <c r="J35">
+        <v>0.29733056001795299</v>
+      </c>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="4">
+        <v>120</v>
+      </c>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5">
+        <v>3.2417642839879697E-2</v>
+      </c>
+      <c r="D36">
+        <v>0.35933558625490702</v>
+      </c>
+      <c r="E36">
+        <v>0.36327933121591299</v>
+      </c>
+      <c r="F36" s="11">
+        <f t="shared" si="2"/>
+        <v>1.0109751026946947</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36">
+        <v>3.4169678168819703E-2</v>
+      </c>
+      <c r="I36">
+        <v>0.33488526020133202</v>
+      </c>
+      <c r="J36">
+        <v>0.350044087283917</v>
+      </c>
+      <c r="K36" s="11">
+        <f t="shared" si="3"/>
+        <v>1.0452657339217364</v>
+      </c>
+      <c r="L36" s="11"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C37" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A37">
+        <v>150</v>
+      </c>
+      <c r="B37" s="5"/>
+      <c r="C37" s="2">
+        <v>3.9055212834252402E-2</v>
+      </c>
+      <c r="D37">
+        <v>0.440983559195115</v>
+      </c>
+      <c r="E37">
+        <v>0.46369387108133497</v>
+      </c>
+      <c r="F37" s="10">
+        <f t="shared" si="2"/>
+        <v>1.0514992257935214</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37">
+        <v>4.1796462699614498E-2</v>
+      </c>
+      <c r="I37">
+        <v>0.41421243624474702</v>
+      </c>
+      <c r="J37">
+        <v>0.44198494489621698</v>
+      </c>
+      <c r="K37" s="10">
+        <f t="shared" si="3"/>
+        <v>1.0670489493344424</v>
+      </c>
+      <c r="L37" s="10"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C38" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="D38" s="14"/>
-      <c r="E38" s="15"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
+      <c r="A38" s="4">
+        <v>250</v>
+      </c>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5">
+        <v>5.8983323870902299E-2</v>
+      </c>
+      <c r="D38">
+        <v>0.69943129650860603</v>
+      </c>
+      <c r="E38">
+        <v>0.74056761334149801</v>
+      </c>
+      <c r="F38" s="11">
+        <f t="shared" si="2"/>
+        <v>1.0588139493303126</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38">
+        <v>6.5796691976300697E-2</v>
+      </c>
+      <c r="I38">
+        <v>0.66184301157104197</v>
+      </c>
+      <c r="J38">
+        <v>0.70419594658632301</v>
+      </c>
+      <c r="K38" s="11">
+        <f t="shared" si="3"/>
+        <v>1.0639924185567</v>
+      </c>
+      <c r="L38" s="11"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C39" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" s="3"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="3"/>
-      <c r="H39" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I39" s="3"/>
-      <c r="J39" s="9"/>
-      <c r="K39" s="9"/>
+      <c r="A39">
+        <v>500</v>
+      </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="2">
+        <v>0.103595084893309</v>
+      </c>
+      <c r="D39">
+        <v>1.3176141318230901</v>
+      </c>
+      <c r="E39">
+        <v>1.4059443021665801</v>
+      </c>
+      <c r="F39" s="10">
+        <f t="shared" si="2"/>
+        <v>1.0670379652207234</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39">
+        <v>0.11839645185777101</v>
+      </c>
+      <c r="I39">
+        <v>1.25292933313</v>
+      </c>
+      <c r="J39">
+        <v>1.3590454721452301</v>
+      </c>
+      <c r="K39" s="10">
+        <f t="shared" si="3"/>
+        <v>1.0846944326462025</v>
+      </c>
+      <c r="L39" s="10"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G40" s="8"/>
-      <c r="H40" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="J40" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K40" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="A40" s="4">
+        <v>750</v>
+      </c>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5">
+        <v>0.14519436153500101</v>
+      </c>
+      <c r="D40">
+        <v>1.9175894049158899</v>
+      </c>
+      <c r="E40">
+        <v>2.0750333201713098</v>
+      </c>
+      <c r="F40" s="11">
+        <f t="shared" si="2"/>
+        <v>1.0821051236786146</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40">
+        <v>0.165934052581929</v>
+      </c>
+      <c r="I40">
+        <v>1.8041504774598101</v>
+      </c>
+      <c r="J40">
+        <v>1.9766773113</v>
+      </c>
+      <c r="K40" s="11">
+        <f t="shared" si="3"/>
+        <v>1.0956277405879706</v>
+      </c>
+      <c r="L40" s="11"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>0.1</v>
+        <v>1000</v>
       </c>
       <c r="B41" s="5"/>
-      <c r="C41">
-        <v>1.38755773111088</v>
+      <c r="C41" s="2">
+        <v>0.185920101577397</v>
       </c>
       <c r="D41">
-        <v>1.3354353849754901</v>
+        <v>2.4565650146404598</v>
       </c>
       <c r="E41">
-        <v>1.33571066860882</v>
+        <v>2.6505145134263399</v>
       </c>
       <c r="F41" s="10">
-        <f>E41/D41</f>
-        <v>1.0002061377408649</v>
+        <f t="shared" si="2"/>
+        <v>1.0789515024556622</v>
       </c>
       <c r="G41" s="4"/>
+      <c r="H41">
+        <v>0.211237572970251</v>
+      </c>
       <c r="I41">
-        <v>1.3355902411931799</v>
+        <v>2.3142913460731198</v>
       </c>
       <c r="J41">
-        <v>1.33570664006712</v>
+        <v>2.4780340620747099</v>
       </c>
       <c r="K41" s="10">
-        <f>J41/I41</f>
-        <v>1.0000871516355467</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="4">
-        <v>15</v>
-      </c>
-      <c r="B42" s="5"/>
-      <c r="C42">
-        <v>1.38409520401011</v>
-      </c>
-      <c r="D42">
-        <v>1.3305745989353699</v>
-      </c>
-      <c r="E42">
-        <v>1.3291243406104201</v>
-      </c>
-      <c r="F42" s="11">
-        <f t="shared" ref="F42:F51" si="4">E42/D42</f>
-        <v>0.99891005109663888</v>
-      </c>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42">
-        <v>1.3283272840070699</v>
-      </c>
-      <c r="J42">
-        <v>1.32707241565139</v>
-      </c>
-      <c r="K42" s="11">
-        <f t="shared" ref="K42:K51" si="5">J42/I42</f>
-        <v>0.99905530182900826</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43">
-        <v>30</v>
-      </c>
-      <c r="B43" s="5"/>
-      <c r="C43">
-        <v>1.3811622398640599</v>
-      </c>
-      <c r="D43">
-        <v>1.3310144038562199</v>
-      </c>
-      <c r="E43">
-        <v>1.3285615218559801</v>
-      </c>
-      <c r="F43" s="10">
-        <f t="shared" si="4"/>
-        <v>0.99815713339154455</v>
-      </c>
-      <c r="G43" s="4"/>
-      <c r="I43">
-        <v>1.32510611680532</v>
-      </c>
-      <c r="J43">
-        <v>1.3232823680411001</v>
-      </c>
-      <c r="K43" s="10">
-        <f t="shared" si="5"/>
-        <v>0.9986236960639675</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="4">
-        <v>60</v>
-      </c>
-      <c r="B44" s="5"/>
-      <c r="C44">
-        <v>1.37486493369789</v>
-      </c>
-      <c r="D44">
-        <v>1.32588118290715</v>
-      </c>
-      <c r="E44">
-        <v>1.3260681746726899</v>
-      </c>
-      <c r="F44" s="11">
-        <f t="shared" si="4"/>
-        <v>1.0001410320682957</v>
-      </c>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44">
-        <v>1.3187223856414001</v>
-      </c>
-      <c r="J44">
-        <v>1.31770759949175</v>
-      </c>
-      <c r="K44" s="11">
-        <f t="shared" si="5"/>
-        <v>0.99923047780131791</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v>1.0707528532565391</v>
+      </c>
+      <c r="L41" s="10"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45">
-        <v>90</v>
-      </c>
-      <c r="B45" s="5"/>
-      <c r="C45">
-        <v>1.36350384779266</v>
-      </c>
-      <c r="D45">
-        <v>1.3250331310758601</v>
-      </c>
-      <c r="E45">
-        <v>1.32283704671966</v>
-      </c>
-      <c r="F45" s="10">
-        <f t="shared" si="4"/>
-        <v>0.99834261928649515</v>
-      </c>
-      <c r="G45" s="4"/>
-      <c r="I45">
-        <v>1.3124798292895099</v>
-      </c>
-      <c r="J45">
-        <v>1.3112535491322701</v>
-      </c>
-      <c r="K45" s="10">
-        <f t="shared" si="5"/>
-        <v>0.99906567694994319</v>
+      <c r="C45" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="4">
-        <v>120</v>
-      </c>
-      <c r="B46" s="5"/>
-      <c r="C46">
-        <v>1.3571706170428599</v>
-      </c>
-      <c r="D46">
-        <v>1.3186752377537301</v>
-      </c>
-      <c r="E46">
-        <v>1.31925522687803</v>
-      </c>
-      <c r="F46" s="11">
-        <f t="shared" si="4"/>
-        <v>1.000439827114133</v>
-      </c>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46">
-        <v>1.3033297752905399</v>
-      </c>
-      <c r="J46">
-        <v>1.3019564075099299</v>
-      </c>
-      <c r="K46" s="11">
-        <f t="shared" si="5"/>
-        <v>0.99894626225330896</v>
-      </c>
+      <c r="C46" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D46" s="14"/>
+      <c r="E46" s="15"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47">
-        <v>150</v>
-      </c>
-      <c r="B47" s="5"/>
-      <c r="C47">
-        <v>1.35109721915133</v>
-      </c>
-      <c r="D47">
-        <v>1.3162252475838401</v>
-      </c>
-      <c r="E47">
-        <v>1.3162028531863199</v>
-      </c>
-      <c r="F47" s="10">
-        <f t="shared" si="4"/>
-        <v>0.99998298589275558</v>
-      </c>
-      <c r="G47" s="4"/>
-      <c r="I47">
-        <v>1.29663015170481</v>
-      </c>
-      <c r="J47">
-        <v>1.2969552292914901</v>
-      </c>
-      <c r="K47" s="10">
-        <f t="shared" si="5"/>
-        <v>1.0002507095691495</v>
-      </c>
+      <c r="C47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D47" s="3"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="3"/>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3"/>
+      <c r="J47" s="9"/>
+      <c r="K47" s="9"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="4">
-        <v>250</v>
-      </c>
-      <c r="B48" s="5"/>
-      <c r="C48">
-        <v>1.32844051248484</v>
-      </c>
-      <c r="D48">
-        <v>1.30260068538983</v>
-      </c>
-      <c r="E48">
-        <v>1.3066950650451801</v>
-      </c>
-      <c r="F48" s="11">
-        <f t="shared" si="4"/>
-        <v>1.0031432346852518</v>
-      </c>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48">
-        <v>1.2708609670523101</v>
-      </c>
-      <c r="J48">
-        <v>1.27351639583336</v>
-      </c>
-      <c r="K48" s="11">
-        <f t="shared" si="5"/>
-        <v>1.0020894722946829</v>
+      <c r="A48" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G48" s="8"/>
+      <c r="H48" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="J48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>500</v>
+        <v>0.1</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49">
-        <v>1.26939305918802</v>
+        <v>1.38755773111088</v>
       </c>
       <c r="D49">
-        <v>1.26652819252339</v>
+        <v>1.3354353849754901</v>
       </c>
       <c r="E49">
-        <v>1.2763205188269799</v>
+        <v>1.33571066860882</v>
       </c>
       <c r="F49" s="10">
-        <f t="shared" si="4"/>
-        <v>1.0077316291586689</v>
+        <f>E49/D49</f>
+        <v>1.0002061377408649</v>
       </c>
       <c r="G49" s="4"/>
       <c r="I49">
-        <v>1.2073775660257999</v>
+        <v>1.3355902411931799</v>
       </c>
       <c r="J49">
-        <v>1.2155197343022801</v>
+        <v>1.33570664006712</v>
       </c>
       <c r="K49" s="10">
-        <f t="shared" si="5"/>
-        <v>1.0067436802749954</v>
+        <f>J49/I49</f>
+        <v>1.0000871516355467</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
-        <v>750</v>
+        <v>15</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50">
-        <v>1.2146497361047901</v>
+        <v>1.38409520401011</v>
       </c>
       <c r="D50">
-        <v>1.2257285387942201</v>
+        <v>1.3305745989353699</v>
       </c>
       <c r="E50">
-        <v>1.2402498141564899</v>
+        <v>1.3291243406104201</v>
       </c>
       <c r="F50" s="11">
-        <f t="shared" si="4"/>
-        <v>1.0118470565893447</v>
+        <f t="shared" ref="F50:F59" si="4">E50/D50</f>
+        <v>0.99891005109663888</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
       <c r="I50">
-        <v>1.1403490012176101</v>
+        <v>1.3283272840070699</v>
       </c>
       <c r="J50">
-        <v>1.15185236456864</v>
+        <v>1.32707241565139</v>
       </c>
       <c r="K50" s="11">
-        <f t="shared" si="5"/>
-        <v>1.0100875813796892</v>
+        <f t="shared" ref="K50:K59" si="5">J50/I50</f>
+        <v>0.99905530182900826</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51">
-        <v>1.1436421352186501</v>
+        <v>1.3811622398640599</v>
       </c>
       <c r="D51">
-        <v>1.1781818408587099</v>
+        <v>1.3310144038562199</v>
       </c>
       <c r="E51">
-        <v>1.19775360779693</v>
+        <v>1.3285615218559801</v>
       </c>
       <c r="F51" s="10">
         <f t="shared" si="4"/>
-        <v>1.0166118389025205</v>
+        <v>0.99815713339154455</v>
       </c>
       <c r="G51" s="4"/>
       <c r="I51">
-        <v>1.072078850564</v>
+        <v>1.32510611680532</v>
       </c>
       <c r="J51">
-        <v>1.0876143945201899</v>
+        <v>1.3232823680411001</v>
       </c>
       <c r="K51" s="10">
         <f t="shared" si="5"/>
-        <v>1.0144910460158942</v>
+        <v>0.9986236960639675</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A52" s="4">
+        <v>60</v>
+      </c>
+      <c r="B52" s="5"/>
+      <c r="C52">
+        <v>1.37486493369789</v>
+      </c>
+      <c r="D52">
+        <v>1.32588118290715</v>
+      </c>
+      <c r="E52">
+        <v>1.3260681746726899</v>
+      </c>
+      <c r="F52" s="11">
+        <f t="shared" si="4"/>
+        <v>1.0001410320682957</v>
+      </c>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52">
+        <v>1.3187223856414001</v>
+      </c>
+      <c r="J52">
+        <v>1.31770759949175</v>
+      </c>
+      <c r="K52" s="11">
+        <f t="shared" si="5"/>
+        <v>0.99923047780131791</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>90</v>
+      </c>
+      <c r="B53" s="5"/>
+      <c r="C53">
+        <v>1.36350384779266</v>
+      </c>
+      <c r="D53">
+        <v>1.3250331310758601</v>
+      </c>
+      <c r="E53">
+        <v>1.32283704671966</v>
+      </c>
+      <c r="F53" s="10">
+        <f t="shared" si="4"/>
+        <v>0.99834261928649515</v>
+      </c>
+      <c r="G53" s="4"/>
+      <c r="I53">
+        <v>1.3124798292895099</v>
+      </c>
+      <c r="J53">
+        <v>1.3112535491322701</v>
+      </c>
+      <c r="K53" s="10">
+        <f t="shared" si="5"/>
+        <v>0.99906567694994319</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A54" s="4">
+        <v>120</v>
+      </c>
+      <c r="B54" s="5"/>
+      <c r="C54">
+        <v>1.3571706170428599</v>
+      </c>
+      <c r="D54">
+        <v>1.3186752377537301</v>
+      </c>
+      <c r="E54">
+        <v>1.31925522687803</v>
+      </c>
+      <c r="F54" s="11">
+        <f t="shared" si="4"/>
+        <v>1.000439827114133</v>
+      </c>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54">
+        <v>1.3033297752905399</v>
+      </c>
+      <c r="J54">
+        <v>1.3019564075099299</v>
+      </c>
+      <c r="K54" s="11">
+        <f t="shared" si="5"/>
+        <v>0.99894626225330896</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C55" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D55" s="12"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
+      <c r="A55">
+        <v>150</v>
+      </c>
+      <c r="B55" s="5"/>
+      <c r="C55">
+        <v>1.35109721915133</v>
+      </c>
+      <c r="D55">
+        <v>1.3162252475838401</v>
+      </c>
+      <c r="E55">
+        <v>1.3162028531863199</v>
+      </c>
+      <c r="F55" s="10">
+        <f t="shared" si="4"/>
+        <v>0.99998298589275558</v>
+      </c>
+      <c r="G55" s="4"/>
+      <c r="I55">
+        <v>1.29663015170481</v>
+      </c>
+      <c r="J55">
+        <v>1.2969552292914901</v>
+      </c>
+      <c r="K55" s="10">
+        <f t="shared" si="5"/>
+        <v>1.0002507095691495</v>
+      </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C56" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D56" s="3"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="3"/>
-      <c r="H56" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I56" s="3"/>
-      <c r="J56" s="9"/>
-      <c r="K56" s="9"/>
+      <c r="A56" s="4">
+        <v>250</v>
+      </c>
+      <c r="B56" s="5"/>
+      <c r="C56">
+        <v>1.32844051248484</v>
+      </c>
+      <c r="D56">
+        <v>1.30260068538983</v>
+      </c>
+      <c r="E56">
+        <v>1.3066950650451801</v>
+      </c>
+      <c r="F56" s="11">
+        <f t="shared" si="4"/>
+        <v>1.0031432346852518</v>
+      </c>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56">
+        <v>1.2708609670523101</v>
+      </c>
+      <c r="J56">
+        <v>1.27351639583336</v>
+      </c>
+      <c r="K56" s="11">
+        <f t="shared" si="5"/>
+        <v>1.0020894722946829</v>
+      </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A57" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G57" s="8"/>
-      <c r="H57" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I57" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="J57" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K57" s="7" t="s">
-        <v>8</v>
+      <c r="A57">
+        <v>500</v>
+      </c>
+      <c r="B57" s="5"/>
+      <c r="C57">
+        <v>1.26939305918802</v>
+      </c>
+      <c r="D57">
+        <v>1.26652819252339</v>
+      </c>
+      <c r="E57">
+        <v>1.2763205188269799</v>
+      </c>
+      <c r="F57" s="10">
+        <f t="shared" si="4"/>
+        <v>1.0077316291586689</v>
+      </c>
+      <c r="G57" s="4"/>
+      <c r="I57">
+        <v>1.2073775660257999</v>
+      </c>
+      <c r="J57">
+        <v>1.2155197343022801</v>
+      </c>
+      <c r="K57" s="10">
+        <f t="shared" si="5"/>
+        <v>1.0067436802749954</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>0.1</v>
+      <c r="A58" s="4">
+        <v>750</v>
       </c>
       <c r="B58" s="5"/>
-      <c r="C58" s="2">
-        <v>2.0906018648200899E-5</v>
-      </c>
-      <c r="D58" s="2">
-        <v>2.0018619481595599E-5</v>
-      </c>
-      <c r="E58" s="2">
-        <v>2.04228717705638E-5</v>
-      </c>
-      <c r="F58" s="10">
-        <f>E58/D58</f>
-        <v>1.0201938145305103</v>
+      <c r="C58">
+        <v>1.2146497361047901</v>
+      </c>
+      <c r="D58">
+        <v>1.2257285387942201</v>
+      </c>
+      <c r="E58">
+        <v>1.2402498141564899</v>
+      </c>
+      <c r="F58" s="11">
+        <f t="shared" si="4"/>
+        <v>1.0118470565893447</v>
       </c>
       <c r="G58" s="4"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2">
-        <v>2.4434932696069799E-5</v>
-      </c>
-      <c r="J58" s="2">
-        <v>2.5518609602937599E-5</v>
-      </c>
-      <c r="K58" s="10">
-        <f>J58/I58</f>
-        <v>1.0443494942403546</v>
+      <c r="H58" s="4"/>
+      <c r="I58">
+        <v>1.1403490012176101</v>
+      </c>
+      <c r="J58">
+        <v>1.15185236456864</v>
+      </c>
+      <c r="K58" s="11">
+        <f t="shared" si="5"/>
+        <v>1.0100875813796892</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A59" s="4">
-        <v>15</v>
+      <c r="A59">
+        <v>1000</v>
       </c>
       <c r="B59" s="5"/>
-      <c r="C59" s="2">
-        <v>3.1327203465188001E-3</v>
+      <c r="C59">
+        <v>1.1436421352186501</v>
       </c>
       <c r="D59">
-        <v>2.9966209956305001E-3</v>
+        <v>1.1781818408587099</v>
       </c>
       <c r="E59">
-        <v>3.14006419786265E-3</v>
-      </c>
-      <c r="F59" s="11">
-        <f t="shared" ref="F59:F68" si="6">E59/D59</f>
-        <v>1.0478683164942482</v>
+        <v>1.19775360779693</v>
+      </c>
+      <c r="F59" s="10">
+        <f t="shared" si="4"/>
+        <v>1.0166118389025205</v>
       </c>
       <c r="G59" s="4"/>
       <c r="I59">
-        <v>3.6561489620800698E-3</v>
+        <v>1.072078850564</v>
       </c>
       <c r="J59">
-        <v>3.8583728177792702E-3</v>
-      </c>
-      <c r="K59" s="11">
-        <f t="shared" ref="K59:K68" si="7">J59/I59</f>
-        <v>1.0553106172085915</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>30</v>
-      </c>
-      <c r="B60" s="5"/>
-      <c r="C60" s="2">
-        <v>6.2691724987101998E-3</v>
-      </c>
-      <c r="D60">
-        <v>6.0122469256428399E-3</v>
-      </c>
-      <c r="E60">
-        <v>6.2971023902297701E-3</v>
-      </c>
-      <c r="F60" s="10">
-        <f t="shared" si="6"/>
-        <v>1.0473792025028101</v>
-      </c>
-      <c r="G60" s="4"/>
-      <c r="I60">
-        <v>7.3167786817070497E-3</v>
-      </c>
-      <c r="J60">
-        <v>7.7206053021012903E-3</v>
-      </c>
-      <c r="K60" s="10">
-        <f t="shared" si="7"/>
-        <v>1.0551918594181156</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A61" s="4">
-        <v>60</v>
-      </c>
-      <c r="B61" s="5"/>
-      <c r="C61" s="2">
-        <v>1.2558983712415E-2</v>
-      </c>
-      <c r="D61">
-        <v>1.2036181905772299E-2</v>
-      </c>
-      <c r="E61">
-        <v>1.26843202591898E-2</v>
-      </c>
-      <c r="F61" s="11">
-        <f t="shared" si="6"/>
-        <v>1.053849165664958</v>
-      </c>
-      <c r="G61" s="4"/>
-      <c r="I61">
-        <v>1.4655010559957399E-2</v>
-      </c>
-      <c r="J61">
-        <v>1.54708347850845E-2</v>
-      </c>
-      <c r="K61" s="11">
-        <f t="shared" si="7"/>
-        <v>1.0556686207621178</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>90</v>
-      </c>
-      <c r="B62" s="5"/>
-      <c r="C62" s="2">
-        <v>1.8782496824776201E-2</v>
-      </c>
-      <c r="D62">
-        <v>1.81922730031659E-2</v>
-      </c>
-      <c r="E62">
-        <v>1.9125340454343599E-2</v>
-      </c>
-      <c r="F62" s="10">
-        <f t="shared" si="6"/>
-        <v>1.051289217736306</v>
-      </c>
-      <c r="G62" s="4"/>
-      <c r="I62">
-        <v>2.20520227131588E-2</v>
-      </c>
-      <c r="J62">
-        <v>2.3279563002525702E-2</v>
-      </c>
-      <c r="K62" s="10">
-        <f t="shared" si="7"/>
-        <v>1.0556656550437167</v>
+        <v>1.0876143945201899</v>
+      </c>
+      <c r="K59" s="10">
+        <f t="shared" si="5"/>
+        <v>1.0144910460158942</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A63" s="4">
-        <v>120</v>
-      </c>
-      <c r="B63" s="5"/>
-      <c r="C63" s="2">
-        <v>2.51046376970986E-2</v>
-      </c>
-      <c r="D63">
-        <v>2.42950363565053E-2</v>
-      </c>
-      <c r="E63">
-        <v>2.55954016873969E-2</v>
-      </c>
-      <c r="F63" s="11">
-        <f t="shared" si="6"/>
-        <v>1.0535239096501048</v>
-      </c>
-      <c r="G63" s="4"/>
-      <c r="I63">
-        <v>2.9379142051595902E-2</v>
-      </c>
-      <c r="J63">
-        <v>3.0966693098777899E-2</v>
-      </c>
-      <c r="K63" s="11">
-        <f t="shared" si="7"/>
-        <v>1.0540366714723639</v>
-      </c>
+      <c r="C63" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D63" s="12"/>
+      <c r="E63" s="13"/>
+      <c r="F63" s="13"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>150</v>
-      </c>
-      <c r="B64" s="5"/>
-      <c r="C64" s="2">
-        <v>3.1476119846668899E-2</v>
-      </c>
-      <c r="D64">
-        <v>3.0568379602756501E-2</v>
-      </c>
-      <c r="E64">
-        <v>3.2160454077141201E-2</v>
-      </c>
-      <c r="F64" s="10">
-        <f t="shared" si="6"/>
-        <v>1.0520823967470339</v>
-      </c>
-      <c r="G64" s="4"/>
-      <c r="I64">
-        <v>3.6804448452257998E-2</v>
-      </c>
-      <c r="J64">
-        <v>3.8844686371276298E-2</v>
-      </c>
-      <c r="K64" s="10">
-        <f t="shared" si="7"/>
-        <v>1.0554345467685748</v>
-      </c>
+      <c r="C64" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D64" s="3"/>
+      <c r="E64" s="9"/>
+      <c r="F64" s="3"/>
+      <c r="H64" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I64" s="3"/>
+      <c r="J64" s="9"/>
+      <c r="K64" s="9"/>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A65" s="4">
-        <v>250</v>
-      </c>
-      <c r="B65" s="5"/>
-      <c r="C65" s="2">
-        <v>5.2878603388737497E-2</v>
-      </c>
-      <c r="D65">
-        <v>5.1688372196524002E-2</v>
-      </c>
-      <c r="E65">
-        <v>5.4514904682317102E-2</v>
-      </c>
-      <c r="F65" s="11">
-        <f t="shared" si="6"/>
-        <v>1.0546841071923558</v>
-      </c>
-      <c r="G65" s="4"/>
-      <c r="I65">
-        <v>6.1567552933483601E-2</v>
-      </c>
-      <c r="J65">
-        <v>6.4958585716827305E-2</v>
-      </c>
-      <c r="K65" s="11">
-        <f t="shared" si="7"/>
-        <v>1.0550782453057264</v>
+      <c r="A65" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B65" s="6"/>
+      <c r="C65" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G65" s="8"/>
+      <c r="H65" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="J65" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K65" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>500</v>
+        <v>0.1</v>
       </c>
       <c r="B66" s="5"/>
       <c r="C66" s="2">
-        <v>0.107716927588289</v>
-      </c>
-      <c r="D66">
-        <v>0.107312205249392</v>
-      </c>
-      <c r="E66">
-        <v>0.11284726504879</v>
+        <v>2.0906018648200899E-5</v>
+      </c>
+      <c r="D66" s="2">
+        <v>2.0018619481595599E-5</v>
+      </c>
+      <c r="E66" s="2">
+        <v>2.04228717705638E-5</v>
       </c>
       <c r="F66" s="10">
-        <f t="shared" si="6"/>
-        <v>1.0515790332193304</v>
+        <f>E66/D66</f>
+        <v>1.0201938145305103</v>
       </c>
       <c r="G66" s="4"/>
-      <c r="I66">
-        <v>0.124585487877085</v>
-      </c>
-      <c r="J66">
-        <v>0.13088073929294</v>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2">
+        <v>2.4434932696069799E-5</v>
+      </c>
+      <c r="J66" s="2">
+        <v>2.5518609602937599E-5</v>
       </c>
       <c r="K66" s="10">
-        <f t="shared" si="7"/>
-        <v>1.0505295722890764</v>
+        <f>J66/I66</f>
+        <v>1.0443494942403546</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
-        <v>750</v>
+        <v>15</v>
       </c>
       <c r="B67" s="5"/>
       <c r="C67" s="2">
-        <v>0.16515386445267599</v>
+        <v>3.1327203465188001E-3</v>
       </c>
       <c r="D67">
-        <v>0.166593474221475</v>
+        <v>2.9966209956305001E-3</v>
       </c>
       <c r="E67">
-        <v>0.17437302973664801</v>
+        <v>3.14006419786265E-3</v>
       </c>
       <c r="F67" s="11">
-        <f t="shared" si="6"/>
-        <v>1.0466978406658991</v>
+        <f t="shared" ref="F67:F76" si="6">E67/D67</f>
+        <v>1.0478683164942482</v>
       </c>
       <c r="G67" s="4"/>
       <c r="I67">
-        <v>0.188315720076114</v>
+        <v>3.6561489620800698E-3</v>
       </c>
       <c r="J67">
-        <v>0.19671890522285099</v>
+        <v>3.8583728177792702E-3</v>
       </c>
       <c r="K67" s="11">
-        <f t="shared" si="7"/>
-        <v>1.0446228554012409</v>
+        <f t="shared" ref="K67:K76" si="7">J67/I67</f>
+        <v>1.0553106172085915</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="B68" s="5"/>
       <c r="C68" s="2">
-        <v>0.22114304090137801</v>
+        <v>6.2691724987101998E-3</v>
       </c>
       <c r="D68">
-        <v>0.22843742858074301</v>
+        <v>6.0122469256428399E-3</v>
       </c>
       <c r="E68">
-        <v>0.23785710518924499</v>
+        <v>6.2971023902297701E-3</v>
       </c>
       <c r="F68" s="10">
         <f t="shared" si="6"/>
-        <v>1.0412352593312988</v>
+        <v>1.0473792025028101</v>
       </c>
       <c r="G68" s="4"/>
       <c r="I68">
+        <v>7.3167786817070497E-3</v>
+      </c>
+      <c r="J68">
+        <v>7.7206053021012903E-3</v>
+      </c>
+      <c r="K68" s="10">
+        <f t="shared" si="7"/>
+        <v>1.0551918594181156</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A69" s="4">
+        <v>60</v>
+      </c>
+      <c r="B69" s="5"/>
+      <c r="C69" s="2">
+        <v>1.2558983712415E-2</v>
+      </c>
+      <c r="D69">
+        <v>1.2036181905772299E-2</v>
+      </c>
+      <c r="E69">
+        <v>1.26843202591898E-2</v>
+      </c>
+      <c r="F69" s="11">
+        <f t="shared" si="6"/>
+        <v>1.053849165664958</v>
+      </c>
+      <c r="G69" s="4"/>
+      <c r="I69">
+        <v>1.4655010559957399E-2</v>
+      </c>
+      <c r="J69">
+        <v>1.54708347850845E-2</v>
+      </c>
+      <c r="K69" s="11">
+        <f t="shared" si="7"/>
+        <v>1.0556686207621178</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>90</v>
+      </c>
+      <c r="B70" s="5"/>
+      <c r="C70" s="2">
+        <v>1.8782496824776201E-2</v>
+      </c>
+      <c r="D70">
+        <v>1.81922730031659E-2</v>
+      </c>
+      <c r="E70">
+        <v>1.9125340454343599E-2</v>
+      </c>
+      <c r="F70" s="10">
+        <f t="shared" si="6"/>
+        <v>1.051289217736306</v>
+      </c>
+      <c r="G70" s="4"/>
+      <c r="I70">
+        <v>2.20520227131588E-2</v>
+      </c>
+      <c r="J70">
+        <v>2.3279563002525702E-2</v>
+      </c>
+      <c r="K70" s="10">
+        <f t="shared" si="7"/>
+        <v>1.0556656550437167</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A71" s="4">
+        <v>120</v>
+      </c>
+      <c r="B71" s="5"/>
+      <c r="C71" s="2">
+        <v>2.51046376970986E-2</v>
+      </c>
+      <c r="D71">
+        <v>2.42950363565053E-2</v>
+      </c>
+      <c r="E71">
+        <v>2.55954016873969E-2</v>
+      </c>
+      <c r="F71" s="11">
+        <f t="shared" si="6"/>
+        <v>1.0535239096501048</v>
+      </c>
+      <c r="G71" s="4"/>
+      <c r="I71">
+        <v>2.9379142051595902E-2</v>
+      </c>
+      <c r="J71">
+        <v>3.0966693098777899E-2</v>
+      </c>
+      <c r="K71" s="11">
+        <f t="shared" si="7"/>
+        <v>1.0540366714723639</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>150</v>
+      </c>
+      <c r="B72" s="5"/>
+      <c r="C72" s="2">
+        <v>3.1476119846668899E-2</v>
+      </c>
+      <c r="D72">
+        <v>3.0568379602756501E-2</v>
+      </c>
+      <c r="E72">
+        <v>3.2160454077141201E-2</v>
+      </c>
+      <c r="F72" s="10">
+        <f t="shared" si="6"/>
+        <v>1.0520823967470339</v>
+      </c>
+      <c r="G72" s="4"/>
+      <c r="I72">
+        <v>3.6804448452257998E-2</v>
+      </c>
+      <c r="J72">
+        <v>3.8844686371276298E-2</v>
+      </c>
+      <c r="K72" s="10">
+        <f t="shared" si="7"/>
+        <v>1.0554345467685748</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A73" s="4">
+        <v>250</v>
+      </c>
+      <c r="B73" s="5"/>
+      <c r="C73" s="2">
+        <v>5.2878603388737497E-2</v>
+      </c>
+      <c r="D73">
+        <v>5.1688372196524002E-2</v>
+      </c>
+      <c r="E73">
+        <v>5.4514904682317102E-2</v>
+      </c>
+      <c r="F73" s="11">
+        <f t="shared" si="6"/>
+        <v>1.0546841071923558</v>
+      </c>
+      <c r="G73" s="4"/>
+      <c r="I73">
+        <v>6.1567552933483601E-2</v>
+      </c>
+      <c r="J73">
+        <v>6.4958585716827305E-2</v>
+      </c>
+      <c r="K73" s="11">
+        <f t="shared" si="7"/>
+        <v>1.0550782453057264</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>500</v>
+      </c>
+      <c r="B74" s="5"/>
+      <c r="C74" s="2">
+        <v>0.107716927588289</v>
+      </c>
+      <c r="D74">
+        <v>0.107312205249392</v>
+      </c>
+      <c r="E74">
+        <v>0.11284726504879</v>
+      </c>
+      <c r="F74" s="10">
+        <f t="shared" si="6"/>
+        <v>1.0515790332193304</v>
+      </c>
+      <c r="G74" s="4"/>
+      <c r="I74">
+        <v>0.124585487877085</v>
+      </c>
+      <c r="J74">
+        <v>0.13088073929294</v>
+      </c>
+      <c r="K74" s="10">
+        <f t="shared" si="7"/>
+        <v>1.0505295722890764</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A75" s="4">
+        <v>750</v>
+      </c>
+      <c r="B75" s="5"/>
+      <c r="C75" s="2">
+        <v>0.16515386445267599</v>
+      </c>
+      <c r="D75">
+        <v>0.166593474221475</v>
+      </c>
+      <c r="E75">
+        <v>0.17437302973664801</v>
+      </c>
+      <c r="F75" s="11">
+        <f t="shared" si="6"/>
+        <v>1.0466978406658991</v>
+      </c>
+      <c r="G75" s="4"/>
+      <c r="I75">
+        <v>0.188315720076114</v>
+      </c>
+      <c r="J75">
+        <v>0.19671890522285099</v>
+      </c>
+      <c r="K75" s="11">
+        <f t="shared" si="7"/>
+        <v>1.0446228554012409</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>1000</v>
+      </c>
+      <c r="B76" s="5"/>
+      <c r="C76" s="2">
+        <v>0.22114304090137801</v>
+      </c>
+      <c r="D76">
+        <v>0.22843742858074301</v>
+      </c>
+      <c r="E76">
+        <v>0.23785710518924499</v>
+      </c>
+      <c r="F76" s="10">
+        <f t="shared" si="6"/>
+        <v>1.0412352593312988</v>
+      </c>
+      <c r="G76" s="4"/>
+      <c r="I76">
         <v>0.25212873564071397</v>
       </c>
-      <c r="J68">
+      <c r="J76">
         <v>0.26159631710660702</v>
       </c>
-      <c r="K68" s="10">
+      <c r="K76" s="10">
         <f t="shared" si="7"/>
         <v>1.0375505847908761</v>
       </c>

--- a/Jupyter/Wedge/wedge_data_2026-03-25.xlsx
+++ b/Jupyter/Wedge/wedge_data_2026-03-25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\patri\projects\emma-openmc\Jupyter\Wedge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D92552F5-14F5-4602-8D22-687681DBA2D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B184866-94F8-47FB-9604-EE9CD1C46C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="11">
   <si>
     <t>Fertile kg/m3</t>
   </si>
@@ -67,14 +67,16 @@
   <si>
     <t>DCLL-Greta</t>
   </si>
+  <si>
+    <t>FISSILE PRODUCTION RATE ERROR PROPAGATION [ RXNS/SRC-N ]</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000"/>
-    <numFmt numFmtId="165" formatCode="0.000000000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -161,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -178,8 +180,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -274,7 +274,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$27:$A$41</c:f>
+              <c:f>'Sheet 1'!$A$26:$A$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
@@ -328,42 +328,54 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$F$27:$F$41</c:f>
+              <c:f>'Sheet 1'!$F$26:$F$40</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.90095484884115951</c:v>
+                  <c:v>0.7274775745944605</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.64347975683918834</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.49583688440425344</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.66859607525333198</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.98605362776739691</c:v>
+                  <c:v>0.73291562987349301</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.98894298080377097</c:v>
+                  <c:v>0.74746751893992558</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.99045126110744741</c:v>
+                  <c:v>0.78627670393149318</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0286907074262921</c:v>
+                  <c:v>0.87619376520123537</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.86809490045634352</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.0109751026946947</c:v>
+                  <c:v>0.79255474288640204</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.0514992257935214</c:v>
+                  <c:v>0.90551396638088599</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.0588139493303126</c:v>
+                  <c:v>0.92837643974491146</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.0670379652207234</c:v>
+                  <c:v>0.93787715524054671</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.0821051236786146</c:v>
+                  <c:v>1.0174259839976012</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.0789515024556622</c:v>
+                  <c:v>1.0246283267351703</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -402,7 +414,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$27:$A$41</c:f>
+              <c:f>'Sheet 1'!$A$26:$A$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
@@ -456,42 +468,54 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$K$27:$K$41</c:f>
+              <c:f>'Sheet 1'!$K$26:$K$40</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.0035506001332684</c:v>
+                  <c:v>0.29264705217301878</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.3315375295667062</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.8971337860952534</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.86727127408207016</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0779572449118415</c:v>
+                  <c:v>0.96019947785672299</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0206668727246053</c:v>
+                  <c:v>0.82054207267800461</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0298609475740441</c:v>
+                  <c:v>0.89620098412984728</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0714308642620487</c:v>
+                  <c:v>0.99789498609321658</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.92546657383389286</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.0452657339217364</c:v>
+                  <c:v>0.95340718196328889</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.0670489493344424</c:v>
+                  <c:v>0.94899688560909901</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.0639924185567</c:v>
+                  <c:v>0.9624346474925255</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.0846944326462025</c:v>
+                  <c:v>1.0215461604572156</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.0956277405879706</c:v>
+                  <c:v>1.0753115641669349</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.0707528532565391</c:v>
+                  <c:v>1.0025476893384362</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -850,7 +874,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$6:$A$20</c:f>
+              <c:f>'Sheet 1'!$A$5:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
@@ -904,7 +928,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$F$6:$F$20</c:f>
+              <c:f>'Sheet 1'!$F$5:$F$19</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="15"/>
@@ -1041,7 +1065,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$6:$A$20</c:f>
+              <c:f>'Sheet 1'!$A$5:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
@@ -1095,13 +1119,22 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$K$6:$K$20</c:f>
+              <c:f>'Sheet 1'!$K$5:$K$19</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.0124595607074192</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.98955684846579572</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.97266576371713243</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.99532217045916183</c:v>
+                </c:pt>
                 <c:pt idx="4">
                   <c:v>1.0246126531897757</c:v>
                 </c:pt>
@@ -1113,6 +1146,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>1.0235838898658773</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.0328136474978709</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0.99238859087523068</c:v>
@@ -1456,34 +1492,34 @@
                   <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>30</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>60</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>90</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>120</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>150</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>250</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>500</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>750</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1495,37 +1531,37 @@
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>1.0201938145305103</c:v>
+                  <c:v>0.98141967163352228</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0478683164942482</c:v>
+                  <c:v>0.92802141334950694</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0473792025028101</c:v>
+                  <c:v>1.0257080460192236</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.053849165664958</c:v>
+                  <c:v>1.0646127665011473</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.051289217736306</c:v>
+                  <c:v>1.0753237074121145</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0535239096501048</c:v>
+                  <c:v>1.0422360763919929</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0520823967470339</c:v>
+                  <c:v>1.0978441524727602</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0546841071923558</c:v>
+                  <c:v>1.0378247495664441</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.0515790332193304</c:v>
+                  <c:v>1.0332088675177227</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.0466978406658991</c:v>
+                  <c:v>1.1033275421994369</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.0412352593312988</c:v>
+                  <c:v>1.0613255687481478</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1779,7 +1815,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Sheet 1'!$F$48</c:f>
+              <c:f>'Sheet 1'!$F$47</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1812,7 +1848,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$49:$A$59</c:f>
+              <c:f>'Sheet 1'!$A$48:$A$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -1820,76 +1856,76 @@
                   <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>30</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>60</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>90</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>120</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>150</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>250</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>500</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>750</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$F$49:$F$59</c:f>
+              <c:f>'Sheet 1'!$F$48:$F$58</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>1.0002061377408649</c:v>
+                  <c:v>0.9985035371420129</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.99891005109663888</c:v>
+                  <c:v>0.98715209394887005</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.99815713339154455</c:v>
+                  <c:v>0.99284501043036377</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0001410320682957</c:v>
+                  <c:v>1.0204895071175968</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.99834261928649515</c:v>
+                  <c:v>1.0049119467662411</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.000439827114133</c:v>
+                  <c:v>0.99460716116426584</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.99998298589275558</c:v>
+                  <c:v>1.0195310334465668</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0031432346852518</c:v>
+                  <c:v>0.98333502299608533</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.0077316291586689</c:v>
+                  <c:v>0.98631763108404502</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.0118470565893447</c:v>
+                  <c:v>1.0290963972436542</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.0166118389025205</c:v>
+                  <c:v>0.99666881879093805</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4318,13 +4354,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>132179</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>56857</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>436979</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>56857</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4360,7 +4396,7 @@
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>605790</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4426,7 +4462,7 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>929640</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
@@ -4724,7 +4760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22416C2-1180-4450-A3B0-0B08DD9AEC85}">
-  <dimension ref="A1:L76"/>
+  <dimension ref="A1:L95"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
@@ -4802,1415 +4838,1515 @@
       <c r="L4" s="7"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="8">
-        <v>0</v>
-      </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="16">
-        <f>1.38911+0.015389</f>
-        <v>1.4044990000000002</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="7"/>
+      <c r="A5">
+        <v>0.1</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5">
+        <v>1.4063862998066801</v>
+      </c>
+      <c r="D5">
+        <v>1.3686193553583801</v>
+      </c>
+      <c r="E5">
+        <v>1.38512260545705</v>
+      </c>
+      <c r="F5" s="10">
+        <f>E5/D5</f>
+        <v>1.0120583199660715</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5">
+        <v>1.4074651112049299</v>
+      </c>
+      <c r="I5">
+        <v>1.3681177802680899</v>
+      </c>
+      <c r="J5">
+        <v>1.3851639268062399</v>
+      </c>
+      <c r="K5" s="10">
+        <f>J5/I5</f>
+        <v>1.0124595607074192</v>
+      </c>
+      <c r="L5" s="10"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6">
-        <v>1.40420707746021</v>
+        <v>1.4065448393936499</v>
       </c>
       <c r="D6">
-        <v>1.3686193553583801</v>
+        <v>1.3922831524096599</v>
       </c>
       <c r="E6">
-        <v>1.38512260545705</v>
+        <v>1.37451308945358</v>
       </c>
       <c r="F6" s="10">
-        <f>E6/D6</f>
-        <v>1.0120583199660715</v>
+        <f t="shared" ref="F6:F19" si="0">E6/D6</f>
+        <v>0.98723674640081305</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6">
-        <v>1.4043892076542099</v>
+        <v>1.4079920998080599</v>
       </c>
       <c r="I6">
-        <v>1.3681177802680899</v>
+        <v>1.3884228746446901</v>
       </c>
       <c r="J6">
-        <v>1.3851639268062399</v>
+        <v>1.3739233641712201</v>
       </c>
       <c r="K6" s="10">
-        <f>J6/I6</f>
-        <v>1.0124595607074192</v>
+        <f t="shared" ref="K6:K19" si="1">J6/I6</f>
+        <v>0.98955684846579572</v>
       </c>
       <c r="L6" s="10"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="B7" s="5"/>
+      <c r="C7">
+        <v>1.40593053429746</v>
+      </c>
       <c r="D7">
-        <v>1.3922831524096599</v>
+        <v>1.4141178954362701</v>
       </c>
       <c r="E7">
-        <v>1.37451308945358</v>
+        <v>1.3766722209354501</v>
       </c>
       <c r="F7" s="10">
-        <f t="shared" ref="F7:F20" si="0">E7/D7</f>
-        <v>0.98723674640081305</v>
+        <f t="shared" si="0"/>
+        <v>0.97352011835670349</v>
       </c>
       <c r="G7" s="4"/>
+      <c r="H7">
+        <v>1.4079445884292401</v>
+      </c>
       <c r="I7">
-        <v>1.3884228746446901</v>
+        <v>1.4147283449213399</v>
       </c>
       <c r="J7">
-        <v>1.3739233641712201</v>
-      </c>
-      <c r="K7" s="10"/>
+        <v>1.3760578260651899</v>
+      </c>
+      <c r="K7" s="10">
+        <f t="shared" si="1"/>
+        <v>0.97266576371713243</v>
+      </c>
       <c r="L7" s="10"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="B8" s="5"/>
+      <c r="C8">
+        <v>1.39838837861919</v>
+      </c>
       <c r="D8">
-        <v>1.4141178954362701</v>
+        <v>1.4052374449883001</v>
       </c>
       <c r="E8">
-        <v>1.3766722209354501</v>
+        <v>1.38656109713547</v>
       </c>
       <c r="F8" s="10">
         <f t="shared" si="0"/>
-        <v>0.97352011835670349</v>
+        <v>0.98670947182667379</v>
       </c>
       <c r="G8" s="4"/>
+      <c r="H8">
+        <v>1.4018754625880101</v>
+      </c>
       <c r="I8">
-        <v>1.4147283449213399</v>
+        <v>1.3952787310994501</v>
       </c>
       <c r="J8">
-        <v>1.3760578260651899</v>
-      </c>
-      <c r="K8" s="10"/>
+        <v>1.3887518550334099</v>
+      </c>
+      <c r="K8" s="10">
+        <f t="shared" si="1"/>
+        <v>0.99532217045916183</v>
+      </c>
       <c r="L8" s="10"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B9" s="5"/>
+      <c r="C9">
+        <v>1.39742877901721</v>
+      </c>
       <c r="D9">
-        <v>1.4052374449883001</v>
+        <v>1.3588321367490299</v>
       </c>
       <c r="E9">
-        <v>1.38656109713547</v>
+        <v>1.3960885502131399</v>
       </c>
       <c r="F9" s="10">
         <f t="shared" si="0"/>
-        <v>0.98670947182667379</v>
-      </c>
-      <c r="G9" s="4"/>
+        <v>1.0274179661023068</v>
+      </c>
+      <c r="H9">
+        <v>1.4018991482118599</v>
+      </c>
       <c r="I9">
-        <v>1.3952787310994501</v>
+        <v>1.36086238814935</v>
       </c>
       <c r="J9">
-        <v>1.3887518550334099</v>
-      </c>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-    </row>
-    <row r="10" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>1.3943568221478799</v>
+      </c>
+      <c r="K9" s="10">
+        <f t="shared" si="1"/>
+        <v>1.0246126531897757</v>
+      </c>
+      <c r="L9" s="11"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B10" s="5"/>
-      <c r="C10" s="4">
-        <v>1.3978225806626601</v>
+      <c r="C10">
+        <v>1.3977734656963801</v>
       </c>
       <c r="D10">
-        <v>1.3588321367490299</v>
+        <v>1.38084479180245</v>
       </c>
       <c r="E10">
-        <v>1.3960885502131399</v>
+        <v>1.3802674426896999</v>
       </c>
       <c r="F10" s="10">
         <f t="shared" si="0"/>
-        <v>1.0274179661023068</v>
-      </c>
-      <c r="H10" s="4">
-        <v>1.3977474767840601</v>
+        <v>0.9995818870330847</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10">
+        <v>1.3914317207496001</v>
       </c>
       <c r="I10">
-        <v>1.36086238814935</v>
+        <v>1.3852911212816701</v>
       </c>
       <c r="J10">
-        <v>1.3943568221478799</v>
-      </c>
-      <c r="K10" s="11">
-        <f t="shared" ref="K10:K20" si="1">J10/I10</f>
-        <v>1.0246126531897757</v>
-      </c>
-      <c r="L10" s="11"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1.3731450592762</v>
+      </c>
+      <c r="K10" s="10">
+        <f t="shared" si="1"/>
+        <v>0.99123212311197628</v>
+      </c>
+      <c r="L10" s="10"/>
+    </row>
+    <row r="11" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11">
-        <v>1.3935791421766499</v>
+        <v>1.39314164652525</v>
       </c>
       <c r="D11">
-        <v>1.38084479180245</v>
+        <v>1.35391575819657</v>
       </c>
       <c r="E11">
-        <v>1.3802674426896999</v>
+        <v>1.35872734366118</v>
       </c>
       <c r="F11" s="10">
         <f t="shared" si="0"/>
-        <v>0.9995818870330847</v>
-      </c>
-      <c r="G11" s="4"/>
+        <v>1.0035538292803527</v>
+      </c>
       <c r="H11">
-        <v>1.3923333952149399</v>
+        <v>1.3881975250755401</v>
       </c>
       <c r="I11">
-        <v>1.3852911212816701</v>
+        <v>1.3558315843768101</v>
       </c>
       <c r="J11">
-        <v>1.3731450592762</v>
+        <v>1.35851656917782</v>
       </c>
       <c r="K11" s="10">
         <f t="shared" si="1"/>
-        <v>0.99123212311197628</v>
-      </c>
-      <c r="L11" s="10"/>
-    </row>
-    <row r="12" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>1.0019803232436455</v>
+      </c>
+      <c r="L11" s="11"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="B12" s="5"/>
-      <c r="C12" s="4">
-        <v>1.38536063754419</v>
+      <c r="C12">
+        <v>1.3818447189929399</v>
       </c>
       <c r="D12">
-        <v>1.35391575819657</v>
+        <v>1.3540665504448699</v>
       </c>
       <c r="E12">
-        <v>1.35872734366118</v>
+        <v>1.3846270062289301</v>
       </c>
       <c r="F12" s="10">
         <f t="shared" si="0"/>
-        <v>1.0035538292803527</v>
-      </c>
-      <c r="H12" s="4">
-        <v>1.3811147115786999</v>
+        <v>1.0225693897940391</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12">
+        <v>1.3733638983322201</v>
       </c>
       <c r="I12">
-        <v>1.3558315843768101</v>
+        <v>1.34423803647162</v>
       </c>
       <c r="J12">
-        <v>1.35851656917782</v>
-      </c>
-      <c r="K12" s="11">
+        <v>1.37594039827729</v>
+      </c>
+      <c r="K12" s="10">
         <f t="shared" si="1"/>
-        <v>1.0019803232436455</v>
-      </c>
-      <c r="L12" s="11"/>
+        <v>1.0235838898658773</v>
+      </c>
+      <c r="L12" s="10"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13">
-        <v>1.37856347972413</v>
+        <v>1.37950613179578</v>
       </c>
       <c r="D13">
-        <v>1.3540665504448699</v>
+        <v>1.3565730983264299</v>
       </c>
       <c r="E13">
-        <v>1.3846270062289301</v>
+        <v>1.37473157938041</v>
       </c>
       <c r="F13" s="10">
         <f t="shared" si="0"/>
-        <v>1.0225693897940391</v>
+        <v>1.0133855529616367</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13">
-        <v>1.3698685473168299</v>
+        <v>1.3697423426526301</v>
       </c>
       <c r="I13">
-        <v>1.34423803647162</v>
+        <v>1.3294388930292</v>
       </c>
       <c r="J13">
-        <v>1.37594039827729</v>
+        <v>1.3730626322350199</v>
       </c>
       <c r="K13" s="10">
         <f t="shared" si="1"/>
-        <v>1.0235838898658773</v>
+        <v>1.0328136474978709</v>
       </c>
       <c r="L13" s="10"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="B14" s="5"/>
+      <c r="C14">
+        <v>1.37505741757767</v>
+      </c>
       <c r="D14">
-        <v>1.3565730983264299</v>
+        <v>1.34077916991197</v>
       </c>
       <c r="E14">
-        <v>1.37473157938041</v>
+        <v>1.3634284951011899</v>
       </c>
       <c r="F14" s="10">
         <f t="shared" si="0"/>
-        <v>1.0133855529616367</v>
-      </c>
-      <c r="G14" s="4"/>
+        <v>1.0168926589087053</v>
+      </c>
+      <c r="H14">
+        <v>1.36267435359262</v>
+      </c>
       <c r="I14">
-        <v>1.3294388930292</v>
+        <v>1.35581073898229</v>
       </c>
       <c r="J14">
-        <v>1.3730626322350199</v>
-      </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-    </row>
-    <row r="15" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>1.34549110875214</v>
+      </c>
+      <c r="K14" s="10">
+        <f t="shared" si="1"/>
+        <v>0.99238859087523068</v>
+      </c>
+      <c r="L14" s="11"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="B15" s="5"/>
-      <c r="C15" s="4">
-        <v>1.3699400435562701</v>
+      <c r="C15">
+        <v>1.3614670031018901</v>
       </c>
       <c r="D15">
-        <v>1.34077916991197</v>
+        <v>1.3628583617894401</v>
       </c>
       <c r="E15">
-        <v>1.3634284951011899</v>
+        <v>1.3660435580514501</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="0"/>
-        <v>1.0168926589087053</v>
-      </c>
-      <c r="H15" s="4">
-        <v>1.35986137171571</v>
+        <v>1.0023371440138709</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15">
+        <v>1.3561935884492</v>
       </c>
       <c r="I15">
-        <v>1.35581073898229</v>
+        <v>1.34642475596859</v>
       </c>
       <c r="J15">
-        <v>1.34549110875214</v>
-      </c>
-      <c r="K15" s="11">
+        <v>1.3556369406847</v>
+      </c>
+      <c r="K15" s="10">
         <f t="shared" si="1"/>
-        <v>0.99238859087523068</v>
-      </c>
-      <c r="L15" s="11"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1.0068419602917082</v>
+      </c>
+      <c r="L15" s="10"/>
+    </row>
+    <row r="16" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16">
-        <v>1.3618779251700099</v>
+        <v>1.3422623387583901</v>
       </c>
       <c r="D16">
-        <v>1.3628583617894401</v>
+        <v>1.31238054231434</v>
       </c>
       <c r="E16">
-        <v>1.3660435580514501</v>
+        <v>1.30114468854049</v>
       </c>
       <c r="F16" s="10">
         <f t="shared" si="0"/>
-        <v>1.0023371440138709</v>
-      </c>
-      <c r="G16" s="4"/>
+        <v>0.99143857028386306</v>
+      </c>
       <c r="H16">
-        <v>1.34863286309854</v>
+        <v>1.3247863550055301</v>
       </c>
       <c r="I16">
-        <v>1.34642475596859</v>
+        <v>1.2854468687873799</v>
       </c>
       <c r="J16">
-        <v>1.3556369406847</v>
+        <v>1.2908172794684301</v>
       </c>
       <c r="K16" s="10">
         <f t="shared" si="1"/>
-        <v>1.0068419602917082</v>
-      </c>
-      <c r="L16" s="10"/>
-    </row>
-    <row r="17" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>1.0041778550412717</v>
+      </c>
+      <c r="L16" s="11"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="B17" s="5"/>
-      <c r="C17" s="4">
-        <v>1.34128105403747</v>
+      <c r="C17">
+        <v>1.3014014859735601</v>
       </c>
       <c r="D17">
-        <v>1.31238054231434</v>
+        <v>1.27106900787611</v>
       </c>
       <c r="E17">
-        <v>1.30114468854049</v>
+        <v>1.2663520004962301</v>
       </c>
       <c r="F17" s="10">
         <f t="shared" si="0"/>
-        <v>0.99143857028386306</v>
-      </c>
-      <c r="H17" s="4">
-        <v>1.31869938927708</v>
+        <v>0.99628894469879192</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17">
+        <v>1.26268865444005</v>
       </c>
       <c r="I17">
-        <v>1.2854468687873799</v>
+        <v>1.24215702849295</v>
       </c>
       <c r="J17">
-        <v>1.2908172794684301</v>
-      </c>
-      <c r="K17" s="11">
+        <v>1.26045747443881</v>
+      </c>
+      <c r="K17" s="10">
         <f t="shared" si="1"/>
-        <v>1.0041778550412717</v>
-      </c>
-      <c r="L17" s="11"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1.0147327958753034</v>
+      </c>
+      <c r="L17" s="10"/>
+    </row>
+    <row r="18" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18">
-        <v>1.2896852557910301</v>
+        <v>1.2615551433943699</v>
       </c>
       <c r="D18">
-        <v>1.27106900787611</v>
+        <v>1.2502327359779</v>
       </c>
       <c r="E18">
-        <v>1.2663520004962301</v>
+        <v>1.26687035022674</v>
       </c>
       <c r="F18" s="10">
         <f t="shared" si="0"/>
-        <v>0.99628894469879192</v>
-      </c>
-      <c r="G18" s="4"/>
+        <v>1.0133076136706871</v>
+      </c>
       <c r="H18">
-        <v>1.24433347413396</v>
+        <v>1.2096572387659299</v>
       </c>
       <c r="I18">
-        <v>1.24215702849295</v>
+        <v>1.20261020085431</v>
       </c>
       <c r="J18">
-        <v>1.26045747443881</v>
+        <v>1.2257592093430201</v>
       </c>
       <c r="K18" s="10">
         <f t="shared" si="1"/>
-        <v>1.0147327958753034</v>
-      </c>
-      <c r="L18" s="10"/>
-    </row>
-    <row r="19" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>1.0192489706741765</v>
+      </c>
+      <c r="L18" s="11"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>750</v>
+        <v>999.99</v>
       </c>
       <c r="B19" s="5"/>
-      <c r="C19" s="4">
-        <v>1.24225887840578</v>
+      <c r="C19">
+        <v>1.2295679722156101</v>
       </c>
       <c r="D19">
-        <v>1.2502327359779</v>
+        <v>1.2216766905077201</v>
       </c>
       <c r="E19">
-        <v>1.26687035022674</v>
+        <v>1.20816790789953</v>
       </c>
       <c r="F19" s="10">
         <f t="shared" si="0"/>
-        <v>1.0133076136706871</v>
-      </c>
-      <c r="H19" s="4">
-        <v>1.1765306054398399</v>
+        <v>0.98894242420015732</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19">
+        <v>1.15612158785918</v>
       </c>
       <c r="I19">
-        <v>1.20261020085431</v>
+        <v>1.1553240194424299</v>
       </c>
       <c r="J19">
-        <v>1.2257592093430201</v>
-      </c>
-      <c r="K19" s="11">
-        <f t="shared" si="1"/>
-        <v>1.0192489706741765</v>
-      </c>
-      <c r="L19" s="11"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>999.99</v>
-      </c>
-      <c r="B20" s="5"/>
-      <c r="C20">
-        <v>1.1938794039418501</v>
-      </c>
-      <c r="D20">
-        <v>1.2216766905077201</v>
-      </c>
-      <c r="E20">
-        <v>1.20816790789953</v>
-      </c>
-      <c r="F20" s="10">
-        <f t="shared" si="0"/>
-        <v>0.98894242420015732</v>
-      </c>
-      <c r="G20" s="4"/>
-      <c r="H20">
-        <v>1.1108715265371401</v>
-      </c>
-      <c r="I20">
-        <v>1.1553240194424299</v>
-      </c>
-      <c r="J20">
         <v>1.13503567173569</v>
       </c>
-      <c r="K20" s="10">
+      <c r="K19" s="10">
         <f t="shared" si="1"/>
         <v>0.9824392574158276</v>
       </c>
-      <c r="L20" s="10"/>
+      <c r="L19" s="10"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C23" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="12"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C24" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="12"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
+      <c r="C24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="3"/>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="3"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C25" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="3"/>
-      <c r="H25" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I25" s="3"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="3"/>
+      <c r="A25" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G25" s="8"/>
+      <c r="H25" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L25" s="7"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G26" s="8"/>
-      <c r="H26" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L26" s="7"/>
+      <c r="A26">
+        <v>0.1</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="2">
+        <v>3.53760968083747E-5</v>
+      </c>
+      <c r="D26" s="2">
+        <v>3.4283030439073703E-5</v>
+      </c>
+      <c r="E26" s="2">
+        <v>2.4940135833565399E-5</v>
+      </c>
+      <c r="F26" s="10">
+        <f>E26/D26</f>
+        <v>0.7274775745944605</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="2">
+        <v>3.2455422398815998E-5</v>
+      </c>
+      <c r="I26" s="2">
+        <v>3.06037506527904E-5</v>
+      </c>
+      <c r="J26" s="2">
+        <v>8.9560974139772096E-6</v>
+      </c>
+      <c r="K26" s="10">
+        <f>J26/I26</f>
+        <v>0.29264705217301878</v>
+      </c>
+      <c r="L26" s="10"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="B27" s="5"/>
-      <c r="C27" s="2">
-        <v>3.52725672373683E-5</v>
+      <c r="C27">
+        <v>1.769377952569E-4</v>
       </c>
       <c r="D27">
-        <v>3.2314434653956498E-4</v>
+        <v>1.7795710468822501E-4</v>
       </c>
       <c r="E27">
-        <v>2.9113846589042902E-4</v>
+        <v>1.1451179445258501E-4</v>
       </c>
       <c r="F27" s="10">
-        <f>E27/D27</f>
-        <v>0.90095484884115951</v>
+        <f t="shared" ref="F27:F40" si="2">E27/D27</f>
+        <v>0.64347975683918834</v>
       </c>
       <c r="G27" s="4"/>
-      <c r="H27" s="2">
-        <v>3.2364516810043102E-5</v>
+      <c r="H27">
+        <v>1.622082823178E-4</v>
       </c>
       <c r="I27">
-        <v>2.8864520587018101E-4</v>
+        <v>1.51128498783429E-4</v>
       </c>
       <c r="J27">
-        <v>2.8967006957661098E-4</v>
+        <v>2.0123326791721201E-4</v>
       </c>
       <c r="K27" s="10">
-        <f>J27/I27</f>
-        <v>1.0035506001332684</v>
+        <f t="shared" ref="K27:K40" si="3">J27/I27</f>
+        <v>1.3315375295667062</v>
       </c>
       <c r="L27" s="10"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="B28" s="5"/>
-      <c r="C28" s="2"/>
+      <c r="C28">
+        <v>5.2503514596129999E-4</v>
+      </c>
       <c r="D28">
-        <v>1.63531469505055E-3</v>
+        <v>5.6289187437775004E-4</v>
       </c>
       <c r="E28">
-        <v>1.5602327945626699E-3</v>
-      </c>
-      <c r="F28" s="10"/>
+        <v>2.79102553247934E-4</v>
+      </c>
+      <c r="F28" s="10">
+        <f t="shared" si="2"/>
+        <v>0.49583688440425344</v>
+      </c>
       <c r="G28" s="4"/>
-      <c r="H28" s="2"/>
+      <c r="H28">
+        <v>4.8498345014689998E-4</v>
+      </c>
       <c r="I28">
-        <v>1.4624167995472899E-3</v>
+        <v>4.4989314990682798E-4</v>
       </c>
       <c r="J28">
-        <v>1.55376135488548E-3</v>
-      </c>
-      <c r="K28" s="10"/>
+        <v>4.03614344914232E-4</v>
+      </c>
+      <c r="K28" s="10">
+        <f t="shared" si="3"/>
+        <v>0.8971337860952534</v>
+      </c>
       <c r="L28" s="10"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="B29" s="5"/>
-      <c r="C29" s="2"/>
+      <c r="C29">
+        <v>3.3839428456904001E-3</v>
+      </c>
       <c r="D29">
-        <v>5.0200091937920499E-3</v>
+        <v>3.3365070331695802E-3</v>
       </c>
       <c r="E29">
-        <v>4.4418725803358596E-3</v>
-      </c>
-      <c r="F29" s="10"/>
+        <v>2.2307755074323201E-3</v>
+      </c>
+      <c r="F29" s="10">
+        <f t="shared" si="2"/>
+        <v>0.66859607525333198</v>
+      </c>
       <c r="G29" s="4"/>
-      <c r="H29" s="2"/>
+      <c r="H29">
+        <v>3.1626406186310001E-3</v>
+      </c>
       <c r="I29">
-        <v>4.4120832608900004E-3</v>
+        <v>3.0155921421882699E-3</v>
       </c>
       <c r="J29">
-        <v>4.3968622699160501E-3</v>
-      </c>
-      <c r="K29" s="10"/>
+        <v>2.6153364392675002E-3</v>
+      </c>
+      <c r="K29" s="10">
+        <f t="shared" si="3"/>
+        <v>0.86727127408207016</v>
+      </c>
       <c r="L29" s="10"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>10</v>
+      <c r="A30" s="4">
+        <v>15</v>
       </c>
       <c r="B30" s="5"/>
-      <c r="C30" s="2"/>
+      <c r="C30">
+        <v>4.9687340175238997E-3</v>
+      </c>
       <c r="D30">
-        <v>3.2233154188020502E-2</v>
+        <v>4.9536689812130401E-3</v>
       </c>
       <c r="E30">
-        <v>3.1830960117675798E-2</v>
-      </c>
-      <c r="F30" s="10"/>
+        <v>3.6306214215505398E-3</v>
+      </c>
+      <c r="F30" s="10">
+        <f t="shared" si="2"/>
+        <v>0.73291562987349301</v>
+      </c>
       <c r="G30" s="4"/>
-      <c r="H30" s="2"/>
+      <c r="H30">
+        <v>4.7034313826145001E-3</v>
+      </c>
       <c r="I30">
-        <v>2.9294700126228299E-2</v>
+        <v>4.2298917106053102E-3</v>
       </c>
       <c r="J30">
-        <v>2.9963416156383201E-2</v>
-      </c>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
+        <v>4.0615398119136998E-3</v>
+      </c>
+      <c r="K30" s="10">
+        <f t="shared" si="3"/>
+        <v>0.96019947785672299</v>
+      </c>
+      <c r="L30" s="11"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="4">
-        <v>15</v>
+      <c r="A31">
+        <v>30</v>
       </c>
       <c r="B31" s="5"/>
-      <c r="C31" s="5">
-        <v>5.02535867346246E-3</v>
+      <c r="C31">
+        <v>9.6668811570342003E-3</v>
       </c>
       <c r="D31">
-        <v>4.8083671005010903E-2</v>
+        <v>9.8049806314099101E-3</v>
       </c>
       <c r="E31">
-        <v>4.7413078230864998E-2</v>
-      </c>
-      <c r="F31" s="11">
-        <f t="shared" ref="F31:F41" si="2">E31/D31</f>
-        <v>0.98605362776739691</v>
+        <v>7.3289045458139902E-3</v>
+      </c>
+      <c r="F31" s="10">
+        <f t="shared" si="2"/>
+        <v>0.74746751893992558</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31">
-        <v>4.7442437671726999E-3</v>
+        <v>9.2377761797262006E-3</v>
       </c>
       <c r="I31">
-        <v>4.28280907778881E-2</v>
+        <v>8.8658994417866593E-3</v>
       </c>
       <c r="J31">
-        <v>4.61668507397665E-2</v>
-      </c>
-      <c r="K31" s="11">
-        <f t="shared" ref="K31:K41" si="3">J31/I31</f>
-        <v>1.0779572449118415</v>
-      </c>
-      <c r="L31" s="11"/>
+        <v>7.2748435041183898E-3</v>
+      </c>
+      <c r="K31" s="10">
+        <f t="shared" si="3"/>
+        <v>0.82054207267800461</v>
+      </c>
+      <c r="L31" s="10"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <v>30</v>
+      <c r="A32" s="4">
+        <v>60</v>
       </c>
       <c r="B32" s="5"/>
-      <c r="C32" s="2">
-        <v>9.6096776712520909E-3</v>
+      <c r="C32">
+        <v>1.7647794082264599E-2</v>
       </c>
       <c r="D32">
-        <v>9.5891818868841697E-2</v>
+        <v>1.6929482364304901E-2</v>
       </c>
       <c r="E32">
-        <v>9.4831541186847598E-2</v>
+        <v>1.3311257592672E-2</v>
       </c>
       <c r="F32" s="10">
         <f t="shared" si="2"/>
-        <v>0.98894298080377097</v>
+        <v>0.78627670393149318</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32">
-        <v>9.3381817414101998E-3</v>
+        <v>1.79734898063151E-2</v>
       </c>
       <c r="I32">
-        <v>8.7192700810209606E-2</v>
+        <v>1.57606335049696E-2</v>
       </c>
       <c r="J32">
-        <v>8.8994701260368805E-2</v>
+        <v>1.41246952576636E-2</v>
       </c>
       <c r="K32" s="10">
         <f t="shared" si="3"/>
-        <v>1.0206668727246053</v>
-      </c>
-      <c r="L32" s="10"/>
+        <v>0.89620098412984728</v>
+      </c>
+      <c r="L32" s="11"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="4">
-        <v>60</v>
+      <c r="A33">
+        <v>90</v>
       </c>
       <c r="B33" s="5"/>
-      <c r="C33" s="5">
-        <v>1.7956202904139199E-2</v>
+      <c r="C33">
+        <v>2.5054917938694E-2</v>
       </c>
       <c r="D33">
-        <v>0.18310601049282599</v>
+        <v>2.3458449507632401E-2</v>
       </c>
       <c r="E33">
-        <v>0.18135757900897301</v>
-      </c>
-      <c r="F33" s="11">
+        <v>2.05541471998755E-2</v>
+      </c>
+      <c r="F33" s="10">
         <f t="shared" si="2"/>
-        <v>0.99045126110744741</v>
+        <v>0.87619376520123537</v>
       </c>
       <c r="G33" s="4"/>
       <c r="H33">
-        <v>1.8093633576609602E-2</v>
+        <v>2.6164917465571601E-2</v>
       </c>
       <c r="I33">
-        <v>0.168976390095402</v>
+        <v>2.3818302176688601E-2</v>
       </c>
       <c r="J33">
-        <v>0.17402218522129201</v>
-      </c>
-      <c r="K33" s="11">
+        <v>2.3768164319370701E-2</v>
+      </c>
+      <c r="K33" s="10">
         <f t="shared" si="3"/>
-        <v>1.0298609475740441</v>
-      </c>
-      <c r="L33" s="11"/>
+        <v>0.99789498609321658</v>
+      </c>
+      <c r="L33" s="10"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <v>90</v>
+      <c r="A34" s="4">
+        <v>100</v>
       </c>
       <c r="B34" s="5"/>
-      <c r="C34" s="2">
-        <v>2.54716677488637E-2</v>
+      <c r="C34">
+        <v>2.73242514617307E-2</v>
       </c>
       <c r="D34">
-        <v>0.27052609093888302</v>
+        <v>2.5947125661509699E-2</v>
       </c>
       <c r="E34">
-        <v>0.27828767586518899</v>
+        <v>2.2524567468256498E-2</v>
       </c>
       <c r="F34" s="10">
         <f t="shared" si="2"/>
-        <v>1.0286907074262921</v>
+        <v>0.86809490045634352</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34">
-        <v>2.63480432958439E-2</v>
+        <v>2.8758676699886999E-2</v>
       </c>
       <c r="I34">
-        <v>0.25226765578979399</v>
+        <v>2.6060698692637999E-2</v>
       </c>
       <c r="J34">
-        <v>0.27028735246822</v>
+        <v>2.41183055307931E-2</v>
       </c>
       <c r="K34" s="10">
         <f t="shared" si="3"/>
-        <v>1.0714308642620487</v>
+        <v>0.92546657383389286</v>
       </c>
       <c r="L34" s="10"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="B35" s="5"/>
-      <c r="C35" s="2"/>
+      <c r="C35">
+        <v>3.1756367537968302E-2</v>
+      </c>
       <c r="D35">
-        <v>0.29782820153673201</v>
+        <v>3.2193504593870201E-2</v>
       </c>
       <c r="E35">
-        <v>0.31219673881320298</v>
-      </c>
-      <c r="F35" s="10"/>
+        <v>2.5515114756006999E-2</v>
+      </c>
+      <c r="F35" s="10">
+        <f t="shared" si="2"/>
+        <v>0.79255474288640204</v>
+      </c>
       <c r="G35" s="4"/>
+      <c r="H35">
+        <v>3.3831181126573399E-2</v>
+      </c>
       <c r="I35">
-        <v>0.27710332040764002</v>
+        <v>3.0884672634417399E-2</v>
       </c>
       <c r="J35">
-        <v>0.29733056001795299</v>
-      </c>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
+        <v>2.9445668702238598E-2</v>
+      </c>
+      <c r="K35" s="10">
+        <f t="shared" si="3"/>
+        <v>0.95340718196328889</v>
+      </c>
+      <c r="L35" s="11"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="4">
-        <v>120</v>
+      <c r="A36">
+        <v>150</v>
       </c>
       <c r="B36" s="5"/>
-      <c r="C36" s="5">
-        <v>3.2417642839879697E-2</v>
+      <c r="C36">
+        <v>3.79760832406765E-2</v>
       </c>
       <c r="D36">
-        <v>0.35933558625490702</v>
+        <v>3.6337278414827603E-2</v>
       </c>
       <c r="E36">
-        <v>0.36327933121591299</v>
-      </c>
-      <c r="F36" s="11">
+        <v>3.2903913104897098E-2</v>
+      </c>
+      <c r="F36" s="10">
         <f t="shared" si="2"/>
-        <v>1.0109751026946947</v>
+        <v>0.90551396638088599</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36">
-        <v>3.4169678168819703E-2</v>
+        <v>4.0827391559504302E-2</v>
       </c>
       <c r="I36">
-        <v>0.33488526020133202</v>
+        <v>3.8123585674305099E-2</v>
       </c>
       <c r="J36">
-        <v>0.350044087283917</v>
-      </c>
-      <c r="K36" s="11">
+        <v>3.6179164073167201E-2</v>
+      </c>
+      <c r="K36" s="10">
         <f t="shared" si="3"/>
-        <v>1.0452657339217364</v>
-      </c>
-      <c r="L36" s="11"/>
+        <v>0.94899688560909901</v>
+      </c>
+      <c r="L36" s="10"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37">
-        <v>150</v>
+      <c r="A37" s="4">
+        <v>250</v>
       </c>
       <c r="B37" s="5"/>
-      <c r="C37" s="2">
-        <v>3.9055212834252402E-2</v>
+      <c r="C37">
+        <v>5.6477544791410803E-2</v>
       </c>
       <c r="D37">
-        <v>0.440983559195115</v>
+        <v>5.5465836690505303E-2</v>
       </c>
       <c r="E37">
-        <v>0.46369387108133497</v>
+        <v>5.1493175994203999E-2</v>
       </c>
       <c r="F37" s="10">
         <f t="shared" si="2"/>
-        <v>1.0514992257935214</v>
+        <v>0.92837643974491146</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37">
-        <v>4.1796462699614498E-2</v>
+        <v>6.2587066941841005E-2</v>
       </c>
       <c r="I37">
-        <v>0.41421243624474702</v>
+        <v>5.8814448863946898E-2</v>
       </c>
       <c r="J37">
-        <v>0.44198494489621698</v>
+        <v>5.6605063359839898E-2</v>
       </c>
       <c r="K37" s="10">
         <f t="shared" si="3"/>
-        <v>1.0670489493344424</v>
-      </c>
-      <c r="L37" s="10"/>
+        <v>0.9624346474925255</v>
+      </c>
+      <c r="L37" s="11"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="4">
-        <v>250</v>
+      <c r="A38">
+        <v>500</v>
       </c>
       <c r="B38" s="5"/>
-      <c r="C38" s="5">
-        <v>5.8983323870902299E-2</v>
+      <c r="C38">
+        <v>9.6749839749360703E-2</v>
       </c>
       <c r="D38">
-        <v>0.69943129650860603</v>
+        <v>9.2698744321603202E-2</v>
       </c>
       <c r="E38">
-        <v>0.74056761334149801</v>
-      </c>
-      <c r="F38" s="11">
+        <v>8.6940034618715994E-2</v>
+      </c>
+      <c r="F38" s="10">
         <f t="shared" si="2"/>
-        <v>1.0588139493303126</v>
+        <v>0.93787715524054671</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38">
-        <v>6.5796691976300697E-2</v>
+        <v>0.10941310652236901</v>
       </c>
       <c r="I38">
-        <v>0.66184301157104197</v>
+        <v>0.101328636998795</v>
       </c>
       <c r="J38">
-        <v>0.70419594658632301</v>
-      </c>
-      <c r="K38" s="11">
+        <v>0.103511880070482</v>
+      </c>
+      <c r="K38" s="10">
         <f t="shared" si="3"/>
-        <v>1.0639924185567</v>
-      </c>
-      <c r="L38" s="11"/>
+        <v>1.0215461604572156</v>
+      </c>
+      <c r="L38" s="10"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39">
-        <v>500</v>
+      <c r="A39" s="4">
+        <v>750</v>
       </c>
       <c r="B39" s="5"/>
-      <c r="C39" s="2">
-        <v>0.103595084893309</v>
+      <c r="C39">
+        <v>0.12913289428404701</v>
       </c>
       <c r="D39">
-        <v>1.3176141318230901</v>
+        <v>0.12658460512460301</v>
       </c>
       <c r="E39">
-        <v>1.4059443021665801</v>
+        <v>0.128790466427847</v>
       </c>
       <c r="F39" s="10">
         <f t="shared" si="2"/>
-        <v>1.0670379652207234</v>
+        <v>1.0174259839976012</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39">
-        <v>0.11839645185777101</v>
+        <v>0.14632252761592299</v>
       </c>
       <c r="I39">
-        <v>1.25292933313</v>
+        <v>0.13858937862319001</v>
       </c>
       <c r="J39">
-        <v>1.3590454721452301</v>
+        <v>0.149026761504226</v>
       </c>
       <c r="K39" s="10">
         <f t="shared" si="3"/>
-        <v>1.0846944326462025</v>
-      </c>
-      <c r="L39" s="10"/>
+        <v>1.0753115641669349</v>
+      </c>
+      <c r="L39" s="11"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="4">
-        <v>750</v>
+      <c r="A40">
+        <v>1000</v>
       </c>
       <c r="B40" s="5"/>
-      <c r="C40" s="5">
-        <v>0.14519436153500101</v>
+      <c r="C40">
+        <v>0.157828985100924</v>
       </c>
       <c r="D40">
-        <v>1.9175894049158899</v>
+        <v>0.15157133316674601</v>
       </c>
       <c r="E40">
-        <v>2.0750333201713098</v>
-      </c>
-      <c r="F40" s="11">
+        <v>0.15530428148366199</v>
+      </c>
+      <c r="F40" s="10">
         <f t="shared" si="2"/>
-        <v>1.0821051236786146</v>
+        <v>1.0246283267351703</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40">
-        <v>0.165934052581929</v>
+        <v>0.178362496787381</v>
       </c>
       <c r="I40">
-        <v>1.8041504774598101</v>
+        <v>0.17072801306535401</v>
       </c>
       <c r="J40">
-        <v>1.9766773113</v>
-      </c>
-      <c r="K40" s="11">
+        <v>0.17116297500401301</v>
+      </c>
+      <c r="K40" s="10">
         <f t="shared" si="3"/>
-        <v>1.0956277405879706</v>
-      </c>
-      <c r="L40" s="11"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <v>1000</v>
-      </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="2">
-        <v>0.185920101577397</v>
-      </c>
-      <c r="D41">
-        <v>2.4565650146404598</v>
-      </c>
-      <c r="E41">
-        <v>2.6505145134263399</v>
-      </c>
-      <c r="F41" s="10">
-        <f t="shared" si="2"/>
-        <v>1.0789515024556622</v>
-      </c>
-      <c r="G41" s="4"/>
-      <c r="H41">
-        <v>0.211237572970251</v>
-      </c>
-      <c r="I41">
-        <v>2.3142913460731198</v>
-      </c>
-      <c r="J41">
-        <v>2.4780340620747099</v>
-      </c>
-      <c r="K41" s="10">
-        <f t="shared" si="3"/>
-        <v>1.0707528532565391</v>
-      </c>
-      <c r="L41" s="10"/>
+        <v>1.0025476893384362</v>
+      </c>
+      <c r="L40" s="10"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C44" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C45" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="C45" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D45" s="14"/>
+      <c r="E45" s="15"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C46" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="D46" s="14"/>
-      <c r="E46" s="15"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
+      <c r="C46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" s="3"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="3"/>
+      <c r="H46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I46" s="3"/>
+      <c r="J46" s="9"/>
+      <c r="K46" s="9"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D47" s="3"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="3"/>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3"/>
-      <c r="J47" s="9"/>
-      <c r="K47" s="9"/>
+      <c r="A47" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="8"/>
+      <c r="H47" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G48" s="8"/>
-      <c r="H48" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I48" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="J48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K48" s="7" t="s">
-        <v>8</v>
+      <c r="A48">
+        <v>0.1</v>
+      </c>
+      <c r="B48" s="5"/>
+      <c r="C48">
+        <v>1.38755773111088</v>
+      </c>
+      <c r="D48">
+        <v>1.33146077610654</v>
+      </c>
+      <c r="E48">
+        <v>1.3294682945082299</v>
+      </c>
+      <c r="F48" s="10">
+        <f>E48/D48</f>
+        <v>0.9985035371420129</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="I48">
+        <v>1.33422182541257</v>
+      </c>
+      <c r="J48">
+        <v>1.3288821396550801</v>
+      </c>
+      <c r="K48" s="10">
+        <f>J48/I48</f>
+        <v>0.99599790255579224</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49">
-        <v>1.38755773111088</v>
+        <v>1.38409520401011</v>
       </c>
       <c r="D49">
-        <v>1.3354353849754901</v>
+        <v>1.35765661048369</v>
       </c>
       <c r="E49">
-        <v>1.33571066860882</v>
+        <v>1.3402135659025001</v>
       </c>
       <c r="F49" s="10">
-        <f>E49/D49</f>
-        <v>1.0002061377408649</v>
+        <f t="shared" ref="F49:F60" si="4">E49/D49</f>
+        <v>0.98715209394887005</v>
       </c>
       <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
       <c r="I49">
-        <v>1.3355902411931799</v>
+        <v>1.3552315082948401</v>
       </c>
       <c r="J49">
-        <v>1.33570664006712</v>
-      </c>
-      <c r="K49" s="10">
-        <f>J49/I49</f>
-        <v>1.0000871516355467</v>
+        <v>1.34024384554322</v>
+      </c>
+      <c r="K49" s="11">
+        <f t="shared" ref="K49:K58" si="5">J49/I49</f>
+        <v>0.98894088378266998</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A50" s="4">
-        <v>15</v>
+      <c r="A50">
+        <v>1</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50">
-        <v>1.38409520401011</v>
+        <v>1.3811622398640599</v>
       </c>
       <c r="D50">
-        <v>1.3305745989353699</v>
+        <v>1.33903476392587</v>
       </c>
       <c r="E50">
-        <v>1.3291243406104201</v>
-      </c>
-      <c r="F50" s="11">
-        <f t="shared" ref="F50:F59" si="4">E50/D50</f>
-        <v>0.99891005109663888</v>
+        <v>1.3294539841566</v>
+      </c>
+      <c r="F50" s="10">
+        <f t="shared" si="4"/>
+        <v>0.99284501043036377</v>
       </c>
       <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
       <c r="I50">
-        <v>1.3283272840070699</v>
+        <v>1.3461367977004299</v>
       </c>
       <c r="J50">
-        <v>1.32707241565139</v>
-      </c>
-      <c r="K50" s="11">
-        <f t="shared" ref="K50:K59" si="5">J50/I50</f>
-        <v>0.99905530182900826</v>
+        <v>1.32904261090945</v>
+      </c>
+      <c r="K50" s="10">
+        <f t="shared" si="5"/>
+        <v>0.98730130041747499</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51">
-        <v>1.3811622398640599</v>
+        <v>1.37486493369789</v>
       </c>
       <c r="D51">
-        <v>1.3310144038562199</v>
+        <v>1.31789010731641</v>
       </c>
       <c r="E51">
-        <v>1.3285615218559801</v>
+        <v>1.3448930260504799</v>
       </c>
       <c r="F51" s="10">
         <f t="shared" si="4"/>
-        <v>0.99815713339154455</v>
+        <v>1.0204895071175968</v>
       </c>
       <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
       <c r="I51">
-        <v>1.32510611680532</v>
+        <v>1.31846450590491</v>
       </c>
       <c r="J51">
-        <v>1.3232823680411001</v>
-      </c>
-      <c r="K51" s="10">
+        <v>1.3511493506913199</v>
+      </c>
+      <c r="K51" s="11">
         <f t="shared" si="5"/>
-        <v>0.9986236960639675</v>
+        <v>1.0247900831914902</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A52" s="4">
-        <v>60</v>
+      <c r="A52">
+        <v>25</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52">
-        <v>1.37486493369789</v>
+        <v>1.36350384779266</v>
       </c>
       <c r="D52">
-        <v>1.32588118290715</v>
+        <v>1.32036564820574</v>
       </c>
       <c r="E52">
-        <v>1.3260681746726899</v>
-      </c>
-      <c r="F52" s="11">
+        <v>1.3268512139816999</v>
+      </c>
+      <c r="F52" s="10">
         <f t="shared" si="4"/>
-        <v>1.0001410320682957</v>
+        <v>1.0049119467662411</v>
       </c>
       <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
       <c r="I52">
-        <v>1.3187223856414001</v>
+        <v>1.33152629750905</v>
       </c>
       <c r="J52">
-        <v>1.31770759949175</v>
-      </c>
-      <c r="K52" s="11">
+        <v>1.33015612015508</v>
+      </c>
+      <c r="K52" s="10">
         <f t="shared" si="5"/>
-        <v>0.99923047780131791</v>
+        <v>0.99897097236717491</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53">
-        <v>1.36350384779266</v>
+        <v>1.3571706170428599</v>
       </c>
       <c r="D53">
-        <v>1.3250331310758601</v>
+        <v>1.3197738196808499</v>
       </c>
       <c r="E53">
-        <v>1.32283704671966</v>
+        <v>1.3126564921716899</v>
       </c>
       <c r="F53" s="10">
         <f t="shared" si="4"/>
-        <v>0.99834261928649515</v>
+        <v>0.99460716116426584</v>
       </c>
       <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
       <c r="I53">
-        <v>1.3124798292895099</v>
+        <v>1.32005527665466</v>
       </c>
       <c r="J53">
-        <v>1.3112535491322701</v>
-      </c>
-      <c r="K53" s="10">
+        <v>1.30244954906179</v>
+      </c>
+      <c r="K53" s="11">
         <f t="shared" si="5"/>
-        <v>0.99906567694994319</v>
+        <v>0.98666288608952257</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A54" s="4">
-        <v>120</v>
+      <c r="A54">
+        <v>75</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54">
-        <v>1.3571706170428599</v>
+        <v>1.35109721915133</v>
       </c>
       <c r="D54">
-        <v>1.3186752377537301</v>
+        <v>1.29935652652886</v>
       </c>
       <c r="E54">
-        <v>1.31925522687803</v>
-      </c>
-      <c r="F54" s="11">
+        <v>1.32473430230751</v>
+      </c>
+      <c r="F54" s="10">
         <f t="shared" si="4"/>
-        <v>1.000439827114133</v>
+        <v>1.0195310334465668</v>
       </c>
       <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
       <c r="I54">
-        <v>1.3033297752905399</v>
+        <v>1.30908256842566</v>
       </c>
       <c r="J54">
-        <v>1.3019564075099299</v>
-      </c>
-      <c r="K54" s="11">
+        <v>1.30672475018709</v>
+      </c>
+      <c r="K54" s="10">
         <f t="shared" si="5"/>
-        <v>0.99894626225330896</v>
+        <v>0.99819887736996948</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55">
-        <v>1.35109721915133</v>
+        <v>1.32844051248484</v>
       </c>
       <c r="D55">
-        <v>1.3162252475838401</v>
+        <v>1.33910590256307</v>
       </c>
       <c r="E55">
-        <v>1.3162028531863199</v>
+        <v>1.3167897334910501</v>
       </c>
       <c r="F55" s="10">
         <f t="shared" si="4"/>
-        <v>0.99998298589275558</v>
+        <v>0.98333502299608533</v>
       </c>
       <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
       <c r="I55">
-        <v>1.29663015170481</v>
+        <v>1.3171859836539099</v>
       </c>
       <c r="J55">
-        <v>1.2969552292914901</v>
-      </c>
-      <c r="K55" s="10">
+        <v>1.31060168409573</v>
+      </c>
+      <c r="K55" s="11">
         <f t="shared" si="5"/>
-        <v>1.0002507095691495</v>
+        <v>0.99500123775997451</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A56" s="4">
-        <v>250</v>
+      <c r="A56">
+        <v>150</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56">
-        <v>1.32844051248484</v>
+        <v>1.26939305918802</v>
       </c>
       <c r="D56">
-        <v>1.30260068538983</v>
+        <v>1.3346899335651701</v>
       </c>
       <c r="E56">
-        <v>1.3066950650451801</v>
-      </c>
-      <c r="F56" s="11">
+        <v>1.3164282135057199</v>
+      </c>
+      <c r="F56" s="10">
         <f t="shared" si="4"/>
-        <v>1.0031432346852518</v>
+        <v>0.98631763108404502</v>
       </c>
       <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
       <c r="I56">
-        <v>1.2708609670523101</v>
+        <v>1.28924587434467</v>
       </c>
       <c r="J56">
-        <v>1.27351639583336</v>
-      </c>
-      <c r="K56" s="11">
+        <v>1.3011790803332</v>
+      </c>
+      <c r="K56" s="10">
         <f t="shared" si="5"/>
-        <v>1.0020894722946829</v>
+        <v>1.0092559582512495</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57">
-        <v>1.26939305918802</v>
+        <v>1.2146497361047901</v>
       </c>
       <c r="D57">
-        <v>1.26652819252339</v>
+        <v>1.29678717701069</v>
       </c>
       <c r="E57">
-        <v>1.2763205188269799</v>
+        <v>1.33451901185347</v>
       </c>
       <c r="F57" s="10">
         <f t="shared" si="4"/>
-        <v>1.0077316291586689</v>
+        <v>1.0290963972436542</v>
       </c>
       <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
       <c r="I57">
-        <v>1.2073775660257999</v>
+        <v>1.2845821783281699</v>
       </c>
       <c r="J57">
-        <v>1.2155197343022801</v>
-      </c>
-      <c r="K57" s="10">
+        <v>1.27732476166037</v>
+      </c>
+      <c r="K57" s="11">
         <f t="shared" si="5"/>
-        <v>1.0067436802749954</v>
+        <v>0.99435036793267273</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A58" s="4">
-        <v>750</v>
+      <c r="A58">
+        <v>500</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58">
-        <v>1.2146497361047901</v>
+        <v>1.1436421352186501</v>
       </c>
       <c r="D58">
-        <v>1.2257285387942201</v>
+        <v>1.2662694099393199</v>
       </c>
       <c r="E58">
-        <v>1.2402498141564899</v>
-      </c>
-      <c r="F58" s="11">
+        <v>1.2620512370753201</v>
+      </c>
+      <c r="F58" s="10">
         <f t="shared" si="4"/>
-        <v>1.0118470565893447</v>
+        <v>0.99666881879093805</v>
       </c>
       <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
       <c r="I58">
-        <v>1.1403490012176101</v>
+        <v>1.2051198250164299</v>
       </c>
       <c r="J58">
-        <v>1.15185236456864</v>
-      </c>
-      <c r="K58" s="11">
+        <v>1.19710463230099</v>
+      </c>
+      <c r="K58" s="10">
         <f t="shared" si="5"/>
-        <v>1.0100875813796892</v>
+        <v>0.99334904915755518</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>1000</v>
-      </c>
-      <c r="B59" s="5"/>
-      <c r="C59">
-        <v>1.1436421352186501</v>
+        <v>750</v>
       </c>
       <c r="D59">
-        <v>1.1781818408587099</v>
+        <v>1.23279071771682</v>
       </c>
       <c r="E59">
-        <v>1.19775360779693</v>
+        <v>1.23649350366719</v>
       </c>
       <c r="F59" s="10">
         <f t="shared" si="4"/>
-        <v>1.0166118389025205</v>
-      </c>
-      <c r="G59" s="4"/>
+        <v>1.0030035803296993</v>
+      </c>
       <c r="I59">
-        <v>1.072078850564</v>
+        <v>1.1807532343395699</v>
       </c>
       <c r="J59">
-        <v>1.0876143945201899</v>
-      </c>
-      <c r="K59" s="10">
-        <f t="shared" si="5"/>
-        <v>1.0144910460158942</v>
+        <v>1.1563239206929501</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>999.99</v>
+      </c>
+      <c r="D60">
+        <v>1.1928852496040101</v>
+      </c>
+      <c r="E60">
+        <v>1.2106403902979499</v>
+      </c>
+      <c r="F60" s="10">
+        <f t="shared" si="4"/>
+        <v>1.0148841983751864</v>
+      </c>
+      <c r="I60">
+        <v>1.13357719050286</v>
+      </c>
+      <c r="J60">
+        <v>1.1342010761596699</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
@@ -6279,326 +6415,794 @@
         <v>2.0906018648200899E-5</v>
       </c>
       <c r="D66" s="2">
-        <v>2.0018619481595599E-5</v>
+        <v>1.9785240862768899E-5</v>
       </c>
       <c r="E66" s="2">
-        <v>2.04228717705638E-5</v>
+        <v>1.9417624590728801E-5</v>
       </c>
       <c r="F66" s="10">
         <f>E66/D66</f>
-        <v>1.0201938145305103</v>
+        <v>0.98141967163352228</v>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="2"/>
       <c r="I66" s="2">
-        <v>2.4434932696069799E-5</v>
+        <v>2.44555572729164E-5</v>
       </c>
       <c r="J66" s="2">
-        <v>2.5518609602937599E-5</v>
+        <v>2.3173152783100001E-5</v>
       </c>
       <c r="K66" s="10">
         <f>J66/I66</f>
-        <v>1.0443494942403546</v>
+        <v>0.94756183735642718</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A67" s="4">
-        <v>15</v>
+      <c r="A67">
+        <v>0.5</v>
       </c>
       <c r="B67" s="5"/>
       <c r="C67" s="2">
         <v>3.1327203465188001E-3</v>
       </c>
       <c r="D67">
-        <v>2.9966209956305001E-3</v>
-      </c>
-      <c r="E67">
-        <v>3.14006419786265E-3</v>
-      </c>
-      <c r="F67" s="11">
-        <f t="shared" ref="F67:F76" si="6">E67/D67</f>
-        <v>1.0478683164942482</v>
+        <v>1.02051178015395E-4</v>
+      </c>
+      <c r="E67" s="2">
+        <v>9.4705678455829002E-5</v>
+      </c>
+      <c r="F67" s="10">
+        <f t="shared" ref="F67:F78" si="6">E67/D67</f>
+        <v>0.92802141334950694</v>
       </c>
       <c r="G67" s="4"/>
       <c r="I67">
-        <v>3.6561489620800698E-3</v>
+        <v>1.237590596311E-4</v>
       </c>
       <c r="J67">
-        <v>3.8583728177792702E-3</v>
+        <v>1.2781285534871299E-4</v>
       </c>
       <c r="K67" s="11">
-        <f t="shared" ref="K67:K76" si="7">J67/I67</f>
-        <v>1.0553106172085915</v>
+        <f t="shared" ref="K67:K78" si="7">J67/I67</f>
+        <v>1.0327555471873857</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="B68" s="5"/>
       <c r="C68" s="2">
         <v>6.2691724987101998E-3</v>
       </c>
       <c r="D68">
-        <v>6.0122469256428399E-3</v>
+        <v>2.0004896550590901E-4</v>
       </c>
       <c r="E68">
-        <v>6.2971023902297701E-3</v>
+        <v>2.0519183351723301E-4</v>
       </c>
       <c r="F68" s="10">
         <f t="shared" si="6"/>
-        <v>1.0473792025028101</v>
+        <v>1.0257080460192236</v>
       </c>
       <c r="G68" s="4"/>
       <c r="I68">
-        <v>7.3167786817070497E-3</v>
+        <v>2.47009346021372E-4</v>
       </c>
       <c r="J68">
-        <v>7.7206053021012903E-3</v>
+        <v>2.5056736662623701E-4</v>
       </c>
       <c r="K68" s="10">
         <f t="shared" si="7"/>
-        <v>1.0551918594181156</v>
+        <v>1.0144043966844767</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A69" s="4">
-        <v>60</v>
+      <c r="A69">
+        <v>10</v>
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="2">
         <v>1.2558983712415E-2</v>
       </c>
       <c r="D69">
-        <v>1.2036181905772299E-2</v>
+        <v>1.9727739159685499E-3</v>
       </c>
       <c r="E69">
-        <v>1.26843202591898E-2</v>
-      </c>
-      <c r="F69" s="11">
+        <v>2.1002402963605799E-3</v>
+      </c>
+      <c r="F69" s="10">
         <f t="shared" si="6"/>
-        <v>1.053849165664958</v>
+        <v>1.0646127665011473</v>
       </c>
       <c r="G69" s="4"/>
       <c r="I69">
-        <v>1.4655010559957399E-2</v>
+        <v>2.41443999850058E-3</v>
       </c>
       <c r="J69">
-        <v>1.54708347850845E-2</v>
+        <v>2.5624129143282902E-3</v>
       </c>
       <c r="K69" s="11">
         <f t="shared" si="7"/>
-        <v>1.0556686207621178</v>
+        <v>1.0612866403470804</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="B70" s="5"/>
       <c r="C70" s="2">
         <v>1.8782496824776201E-2</v>
       </c>
       <c r="D70">
-        <v>1.81922730031659E-2</v>
+        <v>4.9269907229743297E-3</v>
       </c>
       <c r="E70">
-        <v>1.9125340454343599E-2</v>
+        <v>5.2981099306138504E-3</v>
       </c>
       <c r="F70" s="10">
         <f t="shared" si="6"/>
-        <v>1.051289217736306</v>
+        <v>1.0753237074121145</v>
       </c>
       <c r="G70" s="4"/>
       <c r="I70">
-        <v>2.20520227131588E-2</v>
+        <v>6.11270182240103E-3</v>
       </c>
       <c r="J70">
-        <v>2.3279563002525702E-2</v>
+        <v>6.4145321839513504E-3</v>
       </c>
       <c r="K70" s="10">
         <f t="shared" si="7"/>
-        <v>1.0556656550437167</v>
+        <v>1.0493775699060295</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A71" s="4">
-        <v>120</v>
+      <c r="A71">
+        <v>50</v>
       </c>
       <c r="B71" s="5"/>
       <c r="C71" s="2">
         <v>2.51046376970986E-2</v>
       </c>
       <c r="D71">
-        <v>2.42950363565053E-2</v>
+        <v>9.7820010092556295E-3</v>
       </c>
       <c r="E71">
-        <v>2.55954016873969E-2</v>
-      </c>
-      <c r="F71" s="11">
+        <v>1.0195154351149101E-2</v>
+      </c>
+      <c r="F71" s="10">
         <f t="shared" si="6"/>
-        <v>1.0535239096501048</v>
+        <v>1.0422360763919929</v>
       </c>
       <c r="G71" s="4"/>
       <c r="I71">
-        <v>2.9379142051595902E-2</v>
+        <v>1.20970549355645E-2</v>
       </c>
       <c r="J71">
-        <v>3.0966693098777899E-2</v>
+        <v>1.24175942421624E-2</v>
       </c>
       <c r="K71" s="11">
         <f t="shared" si="7"/>
-        <v>1.0540366714723639</v>
+        <v>1.0264973010625533</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="B72" s="5"/>
       <c r="C72" s="2">
         <v>3.1476119846668899E-2</v>
       </c>
       <c r="D72">
-        <v>3.0568379602756501E-2</v>
+        <v>1.43763436727791E-2</v>
       </c>
       <c r="E72">
-        <v>3.2160454077141201E-2</v>
+        <v>1.5782984835099299E-2</v>
       </c>
       <c r="F72" s="10">
         <f t="shared" si="6"/>
-        <v>1.0520823967470339</v>
+        <v>1.0978441524727602</v>
       </c>
       <c r="G72" s="4"/>
       <c r="I72">
-        <v>3.6804448452257998E-2</v>
+        <v>1.8002551123509802E-2</v>
       </c>
       <c r="J72">
-        <v>3.8844686371276298E-2</v>
+        <v>1.8976376994297401E-2</v>
       </c>
       <c r="K72" s="10">
         <f t="shared" si="7"/>
-        <v>1.0554345467685748</v>
+        <v>1.0540937706054263</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A73" s="4">
-        <v>250</v>
+      <c r="A73">
+        <v>100</v>
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="2">
         <v>5.2878603388737497E-2</v>
       </c>
       <c r="D73">
-        <v>5.1688372196524002E-2</v>
+        <v>2.00458898906196E-2</v>
       </c>
       <c r="E73">
-        <v>5.4514904682317102E-2</v>
-      </c>
-      <c r="F73" s="11">
+        <v>2.0804120655568799E-2</v>
+      </c>
+      <c r="F73" s="10">
         <f t="shared" si="6"/>
-        <v>1.0546841071923558</v>
+        <v>1.0378247495664441</v>
       </c>
       <c r="G73" s="4"/>
       <c r="I73">
-        <v>6.1567552933483601E-2</v>
+        <v>2.4309982506840501E-2</v>
       </c>
       <c r="J73">
-        <v>6.4958585716827305E-2</v>
+        <v>2.56065505285916E-2</v>
       </c>
       <c r="K73" s="11">
         <f t="shared" si="7"/>
-        <v>1.0550782453057264</v>
+        <v>1.0533347986320543</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="2">
         <v>0.107716927588289</v>
       </c>
       <c r="D74">
-        <v>0.107312205249392</v>
+        <v>3.0432830381329601E-2</v>
       </c>
       <c r="E74">
-        <v>0.11284726504879</v>
+        <v>3.14434702136525E-2</v>
       </c>
       <c r="F74" s="10">
         <f t="shared" si="6"/>
-        <v>1.0515790332193304</v>
+        <v>1.0332088675177227</v>
       </c>
       <c r="G74" s="4"/>
       <c r="I74">
-        <v>0.124585487877085</v>
+        <v>3.5308084946377202E-2</v>
       </c>
       <c r="J74">
-        <v>0.13088073929294</v>
+        <v>3.7911161854217702E-2</v>
       </c>
       <c r="K74" s="10">
         <f t="shared" si="7"/>
-        <v>1.0505295722890764</v>
+        <v>1.0737246699104135</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A75" s="4">
-        <v>750</v>
+      <c r="A75">
+        <v>250</v>
       </c>
       <c r="B75" s="5"/>
       <c r="C75" s="2">
         <v>0.16515386445267599</v>
       </c>
       <c r="D75">
-        <v>0.166593474221475</v>
+        <v>4.89210306757277E-2</v>
       </c>
       <c r="E75">
-        <v>0.17437302973664801</v>
-      </c>
-      <c r="F75" s="11">
+        <v>5.3975920537313898E-2</v>
+      </c>
+      <c r="F75" s="10">
         <f t="shared" si="6"/>
-        <v>1.0466978406658991</v>
+        <v>1.1033275421994369</v>
       </c>
       <c r="G75" s="4"/>
       <c r="I75">
-        <v>0.188315720076114</v>
+        <v>5.8808790512075798E-2</v>
       </c>
       <c r="J75">
-        <v>0.19671890522285099</v>
+        <v>6.2265324575410202E-2</v>
       </c>
       <c r="K75" s="11">
         <f t="shared" si="7"/>
-        <v>1.0446228554012409</v>
+        <v>1.0587758060187387</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="B76" s="5"/>
       <c r="C76" s="2">
         <v>0.22114304090137801</v>
       </c>
       <c r="D76">
-        <v>0.22843742858074301</v>
+        <v>9.6226590649767796E-2</v>
       </c>
       <c r="E76">
-        <v>0.23785710518924499</v>
+        <v>0.10212774105006001</v>
       </c>
       <c r="F76" s="10">
         <f t="shared" si="6"/>
-        <v>1.0412352593312988</v>
+        <v>1.0613255687481478</v>
       </c>
       <c r="G76" s="4"/>
       <c r="I76">
-        <v>0.25212873564071397</v>
+        <v>0.11146020972599301</v>
       </c>
       <c r="J76">
-        <v>0.26159631710660702</v>
+        <v>0.118001707852343</v>
       </c>
       <c r="K76" s="10">
         <f t="shared" si="7"/>
+        <v>1.0586890886212328</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>750</v>
+      </c>
+      <c r="D77">
+        <v>0.140294088260282</v>
+      </c>
+      <c r="E77">
+        <v>0.15225875418305601</v>
+      </c>
+      <c r="F77" s="10">
+        <f t="shared" si="6"/>
+        <v>1.0852827519045309</v>
+      </c>
+      <c r="I77">
+        <v>0.164782092113922</v>
+      </c>
+      <c r="J77">
+        <v>0.171436913407884</v>
+      </c>
+      <c r="K77" s="11">
+        <f t="shared" si="7"/>
+        <v>1.0403855856458066</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>999.99</v>
+      </c>
+      <c r="D78">
+        <v>0.181401571560247</v>
+      </c>
+      <c r="E78">
+        <v>0.20058148390920799</v>
+      </c>
+      <c r="F78" s="10">
+        <f t="shared" si="6"/>
+        <v>1.1057317871283765</v>
+      </c>
+      <c r="I78">
+        <v>0.211482254080264</v>
+      </c>
+      <c r="J78">
+        <v>0.22688990016688301</v>
+      </c>
+      <c r="K78" s="10">
+        <f t="shared" si="7"/>
+        <v>1.0728555034256981</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C80" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D80" s="12"/>
+      <c r="E80" s="13"/>
+      <c r="F80" s="13"/>
+      <c r="H80" s="2"/>
+      <c r="I80" s="2"/>
+      <c r="J80" s="2"/>
+      <c r="K80" s="2"/>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D81" s="3"/>
+      <c r="E81" s="9"/>
+      <c r="F81" s="3"/>
+      <c r="H81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I81" s="3"/>
+      <c r="J81" s="9"/>
+      <c r="K81" s="9"/>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A82" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B82" s="6"/>
+      <c r="C82" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G82" s="8"/>
+      <c r="H82" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="J82" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K82" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>0.1</v>
+      </c>
+      <c r="B83" s="5"/>
+      <c r="C83" s="2">
+        <v>2.0906018648200899E-5</v>
+      </c>
+      <c r="D83" s="2">
+        <v>2.8143173972499801E-7</v>
+      </c>
+      <c r="E83" s="2">
+        <v>1.46150091119403E-6</v>
+      </c>
+      <c r="F83" s="10">
+        <f t="shared" ref="F83:F94" si="8">F66*((E83/E66)^2 +(D83/D66)^2)^0.5</f>
+        <v>7.5175789820697683E-2</v>
+      </c>
+      <c r="G83" s="4"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="2">
+        <v>2.4434932696069799E-5</v>
+      </c>
+      <c r="J83" s="2">
+        <v>2.5518609602937599E-5</v>
+      </c>
+      <c r="K83" s="10">
+        <f>J83/I83</f>
+        <v>1.0443494942403546</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>0.5</v>
+      </c>
+      <c r="B84" s="5"/>
+      <c r="C84" s="2">
+        <v>3.1327203465188001E-3</v>
+      </c>
+      <c r="D84" s="2">
+        <v>1.5222069872849199E-6</v>
+      </c>
+      <c r="E84" s="2">
+        <v>3.7622530224669299E-6</v>
+      </c>
+      <c r="F84" s="10">
+        <f t="shared" si="8"/>
+        <v>3.9379446327356661E-2</v>
+      </c>
+      <c r="G84" s="4"/>
+      <c r="I84">
+        <v>3.6561489620800698E-3</v>
+      </c>
+      <c r="J84">
+        <v>3.8583728177792702E-3</v>
+      </c>
+      <c r="K84" s="11">
+        <f t="shared" ref="K84:K93" si="9">J84/I84</f>
+        <v>1.0553106172085915</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>1</v>
+      </c>
+      <c r="B85" s="5"/>
+      <c r="C85" s="2">
+        <v>6.2691724987101998E-3</v>
+      </c>
+      <c r="D85" s="2">
+        <v>2.33807312394273E-6</v>
+      </c>
+      <c r="E85" s="2">
+        <v>6.5127278910264096E-6</v>
+      </c>
+      <c r="F85" s="10">
+        <f t="shared" si="8"/>
+        <v>3.4692692812303069E-2</v>
+      </c>
+      <c r="G85" s="4"/>
+      <c r="I85">
+        <v>7.3167786817070497E-3</v>
+      </c>
+      <c r="J85">
+        <v>7.7206053021012903E-3</v>
+      </c>
+      <c r="K85" s="10">
+        <f t="shared" si="9"/>
+        <v>1.0551918594181156</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>10</v>
+      </c>
+      <c r="B86" s="5"/>
+      <c r="C86" s="2">
+        <v>1.2558983712415E-2</v>
+      </c>
+      <c r="D86" s="2">
+        <v>2.7701090496064399E-5</v>
+      </c>
+      <c r="E86" s="2">
+        <v>3.8011060965548303E-5</v>
+      </c>
+      <c r="F86" s="10">
+        <f t="shared" si="8"/>
+        <v>2.4386896067040687E-2</v>
+      </c>
+      <c r="G86" s="4"/>
+      <c r="I86">
+        <v>1.4655010559957399E-2</v>
+      </c>
+      <c r="J86">
+        <v>1.54708347850845E-2</v>
+      </c>
+      <c r="K86" s="11">
+        <f t="shared" si="9"/>
+        <v>1.0556686207621178</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>25</v>
+      </c>
+      <c r="B87" s="5"/>
+      <c r="C87" s="2">
+        <v>1.8782496824776201E-2</v>
+      </c>
+      <c r="D87" s="2">
+        <v>8.0985715172972504E-5</v>
+      </c>
+      <c r="E87" s="2">
+        <v>8.2936422592517207E-5</v>
+      </c>
+      <c r="F87" s="10">
+        <f t="shared" si="8"/>
+        <v>2.4408348565916203E-2</v>
+      </c>
+      <c r="G87" s="4"/>
+      <c r="I87">
+        <v>2.20520227131588E-2</v>
+      </c>
+      <c r="J87">
+        <v>2.3279563002525702E-2</v>
+      </c>
+      <c r="K87" s="10">
+        <f t="shared" si="9"/>
+        <v>1.0556656550437167</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>50</v>
+      </c>
+      <c r="B88" s="5"/>
+      <c r="C88" s="2">
+        <v>2.51046376970986E-2</v>
+      </c>
+      <c r="D88">
+        <v>1.14857385321631E-4</v>
+      </c>
+      <c r="E88">
+        <v>1.40546480514001E-4</v>
+      </c>
+      <c r="F88" s="10">
+        <f t="shared" si="8"/>
+        <v>1.8873133491714433E-2</v>
+      </c>
+      <c r="G88" s="4"/>
+      <c r="I88">
+        <v>2.9379142051595902E-2</v>
+      </c>
+      <c r="J88">
+        <v>3.0966693098777899E-2</v>
+      </c>
+      <c r="K88" s="11">
+        <f t="shared" si="9"/>
+        <v>1.0540366714723639</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>75</v>
+      </c>
+      <c r="B89" s="5"/>
+      <c r="C89" s="2">
+        <v>3.1476119846668899E-2</v>
+      </c>
+      <c r="D89">
+        <v>1.6692001786006801E-4</v>
+      </c>
+      <c r="E89">
+        <v>2.2355768083561999E-4</v>
+      </c>
+      <c r="F89" s="10">
+        <f t="shared" si="8"/>
+        <v>2.0107088599017175E-2</v>
+      </c>
+      <c r="G89" s="4"/>
+      <c r="I89">
+        <v>3.6804448452257998E-2</v>
+      </c>
+      <c r="J89">
+        <v>3.8844686371276298E-2</v>
+      </c>
+      <c r="K89" s="10">
+        <f t="shared" si="9"/>
+        <v>1.0554345467685748</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>100</v>
+      </c>
+      <c r="B90" s="5"/>
+      <c r="C90" s="2">
+        <v>5.2878603388737497E-2</v>
+      </c>
+      <c r="D90">
+        <v>2.77931449091848E-4</v>
+      </c>
+      <c r="E90">
+        <v>2.1739476286188801E-4</v>
+      </c>
+      <c r="F90" s="10">
+        <f t="shared" si="8"/>
+        <v>1.8018315350781095E-2</v>
+      </c>
+      <c r="G90" s="4"/>
+      <c r="I90">
+        <v>6.1567552933483601E-2</v>
+      </c>
+      <c r="J90">
+        <v>6.4958585716827305E-2</v>
+      </c>
+      <c r="K90" s="11">
+        <f t="shared" si="9"/>
+        <v>1.0550782453057264</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>150</v>
+      </c>
+      <c r="B91" s="5"/>
+      <c r="C91" s="2">
+        <v>0.107716927588289</v>
+      </c>
+      <c r="D91">
+        <v>3.3888866496247497E-4</v>
+      </c>
+      <c r="E91">
+        <v>4.2099807481717899E-4</v>
+      </c>
+      <c r="F91" s="10">
+        <f t="shared" si="8"/>
+        <v>1.7992932963347683E-2</v>
+      </c>
+      <c r="G91" s="4"/>
+      <c r="I91">
+        <v>0.124585487877085</v>
+      </c>
+      <c r="J91">
+        <v>0.13088073929294</v>
+      </c>
+      <c r="K91" s="10">
+        <f t="shared" si="9"/>
+        <v>1.0505295722890764</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>250</v>
+      </c>
+      <c r="B92" s="5"/>
+      <c r="C92" s="2">
+        <v>0.16515386445267599</v>
+      </c>
+      <c r="D92">
+        <v>6.0844630496931901E-4</v>
+      </c>
+      <c r="E92">
+        <v>7.1735921087181002E-4</v>
+      </c>
+      <c r="F92" s="10">
+        <f t="shared" si="8"/>
+        <v>2.0082997872230529E-2</v>
+      </c>
+      <c r="G92" s="4"/>
+      <c r="I92">
+        <v>0.188315720076114</v>
+      </c>
+      <c r="J92">
+        <v>0.19671890522285099</v>
+      </c>
+      <c r="K92" s="11">
+        <f t="shared" si="9"/>
+        <v>1.0446228554012409</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>500</v>
+      </c>
+      <c r="B93" s="5"/>
+      <c r="C93" s="2">
+        <v>0.22114304090137801</v>
+      </c>
+      <c r="D93">
+        <v>1.3901143553867799E-3</v>
+      </c>
+      <c r="E93">
+        <v>1.45703989958587E-3</v>
+      </c>
+      <c r="F93" s="10">
+        <f t="shared" si="8"/>
+        <v>2.1548753693625213E-2</v>
+      </c>
+      <c r="G93" s="4"/>
+      <c r="I93">
+        <v>0.25212873564071397</v>
+      </c>
+      <c r="J93">
+        <v>0.26159631710660702</v>
+      </c>
+      <c r="K93" s="10">
+        <f t="shared" si="9"/>
         <v>1.0375505847908761</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>750</v>
+      </c>
+      <c r="D94">
+        <v>1.59024586083695E-3</v>
+      </c>
+      <c r="E94">
+        <v>1.88927153592098E-3</v>
+      </c>
+      <c r="F94" s="10">
+        <f t="shared" si="8"/>
+        <v>1.8239532257896197E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>999.99</v>
+      </c>
+      <c r="D95">
+        <v>2.0916951916344802E-3</v>
+      </c>
+      <c r="E95">
+        <v>2.14759074882869E-3</v>
+      </c>
+      <c r="F95" s="10">
+        <f>F78*((E95/E78)^2 +(D95/D78)^2)^0.5</f>
+        <v>1.7398828006913617E-2</v>
       </c>
     </row>
   </sheetData>

--- a/Jupyter/Wedge/wedge_data_2026-03-25.xlsx
+++ b/Jupyter/Wedge/wedge_data_2026-03-25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\patri\projects\emma-openmc\Jupyter\Wedge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B184866-94F8-47FB-9604-EE9CD1C46C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDAEB268-8B64-460D-9E40-EF1FACC7331B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -274,10 +274,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$26:$A$40</c:f>
+              <c:f>'Sheet 1'!$A$24:$A$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>0.1</c:v>
                 </c:pt>
@@ -285,97 +285,85 @@
                   <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.5</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>15</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>30</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>60</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>90</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>100</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>120</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>150</c:v>
+                  <c:v>500</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>250</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>500</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>750</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1000</c:v>
+                  <c:v>999.99</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$F$26:$F$40</c:f>
+              <c:f>'Sheet 1'!$F$24:$F$36</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.7274775745944605</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.64347975683918834</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.49583688440425344</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.66859607525333198</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.73291562987349301</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.74746751893992558</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.78627670393149318</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.87619376520123537</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.86809490045634352</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.79255474288640204</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.90551396638088599</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.92837643974491146</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.93787715524054671</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1.0174259839976012</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1.0246283267351703</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -414,10 +402,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$26:$A$40</c:f>
+              <c:f>'Sheet 1'!$A$24:$A$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>0.1</c:v>
                 </c:pt>
@@ -425,97 +413,85 @@
                   <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.5</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>15</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>30</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>60</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>90</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>100</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>120</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>150</c:v>
+                  <c:v>500</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>250</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>500</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>750</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1000</c:v>
+                  <c:v>999.99</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$K$26:$K$40</c:f>
+              <c:f>'Sheet 1'!$K$24:$K$36</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.29264705217301878</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.3315375295667062</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.8971337860952534</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.86727127408207016</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.96019947785672299</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.82054207267800461</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.89620098412984728</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.99789498609321658</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.92546657383389286</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.95340718196328889</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.94899688560909901</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.9624346474925255</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.0215461604572156</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1.0753115641669349</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1.0025476893384362</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -874,10 +850,10 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$5:$A$19</c:f>
+              <c:f>'Sheet 1'!$A$5:$A$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>0.1</c:v>
                 </c:pt>
@@ -885,42 +861,36 @@
                   <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.5</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>15</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>30</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>60</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>90</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>100</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>120</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>150</c:v>
+                  <c:v>500</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>250</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>500</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>750</c:v>
-                </c:pt>
-                <c:pt idx="14">
                   <c:v>999.99</c:v>
                 </c:pt>
               </c:numCache>
@@ -928,54 +898,48 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$F$5:$F$19</c:f>
+              <c:f>'Sheet 1'!$F$5:$F$17</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>1.0120583199660715</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.98723674640081305</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.97352011835670349</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.98670947182667379</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0274179661023068</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.9995818870330847</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0035538292803527</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0225693897940391</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.0133855529616367</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.0168926589087053</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.0023371440138709</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.99143857028386306</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.99628894469879192</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1.0133076136706871</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.98894242420015732</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1065,10 +1029,10 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$5:$A$19</c:f>
+              <c:f>'Sheet 1'!$A$5:$A$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>0.1</c:v>
                 </c:pt>
@@ -1076,42 +1040,36 @@
                   <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.5</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>15</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>30</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>60</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>90</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>100</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>120</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>150</c:v>
+                  <c:v>500</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>250</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>500</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>750</c:v>
-                </c:pt>
-                <c:pt idx="14">
                   <c:v>999.99</c:v>
                 </c:pt>
               </c:numCache>
@@ -1119,54 +1077,48 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$K$5:$K$19</c:f>
+              <c:f>'Sheet 1'!$K$5:$K$17</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>1.0124595607074192</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.98955684846579572</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.97266576371713243</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.99532217045916183</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0246126531897757</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.99123212311197628</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0019803232436455</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0235838898658773</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.0328136474978709</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.99238859087523068</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.0068419602917082</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.0041778550412717</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.0147327958753034</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1.0192489706741765</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.9824392574158276</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1451,7 +1403,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Sheet 1'!$F$65</c:f>
+              <c:f>'Sheet 1'!$F$61</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1484,7 +1436,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$66:$A$76</c:f>
+              <c:f>'Sheet 1'!$A$62:$A$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -1526,7 +1478,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$F$66:$F$76</c:f>
+              <c:f>'Sheet 1'!$F$62:$F$72</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="11"/>
@@ -1815,7 +1767,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Sheet 1'!$F$47</c:f>
+              <c:f>'Sheet 1'!$F$43</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1848,7 +1800,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$48:$A$58</c:f>
+              <c:f>'Sheet 1'!$A$44:$A$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -1890,7 +1842,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$F$48:$F$58</c:f>
+              <c:f>'Sheet 1'!$F$44:$F$54</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="11"/>
@@ -4354,13 +4306,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>132179</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>56857</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>436979</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>56857</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4396,8 +4348,8 @@
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>605790</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>99060</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4426,13 +4378,13 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>868680</xdr:colOff>
-      <xdr:row>61</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4462,13 +4414,13 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>929640</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>259080</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4760,7 +4712,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22416C2-1180-4450-A3B0-0B08DD9AEC85}">
-  <dimension ref="A1:L95"/>
+  <dimension ref="A1:L91"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
@@ -4842,32 +4794,17 @@
         <v>0.1</v>
       </c>
       <c r="B5" s="5"/>
-      <c r="C5">
-        <v>1.4063862998066801</v>
-      </c>
-      <c r="D5">
-        <v>1.3686193553583801</v>
-      </c>
       <c r="E5">
-        <v>1.38512260545705</v>
-      </c>
-      <c r="F5" s="10">
+        <v>1.38933589370449</v>
+      </c>
+      <c r="F5" s="10" t="e">
         <f>E5/D5</f>
-        <v>1.0120583199660715</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G5" s="4"/>
-      <c r="H5">
-        <v>1.4074651112049299</v>
-      </c>
-      <c r="I5">
-        <v>1.3681177802680899</v>
-      </c>
-      <c r="J5">
-        <v>1.3851639268062399</v>
-      </c>
-      <c r="K5" s="10">
+      <c r="K5" s="10" t="e">
         <f>J5/I5</f>
-        <v>1.0124595607074192</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L5" s="10"/>
     </row>
@@ -4876,66 +4813,36 @@
         <v>0.5</v>
       </c>
       <c r="B6" s="5"/>
-      <c r="C6">
-        <v>1.4065448393936499</v>
-      </c>
-      <c r="D6">
-        <v>1.3922831524096599</v>
-      </c>
       <c r="E6">
-        <v>1.37451308945358</v>
-      </c>
-      <c r="F6" s="10">
-        <f t="shared" ref="F6:F19" si="0">E6/D6</f>
-        <v>0.98723674640081305</v>
+        <v>1.3891670563732801</v>
+      </c>
+      <c r="F6" s="10" t="e">
+        <f t="shared" ref="F6:F17" si="0">E6/D6</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="G6" s="4"/>
-      <c r="H6">
-        <v>1.4079920998080599</v>
-      </c>
-      <c r="I6">
-        <v>1.3884228746446901</v>
-      </c>
-      <c r="J6">
-        <v>1.3739233641712201</v>
-      </c>
-      <c r="K6" s="10">
-        <f t="shared" ref="K6:K19" si="1">J6/I6</f>
-        <v>0.98955684846579572</v>
+      <c r="K6" s="10" t="e">
+        <f t="shared" ref="K6:K17" si="1">J6/I6</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="L6" s="10"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="B7" s="5"/>
-      <c r="C7">
-        <v>1.40593053429746</v>
-      </c>
-      <c r="D7">
-        <v>1.4141178954362701</v>
-      </c>
       <c r="E7">
-        <v>1.3766722209354501</v>
-      </c>
-      <c r="F7" s="10">
+        <v>1.3888589124812201</v>
+      </c>
+      <c r="F7" s="10" t="e">
         <f t="shared" si="0"/>
-        <v>0.97352011835670349</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G7" s="4"/>
-      <c r="H7">
-        <v>1.4079445884292401</v>
-      </c>
-      <c r="I7">
-        <v>1.4147283449213399</v>
-      </c>
-      <c r="J7">
-        <v>1.3760578260651899</v>
-      </c>
-      <c r="K7" s="10">
+      <c r="K7" s="10" t="e">
         <f t="shared" si="1"/>
-        <v>0.97266576371713243</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L7" s="10"/>
     </row>
@@ -4944,2264 +4851,1809 @@
         <v>10</v>
       </c>
       <c r="B8" s="5"/>
-      <c r="C8">
-        <v>1.39838837861919</v>
-      </c>
-      <c r="D8">
-        <v>1.4052374449883001</v>
-      </c>
       <c r="E8">
-        <v>1.38656109713547</v>
-      </c>
-      <c r="F8" s="10">
+        <v>1.3868055893142199</v>
+      </c>
+      <c r="F8" s="10" t="e">
         <f t="shared" si="0"/>
-        <v>0.98670947182667379</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G8" s="4"/>
-      <c r="H8">
-        <v>1.4018754625880101</v>
-      </c>
-      <c r="I8">
-        <v>1.3952787310994501</v>
-      </c>
-      <c r="J8">
-        <v>1.3887518550334099</v>
-      </c>
-      <c r="K8" s="10">
+      <c r="K8" s="10" t="e">
         <f t="shared" si="1"/>
-        <v>0.99532217045916183</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L8" s="10"/>
     </row>
     <row r="9" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B9" s="5"/>
-      <c r="C9">
-        <v>1.39742877901721</v>
-      </c>
-      <c r="D9">
-        <v>1.3588321367490299</v>
-      </c>
+      <c r="C9"/>
+      <c r="D9"/>
       <c r="E9">
-        <v>1.3960885502131399</v>
-      </c>
-      <c r="F9" s="10">
+        <v>1.3820193582140401</v>
+      </c>
+      <c r="F9" s="10" t="e">
         <f t="shared" si="0"/>
-        <v>1.0274179661023068</v>
-      </c>
-      <c r="H9">
-        <v>1.4018991482118599</v>
-      </c>
-      <c r="I9">
-        <v>1.36086238814935</v>
-      </c>
-      <c r="J9">
-        <v>1.3943568221478799</v>
-      </c>
-      <c r="K9" s="10">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9" s="10" t="e">
         <f t="shared" si="1"/>
-        <v>1.0246126531897757</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L9" s="11"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="B10" s="5"/>
-      <c r="C10">
-        <v>1.3977734656963801</v>
-      </c>
-      <c r="D10">
-        <v>1.38084479180245</v>
-      </c>
       <c r="E10">
-        <v>1.3802674426896999</v>
-      </c>
-      <c r="F10" s="10">
+        <v>1.3754575654543499</v>
+      </c>
+      <c r="F10" s="10" t="e">
         <f t="shared" si="0"/>
-        <v>0.9995818870330847</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G10" s="4"/>
-      <c r="H10">
-        <v>1.3914317207496001</v>
-      </c>
-      <c r="I10">
-        <v>1.3852911212816701</v>
-      </c>
-      <c r="J10">
-        <v>1.3731450592762</v>
-      </c>
-      <c r="K10" s="10">
+      <c r="K10" s="10" t="e">
         <f t="shared" si="1"/>
-        <v>0.99123212311197628</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L10" s="10"/>
     </row>
     <row r="11" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="B11" s="5"/>
-      <c r="C11">
-        <v>1.39314164652525</v>
-      </c>
-      <c r="D11">
-        <v>1.35391575819657</v>
-      </c>
+      <c r="C11"/>
+      <c r="D11"/>
       <c r="E11">
-        <v>1.35872734366118</v>
-      </c>
-      <c r="F11" s="10">
+        <v>1.37040384545697</v>
+      </c>
+      <c r="F11" s="10" t="e">
         <f t="shared" si="0"/>
-        <v>1.0035538292803527</v>
-      </c>
-      <c r="H11">
-        <v>1.3881975250755401</v>
-      </c>
-      <c r="I11">
-        <v>1.3558315843768101</v>
-      </c>
-      <c r="J11">
-        <v>1.35851656917782</v>
-      </c>
-      <c r="K11" s="10">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11" s="10" t="e">
         <f t="shared" si="1"/>
-        <v>1.0019803232436455</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L11" s="11"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B12" s="5"/>
-      <c r="C12">
-        <v>1.3818447189929399</v>
-      </c>
-      <c r="D12">
-        <v>1.3540665504448699</v>
-      </c>
       <c r="E12">
-        <v>1.3846270062289301</v>
-      </c>
-      <c r="F12" s="10">
+        <v>1.3649754350071801</v>
+      </c>
+      <c r="F12" s="10" t="e">
         <f t="shared" si="0"/>
-        <v>1.0225693897940391</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G12" s="4"/>
-      <c r="H12">
-        <v>1.3733638983322201</v>
-      </c>
-      <c r="I12">
-        <v>1.34423803647162</v>
-      </c>
-      <c r="J12">
-        <v>1.37594039827729</v>
-      </c>
-      <c r="K12" s="10">
+      <c r="K12" s="10" t="e">
         <f t="shared" si="1"/>
-        <v>1.0235838898658773</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L12" s="10"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="B13" s="5"/>
-      <c r="C13">
-        <v>1.37950613179578</v>
-      </c>
-      <c r="D13">
-        <v>1.3565730983264299</v>
-      </c>
       <c r="E13">
-        <v>1.37473157938041</v>
-      </c>
-      <c r="F13" s="10">
+        <v>1.35044101904588</v>
+      </c>
+      <c r="F13" s="10" t="e">
         <f t="shared" si="0"/>
-        <v>1.0133855529616367</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G13" s="4"/>
-      <c r="H13">
-        <v>1.3697423426526301</v>
-      </c>
-      <c r="I13">
-        <v>1.3294388930292</v>
-      </c>
-      <c r="J13">
-        <v>1.3730626322350199</v>
-      </c>
-      <c r="K13" s="10">
+      <c r="K13" s="10" t="e">
         <f t="shared" si="1"/>
-        <v>1.0328136474978709</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L13" s="10"/>
     </row>
     <row r="14" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="B14" s="5"/>
-      <c r="C14">
-        <v>1.37505741757767</v>
-      </c>
-      <c r="D14">
-        <v>1.34077916991197</v>
-      </c>
+      <c r="C14"/>
+      <c r="D14"/>
       <c r="E14">
-        <v>1.3634284951011899</v>
-      </c>
-      <c r="F14" s="10">
+        <v>1.3309639224463901</v>
+      </c>
+      <c r="F14" s="10" t="e">
         <f t="shared" si="0"/>
-        <v>1.0168926589087053</v>
-      </c>
-      <c r="H14">
-        <v>1.36267435359262</v>
-      </c>
-      <c r="I14">
-        <v>1.35581073898229</v>
-      </c>
-      <c r="J14">
-        <v>1.34549110875214</v>
-      </c>
-      <c r="K14" s="10">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="K14" s="10" t="e">
         <f t="shared" si="1"/>
-        <v>0.99238859087523068</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L14" s="11"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="B15" s="5"/>
-      <c r="C15">
-        <v>1.3614670031018901</v>
-      </c>
-      <c r="D15">
-        <v>1.3628583617894401</v>
-      </c>
       <c r="E15">
-        <v>1.3660435580514501</v>
-      </c>
-      <c r="F15" s="10">
+        <v>1.2901507582212099</v>
+      </c>
+      <c r="F15" s="10" t="e">
         <f t="shared" si="0"/>
-        <v>1.0023371440138709</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G15" s="4"/>
-      <c r="H15">
-        <v>1.3561935884492</v>
-      </c>
-      <c r="I15">
-        <v>1.34642475596859</v>
-      </c>
-      <c r="J15">
-        <v>1.3556369406847</v>
-      </c>
-      <c r="K15" s="10">
+      <c r="K15" s="10" t="e">
         <f t="shared" si="1"/>
-        <v>1.0068419602917082</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L15" s="10"/>
     </row>
     <row r="16" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>250</v>
+        <v>750</v>
       </c>
       <c r="B16" s="5"/>
-      <c r="C16">
-        <v>1.3422623387583901</v>
-      </c>
-      <c r="D16">
-        <v>1.31238054231434</v>
-      </c>
+      <c r="C16"/>
+      <c r="D16"/>
       <c r="E16">
-        <v>1.30114468854049</v>
-      </c>
-      <c r="F16" s="10">
+        <v>1.2537253487050199</v>
+      </c>
+      <c r="F16" s="10" t="e">
         <f t="shared" si="0"/>
-        <v>0.99143857028386306</v>
-      </c>
-      <c r="H16">
-        <v>1.3247863550055301</v>
-      </c>
-      <c r="I16">
-        <v>1.2854468687873799</v>
-      </c>
-      <c r="J16">
-        <v>1.2908172794684301</v>
-      </c>
-      <c r="K16" s="10">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16" s="10" t="e">
         <f t="shared" si="1"/>
-        <v>1.0041778550412717</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L16" s="11"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>500</v>
+        <v>999.99</v>
       </c>
       <c r="B17" s="5"/>
-      <c r="C17">
-        <v>1.3014014859735601</v>
-      </c>
-      <c r="D17">
-        <v>1.27106900787611</v>
-      </c>
       <c r="E17">
-        <v>1.2663520004962301</v>
-      </c>
-      <c r="F17" s="10">
+        <v>1.2163442531022399</v>
+      </c>
+      <c r="F17" s="10" t="e">
         <f t="shared" si="0"/>
-        <v>0.99628894469879192</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G17" s="4"/>
-      <c r="H17">
-        <v>1.26268865444005</v>
-      </c>
-      <c r="I17">
-        <v>1.24215702849295</v>
-      </c>
-      <c r="J17">
-        <v>1.26045747443881</v>
-      </c>
-      <c r="K17" s="10">
+      <c r="K17" s="10" t="e">
         <f t="shared" si="1"/>
-        <v>1.0147327958753034</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L17" s="10"/>
     </row>
-    <row r="18" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>750</v>
-      </c>
-      <c r="B18" s="5"/>
-      <c r="C18">
-        <v>1.2615551433943699</v>
-      </c>
-      <c r="D18">
-        <v>1.2502327359779</v>
-      </c>
-      <c r="E18">
-        <v>1.26687035022674</v>
-      </c>
-      <c r="F18" s="10">
-        <f t="shared" si="0"/>
-        <v>1.0133076136706871</v>
-      </c>
-      <c r="H18">
-        <v>1.2096572387659299</v>
-      </c>
-      <c r="I18">
-        <v>1.20261020085431</v>
-      </c>
-      <c r="J18">
-        <v>1.2257592093430201</v>
-      </c>
-      <c r="K18" s="10">
-        <f t="shared" si="1"/>
-        <v>1.0192489706741765</v>
-      </c>
-      <c r="L18" s="11"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>999.99</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19">
-        <v>1.2295679722156101</v>
-      </c>
-      <c r="D19">
-        <v>1.2216766905077201</v>
-      </c>
-      <c r="E19">
-        <v>1.20816790789953</v>
-      </c>
-      <c r="F19" s="10">
-        <f t="shared" si="0"/>
-        <v>0.98894242420015732</v>
-      </c>
-      <c r="G19" s="4"/>
-      <c r="H19">
-        <v>1.15612158785918</v>
-      </c>
-      <c r="I19">
-        <v>1.1553240194424299</v>
-      </c>
-      <c r="J19">
-        <v>1.13503567173569</v>
-      </c>
-      <c r="K19" s="10">
-        <f t="shared" si="1"/>
-        <v>0.9824392574158276</v>
-      </c>
-      <c r="L19" s="10"/>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C21" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="12"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="3"/>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="3"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C23" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="12"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
+      <c r="A23" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="8"/>
+      <c r="H23" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="7"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="3"/>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="3"/>
+      <c r="A24">
+        <v>0.1</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2">
+        <v>2.3188386654289999E-5</v>
+      </c>
+      <c r="F24" s="10" t="e">
+        <f>E24/D24</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="10" t="e">
+        <f>J24/I24</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L24" s="10"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G25" s="8"/>
-      <c r="H25" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L25" s="7"/>
+      <c r="A25">
+        <v>0.5</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="E25">
+        <v>1.16379113471186E-4</v>
+      </c>
+      <c r="F25" s="10" t="e">
+        <f t="shared" ref="F25:F36" si="2">E25/D25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="K25" s="10" t="e">
+        <f t="shared" ref="K25:K36" si="3">J25/I25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L25" s="10"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="B26" s="5"/>
-      <c r="C26" s="2">
-        <v>3.53760968083747E-5</v>
-      </c>
-      <c r="D26" s="2">
-        <v>3.4283030439073703E-5</v>
-      </c>
-      <c r="E26" s="2">
-        <v>2.4940135833565399E-5</v>
-      </c>
-      <c r="F26" s="10">
-        <f>E26/D26</f>
-        <v>0.7274775745944605</v>
+      <c r="E26">
+        <v>2.31665379952172E-4</v>
+      </c>
+      <c r="F26" s="10" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="G26" s="4"/>
-      <c r="H26" s="2">
-        <v>3.2455422398815998E-5</v>
-      </c>
-      <c r="I26" s="2">
-        <v>3.06037506527904E-5</v>
-      </c>
-      <c r="J26" s="2">
-        <v>8.9560974139772096E-6</v>
-      </c>
-      <c r="K26" s="10">
-        <f>J26/I26</f>
-        <v>0.29264705217301878</v>
+      <c r="K26" s="10" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="L26" s="10"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="B27" s="5"/>
-      <c r="C27">
-        <v>1.769377952569E-4</v>
-      </c>
-      <c r="D27">
-        <v>1.7795710468822501E-4</v>
-      </c>
       <c r="E27">
-        <v>1.1451179445258501E-4</v>
-      </c>
-      <c r="F27" s="10">
-        <f t="shared" ref="F27:F40" si="2">E27/D27</f>
-        <v>0.64347975683918834</v>
+        <v>2.3274949085023899E-3</v>
+      </c>
+      <c r="F27" s="10" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="G27" s="4"/>
-      <c r="H27">
-        <v>1.622082823178E-4</v>
-      </c>
-      <c r="I27">
-        <v>1.51128498783429E-4</v>
-      </c>
-      <c r="J27">
-        <v>2.0123326791721201E-4</v>
-      </c>
-      <c r="K27" s="10">
-        <f t="shared" ref="K27:K40" si="3">J27/I27</f>
-        <v>1.3315375295667062</v>
+      <c r="K27" s="10" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="L27" s="10"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>1.5</v>
+        <v>25</v>
       </c>
       <c r="B28" s="5"/>
-      <c r="C28">
-        <v>5.2503514596129999E-4</v>
-      </c>
-      <c r="D28">
-        <v>5.6289187437775004E-4</v>
-      </c>
       <c r="E28">
-        <v>2.79102553247934E-4</v>
-      </c>
-      <c r="F28" s="10">
+        <v>5.7868683352336496E-3</v>
+      </c>
+      <c r="F28" s="10" t="e">
         <f t="shared" si="2"/>
-        <v>0.49583688440425344</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G28" s="4"/>
-      <c r="H28">
-        <v>4.8498345014689998E-4</v>
-      </c>
-      <c r="I28">
-        <v>4.4989314990682798E-4</v>
-      </c>
-      <c r="J28">
-        <v>4.03614344914232E-4</v>
-      </c>
-      <c r="K28" s="10">
+      <c r="K28" s="10" t="e">
         <f t="shared" si="3"/>
-        <v>0.8971337860952534</v>
-      </c>
-      <c r="L28" s="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L28" s="11"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="B29" s="5"/>
-      <c r="C29">
-        <v>3.3839428456904001E-3</v>
-      </c>
-      <c r="D29">
-        <v>3.3365070331695802E-3</v>
-      </c>
       <c r="E29">
-        <v>2.2307755074323201E-3</v>
-      </c>
-      <c r="F29" s="10">
+        <v>1.1357972286110201E-2</v>
+      </c>
+      <c r="F29" s="10" t="e">
         <f t="shared" si="2"/>
-        <v>0.66859607525333198</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G29" s="4"/>
-      <c r="H29">
-        <v>3.1626406186310001E-3</v>
-      </c>
-      <c r="I29">
-        <v>3.0155921421882699E-3</v>
-      </c>
-      <c r="J29">
-        <v>2.6153364392675002E-3</v>
-      </c>
-      <c r="K29" s="10">
+      <c r="K29" s="10" t="e">
         <f t="shared" si="3"/>
-        <v>0.86727127408207016</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L29" s="10"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="4">
-        <v>15</v>
+      <c r="A30">
+        <v>75</v>
       </c>
       <c r="B30" s="5"/>
-      <c r="C30">
-        <v>4.9687340175238997E-3</v>
-      </c>
-      <c r="D30">
-        <v>4.9536689812130401E-3</v>
-      </c>
       <c r="E30">
-        <v>3.6306214215505398E-3</v>
-      </c>
-      <c r="F30" s="10">
+        <v>1.6724313084056999E-2</v>
+      </c>
+      <c r="F30" s="10" t="e">
         <f t="shared" si="2"/>
-        <v>0.73291562987349301</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G30" s="4"/>
-      <c r="H30">
-        <v>4.7034313826145001E-3</v>
-      </c>
-      <c r="I30">
-        <v>4.2298917106053102E-3</v>
-      </c>
-      <c r="J30">
-        <v>4.0615398119136998E-3</v>
-      </c>
-      <c r="K30" s="10">
+      <c r="K30" s="10" t="e">
         <f t="shared" si="3"/>
-        <v>0.96019947785672299</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L30" s="11"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="B31" s="5"/>
-      <c r="C31">
-        <v>9.6668811570342003E-3</v>
-      </c>
-      <c r="D31">
-        <v>9.8049806314099101E-3</v>
-      </c>
       <c r="E31">
-        <v>7.3289045458139902E-3</v>
-      </c>
-      <c r="F31" s="10">
+        <v>2.2149757308928399E-2</v>
+      </c>
+      <c r="F31" s="10" t="e">
         <f t="shared" si="2"/>
-        <v>0.74746751893992558</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G31" s="4"/>
-      <c r="H31">
-        <v>9.2377761797262006E-3</v>
-      </c>
-      <c r="I31">
-        <v>8.8658994417866593E-3</v>
-      </c>
-      <c r="J31">
-        <v>7.2748435041183898E-3</v>
-      </c>
-      <c r="K31" s="10">
+      <c r="K31" s="10" t="e">
         <f t="shared" si="3"/>
-        <v>0.82054207267800461</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L31" s="10"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="4">
-        <v>60</v>
+      <c r="A32">
+        <v>150</v>
       </c>
       <c r="B32" s="5"/>
-      <c r="C32">
-        <v>1.7647794082264599E-2</v>
-      </c>
-      <c r="D32">
-        <v>1.6929482364304901E-2</v>
-      </c>
       <c r="E32">
-        <v>1.3311257592672E-2</v>
-      </c>
-      <c r="F32" s="10">
+        <v>3.2103137598192298E-2</v>
+      </c>
+      <c r="F32" s="10" t="e">
         <f t="shared" si="2"/>
-        <v>0.78627670393149318</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G32" s="4"/>
-      <c r="H32">
-        <v>1.79734898063151E-2</v>
-      </c>
-      <c r="I32">
-        <v>1.57606335049696E-2</v>
-      </c>
-      <c r="J32">
-        <v>1.41246952576636E-2</v>
-      </c>
-      <c r="K32" s="10">
+      <c r="K32" s="10" t="e">
         <f t="shared" si="3"/>
-        <v>0.89620098412984728</v>
-      </c>
-      <c r="L32" s="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L32" s="10"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>90</v>
+        <v>250</v>
       </c>
       <c r="B33" s="5"/>
-      <c r="C33">
-        <v>2.5054917938694E-2</v>
-      </c>
-      <c r="D33">
-        <v>2.3458449507632401E-2</v>
-      </c>
       <c r="E33">
-        <v>2.05541471998755E-2</v>
-      </c>
-      <c r="F33" s="10">
+        <v>5.1114734736025402E-2</v>
+      </c>
+      <c r="F33" s="10" t="e">
         <f t="shared" si="2"/>
-        <v>0.87619376520123537</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G33" s="4"/>
-      <c r="H33">
-        <v>2.6164917465571601E-2</v>
-      </c>
-      <c r="I33">
-        <v>2.3818302176688601E-2</v>
-      </c>
-      <c r="J33">
-        <v>2.3768164319370701E-2</v>
-      </c>
-      <c r="K33" s="10">
+      <c r="K33" s="10" t="e">
         <f t="shared" si="3"/>
-        <v>0.99789498609321658</v>
-      </c>
-      <c r="L33" s="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L33" s="11"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="4">
-        <v>100</v>
+      <c r="A34">
+        <v>500</v>
       </c>
       <c r="B34" s="5"/>
-      <c r="C34">
-        <v>2.73242514617307E-2</v>
-      </c>
-      <c r="D34">
-        <v>2.5947125661509699E-2</v>
-      </c>
       <c r="E34">
-        <v>2.2524567468256498E-2</v>
-      </c>
-      <c r="F34" s="10">
+        <v>9.1445222619505398E-2</v>
+      </c>
+      <c r="F34" s="10" t="e">
         <f t="shared" si="2"/>
-        <v>0.86809490045634352</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G34" s="4"/>
-      <c r="H34">
-        <v>2.8758676699886999E-2</v>
-      </c>
-      <c r="I34">
-        <v>2.6060698692637999E-2</v>
-      </c>
-      <c r="J34">
-        <v>2.41183055307931E-2</v>
-      </c>
-      <c r="K34" s="10">
+      <c r="K34" s="10" t="e">
         <f t="shared" si="3"/>
-        <v>0.92546657383389286</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L34" s="10"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="4">
-        <v>120</v>
+      <c r="A35">
+        <v>750</v>
       </c>
       <c r="B35" s="5"/>
-      <c r="C35">
-        <v>3.1756367537968302E-2</v>
-      </c>
-      <c r="D35">
-        <v>3.2193504593870201E-2</v>
-      </c>
       <c r="E35">
-        <v>2.5515114756006999E-2</v>
-      </c>
-      <c r="F35" s="10">
+        <v>0.12725844081883</v>
+      </c>
+      <c r="F35" s="10" t="e">
         <f t="shared" si="2"/>
-        <v>0.79255474288640204</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G35" s="4"/>
-      <c r="H35">
-        <v>3.3831181126573399E-2</v>
-      </c>
-      <c r="I35">
-        <v>3.0884672634417399E-2</v>
-      </c>
-      <c r="J35">
-        <v>2.9445668702238598E-2</v>
-      </c>
-      <c r="K35" s="10">
+      <c r="K35" s="10" t="e">
         <f t="shared" si="3"/>
-        <v>0.95340718196328889</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L35" s="11"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>150</v>
+        <v>999.99</v>
       </c>
       <c r="B36" s="5"/>
-      <c r="C36">
-        <v>3.79760832406765E-2</v>
-      </c>
-      <c r="D36">
-        <v>3.6337278414827603E-2</v>
-      </c>
       <c r="E36">
-        <v>3.2903913104897098E-2</v>
-      </c>
-      <c r="F36" s="10">
+        <v>0.157583868759714</v>
+      </c>
+      <c r="F36" s="10" t="e">
         <f t="shared" si="2"/>
-        <v>0.90551396638088599</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G36" s="4"/>
-      <c r="H36">
-        <v>4.0827391559504302E-2</v>
-      </c>
-      <c r="I36">
-        <v>3.8123585674305099E-2</v>
-      </c>
-      <c r="J36">
-        <v>3.6179164073167201E-2</v>
-      </c>
-      <c r="K36" s="10">
+      <c r="K36" s="10" t="e">
         <f t="shared" si="3"/>
-        <v>0.94899688560909901</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L36" s="10"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="4">
-        <v>250</v>
-      </c>
-      <c r="B37" s="5"/>
-      <c r="C37">
-        <v>5.6477544791410803E-2</v>
-      </c>
-      <c r="D37">
-        <v>5.5465836690505303E-2</v>
-      </c>
-      <c r="E37">
-        <v>5.1493175994203999E-2</v>
-      </c>
-      <c r="F37" s="10">
-        <f t="shared" si="2"/>
-        <v>0.92837643974491146</v>
-      </c>
-      <c r="G37" s="4"/>
-      <c r="H37">
-        <v>6.2587066941841005E-2</v>
-      </c>
-      <c r="I37">
-        <v>5.8814448863946898E-2</v>
-      </c>
-      <c r="J37">
-        <v>5.6605063359839898E-2</v>
-      </c>
-      <c r="K37" s="10">
-        <f t="shared" si="3"/>
-        <v>0.9624346474925255</v>
-      </c>
-      <c r="L37" s="11"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38">
-        <v>500</v>
-      </c>
-      <c r="B38" s="5"/>
-      <c r="C38">
-        <v>9.6749839749360703E-2</v>
-      </c>
-      <c r="D38">
-        <v>9.2698744321603202E-2</v>
-      </c>
-      <c r="E38">
-        <v>8.6940034618715994E-2</v>
-      </c>
-      <c r="F38" s="10">
-        <f t="shared" si="2"/>
-        <v>0.93787715524054671</v>
-      </c>
-      <c r="G38" s="4"/>
-      <c r="H38">
-        <v>0.10941310652236901</v>
-      </c>
-      <c r="I38">
-        <v>0.101328636998795</v>
-      </c>
-      <c r="J38">
-        <v>0.103511880070482</v>
-      </c>
-      <c r="K38" s="10">
-        <f t="shared" si="3"/>
-        <v>1.0215461604572156</v>
-      </c>
-      <c r="L38" s="10"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="4">
-        <v>750</v>
-      </c>
-      <c r="B39" s="5"/>
-      <c r="C39">
-        <v>0.12913289428404701</v>
-      </c>
-      <c r="D39">
-        <v>0.12658460512460301</v>
-      </c>
-      <c r="E39">
-        <v>0.128790466427847</v>
-      </c>
-      <c r="F39" s="10">
-        <f t="shared" si="2"/>
-        <v>1.0174259839976012</v>
-      </c>
-      <c r="G39" s="4"/>
-      <c r="H39">
-        <v>0.14632252761592299</v>
-      </c>
-      <c r="I39">
-        <v>0.13858937862319001</v>
-      </c>
-      <c r="J39">
-        <v>0.149026761504226</v>
-      </c>
-      <c r="K39" s="10">
-        <f t="shared" si="3"/>
-        <v>1.0753115641669349</v>
-      </c>
-      <c r="L39" s="11"/>
-    </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40">
-        <v>1000</v>
-      </c>
-      <c r="B40" s="5"/>
-      <c r="C40">
-        <v>0.157828985100924</v>
-      </c>
-      <c r="D40">
-        <v>0.15157133316674601</v>
-      </c>
-      <c r="E40">
-        <v>0.15530428148366199</v>
-      </c>
-      <c r="F40" s="10">
-        <f t="shared" si="2"/>
-        <v>1.0246283267351703</v>
-      </c>
-      <c r="G40" s="4"/>
-      <c r="H40">
-        <v>0.178362496787381</v>
-      </c>
-      <c r="I40">
-        <v>0.17072801306535401</v>
-      </c>
-      <c r="J40">
-        <v>0.17116297500401301</v>
-      </c>
-      <c r="K40" s="10">
-        <f t="shared" si="3"/>
-        <v>1.0025476893384362</v>
-      </c>
-      <c r="L40" s="10"/>
+      <c r="C40" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C41" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D41" s="14"/>
+      <c r="E41" s="15"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42" s="3"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="3"/>
+      <c r="H42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I42" s="3"/>
+      <c r="J42" s="9"/>
+      <c r="K42" s="9"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="8"/>
+      <c r="H43" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="J43" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C44" s="1" t="s">
-        <v>9</v>
+      <c r="A44">
+        <v>0.1</v>
+      </c>
+      <c r="B44" s="5"/>
+      <c r="C44">
+        <v>1.38755773111088</v>
+      </c>
+      <c r="D44">
+        <v>1.33146077610654</v>
+      </c>
+      <c r="E44">
+        <v>1.3294682945082299</v>
+      </c>
+      <c r="F44" s="10">
+        <f>E44/D44</f>
+        <v>0.9985035371420129</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="I44">
+        <v>1.33422182541257</v>
+      </c>
+      <c r="J44">
+        <v>1.3288821396550801</v>
+      </c>
+      <c r="K44" s="10">
+        <f>J44/I44</f>
+        <v>0.99599790255579224</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C45" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="D45" s="14"/>
-      <c r="E45" s="15"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
+      <c r="A45">
+        <v>0.5</v>
+      </c>
+      <c r="B45" s="5"/>
+      <c r="C45">
+        <v>1.38409520401011</v>
+      </c>
+      <c r="D45">
+        <v>1.35765661048369</v>
+      </c>
+      <c r="E45">
+        <v>1.3402135659025001</v>
+      </c>
+      <c r="F45" s="10">
+        <f t="shared" ref="F45:F56" si="4">E45/D45</f>
+        <v>0.98715209394887005</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45">
+        <v>1.3552315082948401</v>
+      </c>
+      <c r="J45">
+        <v>1.34024384554322</v>
+      </c>
+      <c r="K45" s="11">
+        <f t="shared" ref="K45:K54" si="5">J45/I45</f>
+        <v>0.98894088378266998</v>
+      </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D46" s="3"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="3"/>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3"/>
-      <c r="J46" s="9"/>
-      <c r="K46" s="9"/>
+      <c r="A46">
+        <v>1</v>
+      </c>
+      <c r="B46" s="5"/>
+      <c r="C46">
+        <v>1.3811622398640599</v>
+      </c>
+      <c r="D46">
+        <v>1.33903476392587</v>
+      </c>
+      <c r="E46">
+        <v>1.3294539841566</v>
+      </c>
+      <c r="F46" s="10">
+        <f t="shared" si="4"/>
+        <v>0.99284501043036377</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="I46">
+        <v>1.3461367977004299</v>
+      </c>
+      <c r="J46">
+        <v>1.32904261090945</v>
+      </c>
+      <c r="K46" s="10">
+        <f t="shared" si="5"/>
+        <v>0.98730130041747499</v>
+      </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G47" s="8"/>
-      <c r="H47" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I47" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="J47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K47" s="7" t="s">
-        <v>8</v>
+      <c r="A47">
+        <v>10</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47">
+        <v>1.37486493369789</v>
+      </c>
+      <c r="D47">
+        <v>1.31789010731641</v>
+      </c>
+      <c r="E47">
+        <v>1.3448930260504799</v>
+      </c>
+      <c r="F47" s="10">
+        <f t="shared" si="4"/>
+        <v>1.0204895071175968</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47">
+        <v>1.31846450590491</v>
+      </c>
+      <c r="J47">
+        <v>1.3511493506913199</v>
+      </c>
+      <c r="K47" s="11">
+        <f t="shared" si="5"/>
+        <v>1.0247900831914902</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>0.1</v>
+        <v>25</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48">
-        <v>1.38755773111088</v>
+        <v>1.36350384779266</v>
       </c>
       <c r="D48">
-        <v>1.33146077610654</v>
+        <v>1.32036564820574</v>
       </c>
       <c r="E48">
-        <v>1.3294682945082299</v>
+        <v>1.3268512139816999</v>
       </c>
       <c r="F48" s="10">
-        <f>E48/D48</f>
-        <v>0.9985035371420129</v>
+        <f t="shared" si="4"/>
+        <v>1.0049119467662411</v>
       </c>
       <c r="G48" s="4"/>
       <c r="I48">
-        <v>1.33422182541257</v>
+        <v>1.33152629750905</v>
       </c>
       <c r="J48">
-        <v>1.3288821396550801</v>
+        <v>1.33015612015508</v>
       </c>
       <c r="K48" s="10">
-        <f>J48/I48</f>
-        <v>0.99599790255579224</v>
+        <f t="shared" si="5"/>
+        <v>0.99897097236717491</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>0.5</v>
+        <v>50</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49">
-        <v>1.38409520401011</v>
+        <v>1.3571706170428599</v>
       </c>
       <c r="D49">
-        <v>1.35765661048369</v>
+        <v>1.3197738196808499</v>
       </c>
       <c r="E49">
-        <v>1.3402135659025001</v>
+        <v>1.3126564921716899</v>
       </c>
       <c r="F49" s="10">
-        <f t="shared" ref="F49:F60" si="4">E49/D49</f>
-        <v>0.98715209394887005</v>
+        <f t="shared" si="4"/>
+        <v>0.99460716116426584</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
       <c r="I49">
-        <v>1.3552315082948401</v>
+        <v>1.32005527665466</v>
       </c>
       <c r="J49">
-        <v>1.34024384554322</v>
+        <v>1.30244954906179</v>
       </c>
       <c r="K49" s="11">
-        <f t="shared" ref="K49:K58" si="5">J49/I49</f>
-        <v>0.98894088378266998</v>
+        <f t="shared" si="5"/>
+        <v>0.98666288608952257</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50">
-        <v>1.3811622398640599</v>
+        <v>1.35109721915133</v>
       </c>
       <c r="D50">
-        <v>1.33903476392587</v>
+        <v>1.29935652652886</v>
       </c>
       <c r="E50">
-        <v>1.3294539841566</v>
+        <v>1.32473430230751</v>
       </c>
       <c r="F50" s="10">
         <f t="shared" si="4"/>
-        <v>0.99284501043036377</v>
+        <v>1.0195310334465668</v>
       </c>
       <c r="G50" s="4"/>
       <c r="I50">
-        <v>1.3461367977004299</v>
+        <v>1.30908256842566</v>
       </c>
       <c r="J50">
-        <v>1.32904261090945</v>
+        <v>1.30672475018709</v>
       </c>
       <c r="K50" s="10">
         <f t="shared" si="5"/>
-        <v>0.98730130041747499</v>
+        <v>0.99819887736996948</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51">
-        <v>1.37486493369789</v>
+        <v>1.32844051248484</v>
       </c>
       <c r="D51">
-        <v>1.31789010731641</v>
+        <v>1.33910590256307</v>
       </c>
       <c r="E51">
-        <v>1.3448930260504799</v>
+        <v>1.3167897334910501</v>
       </c>
       <c r="F51" s="10">
         <f t="shared" si="4"/>
-        <v>1.0204895071175968</v>
+        <v>0.98333502299608533</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51">
-        <v>1.31846450590491</v>
+        <v>1.3171859836539099</v>
       </c>
       <c r="J51">
-        <v>1.3511493506913199</v>
+        <v>1.31060168409573</v>
       </c>
       <c r="K51" s="11">
         <f t="shared" si="5"/>
-        <v>1.0247900831914902</v>
+        <v>0.99500123775997451</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52">
-        <v>1.36350384779266</v>
+        <v>1.26939305918802</v>
       </c>
       <c r="D52">
-        <v>1.32036564820574</v>
+        <v>1.3346899335651701</v>
       </c>
       <c r="E52">
-        <v>1.3268512139816999</v>
+        <v>1.3164282135057199</v>
       </c>
       <c r="F52" s="10">
         <f t="shared" si="4"/>
-        <v>1.0049119467662411</v>
+        <v>0.98631763108404502</v>
       </c>
       <c r="G52" s="4"/>
       <c r="I52">
-        <v>1.33152629750905</v>
+        <v>1.28924587434467</v>
       </c>
       <c r="J52">
-        <v>1.33015612015508</v>
+        <v>1.3011790803332</v>
       </c>
       <c r="K52" s="10">
         <f t="shared" si="5"/>
-        <v>0.99897097236717491</v>
+        <v>1.0092559582512495</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53">
-        <v>1.3571706170428599</v>
+        <v>1.2146497361047901</v>
       </c>
       <c r="D53">
-        <v>1.3197738196808499</v>
+        <v>1.29678717701069</v>
       </c>
       <c r="E53">
-        <v>1.3126564921716899</v>
+        <v>1.33451901185347</v>
       </c>
       <c r="F53" s="10">
         <f t="shared" si="4"/>
-        <v>0.99460716116426584</v>
+        <v>1.0290963972436542</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53">
-        <v>1.32005527665466</v>
+        <v>1.2845821783281699</v>
       </c>
       <c r="J53">
-        <v>1.30244954906179</v>
+        <v>1.27732476166037</v>
       </c>
       <c r="K53" s="11">
         <f t="shared" si="5"/>
-        <v>0.98666288608952257</v>
+        <v>0.99435036793267273</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54">
-        <v>1.35109721915133</v>
+        <v>1.1436421352186501</v>
       </c>
       <c r="D54">
-        <v>1.29935652652886</v>
+        <v>1.2662694099393199</v>
       </c>
       <c r="E54">
-        <v>1.32473430230751</v>
+        <v>1.2620512370753201</v>
       </c>
       <c r="F54" s="10">
         <f t="shared" si="4"/>
-        <v>1.0195310334465668</v>
+        <v>0.99666881879093805</v>
       </c>
       <c r="G54" s="4"/>
       <c r="I54">
-        <v>1.30908256842566</v>
+        <v>1.2051198250164299</v>
       </c>
       <c r="J54">
-        <v>1.30672475018709</v>
+        <v>1.19710463230099</v>
       </c>
       <c r="K54" s="10">
         <f t="shared" si="5"/>
-        <v>0.99819887736996948</v>
+        <v>0.99334904915755518</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>100</v>
-      </c>
-      <c r="B55" s="5"/>
-      <c r="C55">
-        <v>1.32844051248484</v>
+        <v>750</v>
       </c>
       <c r="D55">
-        <v>1.33910590256307</v>
+        <v>1.23279071771682</v>
       </c>
       <c r="E55">
-        <v>1.3167897334910501</v>
+        <v>1.23649350366719</v>
       </c>
       <c r="F55" s="10">
         <f t="shared" si="4"/>
-        <v>0.98333502299608533</v>
-      </c>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
+        <v>1.0030035803296993</v>
+      </c>
       <c r="I55">
-        <v>1.3171859836539099</v>
+        <v>1.1807532343395699</v>
       </c>
       <c r="J55">
-        <v>1.31060168409573</v>
-      </c>
-      <c r="K55" s="11">
-        <f t="shared" si="5"/>
-        <v>0.99500123775997451</v>
+        <v>1.1563239206929501</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>150</v>
-      </c>
-      <c r="B56" s="5"/>
-      <c r="C56">
-        <v>1.26939305918802</v>
+        <v>999.99</v>
       </c>
       <c r="D56">
-        <v>1.3346899335651701</v>
+        <v>1.1928852496040101</v>
       </c>
       <c r="E56">
-        <v>1.3164282135057199</v>
+        <v>1.2106403902979499</v>
       </c>
       <c r="F56" s="10">
         <f t="shared" si="4"/>
-        <v>0.98631763108404502</v>
-      </c>
-      <c r="G56" s="4"/>
+        <v>1.0148841983751864</v>
+      </c>
       <c r="I56">
-        <v>1.28924587434467</v>
+        <v>1.13357719050286</v>
       </c>
       <c r="J56">
-        <v>1.3011790803332</v>
-      </c>
-      <c r="K56" s="10">
-        <f t="shared" si="5"/>
-        <v>1.0092559582512495</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>250</v>
-      </c>
-      <c r="B57" s="5"/>
-      <c r="C57">
-        <v>1.2146497361047901</v>
-      </c>
-      <c r="D57">
-        <v>1.29678717701069</v>
-      </c>
-      <c r="E57">
-        <v>1.33451901185347</v>
-      </c>
-      <c r="F57" s="10">
-        <f t="shared" si="4"/>
-        <v>1.0290963972436542</v>
-      </c>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57">
-        <v>1.2845821783281699</v>
-      </c>
-      <c r="J57">
-        <v>1.27732476166037</v>
-      </c>
-      <c r="K57" s="11">
-        <f t="shared" si="5"/>
-        <v>0.99435036793267273</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>500</v>
-      </c>
-      <c r="B58" s="5"/>
-      <c r="C58">
-        <v>1.1436421352186501</v>
-      </c>
-      <c r="D58">
-        <v>1.2662694099393199</v>
-      </c>
-      <c r="E58">
-        <v>1.2620512370753201</v>
-      </c>
-      <c r="F58" s="10">
-        <f t="shared" si="4"/>
-        <v>0.99666881879093805</v>
-      </c>
-      <c r="G58" s="4"/>
-      <c r="I58">
-        <v>1.2051198250164299</v>
-      </c>
-      <c r="J58">
-        <v>1.19710463230099</v>
-      </c>
-      <c r="K58" s="10">
-        <f t="shared" si="5"/>
-        <v>0.99334904915755518</v>
+        <v>1.1342010761596699</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>750</v>
-      </c>
-      <c r="D59">
-        <v>1.23279071771682</v>
-      </c>
-      <c r="E59">
-        <v>1.23649350366719</v>
-      </c>
-      <c r="F59" s="10">
-        <f t="shared" si="4"/>
-        <v>1.0030035803296993</v>
-      </c>
-      <c r="I59">
-        <v>1.1807532343395699</v>
-      </c>
-      <c r="J59">
-        <v>1.1563239206929501</v>
-      </c>
+      <c r="C59" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D59" s="12"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="13"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>999.99</v>
-      </c>
-      <c r="D60">
-        <v>1.1928852496040101</v>
-      </c>
-      <c r="E60">
-        <v>1.2106403902979499</v>
-      </c>
-      <c r="F60" s="10">
-        <f t="shared" si="4"/>
-        <v>1.0148841983751864</v>
-      </c>
-      <c r="I60">
-        <v>1.13357719050286</v>
-      </c>
-      <c r="J60">
-        <v>1.1342010761596699</v>
+      <c r="C60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D60" s="3"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="3"/>
+      <c r="H60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I60" s="3"/>
+      <c r="J60" s="9"/>
+      <c r="K60" s="9"/>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A61" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B61" s="6"/>
+      <c r="C61" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G61" s="8"/>
+      <c r="H61" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="J61" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K61" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>0.1</v>
+      </c>
+      <c r="B62" s="5"/>
+      <c r="C62" s="2">
+        <v>2.0906018648200899E-5</v>
+      </c>
+      <c r="D62" s="2">
+        <v>1.9785240862768899E-5</v>
+      </c>
+      <c r="E62" s="2">
+        <v>1.9417624590728801E-5</v>
+      </c>
+      <c r="F62" s="10">
+        <f>E62/D62</f>
+        <v>0.98141967163352228</v>
+      </c>
+      <c r="G62" s="4"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2">
+        <v>2.44555572729164E-5</v>
+      </c>
+      <c r="J62" s="2">
+        <v>2.3173152783100001E-5</v>
+      </c>
+      <c r="K62" s="10">
+        <f>J62/I62</f>
+        <v>0.94756183735642718</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C63" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D63" s="12"/>
-      <c r="E63" s="13"/>
-      <c r="F63" s="13"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
-      <c r="K63" s="2"/>
+      <c r="A63">
+        <v>0.5</v>
+      </c>
+      <c r="B63" s="5"/>
+      <c r="C63" s="2">
+        <v>3.1327203465188001E-3</v>
+      </c>
+      <c r="D63">
+        <v>1.02051178015395E-4</v>
+      </c>
+      <c r="E63" s="2">
+        <v>9.4705678455829002E-5</v>
+      </c>
+      <c r="F63" s="10">
+        <f t="shared" ref="F63:F74" si="6">E63/D63</f>
+        <v>0.92802141334950694</v>
+      </c>
+      <c r="G63" s="4"/>
+      <c r="I63">
+        <v>1.237590596311E-4</v>
+      </c>
+      <c r="J63">
+        <v>1.2781285534871299E-4</v>
+      </c>
+      <c r="K63" s="11">
+        <f t="shared" ref="K63:K74" si="7">J63/I63</f>
+        <v>1.0327555471873857</v>
+      </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C64" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D64" s="3"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="3"/>
-      <c r="H64" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I64" s="3"/>
-      <c r="J64" s="9"/>
-      <c r="K64" s="9"/>
+      <c r="A64">
+        <v>1</v>
+      </c>
+      <c r="B64" s="5"/>
+      <c r="C64" s="2">
+        <v>6.2691724987101998E-3</v>
+      </c>
+      <c r="D64">
+        <v>2.0004896550590901E-4</v>
+      </c>
+      <c r="E64">
+        <v>2.0519183351723301E-4</v>
+      </c>
+      <c r="F64" s="10">
+        <f t="shared" si="6"/>
+        <v>1.0257080460192236</v>
+      </c>
+      <c r="G64" s="4"/>
+      <c r="I64">
+        <v>2.47009346021372E-4</v>
+      </c>
+      <c r="J64">
+        <v>2.5056736662623701E-4</v>
+      </c>
+      <c r="K64" s="10">
+        <f t="shared" si="7"/>
+        <v>1.0144043966844767</v>
+      </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A65" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E65" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G65" s="8"/>
-      <c r="H65" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I65" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="J65" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K65" s="7" t="s">
-        <v>8</v>
+      <c r="A65">
+        <v>10</v>
+      </c>
+      <c r="B65" s="5"/>
+      <c r="C65" s="2">
+        <v>1.2558983712415E-2</v>
+      </c>
+      <c r="D65">
+        <v>1.9727739159685499E-3</v>
+      </c>
+      <c r="E65">
+        <v>2.1002402963605799E-3</v>
+      </c>
+      <c r="F65" s="10">
+        <f t="shared" si="6"/>
+        <v>1.0646127665011473</v>
+      </c>
+      <c r="G65" s="4"/>
+      <c r="I65">
+        <v>2.41443999850058E-3</v>
+      </c>
+      <c r="J65">
+        <v>2.5624129143282902E-3</v>
+      </c>
+      <c r="K65" s="11">
+        <f t="shared" si="7"/>
+        <v>1.0612866403470804</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>0.1</v>
+        <v>25</v>
       </c>
       <c r="B66" s="5"/>
       <c r="C66" s="2">
-        <v>2.0906018648200899E-5</v>
-      </c>
-      <c r="D66" s="2">
-        <v>1.9785240862768899E-5</v>
-      </c>
-      <c r="E66" s="2">
-        <v>1.9417624590728801E-5</v>
+        <v>1.8782496824776201E-2</v>
+      </c>
+      <c r="D66">
+        <v>4.9269907229743297E-3</v>
+      </c>
+      <c r="E66">
+        <v>5.2981099306138504E-3</v>
       </c>
       <c r="F66" s="10">
-        <f>E66/D66</f>
-        <v>0.98141967163352228</v>
+        <f t="shared" si="6"/>
+        <v>1.0753237074121145</v>
       </c>
       <c r="G66" s="4"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2">
-        <v>2.44555572729164E-5</v>
-      </c>
-      <c r="J66" s="2">
-        <v>2.3173152783100001E-5</v>
+      <c r="I66">
+        <v>6.11270182240103E-3</v>
+      </c>
+      <c r="J66">
+        <v>6.4145321839513504E-3</v>
       </c>
       <c r="K66" s="10">
-        <f>J66/I66</f>
-        <v>0.94756183735642718</v>
+        <f t="shared" si="7"/>
+        <v>1.0493775699060295</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>0.5</v>
+        <v>50</v>
       </c>
       <c r="B67" s="5"/>
       <c r="C67" s="2">
-        <v>3.1327203465188001E-3</v>
+        <v>2.51046376970986E-2</v>
       </c>
       <c r="D67">
-        <v>1.02051178015395E-4</v>
-      </c>
-      <c r="E67" s="2">
-        <v>9.4705678455829002E-5</v>
+        <v>9.7820010092556295E-3</v>
+      </c>
+      <c r="E67">
+        <v>1.0195154351149101E-2</v>
       </c>
       <c r="F67" s="10">
-        <f t="shared" ref="F67:F78" si="6">E67/D67</f>
-        <v>0.92802141334950694</v>
+        <f t="shared" si="6"/>
+        <v>1.0422360763919929</v>
       </c>
       <c r="G67" s="4"/>
       <c r="I67">
-        <v>1.237590596311E-4</v>
+        <v>1.20970549355645E-2</v>
       </c>
       <c r="J67">
-        <v>1.2781285534871299E-4</v>
+        <v>1.24175942421624E-2</v>
       </c>
       <c r="K67" s="11">
-        <f t="shared" ref="K67:K78" si="7">J67/I67</f>
-        <v>1.0327555471873857</v>
+        <f t="shared" si="7"/>
+        <v>1.0264973010625533</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="B68" s="5"/>
       <c r="C68" s="2">
-        <v>6.2691724987101998E-3</v>
+        <v>3.1476119846668899E-2</v>
       </c>
       <c r="D68">
-        <v>2.0004896550590901E-4</v>
+        <v>1.43763436727791E-2</v>
       </c>
       <c r="E68">
-        <v>2.0519183351723301E-4</v>
+        <v>1.5782984835099299E-2</v>
       </c>
       <c r="F68" s="10">
         <f t="shared" si="6"/>
-        <v>1.0257080460192236</v>
+        <v>1.0978441524727602</v>
       </c>
       <c r="G68" s="4"/>
       <c r="I68">
-        <v>2.47009346021372E-4</v>
+        <v>1.8002551123509802E-2</v>
       </c>
       <c r="J68">
-        <v>2.5056736662623701E-4</v>
+        <v>1.8976376994297401E-2</v>
       </c>
       <c r="K68" s="10">
         <f t="shared" si="7"/>
-        <v>1.0144043966844767</v>
+        <v>1.0540937706054263</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="2">
-        <v>1.2558983712415E-2</v>
+        <v>5.2878603388737497E-2</v>
       </c>
       <c r="D69">
-        <v>1.9727739159685499E-3</v>
+        <v>2.00458898906196E-2</v>
       </c>
       <c r="E69">
-        <v>2.1002402963605799E-3</v>
+        <v>2.0804120655568799E-2</v>
       </c>
       <c r="F69" s="10">
         <f t="shared" si="6"/>
-        <v>1.0646127665011473</v>
+        <v>1.0378247495664441</v>
       </c>
       <c r="G69" s="4"/>
       <c r="I69">
-        <v>2.41443999850058E-3</v>
+        <v>2.4309982506840501E-2</v>
       </c>
       <c r="J69">
-        <v>2.5624129143282902E-3</v>
+        <v>2.56065505285916E-2</v>
       </c>
       <c r="K69" s="11">
         <f t="shared" si="7"/>
-        <v>1.0612866403470804</v>
+        <v>1.0533347986320543</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="B70" s="5"/>
       <c r="C70" s="2">
-        <v>1.8782496824776201E-2</v>
+        <v>0.107716927588289</v>
       </c>
       <c r="D70">
-        <v>4.9269907229743297E-3</v>
+        <v>3.0432830381329601E-2</v>
       </c>
       <c r="E70">
-        <v>5.2981099306138504E-3</v>
+        <v>3.14434702136525E-2</v>
       </c>
       <c r="F70" s="10">
         <f t="shared" si="6"/>
-        <v>1.0753237074121145</v>
+        <v>1.0332088675177227</v>
       </c>
       <c r="G70" s="4"/>
       <c r="I70">
-        <v>6.11270182240103E-3</v>
+        <v>3.5308084946377202E-2</v>
       </c>
       <c r="J70">
-        <v>6.4145321839513504E-3</v>
+        <v>3.7911161854217702E-2</v>
       </c>
       <c r="K70" s="10">
         <f t="shared" si="7"/>
-        <v>1.0493775699060295</v>
+        <v>1.0737246699104135</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="B71" s="5"/>
       <c r="C71" s="2">
-        <v>2.51046376970986E-2</v>
+        <v>0.16515386445267599</v>
       </c>
       <c r="D71">
-        <v>9.7820010092556295E-3</v>
+        <v>4.89210306757277E-2</v>
       </c>
       <c r="E71">
-        <v>1.0195154351149101E-2</v>
+        <v>5.3975920537313898E-2</v>
       </c>
       <c r="F71" s="10">
         <f t="shared" si="6"/>
-        <v>1.0422360763919929</v>
+        <v>1.1033275421994369</v>
       </c>
       <c r="G71" s="4"/>
       <c r="I71">
-        <v>1.20970549355645E-2</v>
+        <v>5.8808790512075798E-2</v>
       </c>
       <c r="J71">
-        <v>1.24175942421624E-2</v>
+        <v>6.2265324575410202E-2</v>
       </c>
       <c r="K71" s="11">
         <f t="shared" si="7"/>
-        <v>1.0264973010625533</v>
+        <v>1.0587758060187387</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="B72" s="5"/>
       <c r="C72" s="2">
-        <v>3.1476119846668899E-2</v>
+        <v>0.22114304090137801</v>
       </c>
       <c r="D72">
-        <v>1.43763436727791E-2</v>
+        <v>9.6226590649767796E-2</v>
       </c>
       <c r="E72">
-        <v>1.5782984835099299E-2</v>
+        <v>0.10212774105006001</v>
       </c>
       <c r="F72" s="10">
         <f t="shared" si="6"/>
-        <v>1.0978441524727602</v>
+        <v>1.0613255687481478</v>
       </c>
       <c r="G72" s="4"/>
       <c r="I72">
-        <v>1.8002551123509802E-2</v>
+        <v>0.11146020972599301</v>
       </c>
       <c r="J72">
-        <v>1.8976376994297401E-2</v>
+        <v>0.118001707852343</v>
       </c>
       <c r="K72" s="10">
         <f t="shared" si="7"/>
-        <v>1.0540937706054263</v>
+        <v>1.0586890886212328</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>100</v>
-      </c>
-      <c r="B73" s="5"/>
-      <c r="C73" s="2">
-        <v>5.2878603388737497E-2</v>
+        <v>750</v>
       </c>
       <c r="D73">
-        <v>2.00458898906196E-2</v>
+        <v>0.140294088260282</v>
       </c>
       <c r="E73">
-        <v>2.0804120655568799E-2</v>
+        <v>0.15225875418305601</v>
       </c>
       <c r="F73" s="10">
         <f t="shared" si="6"/>
-        <v>1.0378247495664441</v>
-      </c>
-      <c r="G73" s="4"/>
+        <v>1.0852827519045309</v>
+      </c>
       <c r="I73">
-        <v>2.4309982506840501E-2</v>
+        <v>0.164782092113922</v>
       </c>
       <c r="J73">
-        <v>2.56065505285916E-2</v>
+        <v>0.171436913407884</v>
       </c>
       <c r="K73" s="11">
         <f t="shared" si="7"/>
-        <v>1.0533347986320543</v>
+        <v>1.0403855856458066</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>150</v>
-      </c>
-      <c r="B74" s="5"/>
-      <c r="C74" s="2">
-        <v>0.107716927588289</v>
+        <v>999.99</v>
       </c>
       <c r="D74">
-        <v>3.0432830381329601E-2</v>
+        <v>0.181401571560247</v>
       </c>
       <c r="E74">
-        <v>3.14434702136525E-2</v>
+        <v>0.20058148390920799</v>
       </c>
       <c r="F74" s="10">
         <f t="shared" si="6"/>
-        <v>1.0332088675177227</v>
-      </c>
-      <c r="G74" s="4"/>
+        <v>1.1057317871283765</v>
+      </c>
       <c r="I74">
-        <v>3.5308084946377202E-2</v>
+        <v>0.211482254080264</v>
       </c>
       <c r="J74">
-        <v>3.7911161854217702E-2</v>
+        <v>0.22688990016688301</v>
       </c>
       <c r="K74" s="10">
         <f t="shared" si="7"/>
-        <v>1.0737246699104135</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A75">
-        <v>250</v>
-      </c>
-      <c r="B75" s="5"/>
-      <c r="C75" s="2">
-        <v>0.16515386445267599</v>
-      </c>
-      <c r="D75">
-        <v>4.89210306757277E-2</v>
-      </c>
-      <c r="E75">
-        <v>5.3975920537313898E-2</v>
-      </c>
-      <c r="F75" s="10">
-        <f t="shared" si="6"/>
-        <v>1.1033275421994369</v>
-      </c>
-      <c r="G75" s="4"/>
-      <c r="I75">
-        <v>5.8808790512075798E-2</v>
-      </c>
-      <c r="J75">
-        <v>6.2265324575410202E-2</v>
-      </c>
-      <c r="K75" s="11">
-        <f t="shared" si="7"/>
-        <v>1.0587758060187387</v>
+        <v>1.0728555034256981</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A76">
-        <v>500</v>
-      </c>
-      <c r="B76" s="5"/>
-      <c r="C76" s="2">
-        <v>0.22114304090137801</v>
-      </c>
-      <c r="D76">
-        <v>9.6226590649767796E-2</v>
-      </c>
-      <c r="E76">
-        <v>0.10212774105006001</v>
-      </c>
-      <c r="F76" s="10">
-        <f t="shared" si="6"/>
-        <v>1.0613255687481478</v>
-      </c>
-      <c r="G76" s="4"/>
-      <c r="I76">
-        <v>0.11146020972599301</v>
-      </c>
-      <c r="J76">
-        <v>0.118001707852343</v>
-      </c>
-      <c r="K76" s="10">
-        <f t="shared" si="7"/>
-        <v>1.0586890886212328</v>
-      </c>
+      <c r="C76" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D76" s="12"/>
+      <c r="E76" s="13"/>
+      <c r="F76" s="13"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2"/>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A77">
-        <v>750</v>
-      </c>
-      <c r="D77">
-        <v>0.140294088260282</v>
-      </c>
-      <c r="E77">
-        <v>0.15225875418305601</v>
-      </c>
-      <c r="F77" s="10">
-        <f t="shared" si="6"/>
-        <v>1.0852827519045309</v>
-      </c>
-      <c r="I77">
-        <v>0.164782092113922</v>
-      </c>
-      <c r="J77">
-        <v>0.171436913407884</v>
-      </c>
-      <c r="K77" s="11">
-        <f t="shared" si="7"/>
-        <v>1.0403855856458066</v>
-      </c>
+      <c r="C77" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D77" s="3"/>
+      <c r="E77" s="9"/>
+      <c r="F77" s="3"/>
+      <c r="H77" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I77" s="3"/>
+      <c r="J77" s="9"/>
+      <c r="K77" s="9"/>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A78">
-        <v>999.99</v>
-      </c>
-      <c r="D78">
-        <v>0.181401571560247</v>
-      </c>
-      <c r="E78">
-        <v>0.20058148390920799</v>
-      </c>
-      <c r="F78" s="10">
-        <f t="shared" si="6"/>
-        <v>1.1057317871283765</v>
-      </c>
-      <c r="I78">
-        <v>0.211482254080264</v>
-      </c>
-      <c r="J78">
-        <v>0.22688990016688301</v>
-      </c>
-      <c r="K78" s="10">
-        <f t="shared" si="7"/>
-        <v>1.0728555034256981</v>
+      <c r="A78" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B78" s="6"/>
+      <c r="C78" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G78" s="8"/>
+      <c r="H78" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I78" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="J78" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K78" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>0.1</v>
+      </c>
+      <c r="B79" s="5"/>
+      <c r="C79" s="2">
+        <v>2.0906018648200899E-5</v>
+      </c>
+      <c r="D79" s="2">
+        <v>2.8143173972499801E-7</v>
+      </c>
+      <c r="E79" s="2">
+        <v>1.46150091119403E-6</v>
+      </c>
+      <c r="F79" s="10">
+        <f t="shared" ref="F79:F90" si="8">F62*((E79/E62)^2 +(D79/D62)^2)^0.5</f>
+        <v>7.5175789820697683E-2</v>
+      </c>
+      <c r="G79" s="4"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="2">
+        <v>2.4434932696069799E-5</v>
+      </c>
+      <c r="J79" s="2">
+        <v>2.5518609602937599E-5</v>
+      </c>
+      <c r="K79" s="10">
+        <f>J79/I79</f>
+        <v>1.0443494942403546</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C80" s="12" t="s">
+      <c r="A80">
+        <v>0.5</v>
+      </c>
+      <c r="B80" s="5"/>
+      <c r="C80" s="2">
+        <v>3.1327203465188001E-3</v>
+      </c>
+      <c r="D80" s="2">
+        <v>1.5222069872849199E-6</v>
+      </c>
+      <c r="E80" s="2">
+        <v>3.7622530224669299E-6</v>
+      </c>
+      <c r="F80" s="10">
+        <f t="shared" si="8"/>
+        <v>3.9379446327356661E-2</v>
+      </c>
+      <c r="G80" s="4"/>
+      <c r="I80">
+        <v>3.6561489620800698E-3</v>
+      </c>
+      <c r="J80">
+        <v>3.8583728177792702E-3</v>
+      </c>
+      <c r="K80" s="11">
+        <f t="shared" ref="K80:K89" si="9">J80/I80</f>
+        <v>1.0553106172085915</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>1</v>
+      </c>
+      <c r="B81" s="5"/>
+      <c r="C81" s="2">
+        <v>6.2691724987101998E-3</v>
+      </c>
+      <c r="D81" s="2">
+        <v>2.33807312394273E-6</v>
+      </c>
+      <c r="E81" s="2">
+        <v>6.5127278910264096E-6</v>
+      </c>
+      <c r="F81" s="10">
+        <f t="shared" si="8"/>
+        <v>3.4692692812303069E-2</v>
+      </c>
+      <c r="G81" s="4"/>
+      <c r="I81">
+        <v>7.3167786817070497E-3</v>
+      </c>
+      <c r="J81">
+        <v>7.7206053021012903E-3</v>
+      </c>
+      <c r="K81" s="10">
+        <f t="shared" si="9"/>
+        <v>1.0551918594181156</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A82">
         <v>10</v>
       </c>
-      <c r="D80" s="12"/>
-      <c r="E80" s="13"/>
-      <c r="F80" s="13"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D81" s="3"/>
-      <c r="E81" s="9"/>
-      <c r="F81" s="3"/>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3"/>
-      <c r="J81" s="9"/>
-      <c r="K81" s="9"/>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A82" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B82" s="6"/>
-      <c r="C82" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E82" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F82" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G82" s="8"/>
-      <c r="H82" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I82" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="J82" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K82" s="7" t="s">
-        <v>8</v>
+      <c r="B82" s="5"/>
+      <c r="C82" s="2">
+        <v>1.2558983712415E-2</v>
+      </c>
+      <c r="D82" s="2">
+        <v>2.7701090496064399E-5</v>
+      </c>
+      <c r="E82" s="2">
+        <v>3.8011060965548303E-5</v>
+      </c>
+      <c r="F82" s="10">
+        <f t="shared" si="8"/>
+        <v>2.4386896067040687E-2</v>
+      </c>
+      <c r="G82" s="4"/>
+      <c r="I82">
+        <v>1.4655010559957399E-2</v>
+      </c>
+      <c r="J82">
+        <v>1.54708347850845E-2</v>
+      </c>
+      <c r="K82" s="11">
+        <f t="shared" si="9"/>
+        <v>1.0556686207621178</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>0.1</v>
+        <v>25</v>
       </c>
       <c r="B83" s="5"/>
       <c r="C83" s="2">
-        <v>2.0906018648200899E-5</v>
+        <v>1.8782496824776201E-2</v>
       </c>
       <c r="D83" s="2">
-        <v>2.8143173972499801E-7</v>
+        <v>8.0985715172972504E-5</v>
       </c>
       <c r="E83" s="2">
-        <v>1.46150091119403E-6</v>
+        <v>8.2936422592517207E-5</v>
       </c>
       <c r="F83" s="10">
-        <f t="shared" ref="F83:F94" si="8">F66*((E83/E66)^2 +(D83/D66)^2)^0.5</f>
-        <v>7.5175789820697683E-2</v>
+        <f t="shared" si="8"/>
+        <v>2.4408348565916203E-2</v>
       </c>
       <c r="G83" s="4"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2">
-        <v>2.4434932696069799E-5</v>
-      </c>
-      <c r="J83" s="2">
-        <v>2.5518609602937599E-5</v>
+      <c r="I83">
+        <v>2.20520227131588E-2</v>
+      </c>
+      <c r="J83">
+        <v>2.3279563002525702E-2</v>
       </c>
       <c r="K83" s="10">
-        <f>J83/I83</f>
-        <v>1.0443494942403546</v>
+        <f t="shared" si="9"/>
+        <v>1.0556656550437167</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>0.5</v>
+        <v>50</v>
       </c>
       <c r="B84" s="5"/>
       <c r="C84" s="2">
-        <v>3.1327203465188001E-3</v>
-      </c>
-      <c r="D84" s="2">
-        <v>1.5222069872849199E-6</v>
-      </c>
-      <c r="E84" s="2">
-        <v>3.7622530224669299E-6</v>
+        <v>2.51046376970986E-2</v>
+      </c>
+      <c r="D84">
+        <v>1.14857385321631E-4</v>
+      </c>
+      <c r="E84">
+        <v>1.40546480514001E-4</v>
       </c>
       <c r="F84" s="10">
         <f t="shared" si="8"/>
-        <v>3.9379446327356661E-2</v>
+        <v>1.8873133491714433E-2</v>
       </c>
       <c r="G84" s="4"/>
       <c r="I84">
-        <v>3.6561489620800698E-3</v>
+        <v>2.9379142051595902E-2</v>
       </c>
       <c r="J84">
-        <v>3.8583728177792702E-3</v>
+        <v>3.0966693098777899E-2</v>
       </c>
       <c r="K84" s="11">
-        <f t="shared" ref="K84:K93" si="9">J84/I84</f>
-        <v>1.0553106172085915</v>
+        <f t="shared" si="9"/>
+        <v>1.0540366714723639</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="B85" s="5"/>
       <c r="C85" s="2">
-        <v>6.2691724987101998E-3</v>
-      </c>
-      <c r="D85" s="2">
-        <v>2.33807312394273E-6</v>
-      </c>
-      <c r="E85" s="2">
-        <v>6.5127278910264096E-6</v>
+        <v>3.1476119846668899E-2</v>
+      </c>
+      <c r="D85">
+        <v>1.6692001786006801E-4</v>
+      </c>
+      <c r="E85">
+        <v>2.2355768083561999E-4</v>
       </c>
       <c r="F85" s="10">
         <f t="shared" si="8"/>
-        <v>3.4692692812303069E-2</v>
+        <v>2.0107088599017175E-2</v>
       </c>
       <c r="G85" s="4"/>
       <c r="I85">
-        <v>7.3167786817070497E-3</v>
+        <v>3.6804448452257998E-2</v>
       </c>
       <c r="J85">
-        <v>7.7206053021012903E-3</v>
+        <v>3.8844686371276298E-2</v>
       </c>
       <c r="K85" s="10">
         <f t="shared" si="9"/>
-        <v>1.0551918594181156</v>
+        <v>1.0554345467685748</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="B86" s="5"/>
       <c r="C86" s="2">
-        <v>1.2558983712415E-2</v>
-      </c>
-      <c r="D86" s="2">
-        <v>2.7701090496064399E-5</v>
-      </c>
-      <c r="E86" s="2">
-        <v>3.8011060965548303E-5</v>
+        <v>5.2878603388737497E-2</v>
+      </c>
+      <c r="D86">
+        <v>2.77931449091848E-4</v>
+      </c>
+      <c r="E86">
+        <v>2.1739476286188801E-4</v>
       </c>
       <c r="F86" s="10">
         <f t="shared" si="8"/>
-        <v>2.4386896067040687E-2</v>
+        <v>1.8018315350781095E-2</v>
       </c>
       <c r="G86" s="4"/>
       <c r="I86">
-        <v>1.4655010559957399E-2</v>
+        <v>6.1567552933483601E-2</v>
       </c>
       <c r="J86">
-        <v>1.54708347850845E-2</v>
+        <v>6.4958585716827305E-2</v>
       </c>
       <c r="K86" s="11">
         <f t="shared" si="9"/>
-        <v>1.0556686207621178</v>
+        <v>1.0550782453057264</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="B87" s="5"/>
       <c r="C87" s="2">
-        <v>1.8782496824776201E-2</v>
-      </c>
-      <c r="D87" s="2">
-        <v>8.0985715172972504E-5</v>
-      </c>
-      <c r="E87" s="2">
-        <v>8.2936422592517207E-5</v>
+        <v>0.107716927588289</v>
+      </c>
+      <c r="D87">
+        <v>3.3888866496247497E-4</v>
+      </c>
+      <c r="E87">
+        <v>4.2099807481717899E-4</v>
       </c>
       <c r="F87" s="10">
         <f t="shared" si="8"/>
-        <v>2.4408348565916203E-2</v>
+        <v>1.7992932963347683E-2</v>
       </c>
       <c r="G87" s="4"/>
       <c r="I87">
-        <v>2.20520227131588E-2</v>
+        <v>0.124585487877085</v>
       </c>
       <c r="J87">
-        <v>2.3279563002525702E-2</v>
+        <v>0.13088073929294</v>
       </c>
       <c r="K87" s="10">
         <f t="shared" si="9"/>
-        <v>1.0556656550437167</v>
+        <v>1.0505295722890764</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="B88" s="5"/>
       <c r="C88" s="2">
-        <v>2.51046376970986E-2</v>
+        <v>0.16515386445267599</v>
       </c>
       <c r="D88">
-        <v>1.14857385321631E-4</v>
+        <v>6.0844630496931901E-4</v>
       </c>
       <c r="E88">
-        <v>1.40546480514001E-4</v>
+        <v>7.1735921087181002E-4</v>
       </c>
       <c r="F88" s="10">
         <f t="shared" si="8"/>
-        <v>1.8873133491714433E-2</v>
+        <v>2.0082997872230529E-2</v>
       </c>
       <c r="G88" s="4"/>
       <c r="I88">
-        <v>2.9379142051595902E-2</v>
+        <v>0.188315720076114</v>
       </c>
       <c r="J88">
-        <v>3.0966693098777899E-2</v>
+        <v>0.19671890522285099</v>
       </c>
       <c r="K88" s="11">
         <f t="shared" si="9"/>
-        <v>1.0540366714723639</v>
+        <v>1.0446228554012409</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="B89" s="5"/>
       <c r="C89" s="2">
-        <v>3.1476119846668899E-2</v>
+        <v>0.22114304090137801</v>
       </c>
       <c r="D89">
-        <v>1.6692001786006801E-4</v>
+        <v>1.3901143553867799E-3</v>
       </c>
       <c r="E89">
-        <v>2.2355768083561999E-4</v>
+        <v>1.45703989958587E-3</v>
       </c>
       <c r="F89" s="10">
         <f t="shared" si="8"/>
-        <v>2.0107088599017175E-2</v>
+        <v>2.1548753693625213E-2</v>
       </c>
       <c r="G89" s="4"/>
       <c r="I89">
-        <v>3.6804448452257998E-2</v>
+        <v>0.25212873564071397</v>
       </c>
       <c r="J89">
-        <v>3.8844686371276298E-2</v>
+        <v>0.26159631710660702</v>
       </c>
       <c r="K89" s="10">
         <f t="shared" si="9"/>
-        <v>1.0554345467685748</v>
+        <v>1.0375505847908761</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>100</v>
-      </c>
-      <c r="B90" s="5"/>
-      <c r="C90" s="2">
-        <v>5.2878603388737497E-2</v>
+        <v>750</v>
       </c>
       <c r="D90">
-        <v>2.77931449091848E-4</v>
+        <v>1.59024586083695E-3</v>
       </c>
       <c r="E90">
-        <v>2.1739476286188801E-4</v>
+        <v>1.88927153592098E-3</v>
       </c>
       <c r="F90" s="10">
         <f t="shared" si="8"/>
-        <v>1.8018315350781095E-2</v>
-      </c>
-      <c r="G90" s="4"/>
-      <c r="I90">
-        <v>6.1567552933483601E-2</v>
-      </c>
-      <c r="J90">
-        <v>6.4958585716827305E-2</v>
-      </c>
-      <c r="K90" s="11">
-        <f t="shared" si="9"/>
-        <v>1.0550782453057264</v>
+        <v>1.8239532257896197E-2</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>150</v>
-      </c>
-      <c r="B91" s="5"/>
-      <c r="C91" s="2">
-        <v>0.107716927588289</v>
+        <v>999.99</v>
       </c>
       <c r="D91">
-        <v>3.3888866496247497E-4</v>
+        <v>2.0916951916344802E-3</v>
       </c>
       <c r="E91">
-        <v>4.2099807481717899E-4</v>
+        <v>2.14759074882869E-3</v>
       </c>
       <c r="F91" s="10">
-        <f t="shared" si="8"/>
-        <v>1.7992932963347683E-2</v>
-      </c>
-      <c r="G91" s="4"/>
-      <c r="I91">
-        <v>0.124585487877085</v>
-      </c>
-      <c r="J91">
-        <v>0.13088073929294</v>
-      </c>
-      <c r="K91" s="10">
-        <f t="shared" si="9"/>
-        <v>1.0505295722890764</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A92">
-        <v>250</v>
-      </c>
-      <c r="B92" s="5"/>
-      <c r="C92" s="2">
-        <v>0.16515386445267599</v>
-      </c>
-      <c r="D92">
-        <v>6.0844630496931901E-4</v>
-      </c>
-      <c r="E92">
-        <v>7.1735921087181002E-4</v>
-      </c>
-      <c r="F92" s="10">
-        <f t="shared" si="8"/>
-        <v>2.0082997872230529E-2</v>
-      </c>
-      <c r="G92" s="4"/>
-      <c r="I92">
-        <v>0.188315720076114</v>
-      </c>
-      <c r="J92">
-        <v>0.19671890522285099</v>
-      </c>
-      <c r="K92" s="11">
-        <f t="shared" si="9"/>
-        <v>1.0446228554012409</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A93">
-        <v>500</v>
-      </c>
-      <c r="B93" s="5"/>
-      <c r="C93" s="2">
-        <v>0.22114304090137801</v>
-      </c>
-      <c r="D93">
-        <v>1.3901143553867799E-3</v>
-      </c>
-      <c r="E93">
-        <v>1.45703989958587E-3</v>
-      </c>
-      <c r="F93" s="10">
-        <f t="shared" si="8"/>
-        <v>2.1548753693625213E-2</v>
-      </c>
-      <c r="G93" s="4"/>
-      <c r="I93">
-        <v>0.25212873564071397</v>
-      </c>
-      <c r="J93">
-        <v>0.26159631710660702</v>
-      </c>
-      <c r="K93" s="10">
-        <f t="shared" si="9"/>
-        <v>1.0375505847908761</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A94">
-        <v>750</v>
-      </c>
-      <c r="D94">
-        <v>1.59024586083695E-3</v>
-      </c>
-      <c r="E94">
-        <v>1.88927153592098E-3</v>
-      </c>
-      <c r="F94" s="10">
-        <f t="shared" si="8"/>
-        <v>1.8239532257896197E-2</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A95">
-        <v>999.99</v>
-      </c>
-      <c r="D95">
-        <v>2.0916951916344802E-3</v>
-      </c>
-      <c r="E95">
-        <v>2.14759074882869E-3</v>
-      </c>
-      <c r="F95" s="10">
-        <f>F78*((E95/E78)^2 +(D95/D78)^2)^0.5</f>
+        <f>F74*((E91/E74)^2 +(D91/D74)^2)^0.5</f>
         <v>1.7398828006913617E-2</v>
       </c>
     </row>

--- a/Jupyter/Wedge/wedge_data_2026-03-25.xlsx
+++ b/Jupyter/Wedge/wedge_data_2026-03-25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\patri\projects\emma-openmc\Jupyter\Wedge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDAEB268-8B64-460D-9E40-EF1FACC7331B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AB2CA5D-4A5C-4C3D-AD30-BA95464744A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -327,16 +327,16 @@
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.67015864678428949</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.67399433743759052</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.67258163487423628</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>0.69883311557825745</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -903,16 +903,16 @@
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1.0001629351709587</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1.0000650261216626</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.99996036360746876</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>1.0005266084564297</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -1436,10 +1436,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$62:$A$72</c:f>
+              <c:f>'Sheet 1'!$A$62:$A$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>0.1</c:v>
                 </c:pt>
@@ -1472,16 +1472,22 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>999.99</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$F$62:$F$72</c:f>
+              <c:f>'Sheet 1'!$F$62:$F$74</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>0.98141967163352228</c:v>
                 </c:pt>
@@ -1514,6 +1520,12 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>1.0613255687481478</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.0852827519045309</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.1057317871283765</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1800,10 +1812,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$44:$A$54</c:f>
+              <c:f>'Sheet 1'!$A$44:$A$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>0.1</c:v>
                 </c:pt>
@@ -1836,16 +1848,22 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>999.99</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$F$44:$F$54</c:f>
+              <c:f>'Sheet 1'!$F$44:$F$56</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>0.9985035371420129</c:v>
                 </c:pt>
@@ -1878,6 +1896,12 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.99666881879093805</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.0030035803296993</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0148841983751864</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4305,15 +4329,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>132179</xdr:colOff>
+      <xdr:colOff>383970</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>56857</xdr:rowOff>
+      <xdr:rowOff>103240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>436979</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>79170</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>56857</xdr:rowOff>
+      <xdr:rowOff>103240</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4341,13 +4365,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>300990</xdr:colOff>
+      <xdr:colOff>373877</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>605790</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>69077</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -4376,16 +4400,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>868680</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>7289</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>9939</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>198120</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>310764</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>9939</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4412,16 +4436,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>929640</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>8614</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>20871</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>259080</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
+      <xdr:colOff>312089</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>20871</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4794,12 +4818,15 @@
         <v>0.1</v>
       </c>
       <c r="B5" s="5"/>
+      <c r="D5">
+        <v>1.3891095589010301</v>
+      </c>
       <c r="E5">
         <v>1.38933589370449</v>
       </c>
-      <c r="F5" s="10" t="e">
+      <c r="F5" s="10">
         <f>E5/D5</f>
-        <v>#DIV/0!</v>
+        <v>1.0001629351709587</v>
       </c>
       <c r="G5" s="4"/>
       <c r="K5" s="10" t="e">
@@ -4813,12 +4840,15 @@
         <v>0.5</v>
       </c>
       <c r="B6" s="5"/>
+      <c r="D6">
+        <v>1.38907673010083</v>
+      </c>
       <c r="E6">
         <v>1.3891670563732801</v>
       </c>
-      <c r="F6" s="10" t="e">
+      <c r="F6" s="10">
         <f t="shared" ref="F6:F17" si="0">E6/D6</f>
-        <v>#DIV/0!</v>
+        <v>1.0000650261216626</v>
       </c>
       <c r="G6" s="4"/>
       <c r="K6" s="10" t="e">
@@ -4832,12 +4862,15 @@
         <v>1</v>
       </c>
       <c r="B7" s="5"/>
+      <c r="D7">
+        <v>1.3889139640202901</v>
+      </c>
       <c r="E7">
         <v>1.3888589124812201</v>
       </c>
-      <c r="F7" s="10" t="e">
+      <c r="F7" s="10">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>0.99996036360746876</v>
       </c>
       <c r="G7" s="4"/>
       <c r="K7" s="10" t="e">
@@ -4851,12 +4884,15 @@
         <v>10</v>
       </c>
       <c r="B8" s="5"/>
+      <c r="D8">
+        <v>1.38607567014507</v>
+      </c>
       <c r="E8">
         <v>1.3868055893142199</v>
       </c>
-      <c r="F8" s="10" t="e">
+      <c r="F8" s="10">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>1.0005266084564297</v>
       </c>
       <c r="G8" s="4"/>
       <c r="K8" s="10" t="e">
@@ -5117,13 +5153,15 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
+      <c r="D24" s="2">
+        <v>3.4601339198647797E-5</v>
+      </c>
       <c r="E24" s="2">
         <v>2.3188386654289999E-5</v>
       </c>
-      <c r="F24" s="10" t="e">
+      <c r="F24" s="10">
         <f>E24/D24</f>
-        <v>#DIV/0!</v>
+        <v>0.67015864678428949</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="2"/>
@@ -5140,12 +5178,15 @@
         <v>0.5</v>
       </c>
       <c r="B25" s="5"/>
+      <c r="D25">
+        <v>1.7267075850167999E-4</v>
+      </c>
       <c r="E25">
         <v>1.16379113471186E-4</v>
       </c>
-      <c r="F25" s="10" t="e">
+      <c r="F25" s="10">
         <f t="shared" ref="F25:F36" si="2">E25/D25</f>
-        <v>#DIV/0!</v>
+        <v>0.67399433743759052</v>
       </c>
       <c r="G25" s="4"/>
       <c r="K25" s="10" t="e">
@@ -5159,12 +5200,15 @@
         <v>1</v>
       </c>
       <c r="B26" s="5"/>
+      <c r="D26">
+        <v>3.4444202449192702E-4</v>
+      </c>
       <c r="E26">
         <v>2.31665379952172E-4</v>
       </c>
-      <c r="F26" s="10" t="e">
+      <c r="F26" s="10">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>0.67258163487423628</v>
       </c>
       <c r="G26" s="4"/>
       <c r="K26" s="10" t="e">
@@ -5178,12 +5222,15 @@
         <v>10</v>
       </c>
       <c r="B27" s="5"/>
+      <c r="D27">
+        <v>3.33054467027722E-3</v>
+      </c>
       <c r="E27">
         <v>2.3274949085023899E-3</v>
       </c>
-      <c r="F27" s="10" t="e">
+      <c r="F27" s="10">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>0.69883311557825745</v>
       </c>
       <c r="G27" s="4"/>
       <c r="K27" s="10" t="e">
@@ -5429,9 +5476,6 @@
         <v>0.1</v>
       </c>
       <c r="B44" s="5"/>
-      <c r="C44">
-        <v>1.38755773111088</v>
-      </c>
       <c r="D44">
         <v>1.33146077610654</v>
       </c>
@@ -5459,9 +5503,6 @@
         <v>0.5</v>
       </c>
       <c r="B45" s="5"/>
-      <c r="C45">
-        <v>1.38409520401011</v>
-      </c>
       <c r="D45">
         <v>1.35765661048369</v>
       </c>
@@ -5490,9 +5531,6 @@
         <v>1</v>
       </c>
       <c r="B46" s="5"/>
-      <c r="C46">
-        <v>1.3811622398640599</v>
-      </c>
       <c r="D46">
         <v>1.33903476392587</v>
       </c>
@@ -5520,9 +5558,6 @@
         <v>10</v>
       </c>
       <c r="B47" s="5"/>
-      <c r="C47">
-        <v>1.37486493369789</v>
-      </c>
       <c r="D47">
         <v>1.31789010731641</v>
       </c>
@@ -5551,9 +5586,6 @@
         <v>25</v>
       </c>
       <c r="B48" s="5"/>
-      <c r="C48">
-        <v>1.36350384779266</v>
-      </c>
       <c r="D48">
         <v>1.32036564820574</v>
       </c>
@@ -5581,9 +5613,6 @@
         <v>50</v>
       </c>
       <c r="B49" s="5"/>
-      <c r="C49">
-        <v>1.3571706170428599</v>
-      </c>
       <c r="D49">
         <v>1.3197738196808499</v>
       </c>
@@ -5612,9 +5641,6 @@
         <v>75</v>
       </c>
       <c r="B50" s="5"/>
-      <c r="C50">
-        <v>1.35109721915133</v>
-      </c>
       <c r="D50">
         <v>1.29935652652886</v>
       </c>
@@ -5642,9 +5668,6 @@
         <v>100</v>
       </c>
       <c r="B51" s="5"/>
-      <c r="C51">
-        <v>1.32844051248484</v>
-      </c>
       <c r="D51">
         <v>1.33910590256307</v>
       </c>
@@ -5673,9 +5696,6 @@
         <v>150</v>
       </c>
       <c r="B52" s="5"/>
-      <c r="C52">
-        <v>1.26939305918802</v>
-      </c>
       <c r="D52">
         <v>1.3346899335651701</v>
       </c>
@@ -5703,9 +5723,6 @@
         <v>250</v>
       </c>
       <c r="B53" s="5"/>
-      <c r="C53">
-        <v>1.2146497361047901</v>
-      </c>
       <c r="D53">
         <v>1.29678717701069</v>
       </c>
@@ -5734,9 +5751,6 @@
         <v>500</v>
       </c>
       <c r="B54" s="5"/>
-      <c r="C54">
-        <v>1.1436421352186501</v>
-      </c>
       <c r="D54">
         <v>1.2662694099393199</v>
       </c>
@@ -5763,6 +5777,7 @@
       <c r="A55">
         <v>750</v>
       </c>
+      <c r="B55" s="5"/>
       <c r="D55">
         <v>1.23279071771682</v>
       </c>
@@ -5773,6 +5788,7 @@
         <f t="shared" si="4"/>
         <v>1.0030035803296993</v>
       </c>
+      <c r="G55" s="5"/>
       <c r="I55">
         <v>1.1807532343395699</v>
       </c>
@@ -5784,6 +5800,7 @@
       <c r="A56">
         <v>999.99</v>
       </c>
+      <c r="B56" s="5"/>
       <c r="D56">
         <v>1.1928852496040101</v>
       </c>
@@ -5794,6 +5811,7 @@
         <f t="shared" si="4"/>
         <v>1.0148841983751864</v>
       </c>
+      <c r="G56" s="5"/>
       <c r="I56">
         <v>1.13357719050286</v>
       </c>
@@ -6193,6 +6211,7 @@
       <c r="A73">
         <v>750</v>
       </c>
+      <c r="B73" s="5"/>
       <c r="D73">
         <v>0.140294088260282</v>
       </c>
@@ -6203,6 +6222,7 @@
         <f t="shared" si="6"/>
         <v>1.0852827519045309</v>
       </c>
+      <c r="G73" s="5"/>
       <c r="I73">
         <v>0.164782092113922</v>
       </c>
@@ -6218,6 +6238,7 @@
       <c r="A74">
         <v>999.99</v>
       </c>
+      <c r="B74" s="5"/>
       <c r="D74">
         <v>0.181401571560247</v>
       </c>
@@ -6228,6 +6249,7 @@
         <f t="shared" si="6"/>
         <v>1.1057317871283765</v>
       </c>
+      <c r="G74" s="5"/>
       <c r="I74">
         <v>0.211482254080264</v>
       </c>

--- a/Jupyter/Wedge/wedge_data_2026-03-25.xlsx
+++ b/Jupyter/Wedge/wedge_data_2026-03-25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\patri\projects\emma-openmc\Jupyter\Wedge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AB2CA5D-4A5C-4C3D-AD30-BA95464744A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2727A53E-B710-49C1-8960-17B14C6CB01B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="14">
   <si>
     <t>Fertile kg/m3</t>
   </si>
@@ -70,13 +70,23 @@
   <si>
     <t>FISSILE PRODUCTION RATE ERROR PROPAGATION [ RXNS/SRC-N ]</t>
   </si>
+  <si>
+    <t>A-err</t>
+  </si>
+  <si>
+    <t>C-err</t>
+  </si>
+  <si>
+    <t>=C/A err</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000000"/>
+    <numFmt numFmtId="173" formatCode="0.00000000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -163,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -180,6 +190,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -322,7 +333,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$F$24:$F$36</c:f>
+              <c:f>'Sheet 1'!$H$24:$H$36</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
@@ -339,31 +350,31 @@
                   <c:v>0.69883311557825745</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.73244907600666376</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>0.76691398093902452</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>0.79412199858198884</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>0.82771654679092965</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>0.87277793951821403</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>0.90774216971761523</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>0.96885985849430767</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>1.0035052756769365</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>1.0159556160581653</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -450,7 +461,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$K$24:$K$36</c:f>
+              <c:f>'Sheet 1'!$N$24:$N$36</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
@@ -898,7 +909,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$F$5:$F$17</c:f>
+              <c:f>'Sheet 1'!$H$5:$H$17</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
@@ -915,31 +926,31 @@
                   <c:v>1.0005266084564297</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>1.0018467149465879</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>1.002287048308576</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>1.0038025582102672</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>1.0036838050286592</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>1.002467577491776</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>1.000596548769378</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>1.0015290596941282</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>1.0029865814925498</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>1.0003513071302839</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1077,7 +1088,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$K$5:$K$17</c:f>
+              <c:f>'Sheet 1'!$N$5:$N$17</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
@@ -1403,7 +1414,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Sheet 1'!$F$61</c:f>
+              <c:f>'Sheet 1'!$I$61</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1484,7 +1495,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$F$62:$F$74</c:f>
+              <c:f>'Sheet 1'!$I$62:$I$74</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
@@ -1779,7 +1790,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Sheet 1'!$F$43</c:f>
+              <c:f>'Sheet 1'!$I$43</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1860,7 +1871,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$F$44:$F$56</c:f>
+              <c:f>'Sheet 1'!$I$44:$I$56</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
@@ -4328,13 +4339,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>383970</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>103240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>79170</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>103240</xdr:rowOff>
@@ -4364,13 +4375,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>373877</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>69077</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -4400,13 +4411,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>7289</xdr:colOff>
       <xdr:row>59</xdr:row>
       <xdr:rowOff>9939</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>310764</xdr:colOff>
       <xdr:row>74</xdr:row>
       <xdr:rowOff>9939</xdr:rowOff>
@@ -4436,13 +4447,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>8614</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>20871</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>312089</xdr:colOff>
       <xdr:row>57</xdr:row>
       <xdr:rowOff>20871</xdr:rowOff>
@@ -4736,52 +4747,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22416C2-1180-4450-A3B0-0B08DD9AEC85}">
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
     <col min="2" max="2" width="2.109375" customWidth="1"/>
-    <col min="3" max="4" width="12.21875" customWidth="1"/>
-    <col min="5" max="5" width="15.88671875" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" customWidth="1"/>
-    <col min="7" max="7" width="2.77734375" customWidth="1"/>
-    <col min="8" max="11" width="13.33203125" customWidth="1"/>
-    <col min="12" max="12" width="14.21875" customWidth="1"/>
+    <col min="3" max="5" width="12.21875" customWidth="1"/>
+    <col min="6" max="8" width="15.88671875" customWidth="1"/>
+    <col min="9" max="9" width="15.109375" customWidth="1"/>
+    <col min="10" max="10" width="2.77734375" customWidth="1"/>
+    <col min="11" max="14" width="13.33203125" customWidth="1"/>
+    <col min="15" max="15" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="K1" s="1"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C2" s="14" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="14"/>
-      <c r="E2" s="15"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
       <c r="K2" s="2"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="3"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="3"/>
-      <c r="H3" s="3" t="s">
+      <c r="E3" s="3"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="3"/>
+      <c r="K3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
       <c r="L3" s="3"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="3"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>0</v>
       </c>
@@ -4793,27 +4810,36 @@
         <v>7</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="6" t="s">
+      <c r="I4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="8"/>
+      <c r="K4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="L4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="M4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="N4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="7"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O4" s="7"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>0.1</v>
       </c>
@@ -4822,20 +4848,33 @@
         <v>1.3891095589010301</v>
       </c>
       <c r="E5">
+        <v>1.02494314460544E-4</v>
+      </c>
+      <c r="F5">
         <v>1.38933589370449</v>
       </c>
-      <c r="F5" s="10">
-        <f>E5/D5</f>
+      <c r="G5">
+        <v>1.1377551521665301E-4</v>
+      </c>
+      <c r="H5" s="10">
+        <f>F5/D5</f>
         <v>1.0001629351709587</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="K5" s="10" t="e">
-        <f>J5/I5</f>
+      <c r="I5">
+        <f>H5*((E5/D5)^2 +(G5/F5)^2)^0.5</f>
+        <v>1.1024684824037706E-4</v>
+      </c>
+      <c r="J5" s="4"/>
+      <c r="M5">
+        <v>1.38932778213898</v>
+      </c>
+      <c r="N5" s="10" t="e">
+        <f>M5/L5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L5" s="10"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O5" s="10"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0.5</v>
       </c>
@@ -4844,20 +4883,33 @@
         <v>1.38907673010083</v>
       </c>
       <c r="E6">
+        <v>1.52707495750366E-4</v>
+      </c>
+      <c r="F6">
         <v>1.3891670563732801</v>
       </c>
-      <c r="F6" s="10">
-        <f t="shared" ref="F6:F17" si="0">E6/D6</f>
+      <c r="G6">
+        <v>1.6878154642812701E-4</v>
+      </c>
+      <c r="H6" s="10">
+        <f>F6/D6</f>
         <v>1.0000650261216626</v>
       </c>
-      <c r="G6" s="4"/>
-      <c r="K6" s="10" t="e">
-        <f t="shared" ref="K6:K17" si="1">J6/I6</f>
+      <c r="I6">
+        <f t="shared" ref="I6:I16" si="0">H6*((E6/D6)^2 +(G6/F6)^2)^0.5</f>
+        <v>1.6386259048946993E-4</v>
+      </c>
+      <c r="J6" s="4"/>
+      <c r="M6">
+        <v>1.38912815811046</v>
+      </c>
+      <c r="N6" s="10" t="e">
+        <f t="shared" ref="N6:N17" si="1">M6/L6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L6" s="10"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O6" s="10"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -4866,20 +4918,33 @@
         <v>1.3889139640202901</v>
       </c>
       <c r="E7">
+        <v>1.8201886596701201E-4</v>
+      </c>
+      <c r="F7">
         <v>1.3888589124812201</v>
       </c>
-      <c r="F7" s="10">
+      <c r="G7">
+        <v>1.54337152453701E-4</v>
+      </c>
+      <c r="H7" s="10">
+        <f>F7/D7</f>
+        <v>0.99996036360746876</v>
+      </c>
+      <c r="I7">
         <f t="shared" si="0"/>
-        <v>0.99996036360746876</v>
-      </c>
-      <c r="G7" s="4"/>
-      <c r="K7" s="10" t="e">
+        <v>1.7181641313147609E-4</v>
+      </c>
+      <c r="J7" s="4"/>
+      <c r="M7">
+        <v>1.38877619043423</v>
+      </c>
+      <c r="N7" s="10" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L7" s="10"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O7" s="10"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>10</v>
       </c>
@@ -4888,234 +4953,389 @@
         <v>1.38607567014507</v>
       </c>
       <c r="E8">
+        <v>3.8958612319318502E-4</v>
+      </c>
+      <c r="F8">
         <v>1.3868055893142199</v>
       </c>
-      <c r="F8" s="10">
+      <c r="G8">
+        <v>4.0944327607914799E-4</v>
+      </c>
+      <c r="H8" s="10">
+        <f>F8/D8</f>
+        <v>1.0005266084564297</v>
+      </c>
+      <c r="I8">
         <f t="shared" si="0"/>
-        <v>1.0005266084564297</v>
-      </c>
-      <c r="G8" s="4"/>
-      <c r="K8" s="10" t="e">
+        <v>4.0785290749755253E-4</v>
+      </c>
+      <c r="J8" s="4"/>
+      <c r="M8">
+        <v>1.38594397488493</v>
+      </c>
+      <c r="N8" s="10" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L8" s="10"/>
-    </row>
-    <row r="9" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="O8" s="10"/>
+    </row>
+    <row r="9" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>25</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9"/>
-      <c r="D9"/>
+      <c r="D9">
+        <v>1.37947186689904</v>
+      </c>
       <c r="E9">
+        <v>8.86091661857925E-4</v>
+      </c>
+      <c r="F9">
         <v>1.3820193582140401</v>
       </c>
-      <c r="F9" s="10" t="e">
+      <c r="G9">
+        <v>1.17898543365087E-3</v>
+      </c>
+      <c r="H9" s="10">
+        <f>F9/D9</f>
+        <v>1.0018467149465879</v>
+      </c>
+      <c r="I9">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-      <c r="K9" s="10" t="e">
+        <v>1.0698498708561776E-3</v>
+      </c>
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9">
+        <v>1.3801396333334499</v>
+      </c>
+      <c r="N9" s="10" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L9" s="11"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O9" s="11"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>50</v>
       </c>
       <c r="B10" s="5"/>
+      <c r="D10">
+        <v>1.37231900559378</v>
+      </c>
       <c r="E10">
+        <v>9.8135892237590492E-4</v>
+      </c>
+      <c r="F10">
         <v>1.3754575654543499</v>
       </c>
-      <c r="F10" s="10" t="e">
+      <c r="G10">
+        <v>7.1929329253824501E-4</v>
+      </c>
+      <c r="H10" s="10">
+        <f>F10/D10</f>
+        <v>1.002287048308576</v>
+      </c>
+      <c r="I10">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G10" s="4"/>
-      <c r="K10" s="10" t="e">
+        <v>8.8794780325578441E-4</v>
+      </c>
+      <c r="J10" s="4"/>
+      <c r="M10">
+        <v>1.3711659238629099</v>
+      </c>
+      <c r="N10" s="10" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L10" s="10"/>
-    </row>
-    <row r="11" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="O10" s="10"/>
+    </row>
+    <row r="11" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>75</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11"/>
-      <c r="D11"/>
+      <c r="D11">
+        <v>1.3652125452841399</v>
+      </c>
       <c r="E11">
+        <v>9.36891207849102E-4</v>
+      </c>
+      <c r="F11">
         <v>1.37040384545697</v>
       </c>
-      <c r="F11" s="10" t="e">
+      <c r="G11">
+        <v>1.1043763633645899E-3</v>
+      </c>
+      <c r="H11" s="10">
+        <f>F11/D11</f>
+        <v>1.0038025582102672</v>
+      </c>
+      <c r="I11">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H11"/>
-      <c r="I11"/>
-      <c r="J11"/>
-      <c r="K11" s="10" t="e">
+        <v>1.0625098571799413E-3</v>
+      </c>
+      <c r="K11"/>
+      <c r="L11"/>
+      <c r="M11">
+        <v>1.36351969550464</v>
+      </c>
+      <c r="N11" s="10" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L11" s="11"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O11" s="11"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>100</v>
       </c>
       <c r="B12" s="5"/>
+      <c r="D12">
+        <v>1.35996558693921</v>
+      </c>
       <c r="E12">
+        <v>8.2269713778889005E-4</v>
+      </c>
+      <c r="F12">
         <v>1.3649754350071801</v>
       </c>
-      <c r="F12" s="10" t="e">
+      <c r="G12">
+        <v>1.0934621564654399E-3</v>
+      </c>
+      <c r="H12" s="10">
+        <f>F12/D12</f>
+        <v>1.0036838050286592</v>
+      </c>
+      <c r="I12">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G12" s="4"/>
-      <c r="K12" s="10" t="e">
+        <v>1.0075356465859516E-3</v>
+      </c>
+      <c r="J12" s="4"/>
+      <c r="M12">
+        <v>1.35608844560886</v>
+      </c>
+      <c r="N12" s="10" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L12" s="10"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O12" s="10"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>150</v>
       </c>
       <c r="B13" s="5"/>
+      <c r="D13">
+        <v>1.3471169036955299</v>
+      </c>
       <c r="E13">
+        <v>3.4192473007070602E-3</v>
+      </c>
+      <c r="F13">
         <v>1.35044101904588</v>
       </c>
-      <c r="F13" s="10" t="e">
+      <c r="G13">
+        <v>3.6209913911154899E-3</v>
+      </c>
+      <c r="H13" s="10">
+        <f>F13/D13</f>
+        <v>1.002467577491776</v>
+      </c>
+      <c r="I13">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G13" s="4"/>
-      <c r="K13" s="10" t="e">
+        <v>3.7012678767904027E-3</v>
+      </c>
+      <c r="J13" s="4"/>
+      <c r="M13">
+        <v>1.3448593643039499</v>
+      </c>
+      <c r="N13" s="10" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L13" s="10"/>
-    </row>
-    <row r="14" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="O13" s="10"/>
+    </row>
+    <row r="14" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>250</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14"/>
-      <c r="D14"/>
+      <c r="D14">
+        <v>1.3301704109246899</v>
+      </c>
       <c r="E14">
+        <v>2.6701333301032298E-3</v>
+      </c>
+      <c r="F14">
         <v>1.3309639224463901</v>
       </c>
-      <c r="F14" s="10" t="e">
+      <c r="G14">
+        <v>2.6466416072152398E-3</v>
+      </c>
+      <c r="H14" s="10">
+        <f>F14/D14</f>
+        <v>1.000596548769378</v>
+      </c>
+      <c r="I14">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H14"/>
-      <c r="I14"/>
-      <c r="J14"/>
-      <c r="K14" s="10" t="e">
+        <v>2.8272285541985462E-3</v>
+      </c>
+      <c r="K14"/>
+      <c r="L14"/>
+      <c r="M14">
+        <v>1.3096995917960299</v>
+      </c>
+      <c r="N14" s="10" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L14" s="11"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O14" s="11"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>500</v>
       </c>
       <c r="B15" s="5"/>
+      <c r="D15">
+        <v>1.2881810524951001</v>
+      </c>
       <c r="E15">
+        <v>2.82817615567389E-3</v>
+      </c>
+      <c r="F15">
         <v>1.2901507582212099</v>
       </c>
-      <c r="F15" s="10" t="e">
+      <c r="G15">
+        <v>3.6382982434454399E-3</v>
+      </c>
+      <c r="H15" s="10">
+        <f>F15/D15</f>
+        <v>1.0015290596941282</v>
+      </c>
+      <c r="I15">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G15" s="4"/>
-      <c r="K15" s="10" t="e">
+        <v>3.579377630249193E-3</v>
+      </c>
+      <c r="J15" s="4"/>
+      <c r="M15">
+        <v>1.2497624884637799</v>
+      </c>
+      <c r="N15" s="10" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L15" s="10"/>
-    </row>
-    <row r="16" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="O15" s="10"/>
+    </row>
+    <row r="16" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>750</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16"/>
-      <c r="D16"/>
+      <c r="D16">
+        <v>1.24999214529804</v>
+      </c>
       <c r="E16">
+        <v>2.36320017159778E-3</v>
+      </c>
+      <c r="F16">
         <v>1.2537253487050199</v>
       </c>
-      <c r="F16" s="10" t="e">
+      <c r="G16">
+        <v>3.5797440463882701E-3</v>
+      </c>
+      <c r="H16" s="10">
+        <f>F16/D16</f>
+        <v>1.0029865814925498</v>
+      </c>
+      <c r="I16">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H16"/>
-      <c r="I16"/>
-      <c r="J16"/>
-      <c r="K16" s="10" t="e">
+        <v>3.4346863492251559E-3</v>
+      </c>
+      <c r="K16"/>
+      <c r="L16"/>
+      <c r="M16">
+        <v>1.20221749175355</v>
+      </c>
+      <c r="N16" s="10" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L16" s="11"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O16" s="11"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>999.99</v>
       </c>
       <c r="B17" s="5"/>
+      <c r="D17">
+        <v>1.2159170927577201</v>
+      </c>
       <c r="E17">
+        <v>3.1109769949112399E-3</v>
+      </c>
+      <c r="F17">
         <v>1.2163442531022399</v>
       </c>
-      <c r="F17" s="10" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G17" s="4"/>
-      <c r="K17" s="10" t="e">
+      <c r="G17">
+        <v>3.18424238805618E-3</v>
+      </c>
+      <c r="H17" s="10">
+        <f>F17/D17</f>
+        <v>1.0003513071302839</v>
+      </c>
+      <c r="I17">
+        <f>H17*((E17/D17)^2 +(G17/F17)^2)^0.5</f>
+        <v>3.6618101886275135E-3</v>
+      </c>
+      <c r="J17" s="4"/>
+      <c r="M17">
+        <v>1.1524770375920901</v>
+      </c>
+      <c r="N17" s="10" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L17" s="10"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O17" s="10"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C21" s="12" t="s">
         <v>5</v>
       </c>
       <c r="D21" s="12"/>
-      <c r="E21" s="13"/>
+      <c r="E21" s="12"/>
       <c r="F21" s="13"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
       <c r="K21" s="2"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D22" s="3"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="3"/>
-      <c r="H22" s="3" t="s">
+      <c r="E22" s="3"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="3"/>
+      <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I22" s="3"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
       <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>0</v>
       </c>
@@ -5127,27 +5347,36 @@
         <v>7</v>
       </c>
       <c r="E23" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="G23" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H23" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="G23" s="8"/>
-      <c r="H23" s="6" t="s">
+      <c r="I23" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="8"/>
+      <c r="K23" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="L23" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J23" s="6" t="s">
+      <c r="M23" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="K23" s="7" t="s">
+      <c r="N23" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="L23" s="7"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O23" s="7"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>0.1</v>
       </c>
@@ -5156,24 +5385,36 @@
       <c r="D24" s="2">
         <v>3.4601339198647797E-5</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" s="16">
+        <v>1.22883732368375E-8</v>
+      </c>
+      <c r="F24" s="16">
         <v>2.3188386654289999E-5</v>
       </c>
-      <c r="F24" s="10">
-        <f>E24/D24</f>
+      <c r="G24" s="16">
+        <v>2.5713213345718999E-7</v>
+      </c>
+      <c r="H24" s="10">
+        <f>F24/D24</f>
         <v>0.67015864678428949</v>
       </c>
-      <c r="G24" s="4"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="10" t="e">
-        <f>J24/I24</f>
+      <c r="I24">
+        <f>H24*((E24/D24)^2 +(G24/F24)^2)^0.5</f>
+        <v>7.4350871718769813E-3</v>
+      </c>
+      <c r="J24" s="4"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2">
+        <v>2.5899175434190999E-5</v>
+      </c>
+      <c r="N24" s="10" t="e">
+        <f>M24/L24</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L24" s="10"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O24" s="10"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>0.5</v>
       </c>
@@ -5181,21 +5422,34 @@
       <c r="D25">
         <v>1.7267075850167999E-4</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="16">
+        <v>7.3730405114227898E-8</v>
+      </c>
+      <c r="F25" s="16">
         <v>1.16379113471186E-4</v>
       </c>
-      <c r="F25" s="10">
-        <f t="shared" ref="F25:F36" si="2">E25/D25</f>
+      <c r="G25" s="16">
+        <v>4.9685826902563597E-7</v>
+      </c>
+      <c r="H25" s="10">
+        <f>F25/D25</f>
         <v>0.67399433743759052</v>
       </c>
-      <c r="G25" s="4"/>
-      <c r="K25" s="10" t="e">
-        <f t="shared" ref="K25:K36" si="3">J25/I25</f>
+      <c r="I25">
+        <f t="shared" ref="I25:I35" si="2">H25*((E25/D25)^2 +(G25/F25)^2)^0.5</f>
+        <v>2.8918456475792078E-3</v>
+      </c>
+      <c r="J25" s="4"/>
+      <c r="M25">
+        <v>1.3026224043386099E-4</v>
+      </c>
+      <c r="N25" s="10" t="e">
+        <f t="shared" ref="N25:N36" si="3">M25/L25</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L25" s="10"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O25" s="10"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1</v>
       </c>
@@ -5203,21 +5457,34 @@
       <c r="D26">
         <v>3.4444202449192702E-4</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="16">
+        <v>1.02701859340892E-7</v>
+      </c>
+      <c r="F26" s="16">
         <v>2.31665379952172E-4</v>
       </c>
-      <c r="F26" s="10">
+      <c r="G26" s="16">
+        <v>6.9232886194979901E-7</v>
+      </c>
+      <c r="H26" s="10">
+        <f>F26/D26</f>
+        <v>0.67258163487423628</v>
+      </c>
+      <c r="I26">
         <f t="shared" si="2"/>
-        <v>0.67258163487423628</v>
-      </c>
-      <c r="G26" s="4"/>
-      <c r="K26" s="10" t="e">
+        <v>2.0199806972425911E-3</v>
+      </c>
+      <c r="J26" s="4"/>
+      <c r="M26">
+        <v>2.6089565621297098E-4</v>
+      </c>
+      <c r="N26" s="10" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L26" s="10"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O26" s="10"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>10</v>
       </c>
@@ -5225,222 +5492,385 @@
       <c r="D27">
         <v>3.33054467027722E-3</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="16">
+        <v>3.1023196230951202E-6</v>
+      </c>
+      <c r="F27" s="16">
         <v>2.3274949085023899E-3</v>
       </c>
-      <c r="F27" s="10">
+      <c r="G27" s="16">
+        <v>7.3576810457546899E-6</v>
+      </c>
+      <c r="H27" s="10">
+        <f>F27/D27</f>
+        <v>0.69883311557825745</v>
+      </c>
+      <c r="I27">
         <f t="shared" si="2"/>
-        <v>0.69883311557825745</v>
-      </c>
-      <c r="G27" s="4"/>
-      <c r="K27" s="10" t="e">
+        <v>2.3030599218682355E-3</v>
+      </c>
+      <c r="J27" s="4"/>
+      <c r="M27">
+        <v>2.5949076799098498E-3</v>
+      </c>
+      <c r="N27" s="10" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L27" s="10"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O27" s="10"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>25</v>
       </c>
       <c r="B28" s="5"/>
-      <c r="E28">
+      <c r="D28">
+        <v>7.9007108136224906E-3</v>
+      </c>
+      <c r="E28" s="16">
+        <v>2.1579374269995798E-5</v>
+      </c>
+      <c r="F28" s="16">
         <v>5.7868683352336496E-3</v>
       </c>
-      <c r="F28" s="10" t="e">
+      <c r="G28" s="16">
+        <v>2.2153397083295701E-5</v>
+      </c>
+      <c r="H28" s="10">
+        <f>F28/D28</f>
+        <v>0.73244907600666376</v>
+      </c>
+      <c r="I28">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G28" s="4"/>
-      <c r="K28" s="10" t="e">
+        <v>3.444486925796071E-3</v>
+      </c>
+      <c r="J28" s="4"/>
+      <c r="M28">
+        <v>6.4419405380797103E-3</v>
+      </c>
+      <c r="N28" s="10" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L28" s="11"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O28" s="11"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>50</v>
       </c>
       <c r="B29" s="5"/>
-      <c r="E29">
+      <c r="D29">
+        <v>1.48099690035684E-2</v>
+      </c>
+      <c r="E29" s="16">
+        <v>3.5619384608241799E-5</v>
+      </c>
+      <c r="F29" s="16">
         <v>1.1357972286110201E-2</v>
       </c>
-      <c r="F29" s="10" t="e">
+      <c r="G29" s="16">
+        <v>3.9960656049596501E-5</v>
+      </c>
+      <c r="H29" s="10">
+        <f>F29/D29</f>
+        <v>0.76691398093902452</v>
+      </c>
+      <c r="I29">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G29" s="4"/>
-      <c r="K29" s="10" t="e">
+        <v>3.2684265997479276E-3</v>
+      </c>
+      <c r="J29" s="4"/>
+      <c r="M29">
+        <v>1.26690225425122E-2</v>
+      </c>
+      <c r="N29" s="10" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L29" s="10"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O29" s="10"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>75</v>
       </c>
       <c r="B30" s="5"/>
-      <c r="E30">
+      <c r="D30">
+        <v>2.1060130702738999E-2</v>
+      </c>
+      <c r="E30" s="16">
+        <v>3.0830038687911403E-5</v>
+      </c>
+      <c r="F30" s="16">
         <v>1.6724313084056999E-2</v>
       </c>
-      <c r="F30" s="10" t="e">
+      <c r="G30" s="16">
+        <v>4.6773312275541899E-5</v>
+      </c>
+      <c r="H30" s="10">
+        <f>F30/D30</f>
+        <v>0.79412199858198884</v>
+      </c>
+      <c r="I30">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G30" s="4"/>
-      <c r="K30" s="10" t="e">
+        <v>2.506797039006772E-3</v>
+      </c>
+      <c r="J30" s="4"/>
+      <c r="M30">
+        <v>1.8873120984925901E-2</v>
+      </c>
+      <c r="N30" s="10" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L30" s="11"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O30" s="11"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>100</v>
       </c>
       <c r="B31" s="5"/>
-      <c r="E31">
+      <c r="D31">
+        <v>2.67600755292417E-2</v>
+      </c>
+      <c r="E31" s="16">
+        <v>6.1301138330409899E-5</v>
+      </c>
+      <c r="F31" s="16">
         <v>2.2149757308928399E-2</v>
       </c>
-      <c r="F31" s="10" t="e">
+      <c r="G31" s="16">
+        <v>5.1020148947823797E-5</v>
+      </c>
+      <c r="H31" s="10">
+        <f>F31/D31</f>
+        <v>0.82771654679092965</v>
+      </c>
+      <c r="I31">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G31" s="4"/>
-      <c r="K31" s="10" t="e">
+        <v>2.6889139523652702E-3</v>
+      </c>
+      <c r="J31" s="4"/>
+      <c r="M31">
+        <v>2.4681477633588599E-2</v>
+      </c>
+      <c r="N31" s="10" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L31" s="10"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O31" s="10"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>150</v>
       </c>
       <c r="B32" s="5"/>
-      <c r="E32">
+      <c r="D32">
+        <v>3.6782709718709998E-2</v>
+      </c>
+      <c r="E32" s="16">
+        <v>1.97489580151579E-4</v>
+      </c>
+      <c r="F32" s="16">
         <v>3.2103137598192298E-2</v>
       </c>
-      <c r="F32" s="10" t="e">
+      <c r="G32" s="16">
+        <v>2.08831333646651E-4</v>
+      </c>
+      <c r="H32" s="10">
+        <f>F32/D32</f>
+        <v>0.87277793951821403</v>
+      </c>
+      <c r="I32">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G32" s="4"/>
-      <c r="K32" s="10" t="e">
+        <v>7.3615233968889766E-3</v>
+      </c>
+      <c r="J32" s="4"/>
+      <c r="M32">
+        <v>3.6134840661020101E-2</v>
+      </c>
+      <c r="N32" s="10" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L32" s="10"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O32" s="10"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>250</v>
       </c>
       <c r="B33" s="5"/>
-      <c r="E33">
+      <c r="D33">
+        <v>5.6309750104400702E-2</v>
+      </c>
+      <c r="E33" s="16">
+        <v>2.51687827781958E-4</v>
+      </c>
+      <c r="F33" s="16">
         <v>5.1114734736025402E-2</v>
       </c>
-      <c r="F33" s="10" t="e">
+      <c r="G33" s="16">
+        <v>2.8833834514146198E-4</v>
+      </c>
+      <c r="H33" s="10">
+        <f>F33/D33</f>
+        <v>0.90774216971761523</v>
+      </c>
+      <c r="I33">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G33" s="4"/>
-      <c r="K33" s="10" t="e">
+        <v>6.5331679556135417E-3</v>
+      </c>
+      <c r="J33" s="4"/>
+      <c r="M33">
+        <v>5.7361502212218099E-2</v>
+      </c>
+      <c r="N33" s="10" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L33" s="11"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O33" s="11"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>500</v>
       </c>
       <c r="B34" s="5"/>
-      <c r="E34">
+      <c r="D34">
+        <v>9.4384365104793602E-2</v>
+      </c>
+      <c r="E34" s="16">
+        <v>3.7802904257795602E-4</v>
+      </c>
+      <c r="F34" s="16">
         <v>9.1445222619505398E-2</v>
       </c>
-      <c r="F34" s="10" t="e">
+      <c r="G34" s="16">
+        <v>4.4906828447954003E-4</v>
+      </c>
+      <c r="H34" s="10">
+        <f>F34/D34</f>
+        <v>0.96885985849430767</v>
+      </c>
+      <c r="I34">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G34" s="4"/>
-      <c r="K34" s="10" t="e">
+        <v>6.1396636178584303E-3</v>
+      </c>
+      <c r="J34" s="4"/>
+      <c r="M34">
+        <v>0.102092586065974</v>
+      </c>
+      <c r="N34" s="10" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L34" s="10"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O34" s="10"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>750</v>
       </c>
       <c r="B35" s="5"/>
-      <c r="E35">
+      <c r="D35">
+        <v>0.12681392305883499</v>
+      </c>
+      <c r="E35" s="16">
+        <v>3.7117560576619898E-4</v>
+      </c>
+      <c r="F35" s="16">
         <v>0.12725844081883</v>
       </c>
-      <c r="F35" s="10" t="e">
+      <c r="G35" s="16">
+        <v>3.9277512684765298E-4</v>
+      </c>
+      <c r="H35" s="10">
+        <f>F35/D35</f>
+        <v>1.0035052756769365</v>
+      </c>
+      <c r="I35">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G35" s="4"/>
-      <c r="K35" s="10" t="e">
+        <v>4.2684987159538603E-3</v>
+      </c>
+      <c r="J35" s="4"/>
+      <c r="M35">
+        <v>0.14105605143254499</v>
+      </c>
+      <c r="N35" s="10" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L35" s="11"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O35" s="11"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>999.99</v>
       </c>
       <c r="B36" s="5"/>
-      <c r="E36">
+      <c r="D36">
+        <v>0.15510900896549801</v>
+      </c>
+      <c r="E36" s="16">
+        <v>5.7851797067085496E-4</v>
+      </c>
+      <c r="F36" s="16">
         <v>0.157583868759714</v>
       </c>
-      <c r="F36" s="10" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G36" s="4"/>
-      <c r="K36" s="10" t="e">
+      <c r="G36" s="16">
+        <v>5.8700051779191705E-4</v>
+      </c>
+      <c r="H36" s="10">
+        <f>F36/D36</f>
+        <v>1.0159556160581653</v>
+      </c>
+      <c r="I36">
+        <f>H36*((E36/D36)^2 +(G36/F36)^2)^0.5</f>
+        <v>5.3554157048239367E-3</v>
+      </c>
+      <c r="J36" s="4"/>
+      <c r="M36">
+        <v>0.17395996323018501</v>
+      </c>
+      <c r="N36" s="10" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L36" s="10"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O36" s="10"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C40" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C41" s="14" t="s">
         <v>2</v>
       </c>
       <c r="D41" s="14"/>
-      <c r="E41" s="15"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
       <c r="K41" s="2"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C42" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D42" s="3"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="3"/>
-      <c r="H42" s="3" t="s">
+      <c r="E42" s="3"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="3"/>
+      <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I42" s="3"/>
-      <c r="J42" s="9"/>
-      <c r="K42" s="9"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L42" s="3"/>
+      <c r="M42" s="9"/>
+      <c r="N42" s="9"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
         <v>0</v>
       </c>
@@ -5451,27 +5881,30 @@
       <c r="D43" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E43" s="6" t="s">
+      <c r="E43" s="6"/>
+      <c r="F43" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F43" s="7" t="s">
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="G43" s="8"/>
-      <c r="H43" s="6" t="s">
+      <c r="J43" s="8"/>
+      <c r="K43" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="I43" s="6" t="s">
+      <c r="L43" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J43" s="6" t="s">
+      <c r="M43" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="K43" s="7" t="s">
+      <c r="N43" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>0.1</v>
       </c>
@@ -5479,26 +5912,26 @@
       <c r="D44">
         <v>1.33146077610654</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>1.3294682945082299</v>
       </c>
-      <c r="F44" s="10">
-        <f>E44/D44</f>
+      <c r="I44" s="10">
+        <f>F44/D44</f>
         <v>0.9985035371420129</v>
       </c>
-      <c r="G44" s="4"/>
-      <c r="I44">
+      <c r="J44" s="4"/>
+      <c r="L44">
         <v>1.33422182541257</v>
       </c>
-      <c r="J44">
+      <c r="M44">
         <v>1.3288821396550801</v>
       </c>
-      <c r="K44" s="10">
-        <f>J44/I44</f>
+      <c r="N44" s="10">
+        <f>M44/L44</f>
         <v>0.99599790255579224</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>0.5</v>
       </c>
@@ -5506,27 +5939,27 @@
       <c r="D45">
         <v>1.35765661048369</v>
       </c>
-      <c r="E45">
+      <c r="F45">
         <v>1.3402135659025001</v>
       </c>
-      <c r="F45" s="10">
-        <f t="shared" ref="F45:F56" si="4">E45/D45</f>
+      <c r="I45" s="10">
+        <f t="shared" ref="I45:I56" si="4">F45/D45</f>
         <v>0.98715209394887005</v>
       </c>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45">
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="L45">
         <v>1.3552315082948401</v>
       </c>
-      <c r="J45">
+      <c r="M45">
         <v>1.34024384554322</v>
       </c>
-      <c r="K45" s="11">
-        <f t="shared" ref="K45:K54" si="5">J45/I45</f>
+      <c r="N45" s="11">
+        <f t="shared" ref="N45:N56" si="5">M45/L45</f>
         <v>0.98894088378266998</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>1</v>
       </c>
@@ -5534,26 +5967,26 @@
       <c r="D46">
         <v>1.33903476392587</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>1.3294539841566</v>
       </c>
-      <c r="F46" s="10">
+      <c r="I46" s="10">
         <f t="shared" si="4"/>
         <v>0.99284501043036377</v>
       </c>
-      <c r="G46" s="4"/>
-      <c r="I46">
+      <c r="J46" s="4"/>
+      <c r="L46">
         <v>1.3461367977004299</v>
       </c>
-      <c r="J46">
+      <c r="M46">
         <v>1.32904261090945</v>
       </c>
-      <c r="K46" s="10">
+      <c r="N46" s="10">
         <f t="shared" si="5"/>
         <v>0.98730130041747499</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>10</v>
       </c>
@@ -5561,27 +5994,27 @@
       <c r="D47">
         <v>1.31789010731641</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>1.3448930260504799</v>
       </c>
-      <c r="F47" s="10">
+      <c r="I47" s="10">
         <f t="shared" si="4"/>
         <v>1.0204895071175968</v>
       </c>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47">
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47">
         <v>1.31846450590491</v>
       </c>
-      <c r="J47">
+      <c r="M47">
         <v>1.3511493506913199</v>
       </c>
-      <c r="K47" s="11">
+      <c r="N47" s="11">
         <f t="shared" si="5"/>
         <v>1.0247900831914902</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>25</v>
       </c>
@@ -5589,26 +6022,26 @@
       <c r="D48">
         <v>1.32036564820574</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>1.3268512139816999</v>
       </c>
-      <c r="F48" s="10">
+      <c r="I48" s="10">
         <f t="shared" si="4"/>
         <v>1.0049119467662411</v>
       </c>
-      <c r="G48" s="4"/>
-      <c r="I48">
+      <c r="J48" s="4"/>
+      <c r="L48">
         <v>1.33152629750905</v>
       </c>
-      <c r="J48">
+      <c r="M48">
         <v>1.33015612015508</v>
       </c>
-      <c r="K48" s="10">
+      <c r="N48" s="10">
         <f t="shared" si="5"/>
         <v>0.99897097236717491</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>50</v>
       </c>
@@ -5616,27 +6049,27 @@
       <c r="D49">
         <v>1.3197738196808499</v>
       </c>
-      <c r="E49">
+      <c r="F49">
         <v>1.3126564921716899</v>
       </c>
-      <c r="F49" s="10">
+      <c r="I49" s="10">
         <f t="shared" si="4"/>
         <v>0.99460716116426584</v>
       </c>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49">
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49">
         <v>1.32005527665466</v>
       </c>
-      <c r="J49">
+      <c r="M49">
         <v>1.30244954906179</v>
       </c>
-      <c r="K49" s="11">
+      <c r="N49" s="11">
         <f t="shared" si="5"/>
         <v>0.98666288608952257</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>75</v>
       </c>
@@ -5644,26 +6077,26 @@
       <c r="D50">
         <v>1.29935652652886</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>1.32473430230751</v>
       </c>
-      <c r="F50" s="10">
+      <c r="I50" s="10">
         <f t="shared" si="4"/>
         <v>1.0195310334465668</v>
       </c>
-      <c r="G50" s="4"/>
-      <c r="I50">
+      <c r="J50" s="4"/>
+      <c r="L50">
         <v>1.30908256842566</v>
       </c>
-      <c r="J50">
+      <c r="M50">
         <v>1.30672475018709</v>
       </c>
-      <c r="K50" s="10">
+      <c r="N50" s="10">
         <f t="shared" si="5"/>
         <v>0.99819887736996948</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>100</v>
       </c>
@@ -5671,27 +6104,27 @@
       <c r="D51">
         <v>1.33910590256307</v>
       </c>
-      <c r="E51">
+      <c r="F51">
         <v>1.3167897334910501</v>
       </c>
-      <c r="F51" s="10">
+      <c r="I51" s="10">
         <f t="shared" si="4"/>
         <v>0.98333502299608533</v>
       </c>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51">
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51">
         <v>1.3171859836539099</v>
       </c>
-      <c r="J51">
+      <c r="M51">
         <v>1.31060168409573</v>
       </c>
-      <c r="K51" s="11">
+      <c r="N51" s="11">
         <f t="shared" si="5"/>
         <v>0.99500123775997451</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>150</v>
       </c>
@@ -5699,26 +6132,26 @@
       <c r="D52">
         <v>1.3346899335651701</v>
       </c>
-      <c r="E52">
+      <c r="F52">
         <v>1.3164282135057199</v>
       </c>
-      <c r="F52" s="10">
+      <c r="I52" s="10">
         <f t="shared" si="4"/>
         <v>0.98631763108404502</v>
       </c>
-      <c r="G52" s="4"/>
-      <c r="I52">
+      <c r="J52" s="4"/>
+      <c r="L52">
         <v>1.28924587434467</v>
       </c>
-      <c r="J52">
+      <c r="M52">
         <v>1.3011790803332</v>
       </c>
-      <c r="K52" s="10">
+      <c r="N52" s="10">
         <f t="shared" si="5"/>
         <v>1.0092559582512495</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>250</v>
       </c>
@@ -5726,27 +6159,27 @@
       <c r="D53">
         <v>1.29678717701069</v>
       </c>
-      <c r="E53">
+      <c r="F53">
         <v>1.33451901185347</v>
       </c>
-      <c r="F53" s="10">
+      <c r="I53" s="10">
         <f t="shared" si="4"/>
         <v>1.0290963972436542</v>
       </c>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53">
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53">
         <v>1.2845821783281699</v>
       </c>
-      <c r="J53">
+      <c r="M53">
         <v>1.27732476166037</v>
       </c>
-      <c r="K53" s="11">
+      <c r="N53" s="11">
         <f t="shared" si="5"/>
         <v>0.99435036793267273</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>500</v>
       </c>
@@ -5754,26 +6187,26 @@
       <c r="D54">
         <v>1.2662694099393199</v>
       </c>
-      <c r="E54">
+      <c r="F54">
         <v>1.2620512370753201</v>
       </c>
-      <c r="F54" s="10">
+      <c r="I54" s="10">
         <f t="shared" si="4"/>
         <v>0.99666881879093805</v>
       </c>
-      <c r="G54" s="4"/>
-      <c r="I54">
+      <c r="J54" s="4"/>
+      <c r="L54">
         <v>1.2051198250164299</v>
       </c>
-      <c r="J54">
+      <c r="M54">
         <v>1.19710463230099</v>
       </c>
-      <c r="K54" s="10">
+      <c r="N54" s="10">
         <f t="shared" si="5"/>
         <v>0.99334904915755518</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>750</v>
       </c>
@@ -5781,22 +6214,26 @@
       <c r="D55">
         <v>1.23279071771682</v>
       </c>
-      <c r="E55">
+      <c r="F55">
         <v>1.23649350366719</v>
       </c>
-      <c r="F55" s="10">
+      <c r="I55" s="10">
         <f t="shared" si="4"/>
         <v>1.0030035803296993</v>
       </c>
-      <c r="G55" s="5"/>
-      <c r="I55">
+      <c r="J55" s="5"/>
+      <c r="L55">
         <v>1.1807532343395699</v>
       </c>
-      <c r="J55">
+      <c r="M55">
         <v>1.1563239206929501</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N55" s="10">
+        <f t="shared" si="5"/>
+        <v>0.97931039870470149</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>999.99</v>
       </c>
@@ -5804,48 +6241,58 @@
       <c r="D56">
         <v>1.1928852496040101</v>
       </c>
-      <c r="E56">
+      <c r="F56">
         <v>1.2106403902979499</v>
       </c>
-      <c r="F56" s="10">
+      <c r="I56" s="10">
         <f t="shared" si="4"/>
         <v>1.0148841983751864</v>
       </c>
-      <c r="G56" s="5"/>
-      <c r="I56">
+      <c r="J56" s="5"/>
+      <c r="L56">
         <v>1.13357719050286</v>
       </c>
-      <c r="J56">
+      <c r="M56">
         <v>1.1342010761596699</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N56" s="11">
+        <f t="shared" si="5"/>
+        <v>1.0005503689224138</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C59" s="12" t="s">
         <v>5</v>
       </c>
       <c r="D59" s="12"/>
-      <c r="E59" s="13"/>
+      <c r="E59" s="12"/>
       <c r="F59" s="13"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
+      <c r="G59" s="13"/>
+      <c r="H59" s="13"/>
+      <c r="I59" s="13"/>
       <c r="K59" s="2"/>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L59" s="2"/>
+      <c r="M59" s="2"/>
+      <c r="N59" s="2"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C60" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D60" s="3"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="3"/>
-      <c r="H60" s="3" t="s">
+      <c r="E60" s="3"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="9"/>
+      <c r="I60" s="3"/>
+      <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I60" s="3"/>
-      <c r="J60" s="9"/>
-      <c r="K60" s="9"/>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L60" s="3"/>
+      <c r="M60" s="9"/>
+      <c r="N60" s="9"/>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
         <v>0</v>
       </c>
@@ -5856,27 +6303,30 @@
       <c r="D61" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E61" s="6" t="s">
+      <c r="E61" s="6"/>
+      <c r="F61" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F61" s="7" t="s">
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="G61" s="8"/>
-      <c r="H61" s="6" t="s">
+      <c r="J61" s="8"/>
+      <c r="K61" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="I61" s="6" t="s">
+      <c r="L61" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J61" s="6" t="s">
+      <c r="M61" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="K61" s="7" t="s">
+      <c r="N61" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>0.1</v>
       </c>
@@ -5887,27 +6337,30 @@
       <c r="D62" s="2">
         <v>1.9785240862768899E-5</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62" s="2"/>
+      <c r="F62" s="2">
         <v>1.9417624590728801E-5</v>
       </c>
-      <c r="F62" s="10">
-        <f>E62/D62</f>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="10">
+        <f>F62/D62</f>
         <v>0.98141967163352228</v>
       </c>
-      <c r="G62" s="4"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="2">
+      <c r="J62" s="4"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="2">
         <v>2.44555572729164E-5</v>
       </c>
-      <c r="J62" s="2">
+      <c r="M62" s="2">
         <v>2.3173152783100001E-5</v>
       </c>
-      <c r="K62" s="10">
-        <f>J62/I62</f>
+      <c r="N62" s="10">
+        <f>M62/L62</f>
         <v>0.94756183735642718</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>0.5</v>
       </c>
@@ -5918,26 +6371,28 @@
       <c r="D63">
         <v>1.02051178015395E-4</v>
       </c>
-      <c r="E63" s="2">
+      <c r="F63" s="2">
         <v>9.4705678455829002E-5</v>
       </c>
-      <c r="F63" s="10">
-        <f t="shared" ref="F63:F74" si="6">E63/D63</f>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="10">
+        <f t="shared" ref="I63:I74" si="6">F63/D63</f>
         <v>0.92802141334950694</v>
       </c>
-      <c r="G63" s="4"/>
-      <c r="I63">
+      <c r="J63" s="4"/>
+      <c r="L63">
         <v>1.237590596311E-4</v>
       </c>
-      <c r="J63">
+      <c r="M63">
         <v>1.2781285534871299E-4</v>
       </c>
-      <c r="K63" s="11">
-        <f t="shared" ref="K63:K74" si="7">J63/I63</f>
+      <c r="N63" s="11">
+        <f t="shared" ref="N63:N74" si="7">M63/L63</f>
         <v>1.0327555471873857</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>1</v>
       </c>
@@ -5948,26 +6403,26 @@
       <c r="D64">
         <v>2.0004896550590901E-4</v>
       </c>
-      <c r="E64">
+      <c r="F64">
         <v>2.0519183351723301E-4</v>
       </c>
-      <c r="F64" s="10">
+      <c r="I64" s="10">
         <f t="shared" si="6"/>
         <v>1.0257080460192236</v>
       </c>
-      <c r="G64" s="4"/>
-      <c r="I64">
+      <c r="J64" s="4"/>
+      <c r="L64">
         <v>2.47009346021372E-4</v>
       </c>
-      <c r="J64">
+      <c r="M64">
         <v>2.5056736662623701E-4</v>
       </c>
-      <c r="K64" s="10">
+      <c r="N64" s="10">
         <f t="shared" si="7"/>
         <v>1.0144043966844767</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>10</v>
       </c>
@@ -5978,26 +6433,26 @@
       <c r="D65">
         <v>1.9727739159685499E-3</v>
       </c>
-      <c r="E65">
+      <c r="F65">
         <v>2.1002402963605799E-3</v>
       </c>
-      <c r="F65" s="10">
+      <c r="I65" s="10">
         <f t="shared" si="6"/>
         <v>1.0646127665011473</v>
       </c>
-      <c r="G65" s="4"/>
-      <c r="I65">
+      <c r="J65" s="4"/>
+      <c r="L65">
         <v>2.41443999850058E-3</v>
       </c>
-      <c r="J65">
+      <c r="M65">
         <v>2.5624129143282902E-3</v>
       </c>
-      <c r="K65" s="11">
+      <c r="N65" s="11">
         <f t="shared" si="7"/>
         <v>1.0612866403470804</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>25</v>
       </c>
@@ -6008,26 +6463,26 @@
       <c r="D66">
         <v>4.9269907229743297E-3</v>
       </c>
-      <c r="E66">
+      <c r="F66">
         <v>5.2981099306138504E-3</v>
       </c>
-      <c r="F66" s="10">
+      <c r="I66" s="10">
         <f t="shared" si="6"/>
         <v>1.0753237074121145</v>
       </c>
-      <c r="G66" s="4"/>
-      <c r="I66">
+      <c r="J66" s="4"/>
+      <c r="L66">
         <v>6.11270182240103E-3</v>
       </c>
-      <c r="J66">
+      <c r="M66">
         <v>6.4145321839513504E-3</v>
       </c>
-      <c r="K66" s="10">
+      <c r="N66" s="10">
         <f t="shared" si="7"/>
         <v>1.0493775699060295</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>50</v>
       </c>
@@ -6038,26 +6493,26 @@
       <c r="D67">
         <v>9.7820010092556295E-3</v>
       </c>
-      <c r="E67">
+      <c r="F67">
         <v>1.0195154351149101E-2</v>
       </c>
-      <c r="F67" s="10">
+      <c r="I67" s="10">
         <f t="shared" si="6"/>
         <v>1.0422360763919929</v>
       </c>
-      <c r="G67" s="4"/>
-      <c r="I67">
+      <c r="J67" s="4"/>
+      <c r="L67">
         <v>1.20970549355645E-2</v>
       </c>
-      <c r="J67">
+      <c r="M67">
         <v>1.24175942421624E-2</v>
       </c>
-      <c r="K67" s="11">
+      <c r="N67" s="11">
         <f t="shared" si="7"/>
         <v>1.0264973010625533</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>75</v>
       </c>
@@ -6068,26 +6523,26 @@
       <c r="D68">
         <v>1.43763436727791E-2</v>
       </c>
-      <c r="E68">
+      <c r="F68">
         <v>1.5782984835099299E-2</v>
       </c>
-      <c r="F68" s="10">
+      <c r="I68" s="10">
         <f t="shared" si="6"/>
         <v>1.0978441524727602</v>
       </c>
-      <c r="G68" s="4"/>
-      <c r="I68">
+      <c r="J68" s="4"/>
+      <c r="L68">
         <v>1.8002551123509802E-2</v>
       </c>
-      <c r="J68">
+      <c r="M68">
         <v>1.8976376994297401E-2</v>
       </c>
-      <c r="K68" s="10">
+      <c r="N68" s="10">
         <f t="shared" si="7"/>
         <v>1.0540937706054263</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>100</v>
       </c>
@@ -6098,26 +6553,26 @@
       <c r="D69">
         <v>2.00458898906196E-2</v>
       </c>
-      <c r="E69">
+      <c r="F69">
         <v>2.0804120655568799E-2</v>
       </c>
-      <c r="F69" s="10">
+      <c r="I69" s="10">
         <f t="shared" si="6"/>
         <v>1.0378247495664441</v>
       </c>
-      <c r="G69" s="4"/>
-      <c r="I69">
+      <c r="J69" s="4"/>
+      <c r="L69">
         <v>2.4309982506840501E-2</v>
       </c>
-      <c r="J69">
+      <c r="M69">
         <v>2.56065505285916E-2</v>
       </c>
-      <c r="K69" s="11">
+      <c r="N69" s="11">
         <f t="shared" si="7"/>
         <v>1.0533347986320543</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>150</v>
       </c>
@@ -6128,26 +6583,26 @@
       <c r="D70">
         <v>3.0432830381329601E-2</v>
       </c>
-      <c r="E70">
+      <c r="F70">
         <v>3.14434702136525E-2</v>
       </c>
-      <c r="F70" s="10">
+      <c r="I70" s="10">
         <f t="shared" si="6"/>
         <v>1.0332088675177227</v>
       </c>
-      <c r="G70" s="4"/>
-      <c r="I70">
+      <c r="J70" s="4"/>
+      <c r="L70">
         <v>3.5308084946377202E-2</v>
       </c>
-      <c r="J70">
+      <c r="M70">
         <v>3.7911161854217702E-2</v>
       </c>
-      <c r="K70" s="10">
+      <c r="N70" s="10">
         <f t="shared" si="7"/>
         <v>1.0737246699104135</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>250</v>
       </c>
@@ -6158,26 +6613,26 @@
       <c r="D71">
         <v>4.89210306757277E-2</v>
       </c>
-      <c r="E71">
+      <c r="F71">
         <v>5.3975920537313898E-2</v>
       </c>
-      <c r="F71" s="10">
+      <c r="I71" s="10">
         <f t="shared" si="6"/>
         <v>1.1033275421994369</v>
       </c>
-      <c r="G71" s="4"/>
-      <c r="I71">
+      <c r="J71" s="4"/>
+      <c r="L71">
         <v>5.8808790512075798E-2</v>
       </c>
-      <c r="J71">
+      <c r="M71">
         <v>6.2265324575410202E-2</v>
       </c>
-      <c r="K71" s="11">
+      <c r="N71" s="11">
         <f t="shared" si="7"/>
         <v>1.0587758060187387</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>500</v>
       </c>
@@ -6188,26 +6643,26 @@
       <c r="D72">
         <v>9.6226590649767796E-2</v>
       </c>
-      <c r="E72">
+      <c r="F72">
         <v>0.10212774105006001</v>
       </c>
-      <c r="F72" s="10">
+      <c r="I72" s="10">
         <f t="shared" si="6"/>
         <v>1.0613255687481478</v>
       </c>
-      <c r="G72" s="4"/>
-      <c r="I72">
+      <c r="J72" s="4"/>
+      <c r="L72">
         <v>0.11146020972599301</v>
       </c>
-      <c r="J72">
+      <c r="M72">
         <v>0.118001707852343</v>
       </c>
-      <c r="K72" s="10">
+      <c r="N72" s="10">
         <f t="shared" si="7"/>
         <v>1.0586890886212328</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>750</v>
       </c>
@@ -6215,26 +6670,26 @@
       <c r="D73">
         <v>0.140294088260282</v>
       </c>
-      <c r="E73">
+      <c r="F73">
         <v>0.15225875418305601</v>
       </c>
-      <c r="F73" s="10">
+      <c r="I73" s="10">
         <f t="shared" si="6"/>
         <v>1.0852827519045309</v>
       </c>
-      <c r="G73" s="5"/>
-      <c r="I73">
+      <c r="J73" s="5"/>
+      <c r="L73">
         <v>0.164782092113922</v>
       </c>
-      <c r="J73">
+      <c r="M73">
         <v>0.171436913407884</v>
       </c>
-      <c r="K73" s="11">
+      <c r="N73" s="11">
         <f t="shared" si="7"/>
         <v>1.0403855856458066</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>999.99</v>
       </c>
@@ -6242,52 +6697,58 @@
       <c r="D74">
         <v>0.181401571560247</v>
       </c>
-      <c r="E74">
+      <c r="F74">
         <v>0.20058148390920799</v>
       </c>
-      <c r="F74" s="10">
+      <c r="I74" s="10">
         <f t="shared" si="6"/>
         <v>1.1057317871283765</v>
       </c>
-      <c r="G74" s="5"/>
-      <c r="I74">
+      <c r="J74" s="5"/>
+      <c r="L74">
         <v>0.211482254080264</v>
       </c>
-      <c r="J74">
+      <c r="M74">
         <v>0.22688990016688301</v>
       </c>
-      <c r="K74" s="10">
+      <c r="N74" s="10">
         <f t="shared" si="7"/>
         <v>1.0728555034256981</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C76" s="12" t="s">
         <v>10</v>
       </c>
       <c r="D76" s="12"/>
-      <c r="E76" s="13"/>
+      <c r="E76" s="12"/>
       <c r="F76" s="13"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
+      <c r="G76" s="13"/>
+      <c r="H76" s="13"/>
+      <c r="I76" s="13"/>
       <c r="K76" s="2"/>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L76" s="2"/>
+      <c r="M76" s="2"/>
+      <c r="N76" s="2"/>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C77" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D77" s="3"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="3"/>
-      <c r="H77" s="3" t="s">
+      <c r="E77" s="3"/>
+      <c r="F77" s="9"/>
+      <c r="G77" s="9"/>
+      <c r="H77" s="9"/>
+      <c r="I77" s="3"/>
+      <c r="K77" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I77" s="3"/>
-      <c r="J77" s="9"/>
-      <c r="K77" s="9"/>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L77" s="3"/>
+      <c r="M77" s="9"/>
+      <c r="N77" s="9"/>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
         <v>0</v>
       </c>
@@ -6298,27 +6759,30 @@
       <c r="D78" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E78" s="6" t="s">
+      <c r="E78" s="6"/>
+      <c r="F78" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F78" s="7" t="s">
+      <c r="G78" s="6"/>
+      <c r="H78" s="6"/>
+      <c r="I78" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="G78" s="8"/>
-      <c r="H78" s="6" t="s">
+      <c r="J78" s="8"/>
+      <c r="K78" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="I78" s="6" t="s">
+      <c r="L78" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J78" s="6" t="s">
+      <c r="M78" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="K78" s="7" t="s">
+      <c r="N78" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>0.1</v>
       </c>
@@ -6329,27 +6793,30 @@
       <c r="D79" s="2">
         <v>2.8143173972499801E-7</v>
       </c>
-      <c r="E79" s="2">
+      <c r="E79" s="2"/>
+      <c r="F79" s="2">
         <v>1.46150091119403E-6</v>
       </c>
-      <c r="F79" s="10">
-        <f t="shared" ref="F79:F90" si="8">F62*((E79/E62)^2 +(D79/D62)^2)^0.5</f>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="10">
+        <f t="shared" ref="I79:I90" si="8">I62*((F79/F62)^2 +(D79/D62)^2)^0.5</f>
         <v>7.5175789820697683E-2</v>
       </c>
-      <c r="G79" s="4"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2">
+      <c r="J79" s="4"/>
+      <c r="K79" s="2"/>
+      <c r="L79" s="2">
         <v>2.4434932696069799E-5</v>
       </c>
-      <c r="J79" s="2">
+      <c r="M79" s="2">
         <v>2.5518609602937599E-5</v>
       </c>
-      <c r="K79" s="10">
-        <f>J79/I79</f>
+      <c r="N79" s="10">
+        <f>M79/L79</f>
         <v>1.0443494942403546</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>0.5</v>
       </c>
@@ -6360,26 +6827,29 @@
       <c r="D80" s="2">
         <v>1.5222069872849199E-6</v>
       </c>
-      <c r="E80" s="2">
+      <c r="E80" s="2"/>
+      <c r="F80" s="2">
         <v>3.7622530224669299E-6</v>
       </c>
-      <c r="F80" s="10">
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
+      <c r="I80" s="10">
         <f t="shared" si="8"/>
         <v>3.9379446327356661E-2</v>
       </c>
-      <c r="G80" s="4"/>
-      <c r="I80">
+      <c r="J80" s="4"/>
+      <c r="L80">
         <v>3.6561489620800698E-3</v>
       </c>
-      <c r="J80">
+      <c r="M80">
         <v>3.8583728177792702E-3</v>
       </c>
-      <c r="K80" s="11">
-        <f t="shared" ref="K80:K89" si="9">J80/I80</f>
+      <c r="N80" s="11">
+        <f t="shared" ref="N80:N89" si="9">M80/L80</f>
         <v>1.0553106172085915</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>1</v>
       </c>
@@ -6390,26 +6860,29 @@
       <c r="D81" s="2">
         <v>2.33807312394273E-6</v>
       </c>
-      <c r="E81" s="2">
+      <c r="E81" s="2"/>
+      <c r="F81" s="2">
         <v>6.5127278910264096E-6</v>
       </c>
-      <c r="F81" s="10">
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+      <c r="I81" s="10">
         <f t="shared" si="8"/>
         <v>3.4692692812303069E-2</v>
       </c>
-      <c r="G81" s="4"/>
-      <c r="I81">
+      <c r="J81" s="4"/>
+      <c r="L81">
         <v>7.3167786817070497E-3</v>
       </c>
-      <c r="J81">
+      <c r="M81">
         <v>7.7206053021012903E-3</v>
       </c>
-      <c r="K81" s="10">
+      <c r="N81" s="10">
         <f t="shared" si="9"/>
         <v>1.0551918594181156</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>10</v>
       </c>
@@ -6420,26 +6893,29 @@
       <c r="D82" s="2">
         <v>2.7701090496064399E-5</v>
       </c>
-      <c r="E82" s="2">
+      <c r="E82" s="2"/>
+      <c r="F82" s="2">
         <v>3.8011060965548303E-5</v>
       </c>
-      <c r="F82" s="10">
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
+      <c r="I82" s="10">
         <f t="shared" si="8"/>
         <v>2.4386896067040687E-2</v>
       </c>
-      <c r="G82" s="4"/>
-      <c r="I82">
+      <c r="J82" s="4"/>
+      <c r="L82">
         <v>1.4655010559957399E-2</v>
       </c>
-      <c r="J82">
+      <c r="M82">
         <v>1.54708347850845E-2</v>
       </c>
-      <c r="K82" s="11">
+      <c r="N82" s="11">
         <f t="shared" si="9"/>
         <v>1.0556686207621178</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>25</v>
       </c>
@@ -6450,26 +6926,29 @@
       <c r="D83" s="2">
         <v>8.0985715172972504E-5</v>
       </c>
-      <c r="E83" s="2">
+      <c r="E83" s="2"/>
+      <c r="F83" s="2">
         <v>8.2936422592517207E-5</v>
       </c>
-      <c r="F83" s="10">
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="10">
         <f t="shared" si="8"/>
         <v>2.4408348565916203E-2</v>
       </c>
-      <c r="G83" s="4"/>
-      <c r="I83">
+      <c r="J83" s="4"/>
+      <c r="L83">
         <v>2.20520227131588E-2</v>
       </c>
-      <c r="J83">
+      <c r="M83">
         <v>2.3279563002525702E-2</v>
       </c>
-      <c r="K83" s="10">
+      <c r="N83" s="10">
         <f t="shared" si="9"/>
         <v>1.0556656550437167</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>50</v>
       </c>
@@ -6480,26 +6959,26 @@
       <c r="D84">
         <v>1.14857385321631E-4</v>
       </c>
-      <c r="E84">
+      <c r="F84">
         <v>1.40546480514001E-4</v>
       </c>
-      <c r="F84" s="10">
+      <c r="I84" s="10">
         <f t="shared" si="8"/>
         <v>1.8873133491714433E-2</v>
       </c>
-      <c r="G84" s="4"/>
-      <c r="I84">
+      <c r="J84" s="4"/>
+      <c r="L84">
         <v>2.9379142051595902E-2</v>
       </c>
-      <c r="J84">
+      <c r="M84">
         <v>3.0966693098777899E-2</v>
       </c>
-      <c r="K84" s="11">
+      <c r="N84" s="11">
         <f t="shared" si="9"/>
         <v>1.0540366714723639</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>75</v>
       </c>
@@ -6510,26 +6989,26 @@
       <c r="D85">
         <v>1.6692001786006801E-4</v>
       </c>
-      <c r="E85">
+      <c r="F85">
         <v>2.2355768083561999E-4</v>
       </c>
-      <c r="F85" s="10">
+      <c r="I85" s="10">
         <f t="shared" si="8"/>
         <v>2.0107088599017175E-2</v>
       </c>
-      <c r="G85" s="4"/>
-      <c r="I85">
+      <c r="J85" s="4"/>
+      <c r="L85">
         <v>3.6804448452257998E-2</v>
       </c>
-      <c r="J85">
+      <c r="M85">
         <v>3.8844686371276298E-2</v>
       </c>
-      <c r="K85" s="10">
+      <c r="N85" s="10">
         <f t="shared" si="9"/>
         <v>1.0554345467685748</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>100</v>
       </c>
@@ -6540,26 +7019,26 @@
       <c r="D86">
         <v>2.77931449091848E-4</v>
       </c>
-      <c r="E86">
+      <c r="F86">
         <v>2.1739476286188801E-4</v>
       </c>
-      <c r="F86" s="10">
+      <c r="I86" s="10">
         <f t="shared" si="8"/>
         <v>1.8018315350781095E-2</v>
       </c>
-      <c r="G86" s="4"/>
-      <c r="I86">
+      <c r="J86" s="4"/>
+      <c r="L86">
         <v>6.1567552933483601E-2</v>
       </c>
-      <c r="J86">
+      <c r="M86">
         <v>6.4958585716827305E-2</v>
       </c>
-      <c r="K86" s="11">
+      <c r="N86" s="11">
         <f t="shared" si="9"/>
         <v>1.0550782453057264</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>150</v>
       </c>
@@ -6570,26 +7049,26 @@
       <c r="D87">
         <v>3.3888866496247497E-4</v>
       </c>
-      <c r="E87">
+      <c r="F87">
         <v>4.2099807481717899E-4</v>
       </c>
-      <c r="F87" s="10">
+      <c r="I87" s="10">
         <f t="shared" si="8"/>
         <v>1.7992932963347683E-2</v>
       </c>
-      <c r="G87" s="4"/>
-      <c r="I87">
+      <c r="J87" s="4"/>
+      <c r="L87">
         <v>0.124585487877085</v>
       </c>
-      <c r="J87">
+      <c r="M87">
         <v>0.13088073929294</v>
       </c>
-      <c r="K87" s="10">
+      <c r="N87" s="10">
         <f t="shared" si="9"/>
         <v>1.0505295722890764</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>250</v>
       </c>
@@ -6600,26 +7079,26 @@
       <c r="D88">
         <v>6.0844630496931901E-4</v>
       </c>
-      <c r="E88">
+      <c r="F88">
         <v>7.1735921087181002E-4</v>
       </c>
-      <c r="F88" s="10">
+      <c r="I88" s="10">
         <f t="shared" si="8"/>
         <v>2.0082997872230529E-2</v>
       </c>
-      <c r="G88" s="4"/>
-      <c r="I88">
+      <c r="J88" s="4"/>
+      <c r="L88">
         <v>0.188315720076114</v>
       </c>
-      <c r="J88">
+      <c r="M88">
         <v>0.19671890522285099</v>
       </c>
-      <c r="K88" s="11">
+      <c r="N88" s="11">
         <f t="shared" si="9"/>
         <v>1.0446228554012409</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>500</v>
       </c>
@@ -6630,52 +7109,52 @@
       <c r="D89">
         <v>1.3901143553867799E-3</v>
       </c>
-      <c r="E89">
+      <c r="F89">
         <v>1.45703989958587E-3</v>
       </c>
-      <c r="F89" s="10">
+      <c r="I89" s="10">
         <f t="shared" si="8"/>
         <v>2.1548753693625213E-2</v>
       </c>
-      <c r="G89" s="4"/>
-      <c r="I89">
+      <c r="J89" s="4"/>
+      <c r="L89">
         <v>0.25212873564071397</v>
       </c>
-      <c r="J89">
+      <c r="M89">
         <v>0.26159631710660702</v>
       </c>
-      <c r="K89" s="10">
+      <c r="N89" s="10">
         <f t="shared" si="9"/>
         <v>1.0375505847908761</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>750</v>
       </c>
       <c r="D90">
         <v>1.59024586083695E-3</v>
       </c>
-      <c r="E90">
+      <c r="F90">
         <v>1.88927153592098E-3</v>
       </c>
-      <c r="F90" s="10">
+      <c r="I90" s="10">
         <f t="shared" si="8"/>
         <v>1.8239532257896197E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>999.99</v>
       </c>
       <c r="D91">
         <v>2.0916951916344802E-3</v>
       </c>
-      <c r="E91">
+      <c r="F91">
         <v>2.14759074882869E-3</v>
       </c>
-      <c r="F91" s="10">
-        <f>F74*((E91/E74)^2 +(D91/D74)^2)^0.5</f>
+      <c r="I91" s="10">
+        <f>I74*((F91/F74)^2 +(D91/D74)^2)^0.5</f>
         <v>1.7398828006913617E-2</v>
       </c>
     </row>

--- a/Jupyter/Wedge/wedge_data_2026-03-25.xlsx
+++ b/Jupyter/Wedge/wedge_data_2026-03-25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\patri\projects\emma-openmc\Jupyter\Wedge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2727A53E-B710-49C1-8960-17B14C6CB01B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F889C1-F7F7-41B5-8112-3ECB99FD4818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,8 +84,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000000"/>
+    <numFmt numFmtId="169" formatCode="0.000"/>
     <numFmt numFmtId="173" formatCode="0.00000000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
@@ -173,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -190,6 +191,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -335,7 +337,7 @@
             <c:numRef>
               <c:f>'Sheet 1'!$H$24:$H$36</c:f>
               <c:numCache>
-                <c:formatCode>0.000000</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>0.67015864678428949</c:v>
@@ -609,7 +611,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.000000" sourceLinked="1"/>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4753,7 +4755,8 @@
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
     <col min="2" max="2" width="2.109375" customWidth="1"/>
     <col min="3" max="5" width="12.21875" customWidth="1"/>
-    <col min="6" max="8" width="15.88671875" customWidth="1"/>
+    <col min="6" max="7" width="15.88671875" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" customWidth="1"/>
     <col min="9" max="9" width="15.109375" customWidth="1"/>
     <col min="10" max="10" width="2.77734375" customWidth="1"/>
     <col min="11" max="14" width="13.33203125" customWidth="1"/>
@@ -5385,16 +5388,16 @@
       <c r="D24" s="2">
         <v>3.4601339198647797E-5</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="17">
         <v>1.22883732368375E-8</v>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="17">
         <v>2.3188386654289999E-5</v>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="17">
         <v>2.5713213345718999E-7</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="16">
         <f>F24/D24</f>
         <v>0.67015864678428949</v>
       </c>
@@ -5422,16 +5425,16 @@
       <c r="D25">
         <v>1.7267075850167999E-4</v>
       </c>
-      <c r="E25" s="16">
+      <c r="E25" s="17">
         <v>7.3730405114227898E-8</v>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="17">
         <v>1.16379113471186E-4</v>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="17">
         <v>4.9685826902563597E-7</v>
       </c>
-      <c r="H25" s="10">
+      <c r="H25" s="16">
         <f>F25/D25</f>
         <v>0.67399433743759052</v>
       </c>
@@ -5457,16 +5460,16 @@
       <c r="D26">
         <v>3.4444202449192702E-4</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E26" s="17">
         <v>1.02701859340892E-7</v>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="17">
         <v>2.31665379952172E-4</v>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="17">
         <v>6.9232886194979901E-7</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="16">
         <f>F26/D26</f>
         <v>0.67258163487423628</v>
       </c>
@@ -5492,16 +5495,16 @@
       <c r="D27">
         <v>3.33054467027722E-3</v>
       </c>
-      <c r="E27" s="16">
+      <c r="E27" s="17">
         <v>3.1023196230951202E-6</v>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="17">
         <v>2.3274949085023899E-3</v>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="17">
         <v>7.3576810457546899E-6</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="16">
         <f>F27/D27</f>
         <v>0.69883311557825745</v>
       </c>
@@ -5527,16 +5530,16 @@
       <c r="D28">
         <v>7.9007108136224906E-3</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="17">
         <v>2.1579374269995798E-5</v>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="17">
         <v>5.7868683352336496E-3</v>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="17">
         <v>2.2153397083295701E-5</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="16">
         <f>F28/D28</f>
         <v>0.73244907600666376</v>
       </c>
@@ -5562,16 +5565,16 @@
       <c r="D29">
         <v>1.48099690035684E-2</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="17">
         <v>3.5619384608241799E-5</v>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="17">
         <v>1.1357972286110201E-2</v>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="17">
         <v>3.9960656049596501E-5</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="16">
         <f>F29/D29</f>
         <v>0.76691398093902452</v>
       </c>
@@ -5597,16 +5600,16 @@
       <c r="D30">
         <v>2.1060130702738999E-2</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="17">
         <v>3.0830038687911403E-5</v>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="17">
         <v>1.6724313084056999E-2</v>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="17">
         <v>4.6773312275541899E-5</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="16">
         <f>F30/D30</f>
         <v>0.79412199858198884</v>
       </c>
@@ -5632,16 +5635,16 @@
       <c r="D31">
         <v>2.67600755292417E-2</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="17">
         <v>6.1301138330409899E-5</v>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="17">
         <v>2.2149757308928399E-2</v>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="17">
         <v>5.1020148947823797E-5</v>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="16">
         <f>F31/D31</f>
         <v>0.82771654679092965</v>
       </c>
@@ -5667,16 +5670,16 @@
       <c r="D32">
         <v>3.6782709718709998E-2</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="17">
         <v>1.97489580151579E-4</v>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="17">
         <v>3.2103137598192298E-2</v>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="17">
         <v>2.08831333646651E-4</v>
       </c>
-      <c r="H32" s="10">
+      <c r="H32" s="16">
         <f>F32/D32</f>
         <v>0.87277793951821403</v>
       </c>
@@ -5702,16 +5705,16 @@
       <c r="D33">
         <v>5.6309750104400702E-2</v>
       </c>
-      <c r="E33" s="16">
+      <c r="E33" s="17">
         <v>2.51687827781958E-4</v>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="17">
         <v>5.1114734736025402E-2</v>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="17">
         <v>2.8833834514146198E-4</v>
       </c>
-      <c r="H33" s="10">
+      <c r="H33" s="16">
         <f>F33/D33</f>
         <v>0.90774216971761523</v>
       </c>
@@ -5737,16 +5740,16 @@
       <c r="D34">
         <v>9.4384365104793602E-2</v>
       </c>
-      <c r="E34" s="16">
+      <c r="E34" s="17">
         <v>3.7802904257795602E-4</v>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="17">
         <v>9.1445222619505398E-2</v>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="17">
         <v>4.4906828447954003E-4</v>
       </c>
-      <c r="H34" s="10">
+      <c r="H34" s="16">
         <f>F34/D34</f>
         <v>0.96885985849430767</v>
       </c>
@@ -5772,16 +5775,16 @@
       <c r="D35">
         <v>0.12681392305883499</v>
       </c>
-      <c r="E35" s="16">
+      <c r="E35" s="17">
         <v>3.7117560576619898E-4</v>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="17">
         <v>0.12725844081883</v>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="17">
         <v>3.9277512684765298E-4</v>
       </c>
-      <c r="H35" s="10">
+      <c r="H35" s="16">
         <f>F35/D35</f>
         <v>1.0035052756769365</v>
       </c>
@@ -5807,16 +5810,16 @@
       <c r="D36">
         <v>0.15510900896549801</v>
       </c>
-      <c r="E36" s="16">
+      <c r="E36" s="17">
         <v>5.7851797067085496E-4</v>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="17">
         <v>0.157583868759714</v>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="17">
         <v>5.8700051779191705E-4</v>
       </c>
-      <c r="H36" s="10">
+      <c r="H36" s="16">
         <f>F36/D36</f>
         <v>1.0159556160581653</v>
       </c>

--- a/Jupyter/Wedge/wedge_data_2026-03-25.xlsx
+++ b/Jupyter/Wedge/wedge_data_2026-03-25.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\patri\projects\emma-openmc\Jupyter\Wedge\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ppark\projects\emma-openmc\Jupyter\Wedge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F889C1-F7F7-41B5-8112-3ECB99FD4818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{776A2E84-5435-42BD-BA60-932CE983924B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="13">
   <si>
     <t>Fertile kg/m3</t>
   </si>
@@ -56,40 +56,36 @@
     <t>FISSILE PRODUCTION RATE [ RXNS/SRC-N ]</t>
   </si>
   <si>
-    <t>Wedge-C</t>
-  </si>
-  <si>
-    <t>Wedge-A</t>
-  </si>
-  <si>
     <t>=C/A</t>
   </si>
   <si>
     <t>DCLL-Greta</t>
   </si>
   <si>
-    <t>FISSILE PRODUCTION RATE ERROR PROPAGATION [ RXNS/SRC-N ]</t>
+    <t>Prism A</t>
   </si>
   <si>
-    <t>A-err</t>
+    <t>Prism A stdev</t>
   </si>
   <si>
-    <t>C-err</t>
+    <t>Prism C</t>
   </si>
   <si>
-    <t>=C/A err</t>
+    <t>Prism C stdev</t>
+  </si>
+  <si>
+    <t>=C/A stdev</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000000"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
-    <numFmt numFmtId="173" formatCode="0.00000000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -135,8 +131,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -151,13 +155,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -174,25 +184,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="11" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="11" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -384,7 +398,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-EF5A-449C-BA40-26C8A0D4DFC0}"/>
+              <c16:uniqueId val="{00000000-6F9A-4093-8446-03EAE435C4F9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -463,48 +477,48 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$N$24:$N$36</c:f>
+              <c:f>'Sheet 1'!$P$24:$P$36</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.85719868916492581</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.86272360378029123</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.86473422707265823</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>0.87150263943790185</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.8842176678721938</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>0.89942526896969821</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>0.92270745337377136</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>0.92487302633259483</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>0.95280649072651702</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>0.96680285364811647</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>0.996195710817117</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>1.0164077631511579</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>1.025113077347247</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -512,7 +526,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-EF5A-449C-BA40-26C8A0D4DFC0}"/>
+              <c16:uniqueId val="{00000001-6F9A-4093-8446-03EAE435C4F9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -524,14 +538,13 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1393801328"/>
-        <c:axId val="1647516927"/>
+        <c:axId val="1154162240"/>
+        <c:axId val="1123278832"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1393801328"/>
+        <c:axId val="1154162240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="1015"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -586,12 +599,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1647516927"/>
+        <c:crossAx val="1123278832"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1647516927"/>
+        <c:axId val="1123278832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -648,7 +661,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1393801328"/>
+        <c:crossAx val="1154162240"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -810,57 +823,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:intercept val="1"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="0.11546806649168855"/>
-                  <c:y val="0.18222626017901614"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>'Sheet 1'!$A$5:$A$17</c:f>
@@ -960,7 +922,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0D61-4DCE-9286-72E05B5CD6AC}"/>
+              <c16:uniqueId val="{00000000-F0AF-4FCE-B287-FF786F74DDEF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -989,57 +951,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:intercept val="1"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.14286526684164486"/>
-                  <c:y val="-1.1164529914529915E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>'Sheet 1'!$A$5:$A$17</c:f>
@@ -1090,48 +1001,48 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$N$5:$N$17</c:f>
+              <c:f>'Sheet 1'!$P$5:$P$17</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1.0001778209825207</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1.0000381873265614</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.99990753724213677</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>1.0002355998584036</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>1.0004553713443167</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>1.0005898491614427</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>1.0011630341173221</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>1.0006238901134941</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>1.0042585132338837</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>0.99880156437237411</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>0.99475053432196514</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>1.0016645335554861</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>0.99641459582252734</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1139,7 +1050,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-0D61-4DCE-9286-72E05B5CD6AC}"/>
+              <c16:uniqueId val="{00000001-F0AF-4FCE-B287-FF786F74DDEF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1151,11 +1062,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1641289503"/>
-        <c:axId val="1641287583"/>
+        <c:axId val="1342340016"/>
+        <c:axId val="1342342896"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1641289503"/>
+        <c:axId val="1342340016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1212,12 +1123,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1641287583"/>
+        <c:crossAx val="1342342896"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1641287583"/>
+        <c:axId val="1342342896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1274,7 +1185,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1641289503"/>
+        <c:crossAx val="1342340016"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1414,17 +1325,6 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Sheet 1'!$I$61</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>=C/A</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:noFill/>
@@ -1449,7 +1349,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$62:$A$74</c:f>
+              <c:f>'Sheet 1'!$A$44:$A$56</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
@@ -1497,48 +1397,48 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$I$62:$I$74</c:f>
+              <c:f>'Sheet 1'!$H$44:$H$56</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.98141967163352228</c:v>
+                  <c:v>1.0029352823676327</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.92802141334950694</c:v>
+                  <c:v>0.98224520701169626</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0257080460192236</c:v>
+                  <c:v>0.99535113208221782</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0646127665011473</c:v>
+                  <c:v>1.009239958157601</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0753237074121145</c:v>
+                  <c:v>1.0063851550945806</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0422360763919929</c:v>
+                  <c:v>1.0046707615573558</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0978441524727602</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0378247495664441</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.0332088675177227</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.1033275421994369</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.0613255687481478</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.0852827519045309</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.1057317871283765</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1546,7 +1446,135 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8DCE-479C-9EA8-30A245A0838A}"/>
+              <c16:uniqueId val="{00000000-0C88-4E6E-B386-C7DF904D6E61}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Sheet 1'!$A$44:$A$56</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>999.99</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Sheet 1'!$P$44:$P$56</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0001619611909021</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0001147967856605</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.99972727168909759</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.0009621278127161</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.99965798036547726</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.99728610985822141</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.99904092814030765</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.99984894845423344</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9997025557725211</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.0016101422064423</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.99432829011273149</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.98920834124726476</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0C88-4E6E-B386-C7DF904D6E61}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1558,11 +1586,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="114616576"/>
-        <c:axId val="114617056"/>
+        <c:axId val="1342355856"/>
+        <c:axId val="1342363056"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="114616576"/>
+        <c:axId val="1342355856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1619,12 +1647,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="114617056"/>
+        <c:crossAx val="1342363056"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="114617056"/>
+        <c:axId val="1342363056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1681,7 +1709,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="114616576"/>
+        <c:crossAx val="1342355856"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1693,6 +1721,37 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -1790,17 +1849,6 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Sheet 1'!$I$43</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>=C/A</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:noFill/>
@@ -1825,7 +1873,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$44:$A$56</c:f>
+              <c:f>'Sheet 1'!$A$62:$A$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
@@ -1873,48 +1921,48 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$I$44:$I$56</c:f>
+              <c:f>'Sheet 1'!$H$62:$H$74</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.9985035371420129</c:v>
+                  <c:v>1.0417490015674646</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.98715209394887005</c:v>
+                  <c:v>1.0149892108133356</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.99284501043036377</c:v>
+                  <c:v>1.0382137988437394</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0204895071175968</c:v>
+                  <c:v>1.0585263015095798</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0049119467662411</c:v>
+                  <c:v>1.0608306647563586</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.99460716116426584</c:v>
+                  <c:v>1.0678523167293434</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0195310334465668</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.98333502299608533</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.98631763108404502</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.0290963972436542</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.99666881879093805</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.0030035803296993</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.0148841983751864</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1922,7 +1970,135 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2C96-4BEB-84E0-6A0C66B7B7A7}"/>
+              <c16:uniqueId val="{00000000-6C71-4D74-B5A8-4EE6279B7B3D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Sheet 1'!$A$62:$A$74</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>999.99</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Sheet 1'!$P$62:$P$74</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0468679184142133</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0491120103788383</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0548236283228316</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.0592976963273675</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.0599512468140793</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.0559969197962629</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.0610351455367648</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.0635211665810387</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.0673679820985291</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.0749164325098632</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.0676051493877452</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0682957802000932</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6C71-4D74-B5A8-4EE6279B7B3D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1934,11 +2110,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="111977952"/>
-        <c:axId val="111975072"/>
+        <c:axId val="1342380336"/>
+        <c:axId val="1342369296"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="111977952"/>
+        <c:axId val="1342380336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1995,14 +2171,15 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="111975072"/>
+        <c:crossAx val="1342369296"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="111975072"/>
+        <c:axId val="1342369296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="0.95000000000000007"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2057,7 +2234,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="111977952"/>
+        <c:crossAx val="1342380336"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2069,6 +2246,37 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -4341,23 +4549,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>383970</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>103240</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>583097</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>79170</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>103240</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>278297</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>145775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 4">
+        <xdr:cNvPr id="4" name="Chart 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBBF6084-11AA-97F7-53C2-9A86E48D2648}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{705D9A80-E1AA-E71B-225B-10B9F8C8DC38}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4377,23 +4585,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>373877</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>596348</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>99060</xdr:rowOff>
+      <xdr:rowOff>19878</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>69077</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>291548</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>165652</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Chart 5">
+        <xdr:cNvPr id="7" name="Chart 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C38D171C-51DC-A2DA-08F3-A64A456D651B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCFB409E-0F1D-3927-8CC6-C3C817ACD911}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4413,23 +4621,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>7289</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>9939</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>53010</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>159027</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>310764</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>9939</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>357810</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>119270</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
+        <xdr:cNvPr id="8" name="Chart 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02018F3B-2271-EEFD-8B60-2D067E479517}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20F6E031-1B10-7A61-F473-7E5EC3DC0100}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4449,23 +4657,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>8614</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>20871</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>417444</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>312089</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>20871</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>112644</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>112644</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
+        <xdr:cNvPr id="9" name="Chart 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D82A22E-8B90-A0A4-CE77-0333E07A721B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{245022B1-EA92-9A14-99B5-645E9443F9AD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4749,7 +4957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22416C2-1180-4450-A3B0-0B08DD9AEC85}">
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:Q74"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
@@ -4759,94 +4967,107 @@
     <col min="8" max="8" width="12.5546875" customWidth="1"/>
     <col min="9" max="9" width="15.109375" customWidth="1"/>
     <col min="10" max="10" width="2.77734375" customWidth="1"/>
-    <col min="11" max="14" width="13.33203125" customWidth="1"/>
+    <col min="11" max="13" width="13.33203125" customWidth="1"/>
+    <col min="14" max="14" width="15.5546875" customWidth="1"/>
     <col min="15" max="15" width="14.21875" customWidth="1"/>
+    <col min="16" max="16" width="12.21875" customWidth="1"/>
+    <col min="17" max="17" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C2" s="14" t="s">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C3" s="3" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="3"/>
-      <c r="K3" s="3" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="14"/>
+      <c r="K3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="3"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="3"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="5"/>
+      <c r="C4" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="D4" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="H4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="I4" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="J4" s="6"/>
+      <c r="K4" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="8"/>
-      <c r="K4" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="N4" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="O4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="P4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="O4" s="7"/>
+      <c r="Q4" s="19" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>0.1</v>
       </c>
-      <c r="B5" s="5"/>
+      <c r="B5" s="4"/>
       <c r="D5">
         <v>1.3891095589010301</v>
       </c>
@@ -4859,29 +5080,41 @@
       <c r="G5">
         <v>1.1377551521665301E-4</v>
       </c>
-      <c r="H5" s="10">
-        <f>F5/D5</f>
+      <c r="H5" s="7">
+        <f t="shared" ref="H5:H17" si="0">F5/D5</f>
         <v>1.0001629351709587</v>
       </c>
       <c r="I5">
         <f>H5*((E5/D5)^2 +(G5/F5)^2)^0.5</f>
         <v>1.1024684824037706E-4</v>
       </c>
-      <c r="J5" s="4"/>
+      <c r="J5" s="3"/>
+      <c r="L5">
+        <v>1.38908077443087</v>
+      </c>
       <c r="M5">
+        <v>1.0124318874365601E-4</v>
+      </c>
+      <c r="N5">
         <v>1.38932778213898</v>
       </c>
-      <c r="N5" s="10" t="e">
-        <f>M5/L5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O5" s="10"/>
+      <c r="O5">
+        <v>1.14700118954492E-4</v>
+      </c>
+      <c r="P5" s="7">
+        <f>N5/L5</f>
+        <v>1.0001778209825207</v>
+      </c>
+      <c r="Q5">
+        <f>P5*((M5/L5)^2 +(O5/N5)^2)^0.5</f>
+        <v>1.1014700886063438E-4</v>
+      </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0.5</v>
       </c>
-      <c r="B6" s="5"/>
+      <c r="B6" s="4"/>
       <c r="D6">
         <v>1.38907673010083</v>
       </c>
@@ -4894,29 +5127,41 @@
       <c r="G6">
         <v>1.6878154642812701E-4</v>
       </c>
-      <c r="H6" s="10">
-        <f>F6/D6</f>
+      <c r="H6" s="7">
+        <f t="shared" si="0"/>
         <v>1.0000650261216626</v>
       </c>
       <c r="I6">
-        <f t="shared" ref="I6:I16" si="0">H6*((E6/D6)^2 +(G6/F6)^2)^0.5</f>
+        <f t="shared" ref="I6:I16" si="1">H6*((E6/D6)^2 +(G6/F6)^2)^0.5</f>
         <v>1.6386259048946993E-4</v>
       </c>
-      <c r="J6" s="4"/>
+      <c r="J6" s="3"/>
+      <c r="L6">
+        <v>1.3890751130454999</v>
+      </c>
       <c r="M6">
+        <v>1.5633111145029499E-4</v>
+      </c>
+      <c r="N6">
         <v>1.38912815811046</v>
       </c>
-      <c r="N6" s="10" t="e">
-        <f t="shared" ref="N6:N17" si="1">M6/L6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O6" s="10"/>
+      <c r="O6">
+        <v>1.6988497331219999E-4</v>
+      </c>
+      <c r="P6" s="7">
+        <f>N6/L6</f>
+        <v>1.0000381873265614</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" ref="Q6:Q16" si="2">P6*((M6/L6)^2 +(O6/N6)^2)^0.5</f>
+        <v>1.6620603320820275E-4</v>
+      </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
-      <c r="B7" s="5"/>
+      <c r="B7" s="4"/>
       <c r="D7">
         <v>1.3889139640202901</v>
       </c>
@@ -4929,29 +5174,41 @@
       <c r="G7">
         <v>1.54337152453701E-4</v>
       </c>
-      <c r="H7" s="10">
-        <f>F7/D7</f>
+      <c r="H7" s="7">
+        <f t="shared" si="0"/>
         <v>0.99996036360746876</v>
       </c>
       <c r="I7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.7181641313147609E-4</v>
       </c>
-      <c r="J7" s="4"/>
+      <c r="J7" s="3"/>
+      <c r="L7">
+        <v>1.3889046123851001</v>
+      </c>
       <c r="M7">
+        <v>1.70335691939932E-4</v>
+      </c>
+      <c r="N7">
         <v>1.38877619043423</v>
       </c>
-      <c r="N7" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O7" s="10"/>
+      <c r="O7">
+        <v>1.5373454905333599E-4</v>
+      </c>
+      <c r="P7" s="7">
+        <f>N7/L7</f>
+        <v>0.99990753724213677</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>1.6519568405949642E-4</v>
+      </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>10</v>
       </c>
-      <c r="B8" s="5"/>
+      <c r="B8" s="4"/>
       <c r="D8">
         <v>1.38607567014507</v>
       </c>
@@ -4964,29 +5221,41 @@
       <c r="G8">
         <v>4.0944327607914799E-4</v>
       </c>
-      <c r="H8" s="10">
-        <f>F8/D8</f>
+      <c r="H8" s="7">
+        <f t="shared" si="0"/>
         <v>1.0005266084564297</v>
       </c>
       <c r="I8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.0785290749755253E-4</v>
       </c>
-      <c r="J8" s="4"/>
+      <c r="J8" s="3"/>
+      <c r="L8">
+        <v>1.3856175235925701</v>
+      </c>
       <c r="M8">
+        <v>4.5540286699321999E-4</v>
+      </c>
+      <c r="N8">
         <v>1.38594397488493</v>
       </c>
-      <c r="N8" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O8" s="10"/>
+      <c r="O8">
+        <v>4.3477128848851398E-4</v>
+      </c>
+      <c r="P8" s="7">
+        <f>N8/L8</f>
+        <v>1.0002355998584036</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>4.5445068306877072E-4</v>
+      </c>
     </row>
-    <row r="9" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>25</v>
       </c>
-      <c r="B9" s="5"/>
+      <c r="B9" s="4"/>
       <c r="C9"/>
       <c r="D9">
         <v>1.37947186689904</v>
@@ -5000,30 +5269,41 @@
       <c r="G9">
         <v>1.17898543365087E-3</v>
       </c>
-      <c r="H9" s="10">
-        <f>F9/D9</f>
+      <c r="H9" s="7">
+        <f t="shared" si="0"/>
         <v>1.0018467149465879</v>
       </c>
       <c r="I9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0698498708561776E-3</v>
       </c>
       <c r="K9"/>
-      <c r="L9"/>
+      <c r="L9">
+        <v>1.37951144335299</v>
+      </c>
       <c r="M9">
+        <v>9.6051663666235599E-4</v>
+      </c>
+      <c r="N9">
         <v>1.3801396333334499</v>
       </c>
-      <c r="N9" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O9" s="11"/>
+      <c r="O9">
+        <v>1.0536694518052999E-3</v>
+      </c>
+      <c r="P9" s="7">
+        <f>N9/L9</f>
+        <v>1.0004553713443167</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>1.0337440128011612E-3</v>
+      </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>50</v>
       </c>
-      <c r="B10" s="5"/>
+      <c r="B10" s="4"/>
       <c r="D10">
         <v>1.37231900559378</v>
       </c>
@@ -5036,29 +5316,41 @@
       <c r="G10">
         <v>7.1929329253824501E-4</v>
       </c>
-      <c r="H10" s="10">
-        <f>F10/D10</f>
+      <c r="H10" s="7">
+        <f t="shared" si="0"/>
         <v>1.002287048308576</v>
       </c>
       <c r="I10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.8794780325578441E-4</v>
       </c>
-      <c r="J10" s="4"/>
+      <c r="J10" s="3"/>
+      <c r="L10">
+        <v>1.3703576195701299</v>
+      </c>
       <c r="M10">
+        <v>9.5714052610468097E-4</v>
+      </c>
+      <c r="N10">
         <v>1.3711659238629099</v>
       </c>
-      <c r="N10" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O10" s="10"/>
+      <c r="O10">
+        <v>7.5549871036543397E-4</v>
+      </c>
+      <c r="P10" s="7">
+        <f>N10/L10</f>
+        <v>1.0005898491614427</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>8.901521419890664E-4</v>
+      </c>
     </row>
-    <row r="11" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>75</v>
       </c>
-      <c r="B11" s="5"/>
+      <c r="B11" s="4"/>
       <c r="C11"/>
       <c r="D11">
         <v>1.3652125452841399</v>
@@ -5072,30 +5364,41 @@
       <c r="G11">
         <v>1.1043763633645899E-3</v>
       </c>
-      <c r="H11" s="10">
-        <f>F11/D11</f>
+      <c r="H11" s="7">
+        <f t="shared" si="0"/>
         <v>1.0038025582102672</v>
       </c>
       <c r="I11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0625098571799413E-3</v>
       </c>
       <c r="K11"/>
-      <c r="L11"/>
+      <c r="L11">
+        <v>1.3619357177992399</v>
+      </c>
       <c r="M11">
+        <v>1.14642500606108E-3</v>
+      </c>
+      <c r="N11">
         <v>1.36351969550464</v>
       </c>
-      <c r="N11" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O11" s="11"/>
+      <c r="O11">
+        <v>1.0122047275674399E-3</v>
+      </c>
+      <c r="P11" s="7">
+        <f>N11/L11</f>
+        <v>1.0011630341173221</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="2"/>
+        <v>1.1236427897777903E-3</v>
+      </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>100</v>
       </c>
-      <c r="B12" s="5"/>
+      <c r="B12" s="4"/>
       <c r="D12">
         <v>1.35996558693921</v>
       </c>
@@ -5108,29 +5411,41 @@
       <c r="G12">
         <v>1.0934621564654399E-3</v>
       </c>
-      <c r="H12" s="10">
-        <f>F12/D12</f>
+      <c r="H12" s="7">
+        <f t="shared" si="0"/>
         <v>1.0036838050286592</v>
       </c>
       <c r="I12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0075356465859516E-3</v>
       </c>
-      <c r="J12" s="4"/>
+      <c r="J12" s="3"/>
+      <c r="L12">
+        <v>1.35524292294785</v>
+      </c>
       <c r="M12">
+        <v>9.843423979622231E-4</v>
+      </c>
+      <c r="N12">
         <v>1.35608844560886</v>
       </c>
-      <c r="N12" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O12" s="10"/>
+      <c r="O12">
+        <v>1.04376153989015E-3</v>
+      </c>
+      <c r="P12" s="7">
+        <f>N12/L12</f>
+        <v>1.0006238901134941</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="2"/>
+        <v>1.0589413837370333E-3</v>
+      </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>150</v>
       </c>
-      <c r="B13" s="5"/>
+      <c r="B13" s="4"/>
       <c r="D13">
         <v>1.3471169036955299</v>
       </c>
@@ -5143,29 +5458,41 @@
       <c r="G13">
         <v>3.6209913911154899E-3</v>
       </c>
-      <c r="H13" s="10">
-        <f>F13/D13</f>
+      <c r="H13" s="7">
+        <f t="shared" si="0"/>
         <v>1.002467577491776</v>
       </c>
       <c r="I13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.7012678767904027E-3</v>
       </c>
-      <c r="J13" s="4"/>
+      <c r="J13" s="3"/>
+      <c r="L13">
+        <v>1.3391565484202601</v>
+      </c>
       <c r="M13">
+        <v>3.4513629910370401E-3</v>
+      </c>
+      <c r="N13">
         <v>1.3448593643039499</v>
       </c>
-      <c r="N13" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O13" s="10"/>
+      <c r="O13">
+        <v>3.5460245721196499E-3</v>
+      </c>
+      <c r="P13" s="7">
+        <f>N13/L13</f>
+        <v>1.0042585132338837</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="2"/>
+        <v>3.7027899524461018E-3</v>
+      </c>
     </row>
-    <row r="14" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>250</v>
       </c>
-      <c r="B14" s="5"/>
+      <c r="B14" s="4"/>
       <c r="C14"/>
       <c r="D14">
         <v>1.3301704109246899</v>
@@ -5179,30 +5506,41 @@
       <c r="G14">
         <v>2.6466416072152398E-3</v>
       </c>
-      <c r="H14" s="10">
-        <f>F14/D14</f>
+      <c r="H14" s="7">
+        <f t="shared" si="0"/>
         <v>1.000596548769378</v>
       </c>
       <c r="I14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.8272285541985462E-3</v>
       </c>
       <c r="K14"/>
-      <c r="L14"/>
+      <c r="L14">
+        <v>1.3112710657587101</v>
+      </c>
       <c r="M14">
+        <v>2.67520556095646E-3</v>
+      </c>
+      <c r="N14">
         <v>1.3096995917960299</v>
       </c>
-      <c r="N14" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O14" s="11"/>
+      <c r="O14">
+        <v>2.9409916078694401E-3</v>
+      </c>
+      <c r="P14" s="7">
+        <f>N14/L14</f>
+        <v>0.99880156437237411</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="2"/>
+        <v>3.030295719604469E-3</v>
+      </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>500</v>
       </c>
-      <c r="B15" s="5"/>
+      <c r="B15" s="4"/>
       <c r="D15">
         <v>1.2881810524951001</v>
       </c>
@@ -5215,29 +5553,41 @@
       <c r="G15">
         <v>3.6382982434454399E-3</v>
       </c>
-      <c r="H15" s="10">
-        <f>F15/D15</f>
+      <c r="H15" s="7">
+        <f t="shared" si="0"/>
         <v>1.0015290596941282</v>
       </c>
       <c r="I15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.579377630249193E-3</v>
       </c>
-      <c r="J15" s="4"/>
+      <c r="J15" s="3"/>
+      <c r="L15">
+        <v>1.2563576950633499</v>
+      </c>
       <c r="M15">
+        <v>2.5050181564410701E-3</v>
+      </c>
+      <c r="N15">
         <v>1.2497624884637799</v>
       </c>
-      <c r="N15" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O15" s="10"/>
+      <c r="O15">
+        <v>2.6845051290129399E-3</v>
+      </c>
+      <c r="P15" s="7">
+        <f>N15/L15</f>
+        <v>0.99475053432196514</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="2"/>
+        <v>2.9153977252420692E-3</v>
+      </c>
     </row>
-    <row r="16" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>750</v>
       </c>
-      <c r="B16" s="5"/>
+      <c r="B16" s="4"/>
       <c r="C16"/>
       <c r="D16">
         <v>1.24999214529804</v>
@@ -5251,30 +5601,41 @@
       <c r="G16">
         <v>3.5797440463882701E-3</v>
       </c>
-      <c r="H16" s="10">
-        <f>F16/D16</f>
+      <c r="H16" s="7">
+        <f t="shared" si="0"/>
         <v>1.0029865814925498</v>
       </c>
       <c r="I16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.4346863492251559E-3</v>
       </c>
       <c r="K16"/>
-      <c r="L16"/>
+      <c r="L16">
+        <v>1.20021968581256</v>
+      </c>
       <c r="M16">
+        <v>2.9794094197858E-3</v>
+      </c>
+      <c r="N16">
         <v>1.20221749175355</v>
       </c>
-      <c r="N16" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O16" s="11"/>
+      <c r="O16">
+        <v>2.7545952721865301E-3</v>
+      </c>
+      <c r="P16" s="7">
+        <f>N16/L16</f>
+        <v>1.0016645335554861</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="2"/>
+        <v>3.3838068565250718E-3</v>
+      </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>999.99</v>
       </c>
-      <c r="B17" s="5"/>
+      <c r="B17" s="4"/>
       <c r="D17">
         <v>1.2159170927577201</v>
       </c>
@@ -5287,1878 +5648,2043 @@
       <c r="G17">
         <v>3.18424238805618E-3</v>
       </c>
-      <c r="H17" s="10">
-        <f>F17/D17</f>
+      <c r="H17" s="7">
+        <f t="shared" si="0"/>
         <v>1.0003513071302839</v>
       </c>
       <c r="I17">
         <f>H17*((E17/D17)^2 +(G17/F17)^2)^0.5</f>
         <v>3.6618101886275135E-3</v>
       </c>
-      <c r="J17" s="4"/>
+      <c r="J17" s="3"/>
+      <c r="L17">
+        <v>1.1566240021210601</v>
+      </c>
       <c r="M17">
+        <v>2.5884299434418999E-3</v>
+      </c>
+      <c r="N17">
         <v>1.1524770375920901</v>
       </c>
-      <c r="N17" s="10" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O17" s="10"/>
+      <c r="O17">
+        <v>3.9762001692155704E-3</v>
+      </c>
+      <c r="P17" s="7">
+        <f>N17/L17</f>
+        <v>0.99641459582252734</v>
+      </c>
+      <c r="Q17">
+        <f>P17*((M17/L17)^2 +(O17/N17)^2)^0.5</f>
+        <v>4.0976394678384738E-3</v>
+      </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C21" s="12" t="s">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C21" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C22" s="3" t="s">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C22" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="3"/>
-      <c r="K22" s="3" t="s">
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="14"/>
+      <c r="K22" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="3"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6" t="s">
+      <c r="B23" s="5"/>
+      <c r="C23" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="6" t="s">
+      <c r="D23" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="H23" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="I23" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H23" s="7" t="s">
+      <c r="J23" s="6"/>
+      <c r="K23" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="L23" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="I23" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="8"/>
-      <c r="K23" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="L23" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="M23" s="6" t="s">
+      <c r="M23" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="N23" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="O23" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="P23" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="N23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="O23" s="7"/>
+      <c r="Q23" s="19" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>0.1</v>
       </c>
-      <c r="B24" s="5"/>
+      <c r="B24" s="4"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2">
         <v>3.4601339198647797E-5</v>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="2">
         <v>1.22883732368375E-8</v>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="2">
         <v>2.3188386654289999E-5</v>
       </c>
-      <c r="G24" s="17">
+      <c r="G24" s="2">
         <v>2.5713213345718999E-7</v>
       </c>
-      <c r="H24" s="16">
-        <f>F24/D24</f>
+      <c r="H24" s="13">
+        <f t="shared" ref="H24:H36" si="3">F24/D24</f>
         <v>0.67015864678428949</v>
       </c>
       <c r="I24">
         <f>H24*((E24/D24)^2 +(G24/F24)^2)^0.5</f>
         <v>7.4350871718769813E-3</v>
       </c>
-      <c r="J24" s="4"/>
+      <c r="J24" s="3"/>
       <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
+      <c r="L24" s="2">
+        <v>3.0213736630210799E-5</v>
+      </c>
       <c r="M24" s="2">
+        <v>6.2814290600429797E-9</v>
+      </c>
+      <c r="N24" s="2">
         <v>2.5899175434190999E-5</v>
       </c>
-      <c r="N24" s="10" t="e">
-        <f>M24/L24</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O24" s="10"/>
+      <c r="O24" s="2">
+        <v>2.22045923443069E-7</v>
+      </c>
+      <c r="P24" s="7">
+        <f>N24/L24</f>
+        <v>0.85719868916492581</v>
+      </c>
+      <c r="Q24">
+        <f>P24*((M24/L24)^2 +(O24/N24)^2)^0.5</f>
+        <v>7.3513316350502867E-3</v>
+      </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>0.5</v>
       </c>
-      <c r="B25" s="5"/>
+      <c r="B25" s="4"/>
       <c r="D25">
         <v>1.7267075850167999E-4</v>
       </c>
-      <c r="E25" s="17">
+      <c r="E25" s="2">
         <v>7.3730405114227898E-8</v>
       </c>
-      <c r="F25" s="17">
+      <c r="F25">
         <v>1.16379113471186E-4</v>
       </c>
-      <c r="G25" s="17">
+      <c r="G25" s="2">
         <v>4.9685826902563597E-7</v>
       </c>
-      <c r="H25" s="16">
-        <f>F25/D25</f>
+      <c r="H25" s="13">
+        <f t="shared" si="3"/>
         <v>0.67399433743759052</v>
       </c>
       <c r="I25">
-        <f t="shared" ref="I25:I35" si="2">H25*((E25/D25)^2 +(G25/F25)^2)^0.5</f>
+        <f t="shared" ref="I25:I35" si="4">H25*((E25/D25)^2 +(G25/F25)^2)^0.5</f>
         <v>2.8918456475792078E-3</v>
       </c>
-      <c r="J25" s="4"/>
-      <c r="M25">
+      <c r="J25" s="3"/>
+      <c r="L25">
+        <v>1.50989540407932E-4</v>
+      </c>
+      <c r="M25" s="2">
+        <v>4.1276616778068897E-8</v>
+      </c>
+      <c r="N25">
         <v>1.3026224043386099E-4</v>
       </c>
-      <c r="N25" s="10" t="e">
-        <f t="shared" ref="N25:N36" si="3">M25/L25</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O25" s="10"/>
+      <c r="O25" s="2">
+        <v>5.73466194555137E-7</v>
+      </c>
+      <c r="P25" s="7">
+        <f>N25/L25</f>
+        <v>0.86272360378029123</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" ref="Q25:Q35" si="5">P25*((M25/L25)^2 +(O25/N25)^2)^0.5</f>
+        <v>3.8053680353437123E-3</v>
+      </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1</v>
       </c>
-      <c r="B26" s="5"/>
+      <c r="B26" s="4"/>
       <c r="D26">
         <v>3.4444202449192702E-4</v>
       </c>
-      <c r="E26" s="17">
+      <c r="E26" s="2">
         <v>1.02701859340892E-7</v>
       </c>
-      <c r="F26" s="17">
+      <c r="F26">
         <v>2.31665379952172E-4</v>
       </c>
-      <c r="G26" s="17">
+      <c r="G26" s="2">
         <v>6.9232886194979901E-7</v>
       </c>
-      <c r="H26" s="16">
-        <f>F26/D26</f>
+      <c r="H26" s="13">
+        <f t="shared" si="3"/>
         <v>0.67258163487423628</v>
       </c>
       <c r="I26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.0199806972425911E-3</v>
       </c>
-      <c r="J26" s="4"/>
-      <c r="M26">
+      <c r="J26" s="3"/>
+      <c r="L26">
+        <v>3.0170617519809301E-4</v>
+      </c>
+      <c r="M26" s="2">
+        <v>8.1667143013063195E-8</v>
+      </c>
+      <c r="N26">
         <v>2.6089565621297098E-4</v>
       </c>
-      <c r="N26" s="10" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O26" s="10"/>
+      <c r="O26" s="2">
+        <v>6.2257504496774401E-7</v>
+      </c>
+      <c r="P26" s="7">
+        <f>N26/L26</f>
+        <v>0.86473422707265823</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="5"/>
+        <v>2.0767475932791379E-3</v>
+      </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>10</v>
       </c>
-      <c r="B27" s="5"/>
+      <c r="B27" s="4"/>
       <c r="D27">
         <v>3.33054467027722E-3</v>
       </c>
-      <c r="E27" s="17">
+      <c r="E27" s="2">
         <v>3.1023196230951202E-6</v>
       </c>
-      <c r="F27" s="17">
+      <c r="F27">
         <v>2.3274949085023899E-3</v>
       </c>
-      <c r="G27" s="17">
+      <c r="G27" s="2">
         <v>7.3576810457546899E-6</v>
       </c>
-      <c r="H27" s="16">
-        <f>F27/D27</f>
+      <c r="H27" s="13">
+        <f t="shared" si="3"/>
         <v>0.69883311557825745</v>
       </c>
       <c r="I27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.3030599218682355E-3</v>
       </c>
-      <c r="J27" s="4"/>
-      <c r="M27">
+      <c r="J27" s="3"/>
+      <c r="L27">
+        <v>2.97750983471892E-3</v>
+      </c>
+      <c r="M27" s="2">
+        <v>2.7512545520394498E-6</v>
+      </c>
+      <c r="N27">
         <v>2.5949076799098498E-3</v>
       </c>
-      <c r="N27" s="10" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O27" s="10"/>
+      <c r="O27" s="2">
+        <v>5.6804576370084801E-6</v>
+      </c>
+      <c r="P27" s="7">
+        <f>N27/L27</f>
+        <v>0.87150263943790185</v>
+      </c>
+      <c r="Q27">
+        <f t="shared" si="5"/>
+        <v>2.0707798442735998E-3</v>
+      </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>25</v>
       </c>
-      <c r="B28" s="5"/>
+      <c r="B28" s="4"/>
       <c r="D28">
         <v>7.9007108136224906E-3</v>
       </c>
-      <c r="E28" s="17">
+      <c r="E28" s="2">
         <v>2.1579374269995798E-5</v>
       </c>
-      <c r="F28" s="17">
+      <c r="F28">
         <v>5.7868683352336496E-3</v>
       </c>
-      <c r="G28" s="17">
+      <c r="G28" s="2">
         <v>2.2153397083295701E-5</v>
       </c>
-      <c r="H28" s="16">
-        <f>F28/D28</f>
+      <c r="H28" s="13">
+        <f t="shared" si="3"/>
         <v>0.73244907600666376</v>
       </c>
       <c r="I28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.444486925796071E-3</v>
       </c>
-      <c r="J28" s="4"/>
-      <c r="M28">
+      <c r="J28" s="3"/>
+      <c r="L28">
+        <v>7.2854691465075302E-3</v>
+      </c>
+      <c r="M28" s="2">
+        <v>1.0595331155121401E-5</v>
+      </c>
+      <c r="N28">
         <v>6.4419405380797103E-3</v>
       </c>
-      <c r="N28" s="10" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O28" s="11"/>
+      <c r="O28" s="2">
+        <v>3.0640812604159097E-5</v>
+      </c>
+      <c r="P28" s="7">
+        <f>N28/L28</f>
+        <v>0.8842176678721938</v>
+      </c>
+      <c r="Q28">
+        <f t="shared" si="5"/>
+        <v>4.3979408323316831E-3</v>
+      </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>50</v>
       </c>
-      <c r="B29" s="5"/>
+      <c r="B29" s="4"/>
       <c r="D29">
         <v>1.48099690035684E-2</v>
       </c>
-      <c r="E29" s="17">
+      <c r="E29" s="2">
         <v>3.5619384608241799E-5</v>
       </c>
-      <c r="F29" s="17">
+      <c r="F29">
         <v>1.1357972286110201E-2</v>
       </c>
-      <c r="G29" s="17">
+      <c r="G29" s="2">
         <v>3.9960656049596501E-5</v>
       </c>
-      <c r="H29" s="16">
-        <f>F29/D29</f>
+      <c r="H29" s="13">
+        <f t="shared" si="3"/>
         <v>0.76691398093902452</v>
       </c>
       <c r="I29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.2684265997479276E-3</v>
       </c>
-      <c r="J29" s="4"/>
-      <c r="M29">
+      <c r="J29" s="3"/>
+      <c r="L29">
+        <v>1.4085686693042001E-2</v>
+      </c>
+      <c r="M29" s="2">
+        <v>2.6440325603855101E-5</v>
+      </c>
+      <c r="N29">
         <v>1.26690225425122E-2</v>
       </c>
-      <c r="N29" s="10" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O29" s="10"/>
+      <c r="O29" s="2">
+        <v>3.9839492384589098E-5</v>
+      </c>
+      <c r="P29" s="7">
+        <f>N29/L29</f>
+        <v>0.89942526896969821</v>
+      </c>
+      <c r="Q29">
+        <f t="shared" si="5"/>
+        <v>3.2939448706370833E-3</v>
+      </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>75</v>
       </c>
-      <c r="B30" s="5"/>
+      <c r="B30" s="4"/>
       <c r="D30">
         <v>2.1060130702738999E-2</v>
       </c>
-      <c r="E30" s="17">
+      <c r="E30" s="2">
         <v>3.0830038687911403E-5</v>
       </c>
-      <c r="F30" s="17">
+      <c r="F30">
         <v>1.6724313084056999E-2</v>
       </c>
-      <c r="G30" s="17">
+      <c r="G30" s="2">
         <v>4.6773312275541899E-5</v>
       </c>
-      <c r="H30" s="16">
-        <f>F30/D30</f>
+      <c r="H30" s="13">
+        <f t="shared" si="3"/>
         <v>0.79412199858198884</v>
       </c>
       <c r="I30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.506797039006772E-3</v>
       </c>
-      <c r="J30" s="4"/>
-      <c r="M30">
+      <c r="J30" s="3"/>
+      <c r="L30">
+        <v>2.04540679886334E-2</v>
+      </c>
+      <c r="M30" s="2">
+        <v>4.0017362438723199E-5</v>
+      </c>
+      <c r="N30">
         <v>1.8873120984925901E-2</v>
       </c>
-      <c r="N30" s="10" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O30" s="11"/>
+      <c r="O30" s="2">
+        <v>3.9932428547215201E-5</v>
+      </c>
+      <c r="P30" s="7">
+        <f>N30/L30</f>
+        <v>0.92270745337377136</v>
+      </c>
+      <c r="Q30">
+        <f t="shared" si="5"/>
+        <v>2.6590083093148533E-3</v>
+      </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>100</v>
       </c>
-      <c r="B31" s="5"/>
+      <c r="B31" s="4"/>
       <c r="D31">
         <v>2.67600755292417E-2</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="2">
         <v>6.1301138330409899E-5</v>
       </c>
-      <c r="F31" s="17">
+      <c r="F31">
         <v>2.2149757308928399E-2</v>
       </c>
-      <c r="G31" s="17">
+      <c r="G31" s="2">
         <v>5.1020148947823797E-5</v>
       </c>
-      <c r="H31" s="16">
-        <f>F31/D31</f>
+      <c r="H31" s="13">
+        <f t="shared" si="3"/>
         <v>0.82771654679092965</v>
       </c>
       <c r="I31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.6889139523652702E-3</v>
       </c>
-      <c r="J31" s="4"/>
-      <c r="M31">
+      <c r="J31" s="3"/>
+      <c r="L31">
+        <v>2.6686341725694201E-2</v>
+      </c>
+      <c r="M31" s="2">
+        <v>4.6488373284998899E-5</v>
+      </c>
+      <c r="N31">
         <v>2.4681477633588599E-2</v>
       </c>
-      <c r="N31" s="10" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O31" s="10"/>
+      <c r="O31" s="2">
+        <v>4.3554638662226E-5</v>
+      </c>
+      <c r="P31" s="7">
+        <f>N31/L31</f>
+        <v>0.92487302633259483</v>
+      </c>
+      <c r="Q31">
+        <f t="shared" si="5"/>
+        <v>2.2933719536386309E-3</v>
+      </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>150</v>
       </c>
-      <c r="B32" s="5"/>
+      <c r="B32" s="4"/>
       <c r="D32">
         <v>3.6782709718709998E-2</v>
       </c>
-      <c r="E32" s="17">
+      <c r="E32">
         <v>1.97489580151579E-4</v>
       </c>
-      <c r="F32" s="17">
+      <c r="F32">
         <v>3.2103137598192298E-2</v>
       </c>
-      <c r="G32" s="17">
+      <c r="G32">
         <v>2.08831333646651E-4</v>
       </c>
-      <c r="H32" s="16">
-        <f>F32/D32</f>
+      <c r="H32" s="13">
+        <f t="shared" si="3"/>
         <v>0.87277793951821403</v>
       </c>
       <c r="I32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>7.3615233968889766E-3</v>
       </c>
-      <c r="J32" s="4"/>
+      <c r="J32" s="3"/>
+      <c r="L32">
+        <v>3.7924637387248702E-2</v>
+      </c>
       <c r="M32">
+        <v>1.8428567575269999E-4</v>
+      </c>
+      <c r="N32">
         <v>3.6134840661020101E-2</v>
       </c>
-      <c r="N32" s="10" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O32" s="10"/>
+      <c r="O32">
+        <v>2.42482884021072E-4</v>
+      </c>
+      <c r="P32" s="7">
+        <f>N32/L32</f>
+        <v>0.95280649072651702</v>
+      </c>
+      <c r="Q32">
+        <f t="shared" si="5"/>
+        <v>7.8941171734471308E-3</v>
+      </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>250</v>
       </c>
-      <c r="B33" s="5"/>
+      <c r="B33" s="4"/>
       <c r="D33">
         <v>5.6309750104400702E-2</v>
       </c>
-      <c r="E33" s="17">
+      <c r="E33">
         <v>2.51687827781958E-4</v>
       </c>
-      <c r="F33" s="17">
+      <c r="F33">
         <v>5.1114734736025402E-2</v>
       </c>
-      <c r="G33" s="17">
+      <c r="G33">
         <v>2.8833834514146198E-4</v>
       </c>
-      <c r="H33" s="16">
-        <f>F33/D33</f>
+      <c r="H33" s="13">
+        <f t="shared" si="3"/>
         <v>0.90774216971761523</v>
       </c>
       <c r="I33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>6.5331679556135417E-3</v>
       </c>
-      <c r="J33" s="4"/>
+      <c r="J33" s="3"/>
+      <c r="L33">
+        <v>5.9331126295057199E-2</v>
+      </c>
       <c r="M33">
+        <v>2.7677924057614001E-4</v>
+      </c>
+      <c r="N33">
         <v>5.7361502212218099E-2</v>
       </c>
-      <c r="N33" s="10" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O33" s="11"/>
+      <c r="O33">
+        <v>2.3849126374357799E-4</v>
+      </c>
+      <c r="P33" s="7">
+        <f>N33/L33</f>
+        <v>0.96680285364811647</v>
+      </c>
+      <c r="Q33">
+        <f t="shared" si="5"/>
+        <v>6.041436975368881E-3</v>
+      </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>500</v>
       </c>
-      <c r="B34" s="5"/>
+      <c r="B34" s="4"/>
       <c r="D34">
         <v>9.4384365104793602E-2</v>
       </c>
-      <c r="E34" s="17">
+      <c r="E34">
         <v>3.7802904257795602E-4</v>
       </c>
-      <c r="F34" s="17">
+      <c r="F34">
         <v>9.1445222619505398E-2</v>
       </c>
-      <c r="G34" s="17">
+      <c r="G34">
         <v>4.4906828447954003E-4</v>
       </c>
-      <c r="H34" s="16">
-        <f>F34/D34</f>
+      <c r="H34" s="13">
+        <f t="shared" si="3"/>
         <v>0.96885985849430767</v>
       </c>
       <c r="I34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>6.1396636178584303E-3</v>
       </c>
-      <c r="J34" s="4"/>
+      <c r="J34" s="3"/>
+      <c r="L34">
+        <v>0.102482458976092</v>
+      </c>
       <c r="M34">
+        <v>2.9595828587883197E-4</v>
+      </c>
+      <c r="N34">
         <v>0.102092586065974</v>
       </c>
-      <c r="N34" s="10" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O34" s="10"/>
+      <c r="O34">
+        <v>4.88706826404386E-4</v>
+      </c>
+      <c r="P34" s="7">
+        <f>N34/L34</f>
+        <v>0.996195710817117</v>
+      </c>
+      <c r="Q34">
+        <f t="shared" si="5"/>
+        <v>5.5692878927237057E-3</v>
+      </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>750</v>
       </c>
-      <c r="B35" s="5"/>
+      <c r="B35" s="4"/>
       <c r="D35">
         <v>0.12681392305883499</v>
       </c>
-      <c r="E35" s="17">
+      <c r="E35">
         <v>3.7117560576619898E-4</v>
       </c>
-      <c r="F35" s="17">
+      <c r="F35">
         <v>0.12725844081883</v>
       </c>
-      <c r="G35" s="17">
+      <c r="G35">
         <v>3.9277512684765298E-4</v>
       </c>
-      <c r="H35" s="16">
-        <f>F35/D35</f>
+      <c r="H35" s="13">
+        <f t="shared" si="3"/>
         <v>1.0035052756769365</v>
       </c>
       <c r="I35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4.2684987159538603E-3</v>
       </c>
-      <c r="J35" s="4"/>
+      <c r="J35" s="3"/>
+      <c r="L35">
+        <v>0.13877899849488601</v>
+      </c>
       <c r="M35">
+        <v>4.2009114228035198E-4</v>
+      </c>
+      <c r="N35">
         <v>0.14105605143254499</v>
       </c>
-      <c r="N35" s="10" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O35" s="11"/>
+      <c r="O35">
+        <v>6.4618904182841804E-4</v>
+      </c>
+      <c r="P35" s="7">
+        <f>N35/L35</f>
+        <v>1.0164077631511579</v>
+      </c>
+      <c r="Q35">
+        <f t="shared" si="5"/>
+        <v>5.5809331857695158E-3</v>
+      </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>999.99</v>
       </c>
-      <c r="B36" s="5"/>
+      <c r="B36" s="4"/>
       <c r="D36">
         <v>0.15510900896549801</v>
       </c>
-      <c r="E36" s="17">
+      <c r="E36">
         <v>5.7851797067085496E-4</v>
       </c>
-      <c r="F36" s="17">
+      <c r="F36">
         <v>0.157583868759714</v>
       </c>
-      <c r="G36" s="17">
+      <c r="G36">
         <v>5.8700051779191705E-4</v>
       </c>
-      <c r="H36" s="16">
-        <f>F36/D36</f>
+      <c r="H36" s="13">
+        <f t="shared" si="3"/>
         <v>1.0159556160581653</v>
       </c>
       <c r="I36">
         <f>H36*((E36/D36)^2 +(G36/F36)^2)^0.5</f>
         <v>5.3554157048239367E-3</v>
       </c>
-      <c r="J36" s="4"/>
+      <c r="J36" s="3"/>
+      <c r="L36">
+        <v>0.16969831628755799</v>
+      </c>
       <c r="M36">
+        <v>6.3046734962274005E-4</v>
+      </c>
+      <c r="N36">
         <v>0.17395996323018501</v>
       </c>
-      <c r="N36" s="10" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O36" s="10"/>
+      <c r="O36">
+        <v>7.9326262337449101E-4</v>
+      </c>
+      <c r="P36" s="7">
+        <f>N36/L36</f>
+        <v>1.025113077347247</v>
+      </c>
+      <c r="Q36">
+        <f>P36*((M36/L36)^2 +(O36/N36)^2)^0.5</f>
+        <v>6.0296141732043276E-3</v>
+      </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C40" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C41" s="14" t="s">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C41" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
-      <c r="H41" s="15"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C42" s="3" t="s">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C42" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="3"/>
-      <c r="K42" s="3" t="s">
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="14"/>
+      <c r="K42" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="L42" s="3"/>
-      <c r="M42" s="9"/>
-      <c r="N42" s="9"/>
+      <c r="L42" s="17"/>
+      <c r="M42" s="18"/>
+      <c r="N42" s="18"/>
+      <c r="O42" s="17"/>
+      <c r="P42" s="17"/>
+      <c r="Q42" s="17"/>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A43" s="6" t="s">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A43" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6" t="s">
+      <c r="B43" s="5"/>
+      <c r="C43" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D43" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6" t="s">
+      <c r="D43" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H43" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="7" t="s">
+      <c r="I43" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="J43" s="6"/>
+      <c r="K43" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="L43" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="J43" s="8"/>
-      <c r="K43" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="L43" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="M43" s="6" t="s">
+      <c r="M43" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="N43" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="O43" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="P43" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="N43" s="7" t="s">
-        <v>8</v>
+      <c r="Q43" s="19" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>0.1</v>
       </c>
-      <c r="B44" s="5"/>
-      <c r="D44">
+      <c r="B44" s="4"/>
+      <c r="D44" s="20">
         <v>1.33146077610654</v>
       </c>
+      <c r="E44" s="20">
+        <v>1.29791278993871E-2</v>
+      </c>
       <c r="F44">
-        <v>1.3294682945082299</v>
-      </c>
-      <c r="I44" s="10">
+        <v>1.33536898944584</v>
+      </c>
+      <c r="G44">
+        <v>1.25080703731084E-4</v>
+      </c>
+      <c r="H44" s="7">
         <f>F44/D44</f>
-        <v>0.9985035371420129</v>
-      </c>
-      <c r="J44" s="4"/>
+        <v>1.0029352823676327</v>
+      </c>
+      <c r="I44">
+        <f>H44*((E44/D44)^2 +(G44/F44)^2)^0.5</f>
+        <v>9.7771008098175641E-3</v>
+      </c>
+      <c r="J44" s="3"/>
       <c r="L44">
-        <v>1.33422182541257</v>
-      </c>
-      <c r="M44">
-        <v>1.3288821396550801</v>
-      </c>
-      <c r="N44" s="10">
-        <f>M44/L44</f>
-        <v>0.99599790255579224</v>
+        <v>1.3352318967644701</v>
+      </c>
+      <c r="M44" s="2">
+        <v>9.7356481692860994E-5</v>
+      </c>
+      <c r="P44" s="7">
+        <f>N44/L44</f>
+        <v>0</v>
+      </c>
+      <c r="Q44" t="e">
+        <f>P44*((M44/L44)^2 +(O44/N44)^2)^0.5</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>0.5</v>
       </c>
-      <c r="B45" s="5"/>
-      <c r="D45">
+      <c r="B45" s="4"/>
+      <c r="D45" s="20">
         <v>1.35765661048369</v>
       </c>
+      <c r="E45" s="20">
+        <v>1.33833833770021E-2</v>
+      </c>
       <c r="F45">
-        <v>1.3402135659025001</v>
-      </c>
-      <c r="I45" s="10">
-        <f t="shared" ref="I45:I56" si="4">F45/D45</f>
-        <v>0.98715209394887005</v>
-      </c>
-      <c r="J45" s="4"/>
-      <c r="K45" s="4"/>
+        <v>1.3335516984153499</v>
+      </c>
+      <c r="G45" s="2">
+        <v>9.8571452316726502E-5</v>
+      </c>
+      <c r="H45" s="7">
+        <f>F45/D45</f>
+        <v>0.98224520701169626</v>
+      </c>
+      <c r="I45">
+        <f t="shared" ref="I45:I55" si="6">H45*((E45/D45)^2 +(G45/F45)^2)^0.5</f>
+        <v>9.6829593214113503E-3</v>
+      </c>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
       <c r="L45">
-        <v>1.3552315082948401</v>
+        <v>1.33328060850382</v>
       </c>
       <c r="M45">
-        <v>1.34024384554322</v>
-      </c>
-      <c r="N45" s="11">
-        <f t="shared" ref="N45:N56" si="5">M45/L45</f>
-        <v>0.98894088378266998</v>
+        <v>1.11744636942801E-4</v>
+      </c>
+      <c r="N45">
+        <v>1.33349654821898</v>
+      </c>
+      <c r="O45" s="2">
+        <v>9.9388022927045995E-5</v>
+      </c>
+      <c r="P45" s="8">
+        <f>N45/L45</f>
+        <v>1.0001619611909021</v>
+      </c>
+      <c r="Q45">
+        <f t="shared" ref="Q45:Q55" si="7">P45*((M45/L45)^2 +(O45/N45)^2)^0.5</f>
+        <v>1.1217617716941135E-4</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>1</v>
       </c>
-      <c r="B46" s="5"/>
-      <c r="D46">
+      <c r="B46" s="4"/>
+      <c r="D46" s="20">
         <v>1.33903476392587</v>
       </c>
+      <c r="E46" s="20">
+        <v>1.09198789595156E-2</v>
+      </c>
       <c r="F46">
-        <v>1.3294539841566</v>
-      </c>
-      <c r="I46" s="10">
-        <f t="shared" si="4"/>
-        <v>0.99284501043036377</v>
-      </c>
-      <c r="J46" s="4"/>
+        <v>1.33280976817106</v>
+      </c>
+      <c r="G46">
+        <v>1.10318157044691E-4</v>
+      </c>
+      <c r="H46" s="7">
+        <f>F46/D46</f>
+        <v>0.99535113208221782</v>
+      </c>
+      <c r="I46">
+        <f t="shared" si="6"/>
+        <v>8.1175440777359244E-3</v>
+      </c>
+      <c r="J46" s="3"/>
       <c r="L46">
-        <v>1.3461367977004299</v>
+        <v>1.3325160160175999</v>
       </c>
       <c r="M46">
-        <v>1.32904261090945</v>
-      </c>
-      <c r="N46" s="10">
-        <f t="shared" si="5"/>
-        <v>0.98730130041747499</v>
+        <v>1.2990361944337101E-4</v>
+      </c>
+      <c r="N46">
+        <v>1.3326689845730799</v>
+      </c>
+      <c r="O46">
+        <v>1.0526827110579401E-4</v>
+      </c>
+      <c r="P46" s="7">
+        <f>N46/L46</f>
+        <v>1.0001147967856605</v>
+      </c>
+      <c r="Q46">
+        <f t="shared" si="7"/>
+        <v>1.2548677612360951E-4</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>10</v>
       </c>
-      <c r="B47" s="5"/>
-      <c r="D47">
+      <c r="B47" s="4"/>
+      <c r="D47" s="20">
         <v>1.31789010731641</v>
       </c>
+      <c r="E47" s="20">
+        <v>1.2370870755455E-2</v>
+      </c>
       <c r="F47">
-        <v>1.3448930260504799</v>
-      </c>
-      <c r="I47" s="10">
-        <f t="shared" si="4"/>
-        <v>1.0204895071175968</v>
-      </c>
-      <c r="J47" s="4"/>
-      <c r="K47" s="4"/>
+        <v>1.33006735676433</v>
+      </c>
+      <c r="G47">
+        <v>4.3462506631634999E-4</v>
+      </c>
+      <c r="H47" s="7">
+        <f>F47/D47</f>
+        <v>1.009239958157601</v>
+      </c>
+      <c r="I47">
+        <f t="shared" si="6"/>
+        <v>9.4793485833704651E-3</v>
+      </c>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
       <c r="L47">
-        <v>1.31846450590491</v>
+        <v>1.32875591199513</v>
       </c>
       <c r="M47">
-        <v>1.3511493506913199</v>
-      </c>
-      <c r="N47" s="11">
-        <f t="shared" si="5"/>
-        <v>1.0247900831914902</v>
+        <v>3.6656386812860002E-4</v>
+      </c>
+      <c r="N47">
+        <v>1.3283935226396499</v>
+      </c>
+      <c r="O47">
+        <v>4.6050432456435497E-4</v>
+      </c>
+      <c r="P47" s="8">
+        <f>N47/L47</f>
+        <v>0.99972727168909759</v>
+      </c>
+      <c r="Q47">
+        <f t="shared" si="7"/>
+        <v>4.4291324537064109E-4</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>25</v>
       </c>
-      <c r="B48" s="5"/>
-      <c r="D48">
+      <c r="B48" s="4"/>
+      <c r="D48" s="20">
         <v>1.32036564820574</v>
       </c>
+      <c r="E48" s="20">
+        <v>1.3456104516294001E-2</v>
+      </c>
       <c r="F48">
-        <v>1.3268512139816999</v>
-      </c>
-      <c r="I48" s="10">
-        <f t="shared" si="4"/>
-        <v>1.0049119467662411</v>
-      </c>
-      <c r="J48" s="4"/>
+        <v>1.32879638765109</v>
+      </c>
+      <c r="G48">
+        <v>1.0451282524601201E-3</v>
+      </c>
+      <c r="H48" s="7">
+        <f>F48/D48</f>
+        <v>1.0063851550945806</v>
+      </c>
+      <c r="I48">
+        <f t="shared" si="6"/>
+        <v>1.028676695047087E-2</v>
+      </c>
+      <c r="J48" s="3"/>
       <c r="L48">
-        <v>1.33152629750905</v>
+        <v>1.3245110745965301</v>
       </c>
       <c r="M48">
-        <v>1.33015612015508</v>
-      </c>
-      <c r="N48" s="10">
-        <f t="shared" si="5"/>
-        <v>0.99897097236717491</v>
+        <v>6.3753145972632905E-4</v>
+      </c>
+      <c r="N48">
+        <v>1.32578542353965</v>
+      </c>
+      <c r="O48">
+        <v>1.0645660109259701E-3</v>
+      </c>
+      <c r="P48" s="7">
+        <f>N48/L48</f>
+        <v>1.0009621278127161</v>
+      </c>
+      <c r="Q48">
+        <f t="shared" si="7"/>
+        <v>9.3708596837583497E-4</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>50</v>
       </c>
-      <c r="B49" s="5"/>
-      <c r="D49">
+      <c r="B49" s="4"/>
+      <c r="D49" s="20">
         <v>1.3197738196808499</v>
       </c>
+      <c r="E49" s="20">
+        <v>1.08550142358942E-2</v>
+      </c>
       <c r="F49">
-        <v>1.3126564921716899</v>
-      </c>
-      <c r="I49" s="10">
-        <f t="shared" si="4"/>
-        <v>0.99460716116426584</v>
-      </c>
-      <c r="J49" s="4"/>
-      <c r="K49" s="4"/>
+        <v>1.32593816850222</v>
+      </c>
+      <c r="G49">
+        <v>9.7502159311734795E-4</v>
+      </c>
+      <c r="H49" s="7">
+        <f>F49/D49</f>
+        <v>1.0046707615573558</v>
+      </c>
+      <c r="I49">
+        <f t="shared" si="6"/>
+        <v>8.296280948766499E-3</v>
+      </c>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
       <c r="L49">
-        <v>1.32005527665466</v>
+        <v>1.3197871026024</v>
       </c>
       <c r="M49">
-        <v>1.30244954906179</v>
-      </c>
-      <c r="N49" s="11">
-        <f t="shared" si="5"/>
-        <v>0.98666288608952257</v>
+        <v>8.8312138374329295E-4</v>
+      </c>
+      <c r="N49">
+        <v>1.3193357094999201</v>
+      </c>
+      <c r="O49">
+        <v>9.5862687561023305E-4</v>
+      </c>
+      <c r="P49" s="8">
+        <f>N49/L49</f>
+        <v>0.99965798036547726</v>
+      </c>
+      <c r="Q49">
+        <f t="shared" si="7"/>
+        <v>9.874335070433548E-4</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>75</v>
       </c>
-      <c r="B50" s="5"/>
-      <c r="D50">
+      <c r="B50" s="4"/>
+      <c r="D50" s="20">
         <v>1.29935652652886</v>
       </c>
-      <c r="F50">
-        <v>1.32473430230751</v>
-      </c>
-      <c r="I50" s="10">
-        <f t="shared" si="4"/>
-        <v>1.0195310334465668</v>
-      </c>
-      <c r="J50" s="4"/>
+      <c r="E50" s="20">
+        <v>1.1974083384246499E-2</v>
+      </c>
+      <c r="H50" s="7">
+        <f>F50/D50</f>
+        <v>0</v>
+      </c>
+      <c r="I50" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J50" s="3"/>
       <c r="L50">
-        <v>1.30908256842566</v>
+        <v>1.31486593414251</v>
       </c>
       <c r="M50">
-        <v>1.30672475018709</v>
-      </c>
-      <c r="N50" s="10">
-        <f t="shared" si="5"/>
-        <v>0.99819887736996948</v>
+        <v>8.9177056244582901E-4</v>
+      </c>
+      <c r="N50">
+        <v>1.31129753244608</v>
+      </c>
+      <c r="O50">
+        <v>7.8150296279425404E-4</v>
+      </c>
+      <c r="P50" s="7">
+        <f>N50/L50</f>
+        <v>0.99728610985822141</v>
+      </c>
+      <c r="Q50">
+        <f t="shared" si="7"/>
+        <v>9.004190394956773E-4</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>100</v>
       </c>
-      <c r="B51" s="5"/>
-      <c r="D51">
+      <c r="B51" s="4"/>
+      <c r="D51" s="20">
         <v>1.33910590256307</v>
       </c>
-      <c r="F51">
-        <v>1.3167897334910501</v>
-      </c>
-      <c r="I51" s="10">
-        <f t="shared" si="4"/>
-        <v>0.98333502299608533</v>
-      </c>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
+      <c r="E51" s="20">
+        <v>1.23393298512987E-2</v>
+      </c>
+      <c r="H51" s="7">
+        <f>F51/D51</f>
+        <v>0</v>
+      </c>
+      <c r="I51" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J51" s="3"/>
+      <c r="K51" s="3"/>
       <c r="L51">
-        <v>1.3171859836539099</v>
+        <v>1.3080554428553499</v>
       </c>
       <c r="M51">
-        <v>1.31060168409573</v>
-      </c>
-      <c r="N51" s="11">
-        <f t="shared" si="5"/>
-        <v>0.99500123775997451</v>
+        <v>1.05245064814075E-3</v>
+      </c>
+      <c r="N51">
+        <v>1.30680092368919</v>
+      </c>
+      <c r="O51">
+        <v>1.1966142360113001E-3</v>
+      </c>
+      <c r="P51" s="8">
+        <f>N51/L51</f>
+        <v>0.99904092814030765</v>
+      </c>
+      <c r="Q51">
+        <f t="shared" si="7"/>
+        <v>1.2177819875734308E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>150</v>
       </c>
-      <c r="B52" s="5"/>
-      <c r="D52">
+      <c r="B52" s="4"/>
+      <c r="D52" s="20">
         <v>1.3346899335651701</v>
       </c>
-      <c r="F52">
-        <v>1.3164282135057199</v>
-      </c>
-      <c r="I52" s="10">
-        <f t="shared" si="4"/>
-        <v>0.98631763108404502</v>
-      </c>
-      <c r="J52" s="4"/>
+      <c r="E52" s="20">
+        <v>1.09895445803343E-2</v>
+      </c>
+      <c r="H52" s="7">
+        <f>F52/D52</f>
+        <v>0</v>
+      </c>
+      <c r="I52" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J52" s="3"/>
       <c r="L52">
-        <v>1.28924587434467</v>
+        <v>1.2992314592619101</v>
       </c>
       <c r="M52">
-        <v>1.3011790803332</v>
-      </c>
-      <c r="N52" s="10">
-        <f t="shared" si="5"/>
-        <v>1.0092559582512495</v>
+        <v>2.6598085552900302E-3</v>
+      </c>
+      <c r="N52">
+        <v>1.2990352083416801</v>
+      </c>
+      <c r="O52">
+        <v>2.3388362534294302E-3</v>
+      </c>
+      <c r="P52" s="7">
+        <f>N52/L52</f>
+        <v>0.99984894845423344</v>
+      </c>
+      <c r="Q52">
+        <f t="shared" si="7"/>
+        <v>2.7258832387438308E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>250</v>
       </c>
-      <c r="B53" s="5"/>
-      <c r="D53">
+      <c r="B53" s="4"/>
+      <c r="D53" s="20">
         <v>1.29678717701069</v>
       </c>
-      <c r="F53">
-        <v>1.33451901185347</v>
-      </c>
-      <c r="I53" s="10">
-        <f t="shared" si="4"/>
-        <v>1.0290963972436542</v>
-      </c>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
+      <c r="E53" s="20">
+        <v>1.08165723286055E-2</v>
+      </c>
+      <c r="H53" s="7">
+        <f>F53/D53</f>
+        <v>0</v>
+      </c>
+      <c r="I53" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J53" s="3"/>
+      <c r="K53" s="3"/>
       <c r="L53">
-        <v>1.2845821783281699</v>
+        <v>1.2754633925346801</v>
       </c>
       <c r="M53">
-        <v>1.27732476166037</v>
-      </c>
-      <c r="N53" s="11">
-        <f t="shared" si="5"/>
-        <v>0.99435036793267273</v>
+        <v>2.5670750630042301E-3</v>
+      </c>
+      <c r="N53">
+        <v>1.27508401331121</v>
+      </c>
+      <c r="O53">
+        <v>3.1668437255882899E-3</v>
+      </c>
+      <c r="P53" s="8">
+        <f>N53/L53</f>
+        <v>0.9997025557725211</v>
+      </c>
+      <c r="Q53">
+        <f t="shared" si="7"/>
+        <v>3.1958049501485874E-3</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>500</v>
       </c>
-      <c r="B54" s="5"/>
-      <c r="D54">
+      <c r="B54" s="4"/>
+      <c r="D54" s="20">
         <v>1.2662694099393199</v>
       </c>
-      <c r="F54">
-        <v>1.2620512370753201</v>
-      </c>
-      <c r="I54" s="10">
-        <f t="shared" si="4"/>
-        <v>0.99666881879093805</v>
-      </c>
-      <c r="J54" s="4"/>
+      <c r="E54" s="20">
+        <v>1.3642711353786301E-2</v>
+      </c>
+      <c r="H54" s="7">
+        <f>F54/D54</f>
+        <v>0</v>
+      </c>
+      <c r="I54" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J54" s="3"/>
       <c r="L54">
-        <v>1.2051198250164299</v>
+        <v>1.21433761848289</v>
       </c>
       <c r="M54">
-        <v>1.19710463230099</v>
-      </c>
-      <c r="N54" s="10">
-        <f t="shared" si="5"/>
-        <v>0.99334904915755518</v>
+        <v>1.78305037450447E-3</v>
+      </c>
+      <c r="N54">
+        <v>1.2162928747352799</v>
+      </c>
+      <c r="O54">
+        <v>1.78442571980327E-3</v>
+      </c>
+      <c r="P54" s="7">
+        <f>N54/L54</f>
+        <v>1.0016101422064423</v>
+      </c>
+      <c r="Q54">
+        <f t="shared" si="7"/>
+        <v>2.0790073532015014E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>750</v>
       </c>
-      <c r="B55" s="5"/>
-      <c r="D55">
+      <c r="B55" s="4"/>
+      <c r="D55" s="20">
         <v>1.23279071771682</v>
       </c>
-      <c r="F55">
-        <v>1.23649350366719</v>
-      </c>
-      <c r="I55" s="10">
-        <f t="shared" si="4"/>
-        <v>1.0030035803296993</v>
-      </c>
-      <c r="J55" s="5"/>
+      <c r="E55" s="20">
+        <v>1.1896408260051301E-2</v>
+      </c>
+      <c r="H55" s="7">
+        <f>F55/D55</f>
+        <v>0</v>
+      </c>
+      <c r="I55" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J55" s="4"/>
       <c r="L55">
-        <v>1.1807532343395699</v>
+        <v>1.16893154054166</v>
       </c>
       <c r="M55">
-        <v>1.1563239206929501</v>
-      </c>
-      <c r="N55" s="10">
-        <f t="shared" si="5"/>
-        <v>0.97931039870470149</v>
+        <v>2.5299483816998E-3</v>
+      </c>
+      <c r="N55">
+        <v>1.1623016999656299</v>
+      </c>
+      <c r="O55">
+        <v>2.3537063605707201E-3</v>
+      </c>
+      <c r="P55" s="7">
+        <f>N55/L55</f>
+        <v>0.99432829011273149</v>
+      </c>
+      <c r="Q55">
+        <f t="shared" si="7"/>
+        <v>2.9471542099952473E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>999.99</v>
       </c>
-      <c r="B56" s="5"/>
-      <c r="D56">
+      <c r="B56" s="4"/>
+      <c r="D56" s="20">
         <v>1.1928852496040101</v>
       </c>
-      <c r="F56">
-        <v>1.2106403902979499</v>
-      </c>
-      <c r="I56" s="10">
-        <f t="shared" si="4"/>
-        <v>1.0148841983751864</v>
-      </c>
-      <c r="J56" s="5"/>
+      <c r="E56" s="20">
+        <v>1.19657192345643E-2</v>
+      </c>
+      <c r="H56" s="7">
+        <f>F56/D56</f>
+        <v>0</v>
+      </c>
+      <c r="I56" t="e">
+        <f>H56*((E56/D56)^2 +(G56/F56)^2)^0.5</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J56" s="4"/>
       <c r="L56">
-        <v>1.13357719050286</v>
+        <v>1.1280813456035399</v>
       </c>
       <c r="M56">
-        <v>1.1342010761596699</v>
-      </c>
-      <c r="N56" s="11">
-        <f t="shared" si="5"/>
-        <v>1.0005503689224138</v>
+        <v>2.4503318989518999E-3</v>
+      </c>
+      <c r="N56">
+        <v>1.1159074766764601</v>
+      </c>
+      <c r="O56">
+        <v>2.3868755353182898E-3</v>
+      </c>
+      <c r="P56" s="8">
+        <f>N56/L56</f>
+        <v>0.98920834124726476</v>
+      </c>
+      <c r="Q56">
+        <f>P56*((M56/L56)^2 +(O56/N56)^2)^0.5</f>
+        <v>3.0155845990736735E-3</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C59" s="12" t="s">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C59" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D59" s="12"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="13"/>
-      <c r="H59" s="13"/>
-      <c r="I59" s="13"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="10"/>
+      <c r="G59" s="10"/>
+      <c r="H59" s="10"/>
+      <c r="I59" s="10"/>
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C60" s="3" t="s">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C60" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="9"/>
-      <c r="H60" s="9"/>
-      <c r="I60" s="3"/>
-      <c r="K60" s="3" t="s">
+      <c r="D60" s="14"/>
+      <c r="E60" s="14"/>
+      <c r="F60" s="15"/>
+      <c r="G60" s="15"/>
+      <c r="H60" s="15"/>
+      <c r="I60" s="14"/>
+      <c r="K60" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="L60" s="3"/>
-      <c r="M60" s="9"/>
-      <c r="N60" s="9"/>
+      <c r="L60" s="17"/>
+      <c r="M60" s="18"/>
+      <c r="N60" s="18"/>
+      <c r="O60" s="17"/>
+      <c r="P60" s="17"/>
+      <c r="Q60" s="17"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="6" t="s">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A61" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6" t="s">
+      <c r="B61" s="5"/>
+      <c r="C61" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D61" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E61" s="6"/>
-      <c r="F61" s="6" t="s">
+      <c r="D61" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F61" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G61" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H61" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="7" t="s">
+      <c r="I61" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="J61" s="6"/>
+      <c r="K61" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="L61" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="J61" s="8"/>
-      <c r="K61" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="L61" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="M61" s="6" t="s">
+      <c r="M61" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="N61" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="O61" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="P61" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="N61" s="7" t="s">
-        <v>8</v>
+      <c r="Q61" s="19" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>0.1</v>
       </c>
-      <c r="B62" s="5"/>
+      <c r="B62" s="4"/>
       <c r="C62" s="2">
         <v>2.0906018648200899E-5</v>
       </c>
-      <c r="D62" s="2">
+      <c r="D62" s="21">
         <v>1.9785240862768899E-5</v>
       </c>
-      <c r="E62" s="2"/>
+      <c r="E62" s="21"/>
       <c r="F62" s="2">
-        <v>1.9417624590728801E-5</v>
-      </c>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="10">
+        <v>2.0611254914561302E-5</v>
+      </c>
+      <c r="G62" s="2">
+        <v>2.6942824381894501E-8</v>
+      </c>
+      <c r="H62" s="7">
         <f>F62/D62</f>
-        <v>0.98141967163352228</v>
-      </c>
-      <c r="J62" s="4"/>
+        <v>1.0417490015674646</v>
+      </c>
+      <c r="I62">
+        <f>H62*((E62/D62)^2 +(G62/F62)^2)^0.5</f>
+        <v>1.3617637798180393E-3</v>
+      </c>
+      <c r="J62" s="3"/>
       <c r="K62" s="2"/>
       <c r="L62" s="2">
-        <v>2.44555572729164E-5</v>
+        <v>2.44222139985293E-5</v>
       </c>
       <c r="M62" s="2">
-        <v>2.3173152783100001E-5</v>
-      </c>
-      <c r="N62" s="10">
-        <f>M62/L62</f>
-        <v>0.94756183735642718</v>
+        <v>3.2540004788240401E-9</v>
+      </c>
+      <c r="N62" s="7"/>
+      <c r="P62" s="7">
+        <f>N62/L62</f>
+        <v>0</v>
+      </c>
+      <c r="Q62" t="e">
+        <f>P62*((M62/L62)^2 +(O62/N62)^2)^0.5</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>0.5</v>
       </c>
-      <c r="B63" s="5"/>
+      <c r="B63" s="4"/>
       <c r="C63" s="2">
         <v>3.1327203465188001E-3</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="20">
         <v>1.02051178015395E-4</v>
       </c>
-      <c r="F63" s="2">
-        <v>9.4705678455829002E-5</v>
-      </c>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="10">
-        <f t="shared" ref="I63:I74" si="6">F63/D63</f>
-        <v>0.92802141334950694</v>
-      </c>
-      <c r="J63" s="4"/>
+      <c r="E63" s="20"/>
+      <c r="F63">
+        <v>1.03580844636417E-4</v>
+      </c>
+      <c r="G63" s="2">
+        <v>6.1396317523546606E-8</v>
+      </c>
+      <c r="H63" s="7">
+        <f>F63/D63</f>
+        <v>1.0149892108133356</v>
+      </c>
+      <c r="I63">
+        <f t="shared" ref="I63:I73" si="8">H63*((E63/D63)^2 +(G63/F63)^2)^0.5</f>
+        <v>6.016228202116846E-4</v>
+      </c>
+      <c r="J63" s="3"/>
       <c r="L63">
-        <v>1.237590596311E-4</v>
-      </c>
-      <c r="M63">
-        <v>1.2781285534871299E-4</v>
-      </c>
-      <c r="N63" s="11">
-        <f t="shared" ref="N63:N74" si="7">M63/L63</f>
-        <v>1.0327555471873857</v>
+        <v>1.21907844018741E-4</v>
+      </c>
+      <c r="M63" s="2">
+        <v>1.40834939730919E-8</v>
+      </c>
+      <c r="N63">
+        <v>1.27621410906264E-4</v>
+      </c>
+      <c r="O63" s="2">
+        <v>7.9820165373987095E-8</v>
+      </c>
+      <c r="P63" s="7">
+        <f>N63/L63</f>
+        <v>1.0468679184142133</v>
+      </c>
+      <c r="Q63">
+        <f t="shared" ref="Q63:Q73" si="9">P63*((M63/L63)^2 +(O63/N63)^2)^0.5</f>
+        <v>6.6583397526143498E-4</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>1</v>
       </c>
-      <c r="B64" s="5"/>
+      <c r="B64" s="4"/>
       <c r="C64" s="2">
         <v>6.2691724987101998E-3</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="20">
         <v>2.0004896550590901E-4</v>
       </c>
+      <c r="E64" s="20"/>
       <c r="F64">
-        <v>2.0519183351723301E-4</v>
-      </c>
-      <c r="I64" s="10">
-        <f t="shared" si="6"/>
-        <v>1.0257080460192236</v>
-      </c>
-      <c r="J64" s="4"/>
+        <v>2.0769359643264999E-4</v>
+      </c>
+      <c r="G64" s="2">
+        <v>8.9692390255205302E-8</v>
+      </c>
+      <c r="H64" s="7">
+        <f>F64/D64</f>
+        <v>1.0382137988437394</v>
+      </c>
+      <c r="I64">
+        <f t="shared" si="8"/>
+        <v>4.4835218231886319E-4</v>
+      </c>
+      <c r="J64" s="3"/>
       <c r="L64">
-        <v>2.47009346021372E-4</v>
-      </c>
-      <c r="M64">
-        <v>2.5056736662623701E-4</v>
-      </c>
-      <c r="N64" s="10">
-        <f t="shared" si="7"/>
-        <v>1.0144043966844767</v>
+        <v>2.4364376203713501E-4</v>
+      </c>
+      <c r="M64" s="2">
+        <v>3.6399685613690799E-8</v>
+      </c>
+      <c r="N64">
+        <v>2.5560959700704201E-4</v>
+      </c>
+      <c r="O64" s="2">
+        <v>1.2775665836178299E-7</v>
+      </c>
+      <c r="P64" s="7">
+        <f>N64/L64</f>
+        <v>1.0491120103788383</v>
+      </c>
+      <c r="Q64">
+        <f t="shared" si="9"/>
+        <v>5.4728183879285217E-4</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>10</v>
       </c>
-      <c r="B65" s="5"/>
+      <c r="B65" s="4"/>
       <c r="C65" s="2">
         <v>1.2558983712415E-2</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="20">
         <v>1.9727739159685499E-3</v>
       </c>
+      <c r="E65" s="20"/>
       <c r="F65">
-        <v>2.1002402963605799E-3</v>
-      </c>
-      <c r="I65" s="10">
-        <f t="shared" si="6"/>
-        <v>1.0646127665011473</v>
-      </c>
-      <c r="J65" s="4"/>
+        <v>2.0882330769847598E-3</v>
+      </c>
+      <c r="G65" s="2">
+        <v>1.5267636606574901E-6</v>
+      </c>
+      <c r="H65" s="7">
+        <f>F65/D65</f>
+        <v>1.0585263015095798</v>
+      </c>
+      <c r="I65">
+        <f t="shared" si="8"/>
+        <v>7.7391719765714396E-4</v>
+      </c>
+      <c r="J65" s="3"/>
       <c r="L65">
-        <v>2.41443999850058E-3</v>
-      </c>
-      <c r="M65">
-        <v>2.5624129143282902E-3</v>
-      </c>
-      <c r="N65" s="11">
-        <f t="shared" si="7"/>
-        <v>1.0612866403470804</v>
+        <v>2.4288696331029799E-3</v>
+      </c>
+      <c r="M65" s="2">
+        <v>9.7964708696651905E-7</v>
+      </c>
+      <c r="N65">
+        <v>2.56202907911283E-3</v>
+      </c>
+      <c r="O65" s="2">
+        <v>1.85007690935801E-6</v>
+      </c>
+      <c r="P65" s="7">
+        <f>N65/L65</f>
+        <v>1.0548236283228316</v>
+      </c>
+      <c r="Q65">
+        <f t="shared" si="9"/>
+        <v>8.7246560513766763E-4</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>25</v>
       </c>
-      <c r="B66" s="5"/>
+      <c r="B66" s="4"/>
       <c r="C66" s="2">
         <v>1.8782496824776201E-2</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="20">
         <v>4.9269907229743297E-3</v>
       </c>
+      <c r="E66" s="20"/>
       <c r="F66">
-        <v>5.2981099306138504E-3</v>
-      </c>
-      <c r="I66" s="10">
-        <f t="shared" si="6"/>
-        <v>1.0753237074121145</v>
-      </c>
-      <c r="J66" s="4"/>
+        <v>5.2267028439012698E-3</v>
+      </c>
+      <c r="G66" s="2">
+        <v>5.8392478108713296E-6</v>
+      </c>
+      <c r="H66" s="7">
+        <f>F66/D66</f>
+        <v>1.0608306647563586</v>
+      </c>
+      <c r="I66">
+        <f t="shared" si="8"/>
+        <v>1.1851550244743078E-3</v>
+      </c>
+      <c r="J66" s="3"/>
       <c r="L66">
-        <v>6.11270182240103E-3</v>
-      </c>
-      <c r="M66">
-        <v>6.4145321839513504E-3</v>
-      </c>
-      <c r="N66" s="10">
-        <f t="shared" si="7"/>
-        <v>1.0493775699060295</v>
+        <v>6.0546834237900898E-3</v>
+      </c>
+      <c r="M66" s="2">
+        <v>3.7968621057748099E-6</v>
+      </c>
+      <c r="N66">
+        <v>6.4137122028123401E-3</v>
+      </c>
+      <c r="O66" s="2">
+        <v>5.4200951411111697E-6</v>
+      </c>
+      <c r="P66" s="7">
+        <f>N66/L66</f>
+        <v>1.0592976963273675</v>
+      </c>
+      <c r="Q66">
+        <f t="shared" si="9"/>
+        <v>1.1147351456962668E-3</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>50</v>
       </c>
-      <c r="B67" s="5"/>
+      <c r="B67" s="4"/>
       <c r="C67" s="2">
         <v>2.51046376970986E-2</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="20">
         <v>9.7820010092556295E-3</v>
       </c>
+      <c r="E67" s="20"/>
       <c r="F67">
-        <v>1.0195154351149101E-2</v>
-      </c>
-      <c r="I67" s="10">
-        <f t="shared" si="6"/>
-        <v>1.0422360763919929</v>
-      </c>
-      <c r="J67" s="4"/>
+        <v>1.04457324399824E-2</v>
+      </c>
+      <c r="G67" s="2">
+        <v>1.0966581763202101E-5</v>
+      </c>
+      <c r="H67" s="7">
+        <f>F67/D67</f>
+        <v>1.0678523167293434</v>
+      </c>
+      <c r="I67">
+        <f t="shared" si="8"/>
+        <v>1.1210979995632418E-3</v>
+      </c>
+      <c r="J67" s="3"/>
       <c r="L67">
-        <v>1.20970549355645E-2</v>
-      </c>
-      <c r="M67">
-        <v>1.24175942421624E-2</v>
-      </c>
-      <c r="N67" s="11">
-        <f t="shared" si="7"/>
-        <v>1.0264973010625533</v>
+        <v>1.20608403533201E-2</v>
+      </c>
+      <c r="M67" s="2">
+        <v>1.08240027557222E-5</v>
+      </c>
+      <c r="N67">
+        <v>1.27839027701272E-2</v>
+      </c>
+      <c r="O67" s="2">
+        <v>1.14752038724967E-5</v>
+      </c>
+      <c r="P67" s="7">
+        <f>N67/L67</f>
+        <v>1.0599512468140793</v>
+      </c>
+      <c r="Q67">
+        <f t="shared" si="9"/>
+        <v>1.3454096255822378E-3</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>75</v>
       </c>
-      <c r="B68" s="5"/>
+      <c r="B68" s="4"/>
       <c r="C68" s="2">
         <v>3.1476119846668899E-2</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="20">
         <v>1.43763436727791E-2</v>
       </c>
-      <c r="F68">
-        <v>1.5782984835099299E-2</v>
-      </c>
-      <c r="I68" s="10">
-        <f t="shared" si="6"/>
-        <v>1.0978441524727602</v>
-      </c>
-      <c r="J68" s="4"/>
+      <c r="E68" s="20"/>
+      <c r="H68" s="7">
+        <f>F68/D68</f>
+        <v>0</v>
+      </c>
+      <c r="I68" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J68" s="3"/>
       <c r="L68">
-        <v>1.8002551123509802E-2</v>
-      </c>
-      <c r="M68">
-        <v>1.8976376994297401E-2</v>
-      </c>
-      <c r="N68" s="10">
-        <f t="shared" si="7"/>
-        <v>1.0540937706054263</v>
+        <v>1.8041215453004699E-2</v>
+      </c>
+      <c r="M68" s="2">
+        <v>1.7714094968001101E-5</v>
+      </c>
+      <c r="N68">
+        <v>1.9051467947753701E-2</v>
+      </c>
+      <c r="O68" s="2">
+        <v>1.1429796000528301E-5</v>
+      </c>
+      <c r="P68" s="7">
+        <f>N68/L68</f>
+        <v>1.0559969197962629</v>
+      </c>
+      <c r="Q68">
+        <f t="shared" si="9"/>
+        <v>1.2150834669821305E-3</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>100</v>
       </c>
-      <c r="B69" s="5"/>
+      <c r="B69" s="4"/>
       <c r="C69" s="2">
         <v>5.2878603388737497E-2</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="20">
         <v>2.00458898906196E-2</v>
       </c>
-      <c r="F69">
-        <v>2.0804120655568799E-2</v>
-      </c>
-      <c r="I69" s="10">
-        <f t="shared" si="6"/>
-        <v>1.0378247495664441</v>
-      </c>
-      <c r="J69" s="4"/>
+      <c r="E69" s="20"/>
+      <c r="H69" s="7">
+        <f>F69/D69</f>
+        <v>0</v>
+      </c>
+      <c r="I69" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J69" s="3"/>
       <c r="L69">
-        <v>2.4309982506840501E-2</v>
-      </c>
-      <c r="M69">
-        <v>2.56065505285916E-2</v>
-      </c>
-      <c r="N69" s="11">
-        <f t="shared" si="7"/>
-        <v>1.0533347986320543</v>
+        <v>2.3942727421137198E-2</v>
+      </c>
+      <c r="M69" s="2">
+        <v>2.41011922220882E-5</v>
+      </c>
+      <c r="N69">
+        <v>2.5404075273833399E-2</v>
+      </c>
+      <c r="O69" s="2">
+        <v>2.6871581822638802E-5</v>
+      </c>
+      <c r="P69" s="7">
+        <f>N69/L69</f>
+        <v>1.0610351455367648</v>
+      </c>
+      <c r="Q69">
+        <f t="shared" si="9"/>
+        <v>1.5493114902381951E-3</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>150</v>
       </c>
-      <c r="B70" s="5"/>
+      <c r="B70" s="4"/>
       <c r="C70" s="2">
         <v>0.107716927588289</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="20">
         <v>3.0432830381329601E-2</v>
       </c>
-      <c r="F70">
-        <v>3.14434702136525E-2</v>
-      </c>
-      <c r="I70" s="10">
-        <f t="shared" si="6"/>
-        <v>1.0332088675177227</v>
-      </c>
-      <c r="J70" s="4"/>
+      <c r="E70" s="20"/>
+      <c r="H70" s="7">
+        <f>F70/D70</f>
+        <v>0</v>
+      </c>
+      <c r="I70" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J70" s="3"/>
       <c r="L70">
-        <v>3.5308084946377202E-2</v>
-      </c>
-      <c r="M70">
-        <v>3.7911161854217702E-2</v>
-      </c>
-      <c r="N70" s="10">
-        <f t="shared" si="7"/>
-        <v>1.0737246699104135</v>
+        <v>3.5694610619412301E-2</v>
+      </c>
+      <c r="M70" s="2">
+        <v>8.2524961518027197E-5</v>
+      </c>
+      <c r="N70">
+        <v>3.7961973926613303E-2</v>
+      </c>
+      <c r="O70">
+        <v>1.02905372343833E-4</v>
+      </c>
+      <c r="P70" s="7">
+        <f>N70/L70</f>
+        <v>1.0635211665810387</v>
+      </c>
+      <c r="Q70">
+        <f t="shared" si="9"/>
+        <v>3.7890881489905845E-3</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>250</v>
       </c>
-      <c r="B71" s="5"/>
+      <c r="B71" s="4"/>
       <c r="C71" s="2">
         <v>0.16515386445267599</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="20">
         <v>4.89210306757277E-2</v>
       </c>
-      <c r="F71">
-        <v>5.3975920537313898E-2</v>
-      </c>
-      <c r="I71" s="10">
-        <f t="shared" si="6"/>
-        <v>1.1033275421994369</v>
-      </c>
-      <c r="J71" s="4"/>
+      <c r="E71" s="20"/>
+      <c r="H71" s="7">
+        <f>F71/D71</f>
+        <v>0</v>
+      </c>
+      <c r="I71" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J71" s="3"/>
       <c r="L71">
-        <v>5.8808790512075798E-2</v>
+        <v>5.8503285539065399E-2</v>
       </c>
       <c r="M71">
-        <v>6.2265324575410202E-2</v>
-      </c>
-      <c r="N71" s="11">
-        <f t="shared" si="7"/>
-        <v>1.0587758060187387</v>
+        <v>1.3565230700754799E-4</v>
+      </c>
+      <c r="N71">
+        <v>6.2444533831966298E-2</v>
+      </c>
+      <c r="O71">
+        <v>1.8469627006352599E-4</v>
+      </c>
+      <c r="P71" s="7">
+        <f>N71/L71</f>
+        <v>1.0673679820985291</v>
+      </c>
+      <c r="Q71">
+        <f t="shared" si="9"/>
+        <v>4.0114868768480784E-3</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>500</v>
       </c>
-      <c r="B72" s="5"/>
+      <c r="B72" s="4"/>
       <c r="C72" s="2">
         <v>0.22114304090137801</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="20">
         <v>9.6226590649767796E-2</v>
       </c>
-      <c r="F72">
-        <v>0.10212774105006001</v>
-      </c>
-      <c r="I72" s="10">
-        <f t="shared" si="6"/>
-        <v>1.0613255687481478</v>
-      </c>
-      <c r="J72" s="4"/>
+      <c r="E72" s="20"/>
+      <c r="H72" s="7">
+        <f>F72/D72</f>
+        <v>0</v>
+      </c>
+      <c r="I72" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J72" s="3"/>
       <c r="L72">
-        <v>0.11146020972599301</v>
+        <v>0.111849004597233</v>
       </c>
       <c r="M72">
-        <v>0.118001707852343</v>
-      </c>
-      <c r="N72" s="10">
-        <f t="shared" si="7"/>
-        <v>1.0586890886212328</v>
+        <v>1.9399071169807599E-4</v>
+      </c>
+      <c r="N72">
+        <v>0.120228333001437</v>
+      </c>
+      <c r="O72">
+        <v>2.56613265918605E-4</v>
+      </c>
+      <c r="P72" s="7">
+        <f>N72/L72</f>
+        <v>1.0749164325098632</v>
+      </c>
+      <c r="Q72">
+        <f t="shared" si="9"/>
+        <v>2.9562598512691846E-3</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>750</v>
       </c>
-      <c r="B73" s="5"/>
-      <c r="D73">
+      <c r="B73" s="4"/>
+      <c r="D73" s="20">
         <v>0.140294088260282</v>
       </c>
-      <c r="F73">
-        <v>0.15225875418305601</v>
-      </c>
-      <c r="I73" s="10">
-        <f t="shared" si="6"/>
-        <v>1.0852827519045309</v>
-      </c>
-      <c r="J73" s="5"/>
+      <c r="E73" s="20"/>
+      <c r="H73" s="7">
+        <f>F73/D73</f>
+        <v>0</v>
+      </c>
+      <c r="I73" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J73" s="4"/>
       <c r="L73">
-        <v>0.164782092113922</v>
+        <v>0.16223272595004601</v>
       </c>
       <c r="M73">
-        <v>0.171436913407884</v>
-      </c>
-      <c r="N73" s="11">
-        <f t="shared" si="7"/>
-        <v>1.0403855856458066</v>
+        <v>4.29274074054726E-4</v>
+      </c>
+      <c r="N73">
+        <v>0.17320049362348</v>
+      </c>
+      <c r="O73">
+        <v>3.4421587306751399E-4</v>
+      </c>
+      <c r="P73" s="7">
+        <f>N73/L73</f>
+        <v>1.0676051493877452</v>
+      </c>
+      <c r="Q73">
+        <f t="shared" si="9"/>
+        <v>3.5329852627062406E-3</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>999.99</v>
       </c>
-      <c r="B74" s="5"/>
-      <c r="D74">
+      <c r="B74" s="4"/>
+      <c r="D74" s="20">
         <v>0.181401571560247</v>
       </c>
-      <c r="F74">
-        <v>0.20058148390920799</v>
-      </c>
-      <c r="I74" s="10">
-        <f t="shared" si="6"/>
-        <v>1.1057317871283765</v>
-      </c>
-      <c r="J74" s="5"/>
+      <c r="E74" s="20"/>
+      <c r="H74" s="7">
+        <f>F74/D74</f>
+        <v>0</v>
+      </c>
+      <c r="I74" t="e">
+        <f>H74*((E74/D74)^2 +(G74/F74)^2)^0.5</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J74" s="4"/>
       <c r="L74">
-        <v>0.211482254080264</v>
+        <v>0.208953603264767</v>
       </c>
       <c r="M74">
-        <v>0.22688990016688301</v>
-      </c>
-      <c r="N74" s="10">
-        <f t="shared" si="7"/>
-        <v>1.0728555034256981</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C76" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D76" s="12"/>
-      <c r="E76" s="12"/>
-      <c r="F76" s="13"/>
-      <c r="G76" s="13"/>
-      <c r="H76" s="13"/>
-      <c r="I76" s="13"/>
-      <c r="K76" s="2"/>
-      <c r="L76" s="2"/>
-      <c r="M76" s="2"/>
-      <c r="N76" s="2"/>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C77" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="9"/>
-      <c r="G77" s="9"/>
-      <c r="H77" s="9"/>
-      <c r="I77" s="3"/>
-      <c r="K77" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L77" s="3"/>
-      <c r="M77" s="9"/>
-      <c r="N77" s="9"/>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B78" s="6"/>
-      <c r="C78" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E78" s="6"/>
-      <c r="F78" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G78" s="6"/>
-      <c r="H78" s="6"/>
-      <c r="I78" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J78" s="8"/>
-      <c r="K78" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="L78" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="M78" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="N78" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A79">
-        <v>0.1</v>
-      </c>
-      <c r="B79" s="5"/>
-      <c r="C79" s="2">
-        <v>2.0906018648200899E-5</v>
-      </c>
-      <c r="D79" s="2">
-        <v>2.8143173972499801E-7</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2">
-        <v>1.46150091119403E-6</v>
-      </c>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="10">
-        <f t="shared" ref="I79:I90" si="8">I62*((F79/F62)^2 +(D79/D62)^2)^0.5</f>
-        <v>7.5175789820697683E-2</v>
-      </c>
-      <c r="J79" s="4"/>
-      <c r="K79" s="2"/>
-      <c r="L79" s="2">
-        <v>2.4434932696069799E-5</v>
-      </c>
-      <c r="M79" s="2">
-        <v>2.5518609602937599E-5</v>
-      </c>
-      <c r="N79" s="10">
-        <f>M79/L79</f>
-        <v>1.0443494942403546</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A80">
-        <v>0.5</v>
-      </c>
-      <c r="B80" s="5"/>
-      <c r="C80" s="2">
-        <v>3.1327203465188001E-3</v>
-      </c>
-      <c r="D80" s="2">
-        <v>1.5222069872849199E-6</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2">
-        <v>3.7622530224669299E-6</v>
-      </c>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="10">
-        <f t="shared" si="8"/>
-        <v>3.9379446327356661E-2</v>
-      </c>
-      <c r="J80" s="4"/>
-      <c r="L80">
-        <v>3.6561489620800698E-3</v>
-      </c>
-      <c r="M80">
-        <v>3.8583728177792702E-3</v>
-      </c>
-      <c r="N80" s="11">
-        <f t="shared" ref="N80:N89" si="9">M80/L80</f>
-        <v>1.0553106172085915</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A81">
-        <v>1</v>
-      </c>
-      <c r="B81" s="5"/>
-      <c r="C81" s="2">
-        <v>6.2691724987101998E-3</v>
-      </c>
-      <c r="D81" s="2">
-        <v>2.33807312394273E-6</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2">
-        <v>6.5127278910264096E-6</v>
-      </c>
-      <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="10">
-        <f t="shared" si="8"/>
-        <v>3.4692692812303069E-2</v>
-      </c>
-      <c r="J81" s="4"/>
-      <c r="L81">
-        <v>7.3167786817070497E-3</v>
-      </c>
-      <c r="M81">
-        <v>7.7206053021012903E-3</v>
-      </c>
-      <c r="N81" s="10">
-        <f t="shared" si="9"/>
-        <v>1.0551918594181156</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A82">
-        <v>10</v>
-      </c>
-      <c r="B82" s="5"/>
-      <c r="C82" s="2">
-        <v>1.2558983712415E-2</v>
-      </c>
-      <c r="D82" s="2">
-        <v>2.7701090496064399E-5</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2">
-        <v>3.8011060965548303E-5</v>
-      </c>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="10">
-        <f t="shared" si="8"/>
-        <v>2.4386896067040687E-2</v>
-      </c>
-      <c r="J82" s="4"/>
-      <c r="L82">
-        <v>1.4655010559957399E-2</v>
-      </c>
-      <c r="M82">
-        <v>1.54708347850845E-2</v>
-      </c>
-      <c r="N82" s="11">
-        <f t="shared" si="9"/>
-        <v>1.0556686207621178</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A83">
-        <v>25</v>
-      </c>
-      <c r="B83" s="5"/>
-      <c r="C83" s="2">
-        <v>1.8782496824776201E-2</v>
-      </c>
-      <c r="D83" s="2">
-        <v>8.0985715172972504E-5</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2">
-        <v>8.2936422592517207E-5</v>
-      </c>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="10">
-        <f t="shared" si="8"/>
-        <v>2.4408348565916203E-2</v>
-      </c>
-      <c r="J83" s="4"/>
-      <c r="L83">
-        <v>2.20520227131588E-2</v>
-      </c>
-      <c r="M83">
-        <v>2.3279563002525702E-2</v>
-      </c>
-      <c r="N83" s="10">
-        <f t="shared" si="9"/>
-        <v>1.0556656550437167</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A84">
-        <v>50</v>
-      </c>
-      <c r="B84" s="5"/>
-      <c r="C84" s="2">
-        <v>2.51046376970986E-2</v>
-      </c>
-      <c r="D84">
-        <v>1.14857385321631E-4</v>
-      </c>
-      <c r="F84">
-        <v>1.40546480514001E-4</v>
-      </c>
-      <c r="I84" s="10">
-        <f t="shared" si="8"/>
-        <v>1.8873133491714433E-2</v>
-      </c>
-      <c r="J84" s="4"/>
-      <c r="L84">
-        <v>2.9379142051595902E-2</v>
-      </c>
-      <c r="M84">
-        <v>3.0966693098777899E-2</v>
-      </c>
-      <c r="N84" s="11">
-        <f t="shared" si="9"/>
-        <v>1.0540366714723639</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A85">
-        <v>75</v>
-      </c>
-      <c r="B85" s="5"/>
-      <c r="C85" s="2">
-        <v>3.1476119846668899E-2</v>
-      </c>
-      <c r="D85">
-        <v>1.6692001786006801E-4</v>
-      </c>
-      <c r="F85">
-        <v>2.2355768083561999E-4</v>
-      </c>
-      <c r="I85" s="10">
-        <f t="shared" si="8"/>
-        <v>2.0107088599017175E-2</v>
-      </c>
-      <c r="J85" s="4"/>
-      <c r="L85">
-        <v>3.6804448452257998E-2</v>
-      </c>
-      <c r="M85">
-        <v>3.8844686371276298E-2</v>
-      </c>
-      <c r="N85" s="10">
-        <f t="shared" si="9"/>
-        <v>1.0554345467685748</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A86">
-        <v>100</v>
-      </c>
-      <c r="B86" s="5"/>
-      <c r="C86" s="2">
-        <v>5.2878603388737497E-2</v>
-      </c>
-      <c r="D86">
-        <v>2.77931449091848E-4</v>
-      </c>
-      <c r="F86">
-        <v>2.1739476286188801E-4</v>
-      </c>
-      <c r="I86" s="10">
-        <f t="shared" si="8"/>
-        <v>1.8018315350781095E-2</v>
-      </c>
-      <c r="J86" s="4"/>
-      <c r="L86">
-        <v>6.1567552933483601E-2</v>
-      </c>
-      <c r="M86">
-        <v>6.4958585716827305E-2</v>
-      </c>
-      <c r="N86" s="11">
-        <f t="shared" si="9"/>
-        <v>1.0550782453057264</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A87">
-        <v>150</v>
-      </c>
-      <c r="B87" s="5"/>
-      <c r="C87" s="2">
-        <v>0.107716927588289</v>
-      </c>
-      <c r="D87">
-        <v>3.3888866496247497E-4</v>
-      </c>
-      <c r="F87">
-        <v>4.2099807481717899E-4</v>
-      </c>
-      <c r="I87" s="10">
-        <f t="shared" si="8"/>
-        <v>1.7992932963347683E-2</v>
-      </c>
-      <c r="J87" s="4"/>
-      <c r="L87">
-        <v>0.124585487877085</v>
-      </c>
-      <c r="M87">
-        <v>0.13088073929294</v>
-      </c>
-      <c r="N87" s="10">
-        <f t="shared" si="9"/>
-        <v>1.0505295722890764</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A88">
-        <v>250</v>
-      </c>
-      <c r="B88" s="5"/>
-      <c r="C88" s="2">
-        <v>0.16515386445267599</v>
-      </c>
-      <c r="D88">
-        <v>6.0844630496931901E-4</v>
-      </c>
-      <c r="F88">
-        <v>7.1735921087181002E-4</v>
-      </c>
-      <c r="I88" s="10">
-        <f t="shared" si="8"/>
-        <v>2.0082997872230529E-2</v>
-      </c>
-      <c r="J88" s="4"/>
-      <c r="L88">
-        <v>0.188315720076114</v>
-      </c>
-      <c r="M88">
-        <v>0.19671890522285099</v>
-      </c>
-      <c r="N88" s="11">
-        <f t="shared" si="9"/>
-        <v>1.0446228554012409</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A89">
-        <v>500</v>
-      </c>
-      <c r="B89" s="5"/>
-      <c r="C89" s="2">
-        <v>0.22114304090137801</v>
-      </c>
-      <c r="D89">
-        <v>1.3901143553867799E-3</v>
-      </c>
-      <c r="F89">
-        <v>1.45703989958587E-3</v>
-      </c>
-      <c r="I89" s="10">
-        <f t="shared" si="8"/>
-        <v>2.1548753693625213E-2</v>
-      </c>
-      <c r="J89" s="4"/>
-      <c r="L89">
-        <v>0.25212873564071397</v>
-      </c>
-      <c r="M89">
-        <v>0.26159631710660702</v>
-      </c>
-      <c r="N89" s="10">
-        <f t="shared" si="9"/>
-        <v>1.0375505847908761</v>
-      </c>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A90">
-        <v>750</v>
-      </c>
-      <c r="D90">
-        <v>1.59024586083695E-3</v>
-      </c>
-      <c r="F90">
-        <v>1.88927153592098E-3</v>
-      </c>
-      <c r="I90" s="10">
-        <f t="shared" si="8"/>
-        <v>1.8239532257896197E-2</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A91">
-        <v>999.99</v>
-      </c>
-      <c r="D91">
-        <v>2.0916951916344802E-3</v>
-      </c>
-      <c r="F91">
-        <v>2.14759074882869E-3</v>
-      </c>
-      <c r="I91" s="10">
-        <f>I74*((F91/F74)^2 +(D91/D74)^2)^0.5</f>
-        <v>1.7398828006913617E-2</v>
+        <v>5.3129443828807302E-4</v>
+      </c>
+      <c r="N74">
+        <v>0.223224252625355</v>
+      </c>
+      <c r="O74">
+        <v>5.6545982801596898E-4</v>
+      </c>
+      <c r="P74" s="7">
+        <f>N74/L74</f>
+        <v>1.0682957802000932</v>
+      </c>
+      <c r="Q74">
+        <f>P74*((M74/L74)^2 +(O74/N74)^2)^0.5</f>
+        <v>3.8342543851553339E-3</v>
       </c>
     </row>
   </sheetData>

--- a/Jupyter/Wedge/wedge_data_2026-03-25.xlsx
+++ b/Jupyter/Wedge/wedge_data_2026-03-25.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ppark\projects\emma-openmc\Jupyter\Wedge\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\patri\projects\emma-openmc\Jupyter\Wedge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{776A2E84-5435-42BD-BA60-932CE983924B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00B12B17-FB4D-40C5-9EE9-696C078161DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="14">
   <si>
     <t>Fertile kg/m3</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>=C/A stdev</t>
+  </si>
+  <si>
+    <t>FISSION RATE [ RXNS/SRC-N ]</t>
   </si>
 </sst>
 </file>
@@ -132,9 +135,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="5"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -184,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -205,7 +208,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1349,7 +1351,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$44:$A$56</c:f>
+              <c:f>'Sheet 1'!$A$61:$A$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
@@ -1397,48 +1399,48 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$H$44:$H$56</c:f>
+              <c:f>'Sheet 1'!$H$61:$H$73</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>1.0029352823676327</c:v>
+                  <c:v>1.0000745077223692</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.98224520701169626</c:v>
+                  <c:v>1.0002014544619438</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.99535113208221782</c:v>
+                  <c:v>1.0000596469460914</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.009239958157601</c:v>
+                  <c:v>1.00000611110781</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0063851550945806</c:v>
+                  <c:v>1.00057608641662</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0046707615573558</c:v>
+                  <c:v>0.99968342555686862</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>0.99817858171840435</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>1.0001023551568125</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>1.0006480034698473</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>1.0027093859277671</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>1.0002049375908553</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>0.99885685520863166</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>0.99863620231200012</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1477,7 +1479,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$44:$A$56</c:f>
+              <c:f>'Sheet 1'!$A$61:$A$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
@@ -1525,12 +1527,12 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$P$44:$P$56</c:f>
+              <c:f>'Sheet 1'!$P$61:$P$73</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1.0000859211924744</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1.0001619611909021</c:v>
@@ -1873,7 +1875,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$62:$A$74</c:f>
+              <c:f>'Sheet 1'!$A$79:$A$91</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
@@ -1921,48 +1923,48 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$H$62:$H$74</c:f>
+              <c:f>'Sheet 1'!$H$79:$H$91</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>1.0417490015674646</c:v>
+                  <c:v>1.0311738562325514</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0149892108133356</c:v>
+                  <c:v>1.0381411006968115</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0382137988437394</c:v>
+                  <c:v>1.041357955021911</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0585263015095798</c:v>
+                  <c:v>1.0502695307623404</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0608306647563586</c:v>
+                  <c:v>1.0533689559947954</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0678523167293434</c:v>
+                  <c:v>1.053972343613554</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>1.055280764348149</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>1.0605026588779487</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>1.0606966812709036</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>1.0666080984436301</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>1.0736126000487558</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>1.0753318396098046</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>1.0795351304536034</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2001,7 +2003,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$A$62:$A$74</c:f>
+              <c:f>'Sheet 1'!$A$79:$A$91</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
@@ -2049,12 +2051,12 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet 1'!$P$62:$P$74</c:f>
+              <c:f>'Sheet 1'!$P$79:$P$91</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1.0421829854714089</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1.0468679184142133</c:v>
@@ -2179,7 +2181,8 @@
         <c:axId val="1342369296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:min val="0.95000000000000007"/>
+          <c:max val="1.08"/>
+          <c:min val="1.03"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2235,6 +2238,1056 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="1342380336"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Sheet 1'!$A$79:$A$91</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>999.99</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Sheet 1'!$H$79:$H$91</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>1.0311738562325514</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0381411006968115</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.041357955021911</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0502695307623404</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.0533689559947954</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.053972343613554</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.055280764348149</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.0605026588779487</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.0606966812709036</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.0666080984436301</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.0736126000487558</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.0753318396098046</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0795351304536034</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5362-4A7B-A534-AD8816811D32}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Sheet 1'!$A$79:$A$91</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>999.99</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Sheet 1'!$P$79:$P$91</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>1.0421829854714089</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0468679184142133</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0491120103788383</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0548236283228316</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.0592976963273675</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.0599512468140793</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.0559969197962629</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.0610351455367648</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.0635211665810387</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.0673679820985291</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.0749164325098632</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.0676051493877452</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0682957802000932</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5362-4A7B-A534-AD8816811D32}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1342380336"/>
+        <c:axId val="1342369296"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1342380336"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1342369296"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1342369296"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1.08"/>
+          <c:min val="1.03"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1342380336"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Sheet 1'!$A$24:$A$36</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>999.99</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Sheet 1'!$H$24:$H$36</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0.67015864678428949</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.67399433743759052</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.67258163487423628</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.69883311557825745</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.73244907600666376</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.76691398093902452</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.79412199858198884</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.82771654679092965</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.87277793951821403</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.90774216971761523</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.96885985849430767</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.0035052756769365</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0159556160581653</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9A88-40A7-9744-FFC75830134C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Sheet 1'!$A$24:$A$36</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>999.99</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Sheet 1'!$P$24:$P$36</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0.85719868916492581</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.86272360378029123</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.86473422707265823</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.87150263943790185</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.8842176678721938</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.89942526896969821</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.92270745337377136</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.92487302633259483</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.95280649072651702</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.96680285364811647</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.996195710817117</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.0164077631511579</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.025113077347247</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9A88-40A7-9744-FFC75830134C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1154162240"/>
+        <c:axId val="1123278832"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1154162240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1123278832"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1123278832"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1154162240"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2481,6 +3534,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -4030,6 +5163,1038 @@
 </file>
 
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4623,13 +6788,13 @@
     <xdr:from>
       <xdr:col>18</xdr:col>
       <xdr:colOff>53010</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>159027</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>357810</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>119270</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4659,13 +6824,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>417444</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>76</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>112644</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>91</xdr:row>
       <xdr:rowOff>112644</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4686,6 +6851,82 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>417444</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>112644</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>112644</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47189E82-CA72-4B71-AFAB-BB81E355CB40}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>583097</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>278297</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>145775</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CC834B8-CEE8-4D20-9A4D-2E5F10FBB1B8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4957,7 +7198,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C22416C2-1180-4450-A3B0-0B08DD9AEC85}">
-  <dimension ref="A1:Q74"/>
+  <dimension ref="A1:Q109"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
@@ -5102,7 +7343,7 @@
         <v>1.14700118954492E-4</v>
       </c>
       <c r="P5" s="7">
-        <f>N5/L5</f>
+        <f t="shared" ref="P5:P17" si="1">N5/L5</f>
         <v>1.0001778209825207</v>
       </c>
       <c r="Q5">
@@ -5132,7 +7373,7 @@
         <v>1.0000650261216626</v>
       </c>
       <c r="I6">
-        <f t="shared" ref="I6:I16" si="1">H6*((E6/D6)^2 +(G6/F6)^2)^0.5</f>
+        <f t="shared" ref="I6:I16" si="2">H6*((E6/D6)^2 +(G6/F6)^2)^0.5</f>
         <v>1.6386259048946993E-4</v>
       </c>
       <c r="J6" s="3"/>
@@ -5149,11 +7390,11 @@
         <v>1.6988497331219999E-4</v>
       </c>
       <c r="P6" s="7">
-        <f>N6/L6</f>
+        <f t="shared" si="1"/>
         <v>1.0000381873265614</v>
       </c>
       <c r="Q6">
-        <f t="shared" ref="Q6:Q16" si="2">P6*((M6/L6)^2 +(O6/N6)^2)^0.5</f>
+        <f t="shared" ref="Q6:Q16" si="3">P6*((M6/L6)^2 +(O6/N6)^2)^0.5</f>
         <v>1.6620603320820275E-4</v>
       </c>
     </row>
@@ -5179,7 +7420,7 @@
         <v>0.99996036360746876</v>
       </c>
       <c r="I7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.7181641313147609E-4</v>
       </c>
       <c r="J7" s="3"/>
@@ -5196,11 +7437,11 @@
         <v>1.5373454905333599E-4</v>
       </c>
       <c r="P7" s="7">
-        <f>N7/L7</f>
+        <f t="shared" si="1"/>
         <v>0.99990753724213677</v>
       </c>
       <c r="Q7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.6519568405949642E-4</v>
       </c>
     </row>
@@ -5226,7 +7467,7 @@
         <v>1.0005266084564297</v>
       </c>
       <c r="I8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.0785290749755253E-4</v>
       </c>
       <c r="J8" s="3"/>
@@ -5243,11 +7484,11 @@
         <v>4.3477128848851398E-4</v>
       </c>
       <c r="P8" s="7">
-        <f>N8/L8</f>
+        <f t="shared" si="1"/>
         <v>1.0002355998584036</v>
       </c>
       <c r="Q8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.5445068306877072E-4</v>
       </c>
     </row>
@@ -5274,7 +7515,7 @@
         <v>1.0018467149465879</v>
       </c>
       <c r="I9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.0698498708561776E-3</v>
       </c>
       <c r="K9"/>
@@ -5291,11 +7532,11 @@
         <v>1.0536694518052999E-3</v>
       </c>
       <c r="P9" s="7">
-        <f>N9/L9</f>
+        <f t="shared" si="1"/>
         <v>1.0004553713443167</v>
       </c>
       <c r="Q9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.0337440128011612E-3</v>
       </c>
     </row>
@@ -5321,7 +7562,7 @@
         <v>1.002287048308576</v>
       </c>
       <c r="I10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.8794780325578441E-4</v>
       </c>
       <c r="J10" s="3"/>
@@ -5338,11 +7579,11 @@
         <v>7.5549871036543397E-4</v>
       </c>
       <c r="P10" s="7">
-        <f>N10/L10</f>
+        <f t="shared" si="1"/>
         <v>1.0005898491614427</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>8.901521419890664E-4</v>
       </c>
     </row>
@@ -5369,7 +7610,7 @@
         <v>1.0038025582102672</v>
       </c>
       <c r="I11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.0625098571799413E-3</v>
       </c>
       <c r="K11"/>
@@ -5386,11 +7627,11 @@
         <v>1.0122047275674399E-3</v>
       </c>
       <c r="P11" s="7">
-        <f>N11/L11</f>
+        <f t="shared" si="1"/>
         <v>1.0011630341173221</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.1236427897777903E-3</v>
       </c>
     </row>
@@ -5416,7 +7657,7 @@
         <v>1.0036838050286592</v>
       </c>
       <c r="I12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.0075356465859516E-3</v>
       </c>
       <c r="J12" s="3"/>
@@ -5433,11 +7674,11 @@
         <v>1.04376153989015E-3</v>
       </c>
       <c r="P12" s="7">
-        <f>N12/L12</f>
+        <f t="shared" si="1"/>
         <v>1.0006238901134941</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.0589413837370333E-3</v>
       </c>
     </row>
@@ -5463,7 +7704,7 @@
         <v>1.002467577491776</v>
       </c>
       <c r="I13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.7012678767904027E-3</v>
       </c>
       <c r="J13" s="3"/>
@@ -5480,11 +7721,11 @@
         <v>3.5460245721196499E-3</v>
       </c>
       <c r="P13" s="7">
-        <f>N13/L13</f>
+        <f t="shared" si="1"/>
         <v>1.0042585132338837</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.7027899524461018E-3</v>
       </c>
     </row>
@@ -5511,7 +7752,7 @@
         <v>1.000596548769378</v>
       </c>
       <c r="I14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.8272285541985462E-3</v>
       </c>
       <c r="K14"/>
@@ -5528,11 +7769,11 @@
         <v>2.9409916078694401E-3</v>
       </c>
       <c r="P14" s="7">
-        <f>N14/L14</f>
+        <f t="shared" si="1"/>
         <v>0.99880156437237411</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.030295719604469E-3</v>
       </c>
     </row>
@@ -5558,7 +7799,7 @@
         <v>1.0015290596941282</v>
       </c>
       <c r="I15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.579377630249193E-3</v>
       </c>
       <c r="J15" s="3"/>
@@ -5575,11 +7816,11 @@
         <v>2.6845051290129399E-3</v>
       </c>
       <c r="P15" s="7">
-        <f>N15/L15</f>
+        <f t="shared" si="1"/>
         <v>0.99475053432196514</v>
       </c>
       <c r="Q15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.9153977252420692E-3</v>
       </c>
     </row>
@@ -5606,7 +7847,7 @@
         <v>1.0029865814925498</v>
       </c>
       <c r="I16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.4346863492251559E-3</v>
       </c>
       <c r="K16"/>
@@ -5623,11 +7864,11 @@
         <v>2.7545952721865301E-3</v>
       </c>
       <c r="P16" s="7">
-        <f>N16/L16</f>
+        <f t="shared" si="1"/>
         <v>1.0016645335554861</v>
       </c>
       <c r="Q16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.3838068565250718E-3</v>
       </c>
     </row>
@@ -5670,7 +7911,7 @@
         <v>3.9762001692155704E-3</v>
       </c>
       <c r="P17" s="7">
-        <f>N17/L17</f>
+        <f t="shared" si="1"/>
         <v>0.99641459582252734</v>
       </c>
       <c r="Q17">
@@ -5781,7 +8022,7 @@
         <v>2.5713213345718999E-7</v>
       </c>
       <c r="H24" s="13">
-        <f t="shared" ref="H24:H36" si="3">F24/D24</f>
+        <f t="shared" ref="H24:H36" si="4">F24/D24</f>
         <v>0.67015864678428949</v>
       </c>
       <c r="I24">
@@ -5803,7 +8044,7 @@
         <v>2.22045923443069E-7</v>
       </c>
       <c r="P24" s="7">
-        <f>N24/L24</f>
+        <f t="shared" ref="P24:P36" si="5">N24/L24</f>
         <v>0.85719868916492581</v>
       </c>
       <c r="Q24">
@@ -5829,11 +8070,11 @@
         <v>4.9685826902563597E-7</v>
       </c>
       <c r="H25" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.67399433743759052</v>
       </c>
       <c r="I25">
-        <f t="shared" ref="I25:I35" si="4">H25*((E25/D25)^2 +(G25/F25)^2)^0.5</f>
+        <f t="shared" ref="I25:I35" si="6">H25*((E25/D25)^2 +(G25/F25)^2)^0.5</f>
         <v>2.8918456475792078E-3</v>
       </c>
       <c r="J25" s="3"/>
@@ -5850,11 +8091,11 @@
         <v>5.73466194555137E-7</v>
       </c>
       <c r="P25" s="7">
-        <f>N25/L25</f>
+        <f t="shared" si="5"/>
         <v>0.86272360378029123</v>
       </c>
       <c r="Q25">
-        <f t="shared" ref="Q25:Q35" si="5">P25*((M25/L25)^2 +(O25/N25)^2)^0.5</f>
+        <f t="shared" ref="Q25:Q35" si="7">P25*((M25/L25)^2 +(O25/N25)^2)^0.5</f>
         <v>3.8053680353437123E-3</v>
       </c>
     </row>
@@ -5876,11 +8117,11 @@
         <v>6.9232886194979901E-7</v>
       </c>
       <c r="H26" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.67258163487423628</v>
       </c>
       <c r="I26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2.0199806972425911E-3</v>
       </c>
       <c r="J26" s="3"/>
@@ -5897,11 +8138,11 @@
         <v>6.2257504496774401E-7</v>
       </c>
       <c r="P26" s="7">
-        <f>N26/L26</f>
+        <f t="shared" si="5"/>
         <v>0.86473422707265823</v>
       </c>
       <c r="Q26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>2.0767475932791379E-3</v>
       </c>
     </row>
@@ -5923,11 +8164,11 @@
         <v>7.3576810457546899E-6</v>
       </c>
       <c r="H27" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.69883311557825745</v>
       </c>
       <c r="I27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2.3030599218682355E-3</v>
       </c>
       <c r="J27" s="3"/>
@@ -5944,11 +8185,11 @@
         <v>5.6804576370084801E-6</v>
       </c>
       <c r="P27" s="7">
-        <f>N27/L27</f>
+        <f t="shared" si="5"/>
         <v>0.87150263943790185</v>
       </c>
       <c r="Q27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>2.0707798442735998E-3</v>
       </c>
     </row>
@@ -5970,11 +8211,11 @@
         <v>2.2153397083295701E-5</v>
       </c>
       <c r="H28" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.73244907600666376</v>
       </c>
       <c r="I28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3.444486925796071E-3</v>
       </c>
       <c r="J28" s="3"/>
@@ -5991,11 +8232,11 @@
         <v>3.0640812604159097E-5</v>
       </c>
       <c r="P28" s="7">
-        <f>N28/L28</f>
+        <f t="shared" si="5"/>
         <v>0.8842176678721938</v>
       </c>
       <c r="Q28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>4.3979408323316831E-3</v>
       </c>
     </row>
@@ -6017,11 +8258,11 @@
         <v>3.9960656049596501E-5</v>
       </c>
       <c r="H29" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.76691398093902452</v>
       </c>
       <c r="I29">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3.2684265997479276E-3</v>
       </c>
       <c r="J29" s="3"/>
@@ -6038,11 +8279,11 @@
         <v>3.9839492384589098E-5</v>
       </c>
       <c r="P29" s="7">
-        <f>N29/L29</f>
+        <f t="shared" si="5"/>
         <v>0.89942526896969821</v>
       </c>
       <c r="Q29">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>3.2939448706370833E-3</v>
       </c>
     </row>
@@ -6064,11 +8305,11 @@
         <v>4.6773312275541899E-5</v>
       </c>
       <c r="H30" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.79412199858198884</v>
       </c>
       <c r="I30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2.506797039006772E-3</v>
       </c>
       <c r="J30" s="3"/>
@@ -6085,11 +8326,11 @@
         <v>3.9932428547215201E-5</v>
       </c>
       <c r="P30" s="7">
-        <f>N30/L30</f>
+        <f t="shared" si="5"/>
         <v>0.92270745337377136</v>
       </c>
       <c r="Q30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>2.6590083093148533E-3</v>
       </c>
     </row>
@@ -6111,11 +8352,11 @@
         <v>5.1020148947823797E-5</v>
       </c>
       <c r="H31" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.82771654679092965</v>
       </c>
       <c r="I31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2.6889139523652702E-3</v>
       </c>
       <c r="J31" s="3"/>
@@ -6132,11 +8373,11 @@
         <v>4.3554638662226E-5</v>
       </c>
       <c r="P31" s="7">
-        <f>N31/L31</f>
+        <f t="shared" si="5"/>
         <v>0.92487302633259483</v>
       </c>
       <c r="Q31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>2.2933719536386309E-3</v>
       </c>
     </row>
@@ -6158,11 +8399,11 @@
         <v>2.08831333646651E-4</v>
       </c>
       <c r="H32" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.87277793951821403</v>
       </c>
       <c r="I32">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>7.3615233968889766E-3</v>
       </c>
       <c r="J32" s="3"/>
@@ -6179,11 +8420,11 @@
         <v>2.42482884021072E-4</v>
       </c>
       <c r="P32" s="7">
-        <f>N32/L32</f>
+        <f t="shared" si="5"/>
         <v>0.95280649072651702</v>
       </c>
       <c r="Q32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>7.8941171734471308E-3</v>
       </c>
     </row>
@@ -6205,11 +8446,11 @@
         <v>2.8833834514146198E-4</v>
       </c>
       <c r="H33" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.90774216971761523</v>
       </c>
       <c r="I33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6.5331679556135417E-3</v>
       </c>
       <c r="J33" s="3"/>
@@ -6226,11 +8467,11 @@
         <v>2.3849126374357799E-4</v>
       </c>
       <c r="P33" s="7">
-        <f>N33/L33</f>
+        <f t="shared" si="5"/>
         <v>0.96680285364811647</v>
       </c>
       <c r="Q33">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>6.041436975368881E-3</v>
       </c>
     </row>
@@ -6252,11 +8493,11 @@
         <v>4.4906828447954003E-4</v>
       </c>
       <c r="H34" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.96885985849430767</v>
       </c>
       <c r="I34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6.1396636178584303E-3</v>
       </c>
       <c r="J34" s="3"/>
@@ -6273,11 +8514,11 @@
         <v>4.88706826404386E-4</v>
       </c>
       <c r="P34" s="7">
-        <f>N34/L34</f>
+        <f t="shared" si="5"/>
         <v>0.996195710817117</v>
       </c>
       <c r="Q34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5.5692878927237057E-3</v>
       </c>
     </row>
@@ -6299,11 +8540,11 @@
         <v>3.9277512684765298E-4</v>
       </c>
       <c r="H35" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.0035052756769365</v>
       </c>
       <c r="I35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>4.2684987159538603E-3</v>
       </c>
       <c r="J35" s="3"/>
@@ -6320,11 +8561,11 @@
         <v>6.4618904182841804E-4</v>
       </c>
       <c r="P35" s="7">
-        <f>N35/L35</f>
+        <f t="shared" si="5"/>
         <v>1.0164077631511579</v>
       </c>
       <c r="Q35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5.5809331857695158E-3</v>
       </c>
     </row>
@@ -6346,7 +8587,7 @@
         <v>5.8700051779191705E-4</v>
       </c>
       <c r="H36" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.0159556160581653</v>
       </c>
       <c r="I36">
@@ -6367,7 +8608,7 @@
         <v>7.9326262337449101E-4</v>
       </c>
       <c r="P36" s="7">
-        <f>N36/L36</f>
+        <f t="shared" si="5"/>
         <v>1.025113077347247</v>
       </c>
       <c r="Q36">
@@ -6375,1316 +8616,2825 @@
         <v>6.0296141732043276E-3</v>
       </c>
     </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B37" s="4"/>
+      <c r="H37" s="13"/>
+      <c r="J37" s="3"/>
+      <c r="P37" s="7"/>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C39" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+    </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C40" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="C40" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="14"/>
+      <c r="K40" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="L40" s="17"/>
+      <c r="M40" s="18"/>
+      <c r="N40" s="18"/>
+      <c r="O40" s="17"/>
+      <c r="P40" s="17"/>
+      <c r="Q40" s="17"/>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C41" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
-      <c r="H41" s="12"/>
-      <c r="K41" s="2"/>
-      <c r="L41" s="2"/>
-      <c r="M41" s="2"/>
-      <c r="N41" s="2"/>
+      <c r="A41" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" s="5"/>
+      <c r="C41" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H41" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="I41" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="J41" s="6"/>
+      <c r="K41" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="L41" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="M41" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="N41" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="O41" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="P41" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q41" s="19" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C42" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="15"/>
-      <c r="H42" s="15"/>
-      <c r="I42" s="14"/>
-      <c r="K42" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L42" s="17"/>
-      <c r="M42" s="18"/>
-      <c r="N42" s="18"/>
-      <c r="O42" s="17"/>
-      <c r="P42" s="17"/>
-      <c r="Q42" s="17"/>
+      <c r="A42">
+        <v>0.1</v>
+      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2">
+        <v>3.1823783667320202E-6</v>
+      </c>
+      <c r="E42" s="2">
+        <v>4.1159886287402301E-10</v>
+      </c>
+      <c r="F42" s="2">
+        <v>3.4389546303583601E-6</v>
+      </c>
+      <c r="G42" s="2">
+        <v>7.2754924795352899E-9</v>
+      </c>
+      <c r="H42" s="13">
+        <f t="shared" ref="H42:H54" si="8">F42/D42</f>
+        <v>1.0806240597625159</v>
+      </c>
+      <c r="I42">
+        <f>H42*((E42/D42)^2 +(G42/F42)^2)^0.5</f>
+        <v>2.2904490835581361E-3</v>
+      </c>
+      <c r="J42" s="3"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2">
+        <v>8.9904449370964804E-7</v>
+      </c>
+      <c r="M42" s="2">
+        <v>1.2821299860299399E-10</v>
+      </c>
+      <c r="N42" s="2">
+        <v>9.7063326902119801E-7</v>
+      </c>
+      <c r="O42" s="2">
+        <v>2.34278184812804E-9</v>
+      </c>
+      <c r="P42" s="7">
+        <f t="shared" ref="P42:P54" si="9">N42/L42</f>
+        <v>1.0796276222283054</v>
+      </c>
+      <c r="Q42">
+        <f>P42*((M42/L42)^2 +(O42/N42)^2)^0.5</f>
+        <v>2.6104020588503659E-3</v>
+      </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D43" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G43" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="H43" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="I43" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="J43" s="6"/>
-      <c r="K43" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="L43" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="M43" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="N43" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="O43" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="P43" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q43" s="19" t="s">
-        <v>12</v>
+      <c r="A43">
+        <v>0.5</v>
+      </c>
+      <c r="B43" s="4"/>
+      <c r="D43" s="2">
+        <v>1.6000871976086401E-5</v>
+      </c>
+      <c r="E43" s="2">
+        <v>1.8077035460066801E-9</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1.7406241259005801E-5</v>
+      </c>
+      <c r="G43" s="2">
+        <v>1.6560027342357799E-8</v>
+      </c>
+      <c r="H43" s="13">
+        <f t="shared" si="8"/>
+        <v>1.0878307935354867</v>
+      </c>
+      <c r="I43">
+        <f t="shared" ref="I43:I53" si="10">H43*((E43/D43)^2 +(G43/F43)^2)^0.5</f>
+        <v>1.0422167294252094E-3</v>
+      </c>
+      <c r="J43" s="3"/>
+      <c r="L43" s="2">
+        <v>4.5212579889347804E-6</v>
+      </c>
+      <c r="M43" s="2">
+        <v>5.3867868502524305E-10</v>
+      </c>
+      <c r="N43" s="2">
+        <v>4.9130489454613299E-6</v>
+      </c>
+      <c r="O43" s="2">
+        <v>4.9708765251656597E-9</v>
+      </c>
+      <c r="P43" s="7">
+        <f t="shared" si="9"/>
+        <v>1.0866552975931498</v>
+      </c>
+      <c r="Q43">
+        <f t="shared" ref="Q43:Q53" si="11">P43*((M43/L43)^2 +(O43/N43)^2)^0.5</f>
+        <v>1.1070421177898828E-3</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="B44" s="4"/>
-      <c r="D44" s="20">
-        <v>1.33146077610654</v>
-      </c>
-      <c r="E44" s="20">
-        <v>1.29791278993871E-2</v>
-      </c>
-      <c r="F44">
-        <v>1.33536898944584</v>
-      </c>
-      <c r="G44">
-        <v>1.25080703731084E-4</v>
-      </c>
-      <c r="H44" s="7">
-        <f>F44/D44</f>
-        <v>1.0029352823676327</v>
+      <c r="D44" s="2">
+        <v>3.2035093398018297E-5</v>
+      </c>
+      <c r="E44" s="2">
+        <v>3.6301326712904198E-9</v>
+      </c>
+      <c r="F44" s="2">
+        <v>3.4905945803773603E-5</v>
+      </c>
+      <c r="G44" s="2">
+        <v>3.0128552778278198E-8</v>
+      </c>
+      <c r="H44" s="13">
+        <f t="shared" si="8"/>
+        <v>1.0896158587735816</v>
       </c>
       <c r="I44">
-        <f>H44*((E44/D44)^2 +(G44/F44)^2)^0.5</f>
-        <v>9.7771008098175641E-3</v>
+        <f t="shared" si="10"/>
+        <v>9.4855633081543855E-4</v>
       </c>
       <c r="J44" s="3"/>
-      <c r="L44">
-        <v>1.3352318967644701</v>
+      <c r="L44" s="2">
+        <v>9.0521934433886801E-6</v>
       </c>
       <c r="M44" s="2">
-        <v>9.7356481692860994E-5</v>
+        <v>1.0936079336944401E-9</v>
+      </c>
+      <c r="N44" s="2">
+        <v>9.8552203174057406E-6</v>
+      </c>
+      <c r="O44" s="2">
+        <v>8.7519244572112492E-9</v>
       </c>
       <c r="P44" s="7">
-        <f>N44/L44</f>
-        <v>0</v>
-      </c>
-      <c r="Q44" t="e">
-        <f>P44*((M44/L44)^2 +(O44/N44)^2)^0.5</f>
-        <v>#DIV/0!</v>
+        <f t="shared" si="9"/>
+        <v>1.0887107504981077</v>
+      </c>
+      <c r="Q44">
+        <f t="shared" si="11"/>
+        <v>9.7573479056481415E-4</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="B45" s="4"/>
-      <c r="D45" s="20">
-        <v>1.35765661048369</v>
-      </c>
-      <c r="E45" s="20">
-        <v>1.33833833770021E-2</v>
+      <c r="D45">
+        <v>3.2041283539142699E-4</v>
+      </c>
+      <c r="E45" s="2">
+        <v>1.03089800141475E-7</v>
       </c>
       <c r="F45">
-        <v>1.3335516984153499</v>
+        <v>3.5175355668395599E-4</v>
       </c>
       <c r="G45" s="2">
-        <v>9.8571452316726502E-5</v>
-      </c>
-      <c r="H45" s="7">
-        <f>F45/D45</f>
-        <v>0.98224520701169626</v>
+        <v>3.24163031926656E-7</v>
+      </c>
+      <c r="H45" s="13">
+        <f t="shared" si="8"/>
+        <v>1.0978135637239441</v>
       </c>
       <c r="I45">
-        <f t="shared" ref="I45:I55" si="6">H45*((E45/D45)^2 +(G45/F45)^2)^0.5</f>
-        <v>9.6829593214113503E-3</v>
+        <f t="shared" si="10"/>
+        <v>1.0715892980094322E-3</v>
       </c>
       <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-      <c r="L45">
-        <v>1.33328060850382</v>
-      </c>
-      <c r="M45">
-        <v>1.11744636942801E-4</v>
-      </c>
-      <c r="N45">
-        <v>1.33349654821898</v>
+      <c r="L45" s="2">
+        <v>9.05395895200175E-5</v>
+      </c>
+      <c r="M45" s="2">
+        <v>3.0609885520008502E-8</v>
+      </c>
+      <c r="N45" s="2">
+        <v>9.9327854603406304E-5</v>
       </c>
       <c r="O45" s="2">
-        <v>9.9388022927045995E-5</v>
-      </c>
-      <c r="P45" s="8">
-        <f>N45/L45</f>
-        <v>1.0001619611909021</v>
+        <v>9.6867588469887695E-8</v>
+      </c>
+      <c r="P45" s="7">
+        <f t="shared" si="9"/>
+        <v>1.0970654398808137</v>
       </c>
       <c r="Q45">
-        <f t="shared" ref="Q45:Q55" si="7">P45*((M45/L45)^2 +(O45/N45)^2)^0.5</f>
-        <v>1.1217617716941135E-4</v>
+        <f t="shared" si="11"/>
+        <v>1.1323582189431058E-3</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B46" s="4"/>
-      <c r="D46" s="20">
-        <v>1.33903476392587</v>
-      </c>
-      <c r="E46" s="20">
-        <v>1.09198789595156E-2</v>
+      <c r="D46">
+        <v>7.9832852090792796E-4</v>
+      </c>
+      <c r="E46" s="2">
+        <v>6.4380828459592396E-7</v>
       </c>
       <c r="F46">
-        <v>1.33280976817106</v>
-      </c>
-      <c r="G46">
-        <v>1.10318157044691E-4</v>
-      </c>
-      <c r="H46" s="7">
-        <f>F46/D46</f>
-        <v>0.99535113208221782</v>
+        <v>8.7467769000268295E-4</v>
+      </c>
+      <c r="G46" s="2">
+        <v>1.03125836480735E-6</v>
+      </c>
+      <c r="H46" s="13">
+        <f t="shared" si="8"/>
+        <v>1.0956362789192651</v>
       </c>
       <c r="I46">
-        <f t="shared" si="6"/>
-        <v>8.1175440777359244E-3</v>
+        <f t="shared" si="10"/>
+        <v>1.5650469392181556E-3</v>
       </c>
       <c r="J46" s="3"/>
       <c r="L46">
-        <v>1.3325160160175999</v>
-      </c>
-      <c r="M46">
-        <v>1.2990361944337101E-4</v>
+        <v>2.25447641878588E-4</v>
+      </c>
+      <c r="M46" s="2">
+        <v>1.7922454183224899E-7</v>
       </c>
       <c r="N46">
-        <v>1.3326689845730799</v>
-      </c>
-      <c r="O46">
-        <v>1.0526827110579401E-4</v>
+        <v>2.4682978389793902E-4</v>
+      </c>
+      <c r="O46" s="2">
+        <v>3.0793317165798302E-7</v>
       </c>
       <c r="P46" s="7">
-        <f>N46/L46</f>
-        <v>1.0001147967856605</v>
+        <f t="shared" si="9"/>
+        <v>1.0948430502141429</v>
       </c>
       <c r="Q46">
-        <f t="shared" si="7"/>
-        <v>1.2548677612360951E-4</v>
+        <f t="shared" si="11"/>
+        <v>1.6196160028921747E-3</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="B47" s="4"/>
-      <c r="D47" s="20">
-        <v>1.31789010731641</v>
-      </c>
-      <c r="E47" s="20">
-        <v>1.2370870755455E-2</v>
+      <c r="D47">
+        <v>1.5863990621956901E-3</v>
+      </c>
+      <c r="E47" s="2">
+        <v>6.9872049483164404E-7</v>
       </c>
       <c r="F47">
-        <v>1.33006735676433</v>
-      </c>
-      <c r="G47">
-        <v>4.3462506631634999E-4</v>
-      </c>
-      <c r="H47" s="7">
-        <f>F47/D47</f>
-        <v>1.009239958157601</v>
+        <v>1.7451813935783799E-3</v>
+      </c>
+      <c r="G47" s="2">
+        <v>2.15270592824618E-6</v>
+      </c>
+      <c r="H47" s="13">
+        <f t="shared" si="8"/>
+        <v>1.1000897789002244</v>
       </c>
       <c r="I47">
-        <f t="shared" si="6"/>
-        <v>9.4793485833704651E-3</v>
+        <f t="shared" si="10"/>
+        <v>1.4408859671880526E-3</v>
       </c>
       <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
       <c r="L47">
-        <v>1.32875591199513</v>
-      </c>
-      <c r="M47">
-        <v>3.6656386812860002E-4</v>
+        <v>4.4798082499880598E-4</v>
+      </c>
+      <c r="M47" s="2">
+        <v>2.3058578537097299E-7</v>
       </c>
       <c r="N47">
-        <v>1.3283935226396499</v>
-      </c>
-      <c r="O47">
-        <v>4.6050432456435497E-4</v>
-      </c>
-      <c r="P47" s="8">
-        <f>N47/L47</f>
-        <v>0.99972727168909759</v>
+        <v>4.9222836447885903E-4</v>
+      </c>
+      <c r="O47" s="2">
+        <v>6.1981830802032001E-7</v>
+      </c>
+      <c r="P47" s="7">
+        <f t="shared" si="9"/>
+        <v>1.098771056730321</v>
       </c>
       <c r="Q47">
-        <f t="shared" si="7"/>
-        <v>4.4291324537064109E-4</v>
+        <f t="shared" si="11"/>
+        <v>1.4947107742180631E-3</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="B48" s="4"/>
-      <c r="D48" s="20">
-        <v>1.32036564820574</v>
-      </c>
-      <c r="E48" s="20">
-        <v>1.3456104516294001E-2</v>
+      <c r="D48">
+        <v>2.3694633374357899E-3</v>
+      </c>
+      <c r="E48" s="2">
+        <v>2.0409182758839298E-6</v>
       </c>
       <c r="F48">
-        <v>1.32879638765109</v>
-      </c>
-      <c r="G48">
-        <v>1.0451282524601201E-3</v>
-      </c>
-      <c r="H48" s="7">
-        <f>F48/D48</f>
-        <v>1.0063851550945806</v>
+        <v>2.6035551899146001E-3</v>
+      </c>
+      <c r="G48" s="2">
+        <v>1.69836561383817E-6</v>
+      </c>
+      <c r="H48" s="13">
+        <f t="shared" si="8"/>
+        <v>1.098795304734338</v>
       </c>
       <c r="I48">
-        <f t="shared" si="6"/>
-        <v>1.028676695047087E-2</v>
+        <f t="shared" si="10"/>
+        <v>1.1872271872232696E-3</v>
       </c>
       <c r="J48" s="3"/>
       <c r="L48">
-        <v>1.3245110745965301</v>
-      </c>
-      <c r="M48">
-        <v>6.3753145972632905E-4</v>
+        <v>6.6839992871854095E-4</v>
+      </c>
+      <c r="M48" s="2">
+        <v>5.4020479758105504E-7</v>
       </c>
       <c r="N48">
-        <v>1.32578542353965</v>
-      </c>
-      <c r="O48">
-        <v>1.0645660109259701E-3</v>
+        <v>7.3347330304254701E-4</v>
+      </c>
+      <c r="O48" s="2">
+        <v>5.1651453397623897E-7</v>
       </c>
       <c r="P48" s="7">
-        <f>N48/L48</f>
-        <v>1.0009621278127161</v>
+        <f t="shared" si="9"/>
+        <v>1.0973569438416384</v>
       </c>
       <c r="Q48">
-        <f t="shared" si="7"/>
-        <v>9.3708596837583497E-4</v>
+        <f t="shared" si="11"/>
+        <v>1.176323419733072E-3</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="B49" s="4"/>
-      <c r="D49" s="20">
-        <v>1.3197738196808499</v>
-      </c>
-      <c r="E49" s="20">
-        <v>1.08550142358942E-2</v>
+      <c r="D49">
+        <v>3.1410862514606899E-3</v>
+      </c>
+      <c r="E49" s="2">
+        <v>3.27513526933276E-6</v>
       </c>
       <c r="F49">
-        <v>1.32593816850222</v>
-      </c>
-      <c r="G49">
-        <v>9.7502159311734795E-4</v>
-      </c>
-      <c r="H49" s="7">
-        <f>F49/D49</f>
-        <v>1.0046707615573558</v>
+        <v>3.4466944423003402E-3</v>
+      </c>
+      <c r="G49" s="2">
+        <v>3.2445791725811299E-6</v>
+      </c>
+      <c r="H49" s="13">
+        <f t="shared" si="8"/>
+        <v>1.0972937915020748</v>
       </c>
       <c r="I49">
-        <f t="shared" si="6"/>
-        <v>8.296280948766499E-3</v>
+        <f t="shared" si="10"/>
+        <v>1.541426865977242E-3</v>
       </c>
       <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
       <c r="L49">
-        <v>1.3197871026024</v>
-      </c>
-      <c r="M49">
-        <v>8.8312138374329295E-4</v>
+        <v>8.85793670637662E-4</v>
+      </c>
+      <c r="M49" s="2">
+        <v>9.8356058025338391E-7</v>
       </c>
       <c r="N49">
-        <v>1.3193357094999201</v>
-      </c>
-      <c r="O49">
-        <v>9.5862687561023305E-4</v>
-      </c>
-      <c r="P49" s="8">
-        <f>N49/L49</f>
-        <v>0.99965798036547726</v>
+        <v>9.7084534758771503E-4</v>
+      </c>
+      <c r="O49" s="2">
+        <v>9.6980794977708597E-7</v>
+      </c>
+      <c r="P49" s="7">
+        <f t="shared" si="9"/>
+        <v>1.0960174810109293</v>
       </c>
       <c r="Q49">
-        <f t="shared" si="7"/>
-        <v>9.874335070433548E-4</v>
+        <f t="shared" si="11"/>
+        <v>1.6369931020509556E-3</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="B50" s="4"/>
-      <c r="D50" s="20">
-        <v>1.29935652652886</v>
-      </c>
-      <c r="E50" s="20">
-        <v>1.1974083384246499E-2</v>
-      </c>
-      <c r="H50" s="7">
-        <f>F50/D50</f>
-        <v>0</v>
-      </c>
-      <c r="I50" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+      <c r="D50">
+        <v>4.6445716846820698E-3</v>
+      </c>
+      <c r="E50" s="2">
+        <v>9.6466217564299792E-6</v>
+      </c>
+      <c r="F50">
+        <v>5.1102808521361299E-3</v>
+      </c>
+      <c r="G50" s="2">
+        <v>1.2123213047497999E-5</v>
+      </c>
+      <c r="H50" s="13">
+        <f t="shared" si="8"/>
+        <v>1.1002695617746587</v>
+      </c>
+      <c r="I50">
+        <f t="shared" si="10"/>
+        <v>3.4691982513368859E-3</v>
       </c>
       <c r="J50" s="3"/>
       <c r="L50">
-        <v>1.31486593414251</v>
-      </c>
-      <c r="M50">
-        <v>8.9177056244582901E-4</v>
+        <v>1.3081330620107799E-3</v>
+      </c>
+      <c r="M50" s="2">
+        <v>2.80171745622202E-6</v>
       </c>
       <c r="N50">
-        <v>1.31129753244608</v>
-      </c>
-      <c r="O50">
-        <v>7.8150296279425404E-4</v>
+        <v>1.4366091704730399E-3</v>
+      </c>
+      <c r="O50" s="2">
+        <v>3.9642356132896798E-6</v>
       </c>
       <c r="P50" s="7">
-        <f>N50/L50</f>
-        <v>0.99728610985822141</v>
+        <f t="shared" si="9"/>
+        <v>1.0982133333322945</v>
       </c>
       <c r="Q50">
-        <f t="shared" si="7"/>
-        <v>9.004190394956773E-4</v>
+        <f t="shared" si="11"/>
+        <v>3.8361574919628999E-3</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="B51" s="4"/>
-      <c r="D51" s="20">
-        <v>1.33910590256307</v>
-      </c>
-      <c r="E51" s="20">
-        <v>1.23393298512987E-2</v>
-      </c>
-      <c r="H51" s="7">
-        <f>F51/D51</f>
-        <v>0</v>
-      </c>
-      <c r="I51" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+      <c r="D51">
+        <v>7.5610462202649401E-3</v>
+      </c>
+      <c r="E51" s="2">
+        <v>1.57081565413314E-5</v>
+      </c>
+      <c r="F51">
+        <v>8.3558566219651704E-3</v>
+      </c>
+      <c r="G51" s="2">
+        <v>2.3966742759134201E-5</v>
+      </c>
+      <c r="H51" s="13">
+        <f t="shared" si="8"/>
+        <v>1.1051191036989032</v>
+      </c>
+      <c r="I51">
+        <f t="shared" si="10"/>
+        <v>3.9138927052399545E-3</v>
       </c>
       <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
       <c r="L51">
-        <v>1.3080554428553499</v>
-      </c>
-      <c r="M51">
-        <v>1.05245064814075E-3</v>
+        <v>2.12547254000897E-3</v>
+      </c>
+      <c r="M51" s="2">
+        <v>4.3461545058756504E-6</v>
       </c>
       <c r="N51">
-        <v>1.30680092368919</v>
-      </c>
-      <c r="O51">
-        <v>1.1966142360113001E-3</v>
-      </c>
-      <c r="P51" s="8">
-        <f>N51/L51</f>
-        <v>0.99904092814030765</v>
+        <v>2.34981119128888E-3</v>
+      </c>
+      <c r="O51" s="2">
+        <v>6.0470823655424403E-6</v>
+      </c>
+      <c r="P51" s="7">
+        <f t="shared" si="9"/>
+        <v>1.105547659194394</v>
       </c>
       <c r="Q51">
-        <f t="shared" si="7"/>
-        <v>1.2177819875734308E-3</v>
+        <f t="shared" si="11"/>
+        <v>3.6338299450917248E-3</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="B52" s="4"/>
-      <c r="D52" s="20">
-        <v>1.3346899335651701</v>
-      </c>
-      <c r="E52" s="20">
-        <v>1.09895445803343E-2</v>
-      </c>
-      <c r="H52" s="7">
-        <f>F52/D52</f>
-        <v>0</v>
-      </c>
-      <c r="I52" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+      <c r="D52">
+        <v>1.4415070472640399E-2</v>
+      </c>
+      <c r="E52" s="2">
+        <v>3.9280138415606102E-5</v>
+      </c>
+      <c r="F52">
+        <v>1.57632575158239E-2</v>
+      </c>
+      <c r="G52" s="2">
+        <v>4.6556836615973601E-5</v>
+      </c>
+      <c r="H52" s="13">
+        <f t="shared" si="8"/>
+        <v>1.0935262193648196</v>
+      </c>
+      <c r="I52">
+        <f t="shared" si="10"/>
+        <v>4.3943507224962841E-3</v>
       </c>
       <c r="J52" s="3"/>
       <c r="L52">
-        <v>1.2992314592619101</v>
-      </c>
-      <c r="M52">
-        <v>2.6598085552900302E-3</v>
+        <v>4.0263446679611103E-3</v>
+      </c>
+      <c r="M52" s="2">
+        <v>9.8284022533362494E-6</v>
       </c>
       <c r="N52">
-        <v>1.2990352083416801</v>
-      </c>
-      <c r="O52">
-        <v>2.3388362534294302E-3</v>
+        <v>4.4001147340224003E-3</v>
+      </c>
+      <c r="O52" s="2">
+        <v>1.2233005270844601E-5</v>
       </c>
       <c r="P52" s="7">
-        <f>N52/L52</f>
-        <v>0.99984894845423344</v>
+        <f t="shared" si="9"/>
+        <v>1.0928311152881411</v>
       </c>
       <c r="Q52">
-        <f t="shared" si="7"/>
-        <v>2.7258832387438308E-3</v>
+        <f t="shared" si="11"/>
+        <v>4.0431595724590682E-3</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>250</v>
+        <v>750</v>
       </c>
       <c r="B53" s="4"/>
-      <c r="D53" s="20">
-        <v>1.29678717701069</v>
-      </c>
-      <c r="E53" s="20">
-        <v>1.08165723286055E-2</v>
-      </c>
-      <c r="H53" s="7">
-        <f>F53/D53</f>
-        <v>0</v>
-      </c>
-      <c r="I53" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+      <c r="D53">
+        <v>2.0534104630709499E-2</v>
+      </c>
+      <c r="E53" s="2">
+        <v>5.1678598638391099E-5</v>
+      </c>
+      <c r="F53">
+        <v>2.23393057358535E-2</v>
+      </c>
+      <c r="G53" s="2">
+        <v>5.7826696670158199E-5</v>
+      </c>
+      <c r="H53" s="13">
+        <f t="shared" si="8"/>
+        <v>1.0879123359702889</v>
+      </c>
+      <c r="I53">
+        <f t="shared" si="10"/>
+        <v>3.927730995428016E-3</v>
       </c>
       <c r="J53" s="3"/>
-      <c r="K53" s="3"/>
       <c r="L53">
-        <v>1.2754633925346801</v>
-      </c>
-      <c r="M53">
-        <v>2.5670750630042301E-3</v>
+        <v>5.7060236110456197E-3</v>
+      </c>
+      <c r="M53" s="2">
+        <v>1.35378322351975E-5</v>
       </c>
       <c r="N53">
-        <v>1.27508401331121</v>
-      </c>
-      <c r="O53">
-        <v>3.1668437255882899E-3</v>
-      </c>
-      <c r="P53" s="8">
-        <f>N53/L53</f>
-        <v>0.9997025557725211</v>
+        <v>6.2061024296920604E-3</v>
+      </c>
+      <c r="O53" s="2">
+        <v>1.42865721950832E-5</v>
+      </c>
+      <c r="P53" s="7">
+        <f t="shared" si="9"/>
+        <v>1.0876405098777364</v>
       </c>
       <c r="Q53">
-        <f t="shared" si="7"/>
-        <v>3.1958049501485874E-3</v>
+        <f t="shared" si="11"/>
+        <v>3.5955188836270442E-3</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>500</v>
+        <v>999.99</v>
       </c>
       <c r="B54" s="4"/>
-      <c r="D54" s="20">
-        <v>1.2662694099393199</v>
-      </c>
-      <c r="E54" s="20">
-        <v>1.3642711353786301E-2</v>
-      </c>
-      <c r="H54" s="7">
-        <f>F54/D54</f>
-        <v>0</v>
-      </c>
-      <c r="I54" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+      <c r="D54">
+        <v>2.6037643908025699E-2</v>
+      </c>
+      <c r="E54" s="2">
+        <v>7.16762407558917E-5</v>
+      </c>
+      <c r="F54">
+        <v>2.8423944908042901E-2</v>
+      </c>
+      <c r="G54" s="2">
+        <v>6.8045831633092906E-5</v>
+      </c>
+      <c r="H54" s="13">
+        <f t="shared" si="8"/>
+        <v>1.0916481156454276</v>
+      </c>
+      <c r="I54">
+        <f>H54*((E54/D54)^2 +(G54/F54)^2)^0.5</f>
+        <v>3.9824844315028184E-3</v>
       </c>
       <c r="J54" s="3"/>
       <c r="L54">
-        <v>1.21433761848289</v>
-      </c>
-      <c r="M54">
-        <v>1.78305037450447E-3</v>
+        <v>7.2100975409337296E-3</v>
+      </c>
+      <c r="M54" s="2">
+        <v>1.5881717337174401E-5</v>
       </c>
       <c r="N54">
-        <v>1.2162928747352799</v>
-      </c>
-      <c r="O54">
-        <v>1.78442571980327E-3</v>
+        <v>7.8337967364074702E-3</v>
+      </c>
+      <c r="O54" s="2">
+        <v>1.6587191792760698E-5</v>
       </c>
       <c r="P54" s="7">
-        <f>N54/L54</f>
-        <v>1.0016101422064423</v>
+        <f t="shared" si="9"/>
+        <v>1.0865035725151881</v>
       </c>
       <c r="Q54">
-        <f t="shared" si="7"/>
-        <v>2.0790073532015014E-3</v>
+        <f>P54*((M54/L54)^2 +(O54/N54)^2)^0.5</f>
+        <v>3.3196628738700355E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>750</v>
-      </c>
-      <c r="B55" s="4"/>
-      <c r="D55" s="20">
-        <v>1.23279071771682</v>
-      </c>
-      <c r="E55" s="20">
-        <v>1.1896408260051301E-2</v>
-      </c>
-      <c r="H55" s="7">
-        <f>F55/D55</f>
-        <v>0</v>
-      </c>
-      <c r="I55" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J55" s="4"/>
-      <c r="L55">
-        <v>1.16893154054166</v>
-      </c>
-      <c r="M55">
-        <v>2.5299483816998E-3</v>
-      </c>
-      <c r="N55">
-        <v>1.1623016999656299</v>
-      </c>
-      <c r="O55">
-        <v>2.3537063605707201E-3</v>
-      </c>
-      <c r="P55" s="7">
-        <f>N55/L55</f>
-        <v>0.99432829011273149</v>
-      </c>
-      <c r="Q55">
-        <f t="shared" si="7"/>
-        <v>2.9471542099952473E-3</v>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C57" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>999.99</v>
-      </c>
-      <c r="B56" s="4"/>
-      <c r="D56" s="20">
-        <v>1.1928852496040101</v>
-      </c>
-      <c r="E56" s="20">
-        <v>1.19657192345643E-2</v>
-      </c>
-      <c r="H56" s="7">
-        <f>F56/D56</f>
-        <v>0</v>
-      </c>
-      <c r="I56" t="e">
-        <f>H56*((E56/D56)^2 +(G56/F56)^2)^0.5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J56" s="4"/>
-      <c r="L56">
-        <v>1.1280813456035399</v>
-      </c>
-      <c r="M56">
-        <v>2.4503318989518999E-3</v>
-      </c>
-      <c r="N56">
-        <v>1.1159074766764601</v>
-      </c>
-      <c r="O56">
-        <v>2.3868755353182898E-3</v>
-      </c>
-      <c r="P56" s="8">
-        <f>N56/L56</f>
-        <v>0.98920834124726476</v>
-      </c>
-      <c r="Q56">
-        <f>P56*((M56/L56)^2 +(O56/N56)^2)^0.5</f>
-        <v>3.0155845990736735E-3</v>
-      </c>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C58" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D58" s="11"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="12"/>
+      <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
+      <c r="M58" s="2"/>
+      <c r="N58" s="2"/>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C59" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="10"/>
-      <c r="G59" s="10"/>
-      <c r="H59" s="10"/>
-      <c r="I59" s="10"/>
-      <c r="K59" s="2"/>
-      <c r="L59" s="2"/>
-      <c r="M59" s="2"/>
-      <c r="N59" s="2"/>
+      <c r="C59" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D59" s="14"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="15"/>
+      <c r="G59" s="15"/>
+      <c r="H59" s="15"/>
+      <c r="I59" s="14"/>
+      <c r="K59" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="17"/>
+      <c r="M59" s="18"/>
+      <c r="N59" s="18"/>
+      <c r="O59" s="17"/>
+      <c r="P59" s="17"/>
+      <c r="Q59" s="17"/>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C60" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="15"/>
-      <c r="G60" s="15"/>
-      <c r="H60" s="15"/>
-      <c r="I60" s="14"/>
-      <c r="K60" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="17"/>
-      <c r="M60" s="18"/>
-      <c r="N60" s="18"/>
-      <c r="O60" s="17"/>
-      <c r="P60" s="17"/>
-      <c r="Q60" s="17"/>
+      <c r="A60" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B60" s="5"/>
+      <c r="C60" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D60" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F60" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G60" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H60" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="I60" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="J60" s="6"/>
+      <c r="K60" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="L60" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="M60" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="N60" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="O60" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="P60" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q60" s="19" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A61" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B61" s="5"/>
-      <c r="C61" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D61" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E61" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F61" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G61" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="H61" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="I61" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="J61" s="6"/>
-      <c r="K61" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="L61" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="M61" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="N61" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="O61" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="P61" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q61" s="19" t="s">
-        <v>12</v>
+      <c r="A61">
+        <v>0.1</v>
+      </c>
+      <c r="B61" s="4"/>
+      <c r="D61">
+        <v>1.3352695015565299</v>
+      </c>
+      <c r="E61">
+        <v>1.03018463315712E-4</v>
+      </c>
+      <c r="F61">
+        <v>1.33536898944584</v>
+      </c>
+      <c r="G61">
+        <v>1.25080703731084E-4</v>
+      </c>
+      <c r="H61" s="7">
+        <f t="shared" ref="H61:H73" si="12">F61/D61</f>
+        <v>1.0000745077223692</v>
+      </c>
+      <c r="I61">
+        <f>H61*((E61/D61)^2 +(G61/F61)^2)^0.5</f>
+        <v>1.2135980139653212E-4</v>
+      </c>
+      <c r="J61" s="3"/>
+      <c r="L61">
+        <v>1.3352318967644701</v>
+      </c>
+      <c r="M61" s="2">
+        <v>9.7356481692860994E-5</v>
+      </c>
+      <c r="N61">
+        <v>1.3353466214812699</v>
+      </c>
+      <c r="O61">
+        <v>1.2505601665707E-4</v>
+      </c>
+      <c r="P61" s="7">
+        <f t="shared" ref="P61:P73" si="13">N61/L61</f>
+        <v>1.0000859211924744</v>
+      </c>
+      <c r="Q61">
+        <f>P61*((M61/L61)^2 +(O61/N61)^2)^0.5</f>
+        <v>1.1869810586467566E-4</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="B62" s="4"/>
-      <c r="C62" s="2">
-        <v>2.0906018648200899E-5</v>
-      </c>
-      <c r="D62" s="21">
-        <v>1.9785240862768899E-5</v>
-      </c>
-      <c r="E62" s="21"/>
-      <c r="F62" s="2">
-        <v>2.0611254914561302E-5</v>
+      <c r="D62">
+        <v>1.3332831025853</v>
+      </c>
+      <c r="E62">
+        <v>1.1155132408639799E-4</v>
+      </c>
+      <c r="F62">
+        <v>1.3335516984153499</v>
       </c>
       <c r="G62" s="2">
-        <v>2.6942824381894501E-8</v>
+        <v>9.8571452316726502E-5</v>
       </c>
       <c r="H62" s="7">
-        <f>F62/D62</f>
-        <v>1.0417490015674646</v>
+        <f t="shared" si="12"/>
+        <v>1.0002014544619438</v>
       </c>
       <c r="I62">
-        <f>H62*((E62/D62)^2 +(G62/F62)^2)^0.5</f>
-        <v>1.3617637798180393E-3</v>
+        <f t="shared" ref="I62:I72" si="14">H62*((E62/D62)^2 +(G62/F62)^2)^0.5</f>
+        <v>1.1166367498899214E-4</v>
       </c>
       <c r="J62" s="3"/>
-      <c r="K62" s="2"/>
-      <c r="L62" s="2">
-        <v>2.44222139985293E-5</v>
-      </c>
-      <c r="M62" s="2">
-        <v>3.2540004788240401E-9</v>
-      </c>
-      <c r="N62" s="7"/>
-      <c r="P62" s="7">
-        <f>N62/L62</f>
-        <v>0</v>
-      </c>
-      <c r="Q62" t="e">
-        <f>P62*((M62/L62)^2 +(O62/N62)^2)^0.5</f>
-        <v>#DIV/0!</v>
+      <c r="K62" s="3"/>
+      <c r="L62">
+        <v>1.33328060850382</v>
+      </c>
+      <c r="M62">
+        <v>1.11744636942801E-4</v>
+      </c>
+      <c r="N62">
+        <v>1.33349654821898</v>
+      </c>
+      <c r="O62" s="2">
+        <v>9.9388022927045995E-5</v>
+      </c>
+      <c r="P62" s="8">
+        <f t="shared" si="13"/>
+        <v>1.0001619611909021</v>
+      </c>
+      <c r="Q62">
+        <f t="shared" ref="Q62:Q72" si="15">P62*((M62/L62)^2 +(O62/N62)^2)^0.5</f>
+        <v>1.1217617716941135E-4</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="B63" s="4"/>
-      <c r="C63" s="2">
-        <v>3.1327203465188001E-3</v>
-      </c>
-      <c r="D63" s="20">
-        <v>1.02051178015395E-4</v>
-      </c>
-      <c r="E63" s="20"/>
+      <c r="D63">
+        <v>1.3327302748801999</v>
+      </c>
+      <c r="E63">
+        <v>1.2633176524829901E-4</v>
+      </c>
       <c r="F63">
-        <v>1.03580844636417E-4</v>
-      </c>
-      <c r="G63" s="2">
-        <v>6.1396317523546606E-8</v>
+        <v>1.33280976817106</v>
+      </c>
+      <c r="G63">
+        <v>1.10318157044691E-4</v>
       </c>
       <c r="H63" s="7">
-        <f>F63/D63</f>
-        <v>1.0149892108133356</v>
+        <f t="shared" si="12"/>
+        <v>1.0000596469460914</v>
       </c>
       <c r="I63">
-        <f t="shared" ref="I63:I73" si="8">H63*((E63/D63)^2 +(G63/F63)^2)^0.5</f>
-        <v>6.016228202116846E-4</v>
+        <f t="shared" si="14"/>
+        <v>1.2585075874776679E-4</v>
       </c>
       <c r="J63" s="3"/>
       <c r="L63">
-        <v>1.21907844018741E-4</v>
-      </c>
-      <c r="M63" s="2">
-        <v>1.40834939730919E-8</v>
+        <v>1.3325160160175999</v>
+      </c>
+      <c r="M63">
+        <v>1.2990361944337101E-4</v>
       </c>
       <c r="N63">
-        <v>1.27621410906264E-4</v>
-      </c>
-      <c r="O63" s="2">
-        <v>7.9820165373987095E-8</v>
+        <v>1.3326689845730799</v>
+      </c>
+      <c r="O63">
+        <v>1.0526827110579401E-4</v>
       </c>
       <c r="P63" s="7">
-        <f>N63/L63</f>
-        <v>1.0468679184142133</v>
+        <f t="shared" si="13"/>
+        <v>1.0001147967856605</v>
       </c>
       <c r="Q63">
-        <f t="shared" ref="Q63:Q73" si="9">P63*((M63/L63)^2 +(O63/N63)^2)^0.5</f>
-        <v>6.6583397526143498E-4</v>
+        <f t="shared" si="15"/>
+        <v>1.2548677612360951E-4</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B64" s="4"/>
-      <c r="C64" s="2">
-        <v>6.2691724987101998E-3</v>
-      </c>
-      <c r="D64" s="20">
-        <v>2.0004896550590901E-4</v>
-      </c>
-      <c r="E64" s="20"/>
+      <c r="D64">
+        <v>1.3300592286289901</v>
+      </c>
+      <c r="E64">
+        <v>4.0385977571718098E-4</v>
+      </c>
       <c r="F64">
-        <v>2.0769359643264999E-4</v>
-      </c>
-      <c r="G64" s="2">
-        <v>8.9692390255205302E-8</v>
+        <v>1.33006735676433</v>
+      </c>
+      <c r="G64">
+        <v>4.3462506631634999E-4</v>
       </c>
       <c r="H64" s="7">
-        <f>F64/D64</f>
-        <v>1.0382137988437394</v>
+        <f t="shared" si="12"/>
+        <v>1.00000611110781</v>
       </c>
       <c r="I64">
-        <f t="shared" si="8"/>
-        <v>4.4835218231886319E-4</v>
+        <f t="shared" si="14"/>
+        <v>4.4606958157820904E-4</v>
       </c>
       <c r="J64" s="3"/>
+      <c r="K64" s="3"/>
       <c r="L64">
-        <v>2.4364376203713501E-4</v>
-      </c>
-      <c r="M64" s="2">
-        <v>3.6399685613690799E-8</v>
+        <v>1.32875591199513</v>
+      </c>
+      <c r="M64">
+        <v>3.6656386812860002E-4</v>
       </c>
       <c r="N64">
-        <v>2.5560959700704201E-4</v>
-      </c>
-      <c r="O64" s="2">
-        <v>1.2775665836178299E-7</v>
-      </c>
-      <c r="P64" s="7">
-        <f>N64/L64</f>
-        <v>1.0491120103788383</v>
+        <v>1.3283935226396499</v>
+      </c>
+      <c r="O64">
+        <v>4.6050432456435497E-4</v>
+      </c>
+      <c r="P64" s="8">
+        <f t="shared" si="13"/>
+        <v>0.99972727168909759</v>
       </c>
       <c r="Q64">
-        <f t="shared" si="9"/>
-        <v>5.4728183879285217E-4</v>
+        <f t="shared" si="15"/>
+        <v>4.4291324537064109E-4</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B65" s="4"/>
-      <c r="C65" s="2">
-        <v>1.2558983712415E-2</v>
-      </c>
-      <c r="D65" s="20">
-        <v>1.9727739159685499E-3</v>
-      </c>
-      <c r="E65" s="20"/>
+      <c r="D65">
+        <v>1.3280313268428501</v>
+      </c>
+      <c r="E65">
+        <v>9.3351065376810901E-4</v>
+      </c>
       <c r="F65">
-        <v>2.0882330769847598E-3</v>
-      </c>
-      <c r="G65" s="2">
-        <v>1.5267636606574901E-6</v>
+        <v>1.32879638765109</v>
+      </c>
+      <c r="G65">
+        <v>1.0451282524601201E-3</v>
       </c>
       <c r="H65" s="7">
-        <f>F65/D65</f>
-        <v>1.0585263015095798</v>
+        <f t="shared" si="12"/>
+        <v>1.00057608641662</v>
       </c>
       <c r="I65">
-        <f t="shared" si="8"/>
-        <v>7.7391719765714396E-4</v>
+        <f t="shared" si="14"/>
+        <v>1.0554658196667876E-3</v>
       </c>
       <c r="J65" s="3"/>
       <c r="L65">
-        <v>2.4288696331029799E-3</v>
-      </c>
-      <c r="M65" s="2">
-        <v>9.7964708696651905E-7</v>
+        <v>1.3245110745965301</v>
+      </c>
+      <c r="M65">
+        <v>6.3753145972632905E-4</v>
       </c>
       <c r="N65">
-        <v>2.56202907911283E-3</v>
-      </c>
-      <c r="O65" s="2">
-        <v>1.85007690935801E-6</v>
+        <v>1.32578542353965</v>
+      </c>
+      <c r="O65">
+        <v>1.0645660109259701E-3</v>
       </c>
       <c r="P65" s="7">
-        <f>N65/L65</f>
-        <v>1.0548236283228316</v>
+        <f t="shared" si="13"/>
+        <v>1.0009621278127161</v>
       </c>
       <c r="Q65">
-        <f t="shared" si="9"/>
-        <v>8.7246560513766763E-4</v>
+        <f t="shared" si="15"/>
+        <v>9.3708596837583497E-4</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B66" s="4"/>
-      <c r="C66" s="2">
-        <v>1.8782496824776201E-2</v>
-      </c>
-      <c r="D66" s="20">
-        <v>4.9269907229743297E-3</v>
-      </c>
-      <c r="E66" s="20"/>
+      <c r="D66">
+        <v>1.32635805956632</v>
+      </c>
+      <c r="E66">
+        <v>6.9639455664311498E-4</v>
+      </c>
       <c r="F66">
-        <v>5.2267028439012698E-3</v>
-      </c>
-      <c r="G66" s="2">
-        <v>5.8392478108713296E-6</v>
+        <v>1.32593816850222</v>
+      </c>
+      <c r="G66">
+        <v>9.7502159311734795E-4</v>
       </c>
       <c r="H66" s="7">
-        <f>F66/D66</f>
-        <v>1.0608306647563586</v>
+        <f t="shared" si="12"/>
+        <v>0.99968342555686862</v>
       </c>
       <c r="I66">
-        <f t="shared" si="8"/>
-        <v>1.1851550244743078E-3</v>
+        <f t="shared" si="14"/>
+        <v>9.0326340688159196E-4</v>
       </c>
       <c r="J66" s="3"/>
+      <c r="K66" s="3"/>
       <c r="L66">
-        <v>6.0546834237900898E-3</v>
-      </c>
-      <c r="M66" s="2">
-        <v>3.7968621057748099E-6</v>
+        <v>1.3197871026024</v>
+      </c>
+      <c r="M66">
+        <v>8.8312138374329295E-4</v>
       </c>
       <c r="N66">
-        <v>6.4137122028123401E-3</v>
-      </c>
-      <c r="O66" s="2">
-        <v>5.4200951411111697E-6</v>
-      </c>
-      <c r="P66" s="7">
-        <f>N66/L66</f>
-        <v>1.0592976963273675</v>
+        <v>1.3193357094999201</v>
+      </c>
+      <c r="O66">
+        <v>9.5862687561023305E-4</v>
+      </c>
+      <c r="P66" s="8">
+        <f t="shared" si="13"/>
+        <v>0.99965798036547726</v>
       </c>
       <c r="Q66">
-        <f t="shared" si="9"/>
-        <v>1.1147351456962668E-3</v>
+        <f t="shared" si="15"/>
+        <v>9.874335070433548E-4</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="B67" s="4"/>
-      <c r="C67" s="2">
-        <v>2.51046376970986E-2</v>
-      </c>
-      <c r="D67" s="20">
-        <v>9.7820010092556295E-3</v>
-      </c>
-      <c r="E67" s="20"/>
+      <c r="D67">
+        <v>1.3241746057403101</v>
+      </c>
+      <c r="E67">
+        <v>7.5385260544338895E-4</v>
+      </c>
       <c r="F67">
-        <v>1.04457324399824E-2</v>
-      </c>
-      <c r="G67" s="2">
-        <v>1.0966581763202101E-5</v>
+        <v>1.32176272990539</v>
+      </c>
+      <c r="G67">
+        <v>9.1298526822734501E-4</v>
       </c>
       <c r="H67" s="7">
-        <f>F67/D67</f>
-        <v>1.0678523167293434</v>
+        <f t="shared" si="12"/>
+        <v>0.99817858171840435</v>
       </c>
       <c r="I67">
-        <f t="shared" si="8"/>
-        <v>1.1210979995632418E-3</v>
+        <f t="shared" si="14"/>
+        <v>8.9347561337432412E-4</v>
       </c>
       <c r="J67" s="3"/>
       <c r="L67">
-        <v>1.20608403533201E-2</v>
-      </c>
-      <c r="M67" s="2">
-        <v>1.08240027557222E-5</v>
+        <v>1.31486593414251</v>
+      </c>
+      <c r="M67">
+        <v>8.9177056244582901E-4</v>
       </c>
       <c r="N67">
-        <v>1.27839027701272E-2</v>
-      </c>
-      <c r="O67" s="2">
-        <v>1.14752038724967E-5</v>
+        <v>1.31129753244608</v>
+      </c>
+      <c r="O67">
+        <v>7.8150296279425404E-4</v>
       </c>
       <c r="P67" s="7">
-        <f>N67/L67</f>
-        <v>1.0599512468140793</v>
+        <f t="shared" si="13"/>
+        <v>0.99728610985822141</v>
       </c>
       <c r="Q67">
-        <f t="shared" si="9"/>
-        <v>1.3454096255822378E-3</v>
+        <f t="shared" si="15"/>
+        <v>9.004190394956773E-4</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="B68" s="4"/>
-      <c r="C68" s="2">
-        <v>3.1476119846668899E-2</v>
-      </c>
-      <c r="D68" s="20">
-        <v>1.43763436727791E-2</v>
-      </c>
-      <c r="E68" s="20"/>
+      <c r="D68">
+        <v>1.3201669732916701</v>
+      </c>
+      <c r="E68">
+        <v>8.1198011218001096E-4</v>
+      </c>
+      <c r="F68">
+        <v>1.32030209918924</v>
+      </c>
+      <c r="G68">
+        <v>1.31640184004061E-3</v>
+      </c>
       <c r="H68" s="7">
-        <f>F68/D68</f>
-        <v>0</v>
-      </c>
-      <c r="I68" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <f t="shared" si="12"/>
+        <v>1.0001023551568125</v>
+      </c>
+      <c r="I68">
+        <f t="shared" si="14"/>
+        <v>1.1716137129980835E-3</v>
       </c>
       <c r="J68" s="3"/>
+      <c r="K68" s="3"/>
       <c r="L68">
-        <v>1.8041215453004699E-2</v>
-      </c>
-      <c r="M68" s="2">
-        <v>1.7714094968001101E-5</v>
+        <v>1.3080554428553499</v>
+      </c>
+      <c r="M68">
+        <v>1.05245064814075E-3</v>
       </c>
       <c r="N68">
-        <v>1.9051467947753701E-2</v>
-      </c>
-      <c r="O68" s="2">
-        <v>1.1429796000528301E-5</v>
-      </c>
-      <c r="P68" s="7">
-        <f>N68/L68</f>
-        <v>1.0559969197962629</v>
+        <v>1.30680092368919</v>
+      </c>
+      <c r="O68">
+        <v>1.1966142360113001E-3</v>
+      </c>
+      <c r="P68" s="8">
+        <f t="shared" si="13"/>
+        <v>0.99904092814030765</v>
       </c>
       <c r="Q68">
-        <f t="shared" si="9"/>
-        <v>1.2150834669821305E-3</v>
+        <f t="shared" si="15"/>
+        <v>1.2177819875734308E-3</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="B69" s="4"/>
-      <c r="C69" s="2">
-        <v>5.2878603388737497E-2</v>
-      </c>
-      <c r="D69" s="20">
-        <v>2.00458898906196E-2</v>
-      </c>
-      <c r="E69" s="20"/>
+      <c r="D69">
+        <v>1.3167958235947801</v>
+      </c>
+      <c r="E69">
+        <v>2.9975536579085601E-3</v>
+      </c>
+      <c r="F69">
+        <v>1.31764911185755</v>
+      </c>
+      <c r="G69">
+        <v>2.4611631617419902E-3</v>
+      </c>
       <c r="H69" s="7">
-        <f>F69/D69</f>
-        <v>0</v>
-      </c>
-      <c r="I69" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <f t="shared" si="12"/>
+        <v>1.0006480034698473</v>
+      </c>
+      <c r="I69">
+        <f t="shared" si="14"/>
+        <v>2.9465367028268241E-3</v>
       </c>
       <c r="J69" s="3"/>
       <c r="L69">
-        <v>2.3942727421137198E-2</v>
-      </c>
-      <c r="M69" s="2">
-        <v>2.41011922220882E-5</v>
+        <v>1.2992314592619101</v>
+      </c>
+      <c r="M69">
+        <v>2.6598085552900302E-3</v>
       </c>
       <c r="N69">
-        <v>2.5404075273833399E-2</v>
-      </c>
-      <c r="O69" s="2">
-        <v>2.6871581822638802E-5</v>
+        <v>1.2990352083416801</v>
+      </c>
+      <c r="O69">
+        <v>2.3388362534294302E-3</v>
       </c>
       <c r="P69" s="7">
-        <f>N69/L69</f>
-        <v>1.0610351455367648</v>
+        <f t="shared" si="13"/>
+        <v>0.99984894845423344</v>
       </c>
       <c r="Q69">
-        <f t="shared" si="9"/>
-        <v>1.5493114902381951E-3</v>
+        <f t="shared" si="15"/>
+        <v>2.7258832387438308E-3</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="B70" s="4"/>
-      <c r="C70" s="2">
-        <v>0.107716927588289</v>
-      </c>
-      <c r="D70" s="20">
-        <v>3.0432830381329601E-2</v>
-      </c>
-      <c r="E70" s="20"/>
+      <c r="D70">
+        <v>1.3044437019138699</v>
+      </c>
+      <c r="E70">
+        <v>1.8132333400680499E-3</v>
+      </c>
+      <c r="F70">
+        <v>1.3079779433234</v>
+      </c>
+      <c r="G70">
+        <v>3.6195996594348399E-3</v>
+      </c>
       <c r="H70" s="7">
-        <f>F70/D70</f>
-        <v>0</v>
-      </c>
-      <c r="I70" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <f t="shared" si="12"/>
+        <v>1.0027093859277671</v>
+      </c>
+      <c r="I70">
+        <f t="shared" si="14"/>
+        <v>3.1052124968005581E-3</v>
       </c>
       <c r="J70" s="3"/>
+      <c r="K70" s="3"/>
       <c r="L70">
-        <v>3.5694610619412301E-2</v>
-      </c>
-      <c r="M70" s="2">
-        <v>8.2524961518027197E-5</v>
+        <v>1.2754633925346801</v>
+      </c>
+      <c r="M70">
+        <v>2.5670750630042301E-3</v>
       </c>
       <c r="N70">
-        <v>3.7961973926613303E-2</v>
+        <v>1.27508401331121</v>
       </c>
       <c r="O70">
-        <v>1.02905372343833E-4</v>
-      </c>
-      <c r="P70" s="7">
-        <f>N70/L70</f>
-        <v>1.0635211665810387</v>
+        <v>3.1668437255882899E-3</v>
+      </c>
+      <c r="P70" s="8">
+        <f t="shared" si="13"/>
+        <v>0.9997025557725211</v>
       </c>
       <c r="Q70">
-        <f t="shared" si="9"/>
-        <v>3.7890881489905845E-3</v>
+        <f t="shared" si="15"/>
+        <v>3.1958049501485874E-3</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="B71" s="4"/>
-      <c r="C71" s="2">
-        <v>0.16515386445267599</v>
-      </c>
-      <c r="D71" s="20">
-        <v>4.89210306757277E-2</v>
-      </c>
-      <c r="E71" s="20"/>
+      <c r="D71">
+        <v>1.2726629240712399</v>
+      </c>
+      <c r="E71">
+        <v>2.7166252951841101E-3</v>
+      </c>
+      <c r="F71">
+        <v>1.2729237405448699</v>
+      </c>
+      <c r="G71">
+        <v>2.8623503684927099E-3</v>
+      </c>
       <c r="H71" s="7">
-        <f>F71/D71</f>
-        <v>0</v>
-      </c>
-      <c r="I71" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <f t="shared" si="12"/>
+        <v>1.0002049375908553</v>
+      </c>
+      <c r="I71">
+        <f t="shared" si="14"/>
+        <v>3.101104200533414E-3</v>
       </c>
       <c r="J71" s="3"/>
       <c r="L71">
-        <v>5.8503285539065399E-2</v>
+        <v>1.21433761848289</v>
       </c>
       <c r="M71">
-        <v>1.3565230700754799E-4</v>
+        <v>1.78305037450447E-3</v>
       </c>
       <c r="N71">
-        <v>6.2444533831966298E-2</v>
+        <v>1.2162928747352799</v>
       </c>
       <c r="O71">
-        <v>1.8469627006352599E-4</v>
+        <v>1.78442571980327E-3</v>
       </c>
       <c r="P71" s="7">
-        <f>N71/L71</f>
-        <v>1.0673679820985291</v>
+        <f t="shared" si="13"/>
+        <v>1.0016101422064423</v>
       </c>
       <c r="Q71">
-        <f t="shared" si="9"/>
-        <v>4.0114868768480784E-3</v>
+        <f t="shared" si="15"/>
+        <v>2.0790073532015014E-3</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="B72" s="4"/>
-      <c r="C72" s="2">
-        <v>0.22114304090137801</v>
-      </c>
-      <c r="D72" s="20">
-        <v>9.6226590649767796E-2</v>
-      </c>
-      <c r="E72" s="20"/>
+      <c r="D72">
+        <v>1.2423089205787501</v>
+      </c>
+      <c r="E72">
+        <v>2.3272403104410899E-3</v>
+      </c>
+      <c r="F72">
+        <v>1.2408887816069201</v>
+      </c>
+      <c r="G72">
+        <v>2.17715292950064E-3</v>
+      </c>
       <c r="H72" s="7">
-        <f>F72/D72</f>
-        <v>0</v>
-      </c>
-      <c r="I72" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J72" s="3"/>
+        <f t="shared" si="12"/>
+        <v>0.99885685520863166</v>
+      </c>
+      <c r="I72">
+        <f t="shared" si="14"/>
+        <v>2.5637040120480357E-3</v>
+      </c>
+      <c r="J72" s="4"/>
       <c r="L72">
-        <v>0.111849004597233</v>
+        <v>1.16893154054166</v>
       </c>
       <c r="M72">
-        <v>1.9399071169807599E-4</v>
+        <v>2.5299483816998E-3</v>
       </c>
       <c r="N72">
-        <v>0.120228333001437</v>
+        <v>1.1623016999656299</v>
       </c>
       <c r="O72">
-        <v>2.56613265918605E-4</v>
+        <v>2.3537063605707201E-3</v>
       </c>
       <c r="P72" s="7">
-        <f>N72/L72</f>
-        <v>1.0749164325098632</v>
+        <f t="shared" si="13"/>
+        <v>0.99432829011273149</v>
       </c>
       <c r="Q72">
-        <f t="shared" si="9"/>
-        <v>2.9562598512691846E-3</v>
+        <f t="shared" si="15"/>
+        <v>2.9471542099952473E-3</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>750</v>
+        <v>999.99</v>
       </c>
       <c r="B73" s="4"/>
-      <c r="D73" s="20">
-        <v>0.140294088260282</v>
-      </c>
-      <c r="E73" s="20"/>
+      <c r="D73">
+        <v>1.2087119744332699</v>
+      </c>
+      <c r="E73">
+        <v>2.1559251329615801E-3</v>
+      </c>
+      <c r="F73">
+        <v>1.20706353583708</v>
+      </c>
+      <c r="G73">
+        <v>2.7226280465856702E-3</v>
+      </c>
       <c r="H73" s="7">
-        <f>F73/D73</f>
-        <v>0</v>
-      </c>
-      <c r="I73" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <f t="shared" si="12"/>
+        <v>0.99863620231200012</v>
+      </c>
+      <c r="I73">
+        <f>H73*((E73/D73)^2 +(G73/F73)^2)^0.5</f>
+        <v>2.871676467219969E-3</v>
       </c>
       <c r="J73" s="4"/>
       <c r="L73">
+        <v>1.1280813456035399</v>
+      </c>
+      <c r="M73">
+        <v>2.4503318989518999E-3</v>
+      </c>
+      <c r="N73">
+        <v>1.1159074766764601</v>
+      </c>
+      <c r="O73">
+        <v>2.3868755353182898E-3</v>
+      </c>
+      <c r="P73" s="8">
+        <f t="shared" si="13"/>
+        <v>0.98920834124726476</v>
+      </c>
+      <c r="Q73">
+        <f>P73*((M73/L73)^2 +(O73/N73)^2)^0.5</f>
+        <v>3.0155845990736735E-3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C76" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76" s="9"/>
+      <c r="E76" s="9"/>
+      <c r="F76" s="10"/>
+      <c r="G76" s="10"/>
+      <c r="H76" s="10"/>
+      <c r="I76" s="10"/>
+      <c r="K76" s="2"/>
+      <c r="L76" s="2"/>
+      <c r="M76" s="2"/>
+      <c r="N76" s="2"/>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C77" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D77" s="14"/>
+      <c r="E77" s="14"/>
+      <c r="F77" s="15"/>
+      <c r="G77" s="15"/>
+      <c r="H77" s="15"/>
+      <c r="I77" s="14"/>
+      <c r="K77" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="L77" s="17"/>
+      <c r="M77" s="18"/>
+      <c r="N77" s="18"/>
+      <c r="O77" s="17"/>
+      <c r="P77" s="17"/>
+      <c r="Q77" s="17"/>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A78" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B78" s="5"/>
+      <c r="C78" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D78" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E78" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F78" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G78" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H78" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="I78" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="J78" s="6"/>
+      <c r="K78" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="L78" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="M78" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="N78" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="O78" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="P78" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q78" s="19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>0.1</v>
+      </c>
+      <c r="B79" s="4"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2">
+        <v>1.99881472847514E-5</v>
+      </c>
+      <c r="E79" s="2">
+        <v>3.4269103641913598E-9</v>
+      </c>
+      <c r="F79" s="2">
+        <v>2.0611254914561302E-5</v>
+      </c>
+      <c r="G79" s="2">
+        <v>2.6942824381894501E-8</v>
+      </c>
+      <c r="H79" s="7">
+        <f t="shared" ref="H79:H91" si="16">F79/D79</f>
+        <v>1.0311738562325514</v>
+      </c>
+      <c r="I79">
+        <f>H79*((E79/D79)^2 +(G79/F79)^2)^0.5</f>
+        <v>1.359484363209042E-3</v>
+      </c>
+      <c r="J79" s="3"/>
+      <c r="K79" s="2"/>
+      <c r="L79" s="2">
+        <v>2.44222139985293E-5</v>
+      </c>
+      <c r="M79" s="2">
+        <v>3.2540004788240401E-9</v>
+      </c>
+      <c r="N79" s="2">
+        <v>2.5452415896808901E-5</v>
+      </c>
+      <c r="O79" s="2">
+        <v>3.4511677912228998E-8</v>
+      </c>
+      <c r="P79" s="7">
+        <f t="shared" ref="P79:P91" si="17">N79/L79</f>
+        <v>1.0421829854714089</v>
+      </c>
+      <c r="Q79">
+        <f>P79*((M79/L79)^2 +(O79/N79)^2)^0.5</f>
+        <v>1.419932591807686E-3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>0.5</v>
+      </c>
+      <c r="B80" s="4"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2">
+        <v>9.9775304693063802E-5</v>
+      </c>
+      <c r="E80" s="2">
+        <v>1.12762451750336E-8</v>
+      </c>
+      <c r="F80">
+        <v>1.03580844636417E-4</v>
+      </c>
+      <c r="G80" s="2">
+        <v>6.1396317523546606E-8</v>
+      </c>
+      <c r="H80" s="7">
+        <f t="shared" si="16"/>
+        <v>1.0381411006968115</v>
+      </c>
+      <c r="I80">
+        <f t="shared" ref="I80:I90" si="18">H80*((E80/D80)^2 +(G80/F80)^2)^0.5</f>
+        <v>6.2643124526338815E-4</v>
+      </c>
+      <c r="J80" s="3"/>
+      <c r="L80">
+        <v>1.21907844018741E-4</v>
+      </c>
+      <c r="M80" s="2">
+        <v>1.40834939730919E-8</v>
+      </c>
+      <c r="N80">
+        <v>1.27621410906264E-4</v>
+      </c>
+      <c r="O80" s="2">
+        <v>7.9820165373987095E-8</v>
+      </c>
+      <c r="P80" s="7">
+        <f t="shared" si="17"/>
+        <v>1.0468679184142133</v>
+      </c>
+      <c r="Q80">
+        <f t="shared" ref="Q80:Q90" si="19">P80*((M80/L80)^2 +(O80/N80)^2)^0.5</f>
+        <v>6.6583397526143498E-4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>1</v>
+      </c>
+      <c r="B81" s="4"/>
+      <c r="C81" s="2"/>
+      <c r="D81">
+        <v>1.99444960717931E-4</v>
+      </c>
+      <c r="E81" s="2">
+        <v>4.15103677610828E-8</v>
+      </c>
+      <c r="F81">
+        <v>2.0769359643264999E-4</v>
+      </c>
+      <c r="G81" s="2">
+        <v>8.9692390255205302E-8</v>
+      </c>
+      <c r="H81" s="7">
+        <f t="shared" si="16"/>
+        <v>1.041357955021911</v>
+      </c>
+      <c r="I81">
+        <f t="shared" si="18"/>
+        <v>4.9921348600659747E-4</v>
+      </c>
+      <c r="J81" s="3"/>
+      <c r="L81">
+        <v>2.4364376203713501E-4</v>
+      </c>
+      <c r="M81" s="2">
+        <v>3.6399685613690799E-8</v>
+      </c>
+      <c r="N81">
+        <v>2.5560959700704201E-4</v>
+      </c>
+      <c r="O81" s="2">
+        <v>1.2775665836178299E-7</v>
+      </c>
+      <c r="P81" s="7">
+        <f t="shared" si="17"/>
+        <v>1.0491120103788383</v>
+      </c>
+      <c r="Q81">
+        <f t="shared" si="19"/>
+        <v>5.4728183879285217E-4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>10</v>
+      </c>
+      <c r="B82" s="4"/>
+      <c r="C82" s="2"/>
+      <c r="D82">
+        <v>1.98828302242474E-3</v>
+      </c>
+      <c r="E82" s="2">
+        <v>8.8402559735503801E-7</v>
+      </c>
+      <c r="F82">
+        <v>2.0882330769847598E-3</v>
+      </c>
+      <c r="G82" s="2">
+        <v>1.5267636606574901E-6</v>
+      </c>
+      <c r="H82" s="7">
+        <f t="shared" si="16"/>
+        <v>1.0502695307623404</v>
+      </c>
+      <c r="I82">
+        <f t="shared" si="18"/>
+        <v>8.9872119185191652E-4</v>
+      </c>
+      <c r="J82" s="3"/>
+      <c r="L82">
+        <v>2.4288696331029799E-3</v>
+      </c>
+      <c r="M82" s="2">
+        <v>9.7964708696651905E-7</v>
+      </c>
+      <c r="N82">
+        <v>2.56202907911283E-3</v>
+      </c>
+      <c r="O82" s="2">
+        <v>1.85007690935801E-6</v>
+      </c>
+      <c r="P82" s="7">
+        <f t="shared" si="17"/>
+        <v>1.0548236283228316</v>
+      </c>
+      <c r="Q82">
+        <f t="shared" si="19"/>
+        <v>8.7246560513766763E-4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>25</v>
+      </c>
+      <c r="B83" s="4"/>
+      <c r="C83" s="2"/>
+      <c r="D83">
+        <v>4.96189185579824E-3</v>
+      </c>
+      <c r="E83" s="2">
+        <v>4.7305827494088002E-6</v>
+      </c>
+      <c r="F83">
+        <v>5.2267028439012698E-3</v>
+      </c>
+      <c r="G83" s="2">
+        <v>5.8392478108713296E-6</v>
+      </c>
+      <c r="H83" s="7">
+        <f t="shared" si="16"/>
+        <v>1.0533689559947954</v>
+      </c>
+      <c r="I83">
+        <f t="shared" si="18"/>
+        <v>1.5470774442694489E-3</v>
+      </c>
+      <c r="J83" s="3"/>
+      <c r="L83">
+        <v>6.0546834237900898E-3</v>
+      </c>
+      <c r="M83" s="2">
+        <v>3.7968621057748099E-6</v>
+      </c>
+      <c r="N83">
+        <v>6.4137122028123401E-3</v>
+      </c>
+      <c r="O83" s="2">
+        <v>5.4200951411111697E-6</v>
+      </c>
+      <c r="P83" s="7">
+        <f t="shared" si="17"/>
+        <v>1.0592976963273675</v>
+      </c>
+      <c r="Q83">
+        <f t="shared" si="19"/>
+        <v>1.1147351456962668E-3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>50</v>
+      </c>
+      <c r="B84" s="4"/>
+      <c r="C84" s="2"/>
+      <c r="D84">
+        <v>9.9108221418496706E-3</v>
+      </c>
+      <c r="E84" s="2">
+        <v>7.7799993373927392E-6</v>
+      </c>
+      <c r="F84">
+        <v>1.04457324399824E-2</v>
+      </c>
+      <c r="G84" s="2">
+        <v>1.0966581763202101E-5</v>
+      </c>
+      <c r="H84" s="7">
+        <f t="shared" si="16"/>
+        <v>1.053972343613554</v>
+      </c>
+      <c r="I84">
+        <f t="shared" si="18"/>
+        <v>1.3816434538880609E-3</v>
+      </c>
+      <c r="J84" s="3"/>
+      <c r="L84">
+        <v>1.20608403533201E-2</v>
+      </c>
+      <c r="M84" s="2">
+        <v>1.08240027557222E-5</v>
+      </c>
+      <c r="N84">
+        <v>1.27839027701272E-2</v>
+      </c>
+      <c r="O84" s="2">
+        <v>1.14752038724967E-5</v>
+      </c>
+      <c r="P84" s="7">
+        <f t="shared" si="17"/>
+        <v>1.0599512468140793</v>
+      </c>
+      <c r="Q84">
+        <f t="shared" si="19"/>
+        <v>1.3454096255822378E-3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>75</v>
+      </c>
+      <c r="B85" s="4"/>
+      <c r="C85" s="2"/>
+      <c r="D85">
+        <v>1.4852325171312301E-2</v>
+      </c>
+      <c r="E85" s="2">
+        <v>1.0926773969422099E-5</v>
+      </c>
+      <c r="F85">
+        <v>1.5673373059129699E-2</v>
+      </c>
+      <c r="G85" s="2">
+        <v>1.43528244781444E-5</v>
+      </c>
+      <c r="H85" s="7">
+        <f t="shared" si="16"/>
+        <v>1.055280764348149</v>
+      </c>
+      <c r="I85">
+        <f t="shared" si="18"/>
+        <v>1.2396008323190834E-3</v>
+      </c>
+      <c r="J85" s="3"/>
+      <c r="L85">
+        <v>1.8041215453004699E-2</v>
+      </c>
+      <c r="M85" s="2">
+        <v>1.7714094968001101E-5</v>
+      </c>
+      <c r="N85">
+        <v>1.9051467947753701E-2</v>
+      </c>
+      <c r="O85" s="2">
+        <v>1.1429796000528301E-5</v>
+      </c>
+      <c r="P85" s="7">
+        <f t="shared" si="17"/>
+        <v>1.0559969197962629</v>
+      </c>
+      <c r="Q85">
+        <f t="shared" si="19"/>
+        <v>1.2150834669821305E-3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>100</v>
+      </c>
+      <c r="B86" s="4"/>
+      <c r="C86" s="2"/>
+      <c r="D86">
+        <v>1.9731630447550601E-2</v>
+      </c>
+      <c r="E86" s="2">
+        <v>1.6356103473517E-5</v>
+      </c>
+      <c r="F86">
+        <v>2.0925446553624501E-2</v>
+      </c>
+      <c r="G86" s="2">
+        <v>2.4994452644818202E-5</v>
+      </c>
+      <c r="H86" s="7">
+        <f t="shared" si="16"/>
+        <v>1.0605026588779487</v>
+      </c>
+      <c r="I86">
+        <f t="shared" si="18"/>
+        <v>1.5418697335489266E-3</v>
+      </c>
+      <c r="J86" s="3"/>
+      <c r="L86">
+        <v>2.3942727421137198E-2</v>
+      </c>
+      <c r="M86" s="2">
+        <v>2.41011922220882E-5</v>
+      </c>
+      <c r="N86">
+        <v>2.5404075273833399E-2</v>
+      </c>
+      <c r="O86" s="2">
+        <v>2.6871581822638802E-5</v>
+      </c>
+      <c r="P86" s="7">
+        <f t="shared" si="17"/>
+        <v>1.0610351455367648</v>
+      </c>
+      <c r="Q86">
+        <f t="shared" si="19"/>
+        <v>1.5493114902381951E-3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>150</v>
+      </c>
+      <c r="B87" s="4"/>
+      <c r="C87" s="2"/>
+      <c r="D87">
+        <v>2.9577607515355299E-2</v>
+      </c>
+      <c r="E87" s="2">
+        <v>9.6115259837008704E-5</v>
+      </c>
+      <c r="F87">
+        <v>3.13728701314707E-2</v>
+      </c>
+      <c r="G87" s="2">
+        <v>9.6533695670185797E-5</v>
+      </c>
+      <c r="H87" s="7">
+        <f t="shared" si="16"/>
+        <v>1.0606966812709036</v>
+      </c>
+      <c r="I87">
+        <f t="shared" si="18"/>
+        <v>4.7468608413677059E-3</v>
+      </c>
+      <c r="J87" s="3"/>
+      <c r="L87">
+        <v>3.5694610619412301E-2</v>
+      </c>
+      <c r="M87" s="2">
+        <v>8.2524961518027197E-5</v>
+      </c>
+      <c r="N87">
+        <v>3.7961973926613303E-2</v>
+      </c>
+      <c r="O87">
+        <v>1.02905372343833E-4</v>
+      </c>
+      <c r="P87" s="7">
+        <f t="shared" si="17"/>
+        <v>1.0635211665810387</v>
+      </c>
+      <c r="Q87">
+        <f t="shared" si="19"/>
+        <v>3.7890881489905845E-3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>250</v>
+      </c>
+      <c r="B88" s="4"/>
+      <c r="C88" s="2"/>
+      <c r="D88">
+        <v>4.9063116103833598E-2</v>
+      </c>
+      <c r="E88">
+        <v>1.10308690961243E-4</v>
+      </c>
+      <c r="F88">
+        <v>5.2331116971228997E-2</v>
+      </c>
+      <c r="G88">
+        <v>1.62226546601959E-4</v>
+      </c>
+      <c r="H88" s="7">
+        <f t="shared" si="16"/>
+        <v>1.0666080984436301</v>
+      </c>
+      <c r="I88">
+        <f t="shared" si="18"/>
+        <v>4.0845479394107645E-3</v>
+      </c>
+      <c r="J88" s="3"/>
+      <c r="L88">
+        <v>5.8503285539065399E-2</v>
+      </c>
+      <c r="M88">
+        <v>1.3565230700754799E-4</v>
+      </c>
+      <c r="N88">
+        <v>6.2444533831966298E-2</v>
+      </c>
+      <c r="O88">
+        <v>1.8469627006352599E-4</v>
+      </c>
+      <c r="P88" s="7">
+        <f t="shared" si="17"/>
+        <v>1.0673679820985291</v>
+      </c>
+      <c r="Q88">
+        <f t="shared" si="19"/>
+        <v>4.0114868768480784E-3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>500</v>
+      </c>
+      <c r="B89" s="4"/>
+      <c r="C89" s="2"/>
+      <c r="D89">
+        <v>9.6307772048840001E-2</v>
+      </c>
+      <c r="E89">
+        <v>2.9970899011049499E-4</v>
+      </c>
+      <c r="F89">
+        <v>0.103397237554258</v>
+      </c>
+      <c r="G89">
+        <v>2.9078750115984998E-4</v>
+      </c>
+      <c r="H89" s="7">
+        <f t="shared" si="16"/>
+        <v>1.0736126000487558</v>
+      </c>
+      <c r="I89">
+        <f t="shared" si="18"/>
+        <v>4.503252851926585E-3</v>
+      </c>
+      <c r="J89" s="3"/>
+      <c r="L89">
+        <v>0.111849004597233</v>
+      </c>
+      <c r="M89">
+        <v>1.9399071169807599E-4</v>
+      </c>
+      <c r="N89">
+        <v>0.120228333001437</v>
+      </c>
+      <c r="O89">
+        <v>2.56613265918605E-4</v>
+      </c>
+      <c r="P89" s="7">
+        <f t="shared" si="17"/>
+        <v>1.0749164325098632</v>
+      </c>
+      <c r="Q89">
+        <f t="shared" si="19"/>
+        <v>2.9562598512691846E-3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>750</v>
+      </c>
+      <c r="B90" s="4"/>
+      <c r="D90">
+        <v>0.14171728952561699</v>
+      </c>
+      <c r="E90">
+        <v>3.43948673373356E-4</v>
+      </c>
+      <c r="F90">
+        <v>0.152393113650097</v>
+      </c>
+      <c r="G90">
+        <v>3.4464571027870302E-4</v>
+      </c>
+      <c r="H90" s="7">
+        <f t="shared" si="16"/>
+        <v>1.0753318396098046</v>
+      </c>
+      <c r="I90">
+        <f t="shared" si="18"/>
+        <v>3.567282186186052E-3</v>
+      </c>
+      <c r="J90" s="4"/>
+      <c r="L90">
         <v>0.16223272595004601</v>
       </c>
-      <c r="M73">
+      <c r="M90">
         <v>4.29274074054726E-4</v>
       </c>
-      <c r="N73">
+      <c r="N90">
         <v>0.17320049362348</v>
       </c>
-      <c r="O73">
+      <c r="O90">
         <v>3.4421587306751399E-4</v>
       </c>
-      <c r="P73" s="7">
-        <f>N73/L73</f>
+      <c r="P90" s="7">
+        <f t="shared" si="17"/>
         <v>1.0676051493877452</v>
       </c>
-      <c r="Q73">
-        <f t="shared" si="9"/>
+      <c r="Q90">
+        <f t="shared" si="19"/>
         <v>3.5329852627062406E-3</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A74">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A91">
         <v>999.99</v>
       </c>
-      <c r="B74" s="4"/>
-      <c r="D74" s="20">
-        <v>0.181401571560247</v>
-      </c>
-      <c r="E74" s="20"/>
-      <c r="H74" s="7">
-        <f>F74/D74</f>
+      <c r="B91" s="4"/>
+      <c r="D91">
+        <v>0.18452445645978199</v>
+      </c>
+      <c r="E91">
+        <v>3.9150077450695101E-4</v>
+      </c>
+      <c r="F91">
+        <v>0.19920063317619099</v>
+      </c>
+      <c r="G91">
+        <v>5.5578369458203795E-4</v>
+      </c>
+      <c r="H91" s="7">
+        <f t="shared" si="16"/>
+        <v>1.0795351304536034</v>
+      </c>
+      <c r="I91">
+        <f>H91*((E91/D91)^2 +(G91/F91)^2)^0.5</f>
+        <v>3.7839194656737198E-3</v>
+      </c>
+      <c r="J91" s="4"/>
+      <c r="L91">
+        <v>0.208953603264767</v>
+      </c>
+      <c r="M91">
+        <v>5.3129443828807302E-4</v>
+      </c>
+      <c r="N91">
+        <v>0.223224252625355</v>
+      </c>
+      <c r="O91">
+        <v>5.6545982801596898E-4</v>
+      </c>
+      <c r="P91" s="7">
+        <f t="shared" si="17"/>
+        <v>1.0682957802000932</v>
+      </c>
+      <c r="Q91">
+        <f>P91*((M91/L91)^2 +(O91/N91)^2)^0.5</f>
+        <v>3.8342543851553339E-3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C94" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D94" s="9"/>
+      <c r="E94" s="9"/>
+      <c r="F94" s="10"/>
+      <c r="G94" s="10"/>
+      <c r="H94" s="10"/>
+      <c r="I94" s="10"/>
+      <c r="K94" s="2"/>
+      <c r="L94" s="2"/>
+      <c r="M94" s="2"/>
+      <c r="N94" s="2"/>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C95" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D95" s="14"/>
+      <c r="E95" s="14"/>
+      <c r="F95" s="15"/>
+      <c r="G95" s="15"/>
+      <c r="H95" s="15"/>
+      <c r="I95" s="14"/>
+      <c r="K95" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="L95" s="17"/>
+      <c r="M95" s="18"/>
+      <c r="N95" s="18"/>
+      <c r="O95" s="17"/>
+      <c r="P95" s="17"/>
+      <c r="Q95" s="17"/>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A96" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="I74" t="e">
-        <f>H74*((E74/D74)^2 +(G74/F74)^2)^0.5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J74" s="4"/>
-      <c r="L74">
-        <v>0.208953603264767</v>
-      </c>
-      <c r="M74">
-        <v>5.3129443828807302E-4</v>
-      </c>
-      <c r="N74">
-        <v>0.223224252625355</v>
-      </c>
-      <c r="O74">
-        <v>5.6545982801596898E-4</v>
-      </c>
-      <c r="P74" s="7">
-        <f>N74/L74</f>
-        <v>1.0682957802000932</v>
-      </c>
-      <c r="Q74">
-        <f>P74*((M74/L74)^2 +(O74/N74)^2)^0.5</f>
-        <v>3.8342543851553339E-3</v>
+      <c r="B96" s="5"/>
+      <c r="C96" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D96" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F96" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H96" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="I96" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="J96" s="6"/>
+      <c r="K96" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="L96" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="M96" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="N96" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="O96" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="P96" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q96" s="19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>0.1</v>
+      </c>
+      <c r="B97" s="4"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2">
+        <v>6.3983845876002301E-6</v>
+      </c>
+      <c r="E97" s="2">
+        <v>6.0645437309806802E-10</v>
+      </c>
+      <c r="F97" s="2">
+        <v>7.0760633250553203E-6</v>
+      </c>
+      <c r="G97" s="2">
+        <v>5.1339823454999697E-8</v>
+      </c>
+      <c r="H97" s="7">
+        <f t="shared" ref="H97:H109" si="20">F97/D97</f>
+        <v>1.1059140362972866</v>
+      </c>
+      <c r="I97">
+        <f>H97*((E97/D97)^2 +(G97/F97)^2)^0.5</f>
+        <v>8.0245573515277287E-3</v>
+      </c>
+      <c r="J97" s="3"/>
+      <c r="K97" s="2"/>
+      <c r="L97" s="2">
+        <v>1.6592058395195499E-6</v>
+      </c>
+      <c r="M97" s="2">
+        <v>1.41505102275899E-10</v>
+      </c>
+      <c r="N97" s="2">
+        <v>1.8483734702828199E-6</v>
+      </c>
+      <c r="O97" s="2">
+        <v>1.55513175046048E-8</v>
+      </c>
+      <c r="P97" s="7">
+        <f t="shared" ref="P97:P109" si="21">N97/L97</f>
+        <v>1.1140109480437017</v>
+      </c>
+      <c r="Q97">
+        <f>P97*((M97/L97)^2 +(O97/N97)^2)^0.5</f>
+        <v>9.3732290926810593E-3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>0.5</v>
+      </c>
+      <c r="B98" s="4"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2">
+        <v>3.1982922448625398E-5</v>
+      </c>
+      <c r="E98" s="2">
+        <v>2.6566200546188399E-9</v>
+      </c>
+      <c r="F98" s="2">
+        <v>3.4767174950012798E-5</v>
+      </c>
+      <c r="G98" s="2">
+        <v>1.1875175668033E-7</v>
+      </c>
+      <c r="H98" s="7">
+        <f t="shared" si="20"/>
+        <v>1.0870543492659179</v>
+      </c>
+      <c r="I98">
+        <f t="shared" ref="I98:I108" si="22">H98*((E98/D98)^2 +(G98/F98)^2)^0.5</f>
+        <v>3.7140716760854261E-3</v>
+      </c>
+      <c r="J98" s="3"/>
+      <c r="L98" s="2">
+        <v>8.2939222535956595E-6</v>
+      </c>
+      <c r="M98" s="2">
+        <v>6.5137642973133701E-10</v>
+      </c>
+      <c r="N98" s="2">
+        <v>9.0584844834530308E-6</v>
+      </c>
+      <c r="O98" s="2">
+        <v>3.4986008675390597E-8</v>
+      </c>
+      <c r="P98" s="7">
+        <f t="shared" si="21"/>
+        <v>1.0921834334202869</v>
+      </c>
+      <c r="Q98">
+        <f t="shared" ref="Q98:Q108" si="23">P98*((M98/L98)^2 +(O98/N98)^2)^0.5</f>
+        <v>4.2191426521967484E-3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>1</v>
+      </c>
+      <c r="B99" s="4"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2">
+        <v>6.3953234731347494E-5</v>
+      </c>
+      <c r="E99" s="2">
+        <v>4.1750562646257501E-9</v>
+      </c>
+      <c r="F99" s="2">
+        <v>6.9186409819058705E-5</v>
+      </c>
+      <c r="G99" s="2">
+        <v>1.5688061721788999E-7</v>
+      </c>
+      <c r="H99" s="7">
+        <f t="shared" si="20"/>
+        <v>1.0818281531762162</v>
+      </c>
+      <c r="I99">
+        <f t="shared" si="22"/>
+        <v>2.4540685652037473E-3</v>
+      </c>
+      <c r="J99" s="3"/>
+      <c r="L99" s="2">
+        <v>1.6584717487230401E-5</v>
+      </c>
+      <c r="M99" s="2">
+        <v>9.5827412509581596E-10</v>
+      </c>
+      <c r="N99" s="2">
+        <v>1.8015958629727299E-5</v>
+      </c>
+      <c r="O99" s="2">
+        <v>4.7067091196410602E-8</v>
+      </c>
+      <c r="P99" s="7">
+        <f t="shared" si="21"/>
+        <v>1.0862987954783612</v>
+      </c>
+      <c r="Q99">
+        <f t="shared" si="23"/>
+        <v>2.8386736943042967E-3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>10</v>
+      </c>
+      <c r="B100" s="4"/>
+      <c r="C100" s="2"/>
+      <c r="D100">
+        <v>6.3770258635905503E-4</v>
+      </c>
+      <c r="E100" s="2">
+        <v>1.7008235462207999E-7</v>
+      </c>
+      <c r="F100">
+        <v>6.8424659690765797E-4</v>
+      </c>
+      <c r="G100" s="2">
+        <v>1.26356866859494E-6</v>
+      </c>
+      <c r="H100" s="7">
+        <f t="shared" si="20"/>
+        <v>1.0729870186262607</v>
+      </c>
+      <c r="I100">
+        <f t="shared" si="22"/>
+        <v>2.0019983603584914E-3</v>
+      </c>
+      <c r="J100" s="3"/>
+      <c r="L100">
+        <v>1.65347418242078E-4</v>
+      </c>
+      <c r="M100" s="2">
+        <v>4.4169022911434699E-8</v>
+      </c>
+      <c r="N100">
+        <v>1.7808774168493101E-4</v>
+      </c>
+      <c r="O100" s="2">
+        <v>3.7860183174411499E-7</v>
+      </c>
+      <c r="P100" s="7">
+        <f t="shared" si="21"/>
+        <v>1.077051843798374</v>
+      </c>
+      <c r="Q100">
+        <f t="shared" si="23"/>
+        <v>2.3077404266662912E-3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>25</v>
+      </c>
+      <c r="B101" s="4"/>
+      <c r="C101" s="2"/>
+      <c r="D101">
+        <v>1.58536962453175E-3</v>
+      </c>
+      <c r="E101" s="2">
+        <v>8.2305883701450097E-7</v>
+      </c>
+      <c r="F101">
+        <v>1.70168423125754E-3</v>
+      </c>
+      <c r="G101" s="2">
+        <v>4.5751138691945904E-6</v>
+      </c>
+      <c r="H101" s="7">
+        <f t="shared" si="20"/>
+        <v>1.0733675005033254</v>
+      </c>
+      <c r="I101">
+        <f t="shared" si="22"/>
+        <v>2.9391435327145573E-3</v>
+      </c>
+      <c r="J101" s="3"/>
+      <c r="L101">
+        <v>4.1085203990469599E-4</v>
+      </c>
+      <c r="M101" s="2">
+        <v>2.4691399158869002E-7</v>
+      </c>
+      <c r="N101">
+        <v>4.4228220783613199E-4</v>
+      </c>
+      <c r="O101" s="2">
+        <v>1.39675310994538E-6</v>
+      </c>
+      <c r="P101" s="7">
+        <f t="shared" si="21"/>
+        <v>1.0764999680632636</v>
+      </c>
+      <c r="Q101">
+        <f t="shared" si="23"/>
+        <v>3.4606604608369345E-3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <v>50</v>
+      </c>
+      <c r="B102" s="4"/>
+      <c r="C102" s="2"/>
+      <c r="D102">
+        <v>3.14770244875852E-3</v>
+      </c>
+      <c r="E102" s="2">
+        <v>1.70471325451899E-6</v>
+      </c>
+      <c r="F102">
+        <v>3.3690666583675402E-3</v>
+      </c>
+      <c r="G102" s="2">
+        <v>7.0636227876246404E-6</v>
+      </c>
+      <c r="H102" s="7">
+        <f t="shared" si="20"/>
+        <v>1.0703256464715487</v>
+      </c>
+      <c r="I102">
+        <f t="shared" si="22"/>
+        <v>2.3177136631774022E-3</v>
+      </c>
+      <c r="J102" s="3"/>
+      <c r="L102">
+        <v>8.1568580924759203E-4</v>
+      </c>
+      <c r="M102" s="2">
+        <v>4.4132856865932101E-7</v>
+      </c>
+      <c r="N102">
+        <v>8.7599322258741696E-4</v>
+      </c>
+      <c r="O102" s="2">
+        <v>2.1248965167792701E-6</v>
+      </c>
+      <c r="P102" s="7">
+        <f t="shared" si="21"/>
+        <v>1.0739346114105552</v>
+      </c>
+      <c r="Q102">
+        <f t="shared" si="23"/>
+        <v>2.6690584383735365E-3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <v>75</v>
+      </c>
+      <c r="B103" s="4"/>
+      <c r="C103" s="2"/>
+      <c r="D103">
+        <v>4.6821412877730796E-3</v>
+      </c>
+      <c r="E103" s="2">
+        <v>2.9980531833075998E-6</v>
+      </c>
+      <c r="F103">
+        <v>5.0102965379429602E-3</v>
+      </c>
+      <c r="G103" s="2">
+        <v>7.41874286054488E-6</v>
+      </c>
+      <c r="H103" s="7">
+        <f t="shared" si="20"/>
+        <v>1.0700865757782285</v>
+      </c>
+      <c r="I103">
+        <f t="shared" si="22"/>
+        <v>1.7262841610951405E-3</v>
+      </c>
+      <c r="J103" s="3"/>
+      <c r="L103">
+        <v>1.21297096634525E-3</v>
+      </c>
+      <c r="M103" s="2">
+        <v>6.5707220069548105E-7</v>
+      </c>
+      <c r="N103">
+        <v>1.3016696026088199E-3</v>
+      </c>
+      <c r="O103" s="2">
+        <v>2.2955550158876999E-6</v>
+      </c>
+      <c r="P103" s="7">
+        <f t="shared" si="21"/>
+        <v>1.0731251107607496</v>
+      </c>
+      <c r="Q103">
+        <f t="shared" si="23"/>
+        <v>1.9797749930070513E-3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <v>100</v>
+      </c>
+      <c r="B104" s="4"/>
+      <c r="C104" s="2"/>
+      <c r="D104">
+        <v>6.1899154453296098E-3</v>
+      </c>
+      <c r="E104" s="2">
+        <v>4.0490717181387601E-6</v>
+      </c>
+      <c r="F104">
+        <v>6.6193605525505898E-3</v>
+      </c>
+      <c r="G104" s="2">
+        <v>8.7198128104074496E-6</v>
+      </c>
+      <c r="H104" s="7">
+        <f t="shared" si="20"/>
+        <v>1.0693781863442098</v>
+      </c>
+      <c r="I104">
+        <f t="shared" si="22"/>
+        <v>1.5728331790708799E-3</v>
+      </c>
+      <c r="J104" s="3"/>
+      <c r="L104">
+        <v>1.6025253128139399E-3</v>
+      </c>
+      <c r="M104" s="2">
+        <v>8.43601312390377E-7</v>
+      </c>
+      <c r="N104">
+        <v>1.7192967813367899E-3</v>
+      </c>
+      <c r="O104" s="2">
+        <v>2.5653488738575302E-6</v>
+      </c>
+      <c r="P104" s="7">
+        <f t="shared" si="21"/>
+        <v>1.072867160093594</v>
+      </c>
+      <c r="Q104">
+        <f t="shared" si="23"/>
+        <v>1.6975241549356845E-3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <v>150</v>
+      </c>
+      <c r="B105" s="4"/>
+      <c r="C105" s="2"/>
+      <c r="D105">
+        <v>9.1206747221927297E-3</v>
+      </c>
+      <c r="E105" s="2">
+        <v>1.71531604233736E-5</v>
+      </c>
+      <c r="F105">
+        <v>9.7574042765682899E-3</v>
+      </c>
+      <c r="G105" s="2">
+        <v>5.0763712104761498E-5</v>
+      </c>
+      <c r="H105" s="7">
+        <f t="shared" si="20"/>
+        <v>1.0698116722468183</v>
+      </c>
+      <c r="I105">
+        <f t="shared" si="22"/>
+        <v>5.9182800814773073E-3</v>
+      </c>
+      <c r="J105" s="3"/>
+      <c r="L105">
+        <v>2.3624849736499499E-3</v>
+      </c>
+      <c r="M105" s="2">
+        <v>4.7793189465346599E-6</v>
+      </c>
+      <c r="N105">
+        <v>2.5326367860936398E-3</v>
+      </c>
+      <c r="O105" s="2">
+        <v>1.52949389777083E-5</v>
+      </c>
+      <c r="P105" s="7">
+        <f t="shared" si="21"/>
+        <v>1.0720223892814065</v>
+      </c>
+      <c r="Q105">
+        <f t="shared" si="23"/>
+        <v>6.8276732829171474E-3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>250</v>
+      </c>
+      <c r="B106" s="4"/>
+      <c r="C106" s="2"/>
+      <c r="D106">
+        <v>1.47299587411562E-2</v>
+      </c>
+      <c r="E106" s="2">
+        <v>2.83634553943966E-5</v>
+      </c>
+      <c r="F106">
+        <v>1.5695987941923999E-2</v>
+      </c>
+      <c r="G106" s="2">
+        <v>6.5669723693706494E-5</v>
+      </c>
+      <c r="H106" s="7">
+        <f t="shared" si="20"/>
+        <v>1.0655826141636546</v>
+      </c>
+      <c r="I106">
+        <f t="shared" si="22"/>
+        <v>4.9077484642792522E-3</v>
+      </c>
+      <c r="J106" s="3"/>
+      <c r="L106">
+        <v>3.8066986683040699E-3</v>
+      </c>
+      <c r="M106" s="2">
+        <v>7.1199445287493598E-6</v>
+      </c>
+      <c r="N106">
+        <v>4.06594125013788E-3</v>
+      </c>
+      <c r="O106" s="2">
+        <v>1.9233271963887199E-5</v>
+      </c>
+      <c r="P106" s="7">
+        <f t="shared" si="21"/>
+        <v>1.0681016819094078</v>
+      </c>
+      <c r="Q106">
+        <f t="shared" si="23"/>
+        <v>5.4330985143524625E-3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <v>500</v>
+      </c>
+      <c r="B107" s="4"/>
+      <c r="C107" s="2"/>
+      <c r="D107">
+        <v>2.7456267527901899E-2</v>
+      </c>
+      <c r="E107" s="2">
+        <v>5.9948553995571798E-5</v>
+      </c>
+      <c r="F107">
+        <v>2.8912613800000798E-2</v>
+      </c>
+      <c r="G107" s="2">
+        <v>9.1012167694938599E-5</v>
+      </c>
+      <c r="H107" s="7">
+        <f t="shared" si="20"/>
+        <v>1.0530423980833854</v>
+      </c>
+      <c r="I107">
+        <f t="shared" si="22"/>
+        <v>4.0341548620963352E-3</v>
+      </c>
+      <c r="J107" s="3"/>
+      <c r="L107">
+        <v>7.0792469987117704E-3</v>
+      </c>
+      <c r="M107" s="2">
+        <v>1.4039153971000801E-5</v>
+      </c>
+      <c r="N107">
+        <v>7.4545207369257497E-3</v>
+      </c>
+      <c r="O107" s="2">
+        <v>2.74836429813361E-5</v>
+      </c>
+      <c r="P107" s="7">
+        <f t="shared" si="21"/>
+        <v>1.0530104032649614</v>
+      </c>
+      <c r="Q107">
+        <f t="shared" si="23"/>
+        <v>4.4082869149599533E-3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <v>750</v>
+      </c>
+      <c r="B108" s="4"/>
+      <c r="D108">
+        <v>3.8497051854446997E-2</v>
+      </c>
+      <c r="E108" s="2">
+        <v>6.8482694464160805E-5</v>
+      </c>
+      <c r="F108">
+        <v>4.0528418631172798E-2</v>
+      </c>
+      <c r="G108">
+        <v>1.2503969593389799E-4</v>
+      </c>
+      <c r="H108" s="7">
+        <f t="shared" si="20"/>
+        <v>1.0527668140512725</v>
+      </c>
+      <c r="I108">
+        <f t="shared" si="22"/>
+        <v>3.7492671226656503E-3</v>
+      </c>
+      <c r="J108" s="4"/>
+      <c r="L108">
+        <v>9.8591559798638494E-3</v>
+      </c>
+      <c r="M108" s="2">
+        <v>1.78953637014576E-5</v>
+      </c>
+      <c r="N108">
+        <v>1.03866620055335E-2</v>
+      </c>
+      <c r="O108" s="2">
+        <v>3.5045910152349199E-5</v>
+      </c>
+      <c r="P108" s="7">
+        <f t="shared" si="21"/>
+        <v>1.0535041769038871</v>
+      </c>
+      <c r="Q108">
+        <f t="shared" si="23"/>
+        <v>4.0363538835675129E-3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <v>999.99</v>
+      </c>
+      <c r="B109" s="4"/>
+      <c r="D109">
+        <v>4.8305626476870103E-2</v>
+      </c>
+      <c r="E109" s="2">
+        <v>9.3124971795816396E-5</v>
+      </c>
+      <c r="F109">
+        <v>5.0429348149806201E-2</v>
+      </c>
+      <c r="G109">
+        <v>1.4820629340951599E-4</v>
+      </c>
+      <c r="H109" s="7">
+        <f t="shared" si="20"/>
+        <v>1.0439642714074515</v>
+      </c>
+      <c r="I109">
+        <f>H109*((E109/D109)^2 +(G109/F109)^2)^0.5</f>
+        <v>3.6692925334463221E-3</v>
+      </c>
+      <c r="J109" s="4"/>
+      <c r="L109">
+        <v>1.21377195834136E-2</v>
+      </c>
+      <c r="M109" s="2">
+        <v>2.3785825815868901E-5</v>
+      </c>
+      <c r="N109">
+        <v>1.2901873532126599E-2</v>
+      </c>
+      <c r="O109" s="2">
+        <v>3.9818562387638897E-5</v>
+      </c>
+      <c r="P109" s="7">
+        <f t="shared" si="21"/>
+        <v>1.0629569618462127</v>
+      </c>
+      <c r="Q109">
+        <f>P109*((M109/L109)^2 +(O109/N109)^2)^0.5</f>
+        <v>3.8860182732644031E-3</v>
       </c>
     </row>
   </sheetData>

--- a/Jupyter/Wedge/wedge_data_2026-03-25.xlsx
+++ b/Jupyter/Wedge/wedge_data_2026-03-25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\patri\projects\emma-openmc\Jupyter\Wedge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00B12B17-FB4D-40C5-9EE9-696C078161DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D95984-55C4-4974-81A4-E3E612C99D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1404,7 +1404,7 @@
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>1.0000745077223692</c:v>
+                  <c:v>0.9999824908852174</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1.0002014544619438</c:v>
@@ -1440,7 +1440,7 @@
                   <c:v>0.99885685520863166</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.99863620231200012</c:v>
+                  <c:v>0.99924465510488625</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1928,7 +1928,7 @@
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>1.0311738562325514</c:v>
+                  <c:v>1.0140569512365374</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1.0381411006968115</c:v>
@@ -1964,7 +1964,7 @@
                   <c:v>1.0753318396098046</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.0795351304536034</c:v>
+                  <c:v>1.0416680530362807</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2118,6 +2118,7 @@
       <c:valAx>
         <c:axId val="1342380336"/>
         <c:scaling>
+          <c:logBase val="10"/>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -2454,7 +2455,7 @@
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>1.0311738562325514</c:v>
+                  <c:v>1.0140569512365374</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1.0381411006968115</c:v>
@@ -2490,7 +2491,7 @@
                   <c:v>1.0753318396098046</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.0795351304536034</c:v>
+                  <c:v>1.0416680530362807</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2644,6 +2645,7 @@
       <c:valAx>
         <c:axId val="1342380336"/>
         <c:scaling>
+          <c:logBase val="10"/>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -9413,24 +9415,24 @@
       </c>
       <c r="B61" s="4"/>
       <c r="D61">
-        <v>1.3352695015565299</v>
-      </c>
-      <c r="E61">
-        <v>1.03018463315712E-4</v>
+        <v>1.3534903554118201</v>
+      </c>
+      <c r="E61" s="2">
+        <v>9.6553174901567196E-5</v>
       </c>
       <c r="F61">
-        <v>1.33536898944584</v>
+        <v>1.3534666569938301</v>
       </c>
       <c r="G61">
-        <v>1.25080703731084E-4</v>
+        <v>1.10337185935699E-4</v>
       </c>
       <c r="H61" s="7">
         <f t="shared" ref="H61:H73" si="12">F61/D61</f>
-        <v>1.0000745077223692</v>
+        <v>0.9999824908852174</v>
       </c>
       <c r="I61">
         <f>H61*((E61/D61)^2 +(G61/F61)^2)^0.5</f>
-        <v>1.2135980139653212E-4</v>
+        <v>1.0832496258568765E-4</v>
       </c>
       <c r="J61" s="3"/>
       <c r="L61">
@@ -9982,24 +9984,24 @@
       </c>
       <c r="B73" s="4"/>
       <c r="D73">
-        <v>1.2087119744332699</v>
+        <v>1.22576284834816</v>
       </c>
       <c r="E73">
-        <v>2.1559251329615801E-3</v>
+        <v>1.23273496553573E-3</v>
       </c>
       <c r="F73">
-        <v>1.20706353583708</v>
+        <v>1.2248369746380401</v>
       </c>
       <c r="G73">
-        <v>2.7226280465856702E-3</v>
+        <v>1.1081569319058801E-3</v>
       </c>
       <c r="H73" s="7">
         <f t="shared" si="12"/>
-        <v>0.99863620231200012</v>
+        <v>0.99924465510488625</v>
       </c>
       <c r="I73">
         <f>H73*((E73/D73)^2 +(G73/F73)^2)^0.5</f>
-        <v>2.871676467219969E-3</v>
+        <v>1.3517382386515301E-3</v>
       </c>
       <c r="J73" s="4"/>
       <c r="L73">
@@ -10114,24 +10116,24 @@
       <c r="B79" s="4"/>
       <c r="C79" s="2"/>
       <c r="D79" s="2">
-        <v>1.99881472847514E-5</v>
+        <v>2.0290990203204199E-5</v>
       </c>
       <c r="E79" s="2">
-        <v>3.4269103641913598E-9</v>
+        <v>2.24743174860222E-9</v>
       </c>
       <c r="F79" s="2">
-        <v>2.0611254914561302E-5</v>
+        <v>2.0576219663031699E-5</v>
       </c>
       <c r="G79" s="2">
-        <v>2.6942824381894501E-8</v>
+        <v>3.5531142886299199E-8</v>
       </c>
       <c r="H79" s="7">
         <f t="shared" ref="H79:H91" si="16">F79/D79</f>
-        <v>1.0311738562325514</v>
+        <v>1.0140569512365374</v>
       </c>
       <c r="I79">
         <f>H79*((E79/D79)^2 +(G79/F79)^2)^0.5</f>
-        <v>1.359484363209042E-3</v>
+        <v>1.7546781899791095E-3</v>
       </c>
       <c r="J79" s="3"/>
       <c r="K79" s="2"/>
@@ -10689,24 +10691,24 @@
       </c>
       <c r="B91" s="4"/>
       <c r="D91">
-        <v>0.18452445645978199</v>
+        <v>0.187638403751727</v>
       </c>
       <c r="E91">
-        <v>3.9150077450695101E-4</v>
+        <v>2.42561007732737E-4</v>
       </c>
       <c r="F91">
-        <v>0.19920063317619099</v>
+        <v>0.19545693071089701</v>
       </c>
       <c r="G91">
-        <v>5.5578369458203795E-4</v>
+        <v>2.2828736692647101E-4</v>
       </c>
       <c r="H91" s="7">
         <f t="shared" si="16"/>
-        <v>1.0795351304536034</v>
+        <v>1.0416680530362807</v>
       </c>
       <c r="I91">
         <f>H91*((E91/D91)^2 +(G91/F91)^2)^0.5</f>
-        <v>3.7839194656737198E-3</v>
+        <v>1.8147858424330007E-3</v>
       </c>
       <c r="J91" s="4"/>
       <c r="L91">
@@ -10821,24 +10823,24 @@
       <c r="B97" s="4"/>
       <c r="C97" s="2"/>
       <c r="D97" s="2">
-        <v>6.3983845876002301E-6</v>
+        <v>6.1377059341901304E-6</v>
       </c>
       <c r="E97" s="2">
-        <v>6.0645437309806802E-10</v>
+        <v>6.5011853459754501E-10</v>
       </c>
       <c r="F97" s="2">
-        <v>7.0760633250553203E-6</v>
+        <v>6.3252030232185003E-6</v>
       </c>
       <c r="G97" s="2">
-        <v>5.1339823454999697E-8</v>
+        <v>9.6222765983219803E-9</v>
       </c>
       <c r="H97" s="7">
         <f t="shared" ref="H97:H109" si="20">F97/D97</f>
-        <v>1.1059140362972866</v>
+        <v>1.0305483988706459</v>
       </c>
       <c r="I97">
         <f>H97*((E97/D97)^2 +(G97/F97)^2)^0.5</f>
-        <v>8.0245573515277287E-3</v>
+        <v>1.5715273902097899E-3</v>
       </c>
       <c r="J97" s="3"/>
       <c r="K97" s="2"/>
@@ -11396,24 +11398,24 @@
       </c>
       <c r="B109" s="4"/>
       <c r="D109">
-        <v>4.8305626476870103E-2</v>
+        <v>4.6422474047506802E-2</v>
       </c>
       <c r="E109" s="2">
-        <v>9.3124971795816396E-5</v>
+        <v>4.3252132292944603E-5</v>
       </c>
       <c r="F109">
-        <v>5.0429348149806201E-2</v>
-      </c>
-      <c r="G109">
-        <v>1.4820629340951599E-4</v>
+        <v>4.8246079336616003E-2</v>
+      </c>
+      <c r="G109" s="2">
+        <v>4.9195732418165402E-5</v>
       </c>
       <c r="H109" s="7">
         <f t="shared" si="20"/>
-        <v>1.0439642714074515</v>
+        <v>1.0392828113220118</v>
       </c>
       <c r="I109">
         <f>H109*((E109/D109)^2 +(G109/F109)^2)^0.5</f>
-        <v>3.6692925334463221E-3</v>
+        <v>1.4355020089272224E-3</v>
       </c>
       <c r="J109" s="4"/>
       <c r="L109">
